--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,8 +526,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -557,6 +555,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-184.19</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.11386e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.643</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5681574138265125</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.60227503578306</v>
+      </c>
+      <c r="H2" t="n">
+        <v>2.231673111673855</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.797836423690727</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23.9320108645923</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.49221849863669</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 16.313x + -8303.679</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>441.8751299021471</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>245712547.1356277</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>9.077035214013106e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8801445757784034</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-171.579</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.11095e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.05</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6696596687227759</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.352601367110984</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.973355036064676</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.727283138734068</v>
+      </c>
+      <c r="J3" t="n">
+        <v>24.85426467531383</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.65194974328436</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.094x + -8487.128</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>434.3481901031161</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>38491344.48331343</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>8.496679723174884e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8899859477585453</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-164.317</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.11214e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-80.32899999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4615968870788024</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7885838132438485</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.773394018974194</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.567804572679223</v>
+      </c>
+      <c r="J4" t="n">
+        <v>25.55340974527982</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.65947280398476</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.132x + -8310.605</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>427.7779039390333</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>59686438.34264517</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>8.143957286588159e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8964225003084479</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-157.765</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.11614e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-80.542</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.4229508573827554</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.145149732712472</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.948587885801673</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.867653758616919</v>
+      </c>
+      <c r="J5" t="n">
+        <v>28.98402889414337</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.8244916387948</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 18.025x + -8611.818</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>421.5797911742441</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>63508959.18336506</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.892827574397358e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9013032144441889</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-154.299</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.12326e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-80.705</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.6560948736901148</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.007303162440803</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.697363023508245</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.811289985461836</v>
+      </c>
+      <c r="J6" t="n">
+        <v>28.92607989266839</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.87144478999733</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 18.296x + -8591.413</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>415.6768547387593</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>30128315.26671074</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7.71485166579219e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9050139365760173</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-150.893</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.12857e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-80.86</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.4710873013870996</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.019647458260897</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.96940584744119</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.802398690124514</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.65413701388699</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.92248349849262</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 18.600x + -8596.735</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>409.977589424865</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>675381081.8686706</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.565498516939744e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.908154540578976</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-147.951</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.13321e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-80.992</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.131237450091643</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.329791949651252</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.231570477672867</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.148310726445605</v>
+      </c>
+      <c r="J8" t="n">
+        <v>32.04423865046279</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.01407570627818</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 19.171x + -8740.130</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>404.4319783582843</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>111313918.0968795</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7.434343053118211e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9109785219444676</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-147.2149999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.13835e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.125</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.32748020843396</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.226352510236725</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.846409623918039</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.028512578551965</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30.52725586883264</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.94631826068088</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 18.745x + -8382.359</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>399.2435837759633</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>164357452.0273654</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>7.313158604715136e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9136482768902352</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-145.519</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.14111e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-81.253</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.06517366898170843</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.6834135199323136</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.566144438550274</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.716166197388699</v>
+      </c>
+      <c r="J10" t="n">
+        <v>28.76978189435176</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.91908270045455</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.579x + -8177.335</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>394.6339166541012</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1081600138.813152</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.200036925052079e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.916102328578133</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-143.198</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.14408e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-81.367</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.3891260344940065</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.7575077114716539</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.732859411402087</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.090234913222961</v>
+      </c>
+      <c r="J11" t="n">
+        <v>31.89528338918303</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.93416468923911</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.671x + -8112.778</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>390.5236675824672</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>121300484.0697669</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>7.10358220782034e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9182480339726223</v>
       </c>
     </row>
   </sheetData>
@@ -570,7 +1088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,8 +1192,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -705,6 +1221,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-175.045</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.45364e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.059</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.3035305152156914</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.742721446445516</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.720964612167591</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.565547367885113</v>
+      </c>
+      <c r="J2" t="n">
+        <v>23.73392580872853</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.34442876493496</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 15.652x + -7830.369</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>435.0186249382122</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>79437038.25296503</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.008483203030008e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8768153250799705</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-156.492</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.44371e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-79.75</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.5308606703994583</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.066643470228123</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.847287116683712</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.467681376095283</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.30733145970917</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.79828850962785</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 17.877x + -8555.250</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>424.1085412556876</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>103316021.9869039</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>8.943508687437834e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8945247794697502</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-149.898</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.43179e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-80.03700000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.4177912602354802</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.283337904151673</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.91558603773612</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.826168263619314</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27.39830601857852</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.87648169382103</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 18.325x + -8601.813</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>418.9522391080113</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>37718787.45935754</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>8.557950415430884e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9007270019340107</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-146.881</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.41995e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-80.22</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3600575886295302</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.239001315439677</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.53561362418326</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.724795416656296</v>
+      </c>
+      <c r="J5" t="n">
+        <v>27.02533422649617</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.91729452845723</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 18.568x + -8602.648</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>415.0262851245232</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>341754844.5517014</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>8.321549054307094e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9045421916477052</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-142.6010000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.40925e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-80.378</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.5990697604568355</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.552942595012983</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.256470623755742</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.265611788597336</v>
+      </c>
+      <c r="J6" t="n">
+        <v>30.61320336474484</v>
+      </c>
+      <c r="K6" t="n">
+        <v>87.06485746626791</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 19.504x + -8960.891</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>410.983898887697</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>169185510.2121852</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8.130490827824994e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9076742869282133</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-140.2689999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.40216e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-80.526</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.7619811005484578</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.183091260408998</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.988371984112647</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.776744030066177</v>
+      </c>
+      <c r="J7" t="n">
+        <v>29.02189866035797</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.13659687627519</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 19.993x + -9088.720</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>406.7603474091602</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>225999761.0266023</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.966910835692676e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9104862549558547</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-140.942</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.39602e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-80.64700000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5892734246575295</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.70241243796654</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.540306905689112</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.915860305846135</v>
+      </c>
+      <c r="J8" t="n">
+        <v>29.47423711146282</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.99756703532763</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 19.066x + -8516.875</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>402.4949007440025</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>221187425.3334227</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7.834205066514079e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.912799689768508</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-136.867</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.39295e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-80.792</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.3477241245855221</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9500276694369202</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.974788373776023</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.80044601587177</v>
+      </c>
+      <c r="J9" t="n">
+        <v>30.23576260266869</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.14472927873885</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 20.050x + -8878.658</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>398.5084272840842</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>440368840.7393088</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>7.699376669980727e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9152875675368441</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-135.136</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.38897e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-80.92</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5612826695462825</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.181093393257172</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.924972686406323</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.05729772029831</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.7829148001345</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.12928594521571</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.942x + -8718.879</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>394.7192300493788</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>216432961.9668211</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.579703599375671e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9175166126156107</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-133.176</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.38463e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-81.033</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2226021309923061</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9776475871479843</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.194538745994547</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.049002249284264</v>
+      </c>
+      <c r="J11" t="n">
+        <v>32.47172063626965</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.17486865025123</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 20.264x + -8776.357</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>391.2934095908259</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>164604808.5796399</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>7.476361312322177e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9194328954308543</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-130.953</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.38079e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-81.13500000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4321459692223827</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.062883715545529</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.952985140021669</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.213794953543763</v>
+      </c>
+      <c r="J12" t="n">
+        <v>32.86381915467833</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.23000221781973</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 20.668x + -8867.960</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>387.9888220539746</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>636982177.1051949</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7.38636039839273e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9211144844976697</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-131.1779999999999</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.38024e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-81.221</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.01519574087747258</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.7930543059485983</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.746863884360521</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.848432668905209</v>
+      </c>
+      <c r="J13" t="n">
+        <v>32.46682382219134</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.17390846088941</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 20.257x + -8588.119</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>384.8544064891893</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>210467638.5578675</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>7.313274669477334e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9225964107236322</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-128.843</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.3775e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-81.29900000000001</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3986826700490189</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.289527006091306</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.078687275684449</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.272934469178723</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.47728634871119</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.31095941786431</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 21.291x + -8983.087</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>381.7959252873379</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>417794686.5864821</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>7.24701217516823e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9238740285267643</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-124.3559999999999</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.37654e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-81.40900000000001</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.896774922013251</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.20519170497895</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.978680142721921</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.971597406906195</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.58969867692985</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.47135818949879</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 22.644x + -9509.996</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>378.7175037836427</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>103760347.6214598</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>7.16790368695532e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9254795226227149</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-125.044</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.3758e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-81.482</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5529189196139203</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.518478942944718</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.851285512719434</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.632592122783522</v>
+      </c>
+      <c r="J16" t="n">
+        <v>33.15186767796791</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.40001507291713</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 22.022x + -9138.471</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>375.6815895349957</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>208214067.9970274</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.11348877747008e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.92660086639399</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-124.75</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.37357e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-81.551</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5371905581476721</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.334460577611811</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.066987066847668</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.427173111871302</v>
+      </c>
+      <c r="J17" t="n">
+        <v>35.73244134806395</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.41102247673675</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 22.116x + -9095.563</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>372.6977934854936</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>152890524.945729</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7.058668754276769e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9276890120226792</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-125.069</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.37256e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-81.62</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.4131698078420023</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.120851246717673</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.969022637589614</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.162376291679404</v>
+      </c>
+      <c r="J18" t="n">
+        <v>35.05904922523229</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.34533099165118</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 21.568x + -8768.553</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>369.7578174330148</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>151738271.3552929</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>7.006918199967112e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9287636180396069</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-121.879</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.37343e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-81.717</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3917927230189602</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.086239504056887</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.987026126241638</v>
+      </c>
+      <c r="I19" t="n">
+        <v>3.134529208477979</v>
+      </c>
+      <c r="J19" t="n">
+        <v>35.10312664746759</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.44064922809999</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 22.372x + -9033.733</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>366.856079214409</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>306931823.3678589</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>6.943042421514423e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9301653470366122</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-119.655</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.37165e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-81.806</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4158627640689363</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.474027121981117</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.1300547322357</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.402016674772887</v>
+      </c>
+      <c r="J20" t="n">
+        <v>37.60258927116103</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.50195610308231</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 22.922x + -9187.913</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>363.8768205576325</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>199021235.4283823</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>6.88108748222111e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9314461273523972</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-119.123</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.37066e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-81.869</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.7218498449233445</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.094878462762556</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.099488340375157</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.086430746289308</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.24183328729301</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.53564373187106</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 23.235x + -9241.637</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>360.9486237394665</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>183919532.2370981</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>6.83569896970495e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9324109709795777</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-120.2</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.36996e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-81.92700000000001</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.3146995967741957</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.038226905758256</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.949135719967094</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.867476322719746</v>
+      </c>
+      <c r="J22" t="n">
+        <v>34.48569394164862</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.47095526829668</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 22.640x + -8897.679</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>357.9682818640612</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1270462204.530481</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>6.795181011603263e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9332925960956555</v>
       </c>
     </row>
   </sheetData>
@@ -718,7 +2326,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -822,8 +2430,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -853,6 +2459,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-196.03</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.28239e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-79.121</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7580044085163533</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.047039608695946</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.53369756647797</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.3428777038827</v>
+      </c>
+      <c r="J2" t="n">
+        <v>20.75046368617551</v>
+      </c>
+      <c r="K2" t="n">
+        <v>86.13945377474806</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 14.819x + -7446.211</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>433.0755477598454</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>189294391.1809571</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>9.922148824033418e-07</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8731068589040796</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-165.46</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.26096e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-80.06699999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4331237516949231</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.9027047774675002</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.646491777668277</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.508118438070054</v>
+      </c>
+      <c r="J3" t="n">
+        <v>25.23207274223694</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.61714570465722</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 16.917x + -8081.027</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>422.2385358405232</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>59708384.05879393</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>8.529639486165217e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8950227877615352</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-156.611</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.2453e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-80.383</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2641051089198811</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9133340111180765</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.792818019064352</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.753906751123438</v>
+      </c>
+      <c r="J4" t="n">
+        <v>27.82674561578071</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.72188768178023</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 17.459x + -8188.276</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>417.5884862461021</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>36044888.17761886</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>8.125703972419277e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9017663342807797</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-146.769</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.23514e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-80.604</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.7449740286358222</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.727533627246282</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.983613256898368</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.077063720019141</v>
+      </c>
+      <c r="J5" t="n">
+        <v>30.33115552566098</v>
+      </c>
+      <c r="K5" t="n">
+        <v>87.04977891610596</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 19.404x + -9059.945</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>413.5496620947689</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>454790505.9308857</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>7.88163149573542e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9059829782551166</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-145.914</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.22845e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-80.76900000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1071144234081276</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8668935149178595</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.602737724316307</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.7010504938406</v>
+      </c>
+      <c r="J6" t="n">
+        <v>29.54076198576941</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.87749246948361</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 18.331x + -8396.356</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>409.3882828900535</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>449681904.7030554</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7.704798527426754e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.909159406293183</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-140.85</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.22367e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-80.926</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.641641405493112</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.137491425722362</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.765405575116243</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.868952816744496</v>
+      </c>
+      <c r="J7" t="n">
+        <v>30.57225729730976</v>
+      </c>
+      <c r="K7" t="n">
+        <v>87.02747491937123</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 19.258x + -8742.079</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>405.0572527687936</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>222551452.9046378</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.550447286602293e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.912034098651431</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-138.72</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.2209e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-81.066</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.5471248430038087</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.073639714871742</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.87414251502297</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.068525781654061</v>
+      </c>
+      <c r="J8" t="n">
+        <v>33.34317869809441</v>
+      </c>
+      <c r="K8" t="n">
+        <v>87.03897266560439</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 19.333x + -8657.705</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>400.7303388075825</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>219694685.1342096</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7.417855691438191e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9145978154303235</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-138.199</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.22084e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.17100000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.5272051621102377</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.8960002680996696</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.758519088455415</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.632086654818046</v>
+      </c>
+      <c r="J9" t="n">
+        <v>31.77494872331662</v>
+      </c>
+      <c r="K9" t="n">
+        <v>87.02591137060513</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 19.248x + -8507.557</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>396.5803041922406</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>326131378.9680545</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>7.318785446524434e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9166306031253019</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-135.258</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.21893e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-81.298</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5089215687668838</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9840161176847104</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.780361765517368</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.698849499303962</v>
+      </c>
+      <c r="J10" t="n">
+        <v>31.66683623950517</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.05236168936062</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.421x + -8480.874</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>392.6631975947702</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>329255284.1881668</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.208276239277801e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9188212921463067</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-131.565</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.21756e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-81.41</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.6311116594471925</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.190788364940084</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.715450167153055</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.941862173878197</v>
+      </c>
+      <c r="J11" t="n">
+        <v>33.21851543396568</v>
+      </c>
+      <c r="K11" t="n">
+        <v>87.22185598824058</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 20.608x + -8937.783</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>388.9439630694364</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>159855868.3902268</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>7.111089980067962e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9208507833971519</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-132.447</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.21658e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-81.482</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4698890342363808</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.7989095471713057</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.856665351090147</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.792718594106645</v>
+      </c>
+      <c r="J12" t="n">
+        <v>33.43842937593461</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.15281124632121</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 20.107x + -8607.014</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>385.4121407138171</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>116870617.8895902</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7.044464394495368e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9222454363731062</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-131.004</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.21741e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-81.566</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4745324101330487</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.263886113271488</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.101033021062743</v>
+      </c>
+      <c r="I13" t="n">
+        <v>3.064672468352813</v>
+      </c>
+      <c r="J13" t="n">
+        <v>34.73556627684425</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.20564446519681</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 20.488x + -8691.976</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>382.0050234085486</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>209171369.0694711</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>6.981204294314548e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.923637857137142</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-129.723</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.21776e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-81.652</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2622054142834409</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.011102131540446</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.780667617535387</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.651165291170198</v>
+      </c>
+      <c r="J14" t="n">
+        <v>34.13302308270965</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.21069814602048</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 20.525x + -8616.665</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>378.6541941245881</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>385677221.7194996</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>6.916289298655832e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.925056602424427</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-127.657</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.21873e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-81.748</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3954160199403361</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.145370196000948</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.579323807179243</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.774708509500377</v>
+      </c>
+      <c r="J15" t="n">
+        <v>33.07536172581578</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.21677231629147</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 20.570x + -8548.287</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>375.5427336321978</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>154990064.9209351</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>6.85072256865229e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9265142162307757</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-126.3220000000001</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.21857e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-81.818</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6146277395404575</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.289789068764456</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.984390466918733</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.125616519698762</v>
+      </c>
+      <c r="J16" t="n">
+        <v>36.43333848300041</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.29973932488761</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 21.203x + -8751.373</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>372.5235151616664</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>305699367.8179162</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>6.798831791571903e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9276594653105199</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-127.994</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.21774e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-81.87</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.152219029873058</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9192870978648067</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.762397076333466</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.665762339594186</v>
+      </c>
+      <c r="J17" t="n">
+        <v>34.23526805482251</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.20030488207833</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 20.449x + -8336.352</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>369.5490524095136</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>112075823.0648189</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>6.754387727039867e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9286325555176161</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-125.971</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.21905e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-81.938</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.517624912684474</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.203165765149636</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.033210888546007</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.19446017912051</v>
+      </c>
+      <c r="J18" t="n">
+        <v>36.49612277351245</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.33122650575744</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 21.453x + -8702.471</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>366.5906727641661</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>200470441.3851776</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>6.711142224885672e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9296439902348186</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-126.248</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.22086e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-81.989</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2957908723988649</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.206673206556426</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.670764053232117</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.764689538576051</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33.70069565210456</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.30840048171451</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 21.271x + -8541.704</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>363.711147851523</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>101810104.8653887</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>6.675263665375564e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9305279391280012</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-125.181</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.22095e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-82.065</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4362367820946644</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.9002696537244468</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.975667884444588</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.094909033016787</v>
+      </c>
+      <c r="J20" t="n">
+        <v>37.05390261795557</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.31407338683741</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 21.316x + -8481.658</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>360.8848523078199</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>788563842.0398979</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>6.626457979894738e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9316335793742081</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-124.092</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.22186e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-82.13200000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.2175472542250773</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.006346500702574</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.079224648957275</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.833176732287887</v>
+      </c>
+      <c r="J21" t="n">
+        <v>35.56765125367694</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.31091147042447</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 21.291x + -8392.941</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>358.1705882762301</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>294176667.7708919</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>6.582015866471859e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.932678957115012</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-121.503</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.22288e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-82.20699999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5209849125716777</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.9781083559493974</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.83056779949244</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.807092832729078</v>
+      </c>
+      <c r="J22" t="n">
+        <v>35.01261744818088</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.39840699619239</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 22.008x + -8624.156</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>355.4980297768718</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>195786323.3136893</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>6.538806611654203e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9337020090745738</v>
       </c>
     </row>
   </sheetData>
@@ -866,7 +3564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -970,8 +3668,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1001,6 +3697,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-293.102</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.58367e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.13800000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1463203083764137</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.302056891951591</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.9470774943129501</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.957631634162051</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.53871839119138</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.17588870299647</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.804x + -4623.595</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>399.1107394250932</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>438446194.1489649</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.317512045825061e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8416291881512713</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-236.3339999999999</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.64888e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-78.84</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.2234503193713178</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8073057277272875</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.459098554930882</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.562275791618747</v>
+      </c>
+      <c r="J3" t="n">
+        <v>15.49385348336992</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.33752804804207</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.262x + -5156.461</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>376.7446016448904</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>412906226.6559771</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>9.982360272586506e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8852216569213783</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-215.6709999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.62057e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-79.514</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3147502930828046</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.9692613725208954</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.586678488291368</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.705887141717686</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.26524941121385</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.77189009505075</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 13.527x + -5514.607</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>368.9296501274155</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>202042743.9430597</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9.120585127132215e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8977624772184749</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-204.578</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.58705e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-79.92700000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5120185371398708</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.704682049369021</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.621382130168136</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.30818891504761</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.93663182450629</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.077x + -5623.005</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>363.7664924369331</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>200541967.061127</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>8.648920944189094e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9045702042963808</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-194.877</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.5565e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-80.252</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1947864930130442</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8273499509849747</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.677622250412332</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.7819155473789</v>
+      </c>
+      <c r="J6" t="n">
+        <v>19.40002475287198</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.16882978339994</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.933x + -5891.785</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>359.0947097940731</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>98275559.66834185</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8.299639251073624e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9097148724775582</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-186.837</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.53261e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-80.533</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.8770368025089244</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.9956636552152082</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.90254474665536</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.659554075953091</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20.13699362018835</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.36335575721175</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 15.734x + -6129.946</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>354.4718578756008</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>389018917.1033631</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.025533379876564e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.913935640009838</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-181.823</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.51167e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-80.76600000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4062677964833233</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.217862213406838</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.199471402173077</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.967107142805292</v>
+      </c>
+      <c r="J8" t="n">
+        <v>21.76080150509097</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.44976604876672</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.118x + -6183.843</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>349.8973545128995</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>143423329.243043</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7.800550646503015e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9174801160845886</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-176.717</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.49551e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-80.988</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2970371076996507</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.137128534543391</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.066446039623483</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.845722264070799</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.35762264150804</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.54388671203137</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 16.558x + -6260.835</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>345.5275287145916</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>188617771.1430337</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>7.609167513772127e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9206359726549826</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-173.245</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.47803e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-81.163</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.5304710000706385</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.133417628803185</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.09633733628851</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.813605256805852</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.5816287823947</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.61620074139398</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 16.913x + -6308.095</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>341.3931195897867</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>279365939.1792666</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.449007832611085e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9232423324097968</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-166.891</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.46535e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-81.36</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.8416803435876054</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.29058777787983</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.005536711153777</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.81958777244175</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23.52136848929209</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.76947872918841</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 17.717x + -6541.747</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>337.5217223839763</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>184256538.910268</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>7.29545926736977e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9259093123015187</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +4230,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1118,8 +4334,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1149,6 +4363,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-236.588</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.62212e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.533</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2431147979108321</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7762854345776665</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.376202406963833</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.156349881133764</v>
+      </c>
+      <c r="J2" t="n">
+        <v>15.51323369961583</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.19589780308293</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.898x + -5928.531</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>430.3375601763885</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>177345990.1357034</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.312691647084753e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8430872232040106</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-199.874</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.59991e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-78.64400000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6017770693438421</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.164326744949632</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.57427558654892</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.608102878218628</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.88448549009986</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.93749408650241</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 14.080x + -6692.469</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>419.8009996635196</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>50360310.56373951</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.074401804569402e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8722769932975619</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-186.5889999999999</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.57266e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-79.117</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1188891375863978</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.6612520285518163</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.339316486386084</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.523463437044482</v>
+      </c>
+      <c r="J4" t="n">
+        <v>20.39312345716109</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.11405165353406</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.722x + -6860.358</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>415.1516060485824</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>161636050.9926125</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9.967437724492801e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8825948931388248</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-176.016</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.54742e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-79.43300000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5995335870248248</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.9780207895237867</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.642039133933071</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.791090578730343</v>
+      </c>
+      <c r="J5" t="n">
+        <v>22.08222797597267</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.38286258754704</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.819x + -7310.533</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>411.1660005968433</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>171120962.1477516</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>9.500555416419336e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8889321327035962</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-170.3299999999999</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.52903e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-79.693</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1486552050200159</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6228018153241636</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.574913261526477</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.685102450538515</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22.81717006988999</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.40908360630586</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.935x + -7253.939</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>407.0124660538758</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>224782532.1097848</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9.148654314970473e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8939534840873773</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-164.851</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.51503e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-79.92100000000001</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1636563353997005</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.027678262561383</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.687178102884416</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.746857459335125</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.39167720784301</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.52511975594811</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.468x + -7410.800</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>402.6703652962622</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>221444165.4908842</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.865235839604954e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8981973383088065</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-159.932</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.50016e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-80.12</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1196566316599201</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8761862047949257</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.874230061387735</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.583498309381157</v>
+      </c>
+      <c r="J8" t="n">
+        <v>24.12551441331144</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.66171887850922</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 17.144x + -7632.948</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>398.3747443705986</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>218891627.6862209</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8.617305433626118e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9019582986173899</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-156.7839999999999</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.48717e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-80.29900000000001</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.6741443795002749</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.116995891298605</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.620709191932643</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.649998209069935</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24.80613335068082</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.73939803914961</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 17.553x + -7727.754</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>394.4347314518075</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>432269489.553234</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.409253555724308e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9051804329360816</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-151.453</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.47817e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-80.49299999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.116864659370492</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7499596405437363</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.736718790107192</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.710733340992654</v>
+      </c>
+      <c r="J10" t="n">
+        <v>26.47674219985563</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.76321307466895</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 17.683x + -7688.241</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>390.8375003359115</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>428395885.152842</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.211383059960402e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9084283692325341</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-148.8439999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.46873e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-80.629</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.5006006002350949</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9932322585569578</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.100630783927933</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.822556704834637</v>
+      </c>
+      <c r="J11" t="n">
+        <v>27.70198015683637</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.84478497143563</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.141x + -7815.289</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>387.453420771319</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>213964053.8038524</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8.063701352079936e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9108344549519343</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-144.881</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.45936e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-80.765</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.8560662265338262</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.996947515693811</v>
+      </c>
+      <c r="H12" t="n">
+        <v>1.76234036100377</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.747803343014812</v>
+      </c>
+      <c r="J12" t="n">
+        <v>27.85302455033056</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.96952641648392</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 18.889x + -8081.106</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>384.2698611246886</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>211121508.1296392</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>7.926384331754758e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9130852599706556</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-144.603</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.45247e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-80.878</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.05214015702900616</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.5747935290142421</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.62403235385791</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.607447803069926</v>
+      </c>
+      <c r="J13" t="n">
+        <v>27.16379414055731</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.89056668718435</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 18.408x + -7775.949</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>381.2286649902834</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>313014959.4294567</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>7.814934457548496e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9149875159325446</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-142.214</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.44504e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-80.977</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6500869484669535</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.204129815563921</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.879388107853398</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.969197782342656</v>
+      </c>
+      <c r="J14" t="n">
+        <v>29.37968596747114</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.99326370493998</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 19.038x + -7988.597</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>378.2434279452024</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>414211151.969752</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>7.716591258289905e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9166372125299204</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-139.795</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.43868e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-81.093</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3494183904713054</v>
+      </c>
+      <c r="G15" t="n">
+        <v>1.458579466504667</v>
+      </c>
+      <c r="H15" t="n">
+        <v>2.186867206119076</v>
+      </c>
+      <c r="I15" t="n">
+        <v>3.223656601366077</v>
+      </c>
+      <c r="J15" t="n">
+        <v>30.9071456711145</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.06119563420363</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 19.479x + -8110.328</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>375.3233192145844</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>411216768.2207509</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>7.612174688380247e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9184570620464072</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-137.646</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.4356e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-81.188</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.4729260390438598</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.138845252122794</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.924941098874144</v>
+      </c>
+      <c r="I16" t="n">
+        <v>2.816271616049777</v>
+      </c>
+      <c r="J16" t="n">
+        <v>29.94970937344211</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.06598764755772</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 19.511x + -8048.507</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>372.4727883082132</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>305868352.3892522</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.530725144062699e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9199711053264399</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-136.5240000000001</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.42902e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-81.29300000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.2505220786918179</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.175612510913872</v>
+      </c>
+      <c r="H17" t="n">
+        <v>2.013912801438306</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.959250103598053</v>
+      </c>
+      <c r="J17" t="n">
+        <v>31.28553970527411</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.04669351874476</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 19.383x + -7914.748</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>369.6354063846488</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>151861490.4505496</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7.440256920703068e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9215555928106822</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-133.609</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.42504e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-81.392</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5160697144644095</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.926100674199054</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.739834193225407</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2.933940000541746</v>
+      </c>
+      <c r="J18" t="n">
+        <v>30.41293140374787</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.12844946748636</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 19.936x + -8083.851</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>366.8052324291342</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>301223118.9624547</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>7.358434797363799e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9230799910191222</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-133.562</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.42194e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-81.462</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.3268530045486853</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9258068955943083</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.88274302439386</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.93387623618843</v>
+      </c>
+      <c r="J19" t="n">
+        <v>31.34639243627744</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.16442505823083</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 20.190x + -8124.669</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>363.958078806506</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>896000990.8613718</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7.300207471263049e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9241690328716775</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-130.462</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.41998e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-81.56100000000001</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4362144775262793</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.229256742440439</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.971876764895818</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.217635716338387</v>
+      </c>
+      <c r="J20" t="n">
+        <v>32.9071024858909</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.22282850808183</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 20.615x + -8232.125</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>361.1030437426311</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>197523750.4443202</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7.227657215465091e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9255939660528533</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-129.615</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.41749e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-81.64700000000001</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.3395909422383063</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.9546750307990517</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.682906699589026</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.690532180267566</v>
+      </c>
+      <c r="J21" t="n">
+        <v>31.00696512859828</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.19541185281336</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 20.413x + -8065.045</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>358.2517734184513</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>195866476.6688291</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7.159869467681006e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9269266376916596</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-128.767</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.4155e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-81.724</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4305789690475726</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.113593186149117</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.913686830970686</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.241324788414472</v>
+      </c>
+      <c r="J22" t="n">
+        <v>33.69801905733078</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.21832621275446</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 20.581x + -8061.253</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>355.4193524940902</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>388608664.1277252</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>7.103629344653632e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.928042798095171</v>
       </c>
     </row>
   </sheetData>
@@ -1162,7 +5468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1266,8 +5572,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1297,6 +5601,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-299.283</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.8887e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-76.15000000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2883807891840778</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.5321887964661228</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.046348451220827</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.829887672908616</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.21769244937792</v>
+      </c>
+      <c r="K2" t="n">
+        <v>83.78116345221645</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.177x + -4283.494</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>396.0480226192574</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>220341120.03033</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.580864204228818e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8244772858779522</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-242.703</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.96942e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.90900000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.01771462920432121</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7900758989984019</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.414944697999545</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.278831558907785</v>
+      </c>
+      <c r="J3" t="n">
+        <v>13.736387337216</v>
+      </c>
+      <c r="K3" t="n">
+        <v>84.95858072274089</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.336x + -4759.724</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>376.1619019626904</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>206917800.2606733</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.167982552580774e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8720335294883568</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-222.64</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.93326e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-78.60299999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.317524724824112</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.7753778490641553</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.796786024792982</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.440617107243188</v>
+      </c>
+      <c r="J4" t="n">
+        <v>15.15050099366386</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.40294984965661</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.437x + -5075.481</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>369.0674309948403</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>209377630.0668765</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.057263656926392e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8857564486800935</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-210.065</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.891439999999999e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-79.069</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.411623251149394</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.082766739584801</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.609062161150477</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.726828601762241</v>
+      </c>
+      <c r="J5" t="n">
+        <v>16.51203503602854</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.68953496840582</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 13.267x + -5329.797</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>364.1423670579533</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>697729078.7444665</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>9.933647794257932e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8937343265313835</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-203.334</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.85406e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-79.43600000000001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6907115191387228</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.571388191479304</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.720839364322617</v>
+      </c>
+      <c r="J6" t="n">
+        <v>17.48952097215687</v>
+      </c>
+      <c r="K6" t="n">
+        <v>85.76830569346231</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 13.515x + -5324.501</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>359.4395566651669</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>196807789.3057901</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9.460835482645655e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8998354049591756</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-195.395</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.8182e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-79.753</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2555665193909649</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8490121594829868</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.713350156144967</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.709595061188523</v>
+      </c>
+      <c r="J7" t="n">
+        <v>18.31633276072394</v>
+      </c>
+      <c r="K7" t="n">
+        <v>85.98534782726016</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 14.248x + -5542.815</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>354.6544064970562</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>679380841.0213003</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9.079446112459932e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.904846474563714</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-188.716</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.78968e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-80.051</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.1531508361439901</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.8188503572383034</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.507520394695414</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.786339152844548</v>
+      </c>
+      <c r="J8" t="n">
+        <v>19.01499402521065</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.1179253403461</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 14.736x + -5645.649</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>349.9431300454831</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>143457803.3713763</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8.75602241623646e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9093469545645744</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-181.854</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.76339e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-80.32599999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1839326477271538</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9785566142369828</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.070528077283066</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.023096351056176</v>
+      </c>
+      <c r="J9" t="n">
+        <v>20.43472388221183</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.29248315753577</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 15.432x + -5835.432</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>345.4540720477756</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>849363057.4685625</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.473050545763279e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9134011861238815</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-176.543</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.73825e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-80.574</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2391212664022261</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.9157932615623966</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.879885299195631</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.87321016345282</v>
+      </c>
+      <c r="J10" t="n">
+        <v>21.02856807254446</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.39895569203611</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 15.890x + -5922.040</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>341.2259099112376</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>472832364.0553477</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.225130505633036e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9170265949096936</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-173.7449999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.71744e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-80.77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.2382283908017906</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.6565990320108703</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.689928116190377</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.644874138205106</v>
+      </c>
+      <c r="J11" t="n">
+        <v>20.85108052391334</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.39634014755802</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 15.878x + -5821.153</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>337.3381906520464</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>261051548.6262453</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8.035422719802362e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9198480491341916</v>
       </c>
     </row>
   </sheetData>
@@ -1310,7 +6134,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1414,8 +6238,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1445,6 +6267,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-234.4999999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.84296e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.185</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.1623965435353185</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.8092800366591126</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.316430163586498</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.202748515029585</v>
+      </c>
+      <c r="J2" t="n">
+        <v>14.64030760710914</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.12960059451331</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 11.736x + -5683.332</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>417.7472076657106</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>226821460.078298</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.44353238429869e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8359661112213421</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-202.218</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.81725e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-78.242</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.3814980439111771</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1.272972744264743</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.852466773046397</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.909291168545661</v>
+      </c>
+      <c r="J3" t="n">
+        <v>18.20706193145119</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.79000605363042</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 13.585x + -6306.152</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>409.2528650031653</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>228500177.6122265</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.185563077314297e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8645279071681522</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-188.469</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.78223e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-78.70999999999999</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.5213230390529552</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.004711469730084</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.779428672820511</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.784266052922787</v>
+      </c>
+      <c r="J4" t="n">
+        <v>18.82812041795541</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.09604588803867</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.654x + -6706.369</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>404.9730002838888</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>224601886.0095915</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.096061458687113e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8751476842042138</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-181.8340000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.75225e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-79.051</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.5121455487054143</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.595991076440078</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.412217662441499</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19.35929534743119</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.07010806880217</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.557x + -6538.014</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>400.9688127253339</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>233810940.7085494</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1.038776231899943e-06</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8822300035820875</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-172.51</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.7266e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-79.343</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.8140840546572412</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.243309414853227</v>
+      </c>
+      <c r="H6" t="n">
+        <v>2.256356632628583</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.111021107059876</v>
+      </c>
+      <c r="J6" t="n">
+        <v>22.34143144567199</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.3974213244698</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 15.883x + -7090.955</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>396.5798434487414</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>655130097.0375171</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9.937445627067558e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8880242328620667</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-168.513</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.7051e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-79.599</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.03167957378555899</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.05799267816026</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.846316946268489</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.866833868380211</v>
+      </c>
+      <c r="J7" t="n">
+        <v>22.83206017039094</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.39990871394555</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 15.894x + -6975.741</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>391.9445455530394</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>161931033.7023265</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>9.567497309654283e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.8930081884427498</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-164.125</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.68669e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-79.828</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2476222924378204</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.9489861593759239</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.818868025082613</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.449168017004949</v>
+      </c>
+      <c r="J8" t="n">
+        <v>22.30368778780296</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.52055460344455</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 16.447x + -7128.936</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>387.4690119672044</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>236660655.3961978</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9.260766037454285e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.8972817891371527</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-159.772</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.66931e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-80.042</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2196336436880204</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.9043474548469617</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.42452217486419</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.524003465387857</v>
+      </c>
+      <c r="J9" t="n">
+        <v>23.16760104759276</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.61093400004739</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 16.886x + -7229.802</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>383.2822621587598</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>210447611.5556608</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.986873886286346e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9012238717351333</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-155.4420000000001</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.65709e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-80.233</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3101274608736999</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.8747583848827745</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.009664899115111</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.601448608230351</v>
+      </c>
+      <c r="J10" t="n">
+        <v>23.94576419934643</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.69588850910867</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 17.322x + -7331.279</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>379.4042988125393</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>624009656.8922387</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.768879609255373e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9044926105548891</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-151.945</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.64191e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-80.40600000000001</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4523687698168246</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.9177662989676423</v>
+      </c>
+      <c r="H11" t="n">
+        <v>2.002530197280932</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.066245506968277</v>
+      </c>
+      <c r="J11" t="n">
+        <v>26.25759194382906</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.74793919765791</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 17.599x + -7361.998</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>375.7329626332076</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>159994176.9848319</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8.561757955896253e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9075872903422426</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-150.413</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.63033e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-80.53700000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.4270857647481843</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.212496589357122</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.015776108282767</v>
+      </c>
+      <c r="I12" t="n">
+        <v>3.08968663734819</v>
+      </c>
+      <c r="J12" t="n">
+        <v>26.69928541848866</v>
+      </c>
+      <c r="K12" t="n">
+        <v>86.80761449780843</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 17.929x + -7422.985</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>372.2798102040754</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>217591330.8219371</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>8.407841750404369e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9099342884053379</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-145.576</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.62104e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-80.702</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.2424974841333522</v>
+      </c>
+      <c r="G13" t="n">
+        <v>1.149520551129594</v>
+      </c>
+      <c r="H13" t="n">
+        <v>2.050908912207502</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.535372101897286</v>
+      </c>
+      <c r="J13" t="n">
+        <v>25.96298396349746</v>
+      </c>
+      <c r="K13" t="n">
+        <v>86.90405563077231</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 18.489x + -7584.620</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>368.9567173075583</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>303843703.1087019</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>8.243302362294342e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9125830831068515</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-144.2629999999999</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.61169e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-80.84</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.3352050718671497</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.958755746146509</v>
+      </c>
+      <c r="H14" t="n">
+        <v>2.001668244491126</v>
+      </c>
+      <c r="I14" t="n">
+        <v>3.123675625299848</v>
+      </c>
+      <c r="J14" t="n">
+        <v>27.77352621232956</v>
+      </c>
+      <c r="K14" t="n">
+        <v>86.85032697074804</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 18.173x + -7356.408</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>365.7232932991741</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>200496852.5317627</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>8.10485472374145e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9148156246906155</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-142.094</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.6039e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-80.958</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3572078547478958</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.6480608949260144</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.631086403487551</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.689751497767332</v>
+      </c>
+      <c r="J15" t="n">
+        <v>26.48262219080131</v>
+      </c>
+      <c r="K15" t="n">
+        <v>86.91608356221145</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 18.561x + -7444.026</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>362.4449858407583</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>99398386.45434077</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>7.985641322860091e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9167876429668199</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-139.393</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.59584e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-81.07899999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5552965071706004</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.482768992555256</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2.043931506468009</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.230491285076649</v>
+      </c>
+      <c r="J16" t="n">
+        <v>29.43307112087036</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.04139134951386</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 19.349x + -7707.085</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>359.2066827937394</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>150058737.6249207</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.872979423758546e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9186516067912844</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-137.705</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.5913e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-81.176</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.436268012858271</v>
+      </c>
+      <c r="G17" t="n">
+        <v>1.248635917128191</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.866266752416742</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.154088624055564</v>
+      </c>
+      <c r="J17" t="n">
+        <v>29.83209795293848</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.08235123250444</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 19.621x + -7739.443</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>355.9968355252498</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>194849446.0354508</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7.782783084268183e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9202361608546163</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-137.09</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.58504e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-81.274</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.514638049620759</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.086332455754805</v>
+      </c>
+      <c r="H18" t="n">
+        <v>2.238722145157286</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.187096065802534</v>
+      </c>
+      <c r="J18" t="n">
+        <v>29.57709165460403</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.0904819324337</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 19.676x + -7682.685</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>352.8422565355276</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>224647548.3459699</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>7.697054488548521e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9216871260833548</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-134.0170000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.5813e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-81.398</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4700349147343521</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.9619189249930687</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.299034811079055</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.829410159049698</v>
+      </c>
+      <c r="J19" t="n">
+        <v>29.73491710030678</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.12274139930787</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 19.897x + -7687.783</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>349.6816558741185</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>143577996.6829306</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7.596315165932298e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9235366745520968</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-132.952</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.5765e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-81.491</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2929770961099574</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.175667931061104</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.866004361219266</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2.822874190548094</v>
+      </c>
+      <c r="J20" t="n">
+        <v>29.41597137133795</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.14911157335852</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 20.081x + -7681.191</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>346.5167564290449</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>378870519.4103824</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7.51514431538005e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9250009720161539</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-131.369</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.57344e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-81.575</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.8270406033491171</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1.380363339654291</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.809232970825728</v>
+      </c>
+      <c r="I21" t="n">
+        <v>3.341352473016772</v>
+      </c>
+      <c r="J21" t="n">
+        <v>31.63344129499119</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.22916975012306</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 20.662x + -7841.170</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>343.3036977339311</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>187752679.7979519</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7.447306624467331e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9262621540039233</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-129.769</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.57011e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-81.69199999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4288725566562775</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.8783699069976134</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.048508291328718</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.862473984124695</v>
+      </c>
+      <c r="J22" t="n">
+        <v>29.81380469916768</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.21428760940691</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 20.552x + -7703.352</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>340.0849493883837</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>743855828.3581824</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>7.359385478192486e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9279323355349972</v>
       </c>
     </row>
   </sheetData>
@@ -1458,7 +7372,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1562,8 +7476,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1593,6 +7505,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-276.889</v>
+      </c>
+      <c r="D2" t="n">
+        <v>5.06168e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-75.729</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.5001486590850153</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.7562228226069914</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.522026743938313</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.160764579501233</v>
+      </c>
+      <c r="J2" t="n">
+        <v>11.96880315907912</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.13590972262895</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 9.736x + -4706.862</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>409.5966677084947</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>23643246.47042691</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.680464557764971e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8210742518935598</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-229.763</v>
+      </c>
+      <c r="D3" t="n">
+        <v>5.05983e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-77.738</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.5808939926402973</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.388584761184423</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.366079639626519</v>
+      </c>
+      <c r="J3" t="n">
+        <v>14.37234780327933</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.06619720273187</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 11.584x + -4976.356</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>387.9620306346272</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>425516878.9159348</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.17313974285562e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8744203424859919</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-209.499</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.98707e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-78.54900000000001</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.1424282531357242</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.8589615223274628</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.565193277231401</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.673473578485488</v>
+      </c>
+      <c r="J4" t="n">
+        <v>16.46437352006917</v>
+      </c>
+      <c r="K4" t="n">
+        <v>85.58516677937202</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 12.952x + -5411.810</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>380.4854366236969</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>156286969.7261375</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1.042702286983623e-06</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8897456183513072</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-194.066</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.91899e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-79.108</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5893254520247888</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.285754398867361</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.0273833269426</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.968174921257336</v>
+      </c>
+      <c r="J5" t="n">
+        <v>18.32366201674681</v>
+      </c>
+      <c r="K5" t="n">
+        <v>85.99007229705575</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 14.265x + -5882.446</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>375.3988591102163</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>411004768.3896478</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>9.667632009195438e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8988976992951779</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-187.0000000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.86304e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-79.521</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1849589041422322</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.6327020060024939</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.68958607681293</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.494243346784313</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18.88314099900246</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.08654354099457</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 14.618x + -5912.551</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>370.5521640097273</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>252678220.7777854</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9.154067010114607e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.905276494417247</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-178.0450000000001</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.81797e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-79.883</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.6486647436649666</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8560208691567313</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.785096156789869</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.615233704197306</v>
+      </c>
+      <c r="J7" t="n">
+        <v>20.07945041236714</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.33257021576475</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 15.602x + -6235.442</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>365.6591788806057</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>199763291.0778566</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.743835325129439e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9106807515897078</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-173.8440000000001</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.7786e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-80.18600000000001</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.4740426777675529</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.573847299797207</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.63391102063363</v>
+      </c>
+      <c r="J8" t="n">
+        <v>20.80610951758174</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.34633725051124</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 15.660x + -6135.529</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>360.6028353008273</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>393828248.638447</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8.417608574416963e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9151058740197378</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-165.977</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.74438e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-80.47199999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8234537176857212</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.682203796314076</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.95193306293261</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.110994581119319</v>
+      </c>
+      <c r="J9" t="n">
+        <v>22.36865819095963</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.62592367176711</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 16.962x + -6578.014</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>355.5571271536988</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>291080314.3059894</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.130776909525363e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9191796398091944</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-162.939</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.71805e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-80.72</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.2350043506940432</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.914260050956486</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.778509844187109</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.905110282901658</v>
+      </c>
+      <c r="J10" t="n">
+        <v>22.99686477583796</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.60634163310644</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 16.863x + -6410.810</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>350.7256056046506</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>202197978.6934312</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.900417733723573e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9225975243207039</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-158.1829999999999</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.69256e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-80.943</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.4666709475032766</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.041937800938761</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.658584385776407</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.684840930116787</v>
+      </c>
+      <c r="J11" t="n">
+        <v>23.23310998169568</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.73447448770771</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 17.527x + -6576.717</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>346.2620188885043</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>283062746.1524704</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>7.698221397174921e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.925669087504264</v>
       </c>
     </row>
   </sheetData>
@@ -1606,7 +8038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1710,8 +8142,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1741,6 +8171,1098 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-202.537</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.76632e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.64400000000001</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.7771873896084369</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1.083176045982918</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.626548869867174</v>
+      </c>
+      <c r="I2" t="n">
+        <v>2.644994475207516</v>
+      </c>
+      <c r="J2" t="n">
+        <v>18.18406376769286</v>
+      </c>
+      <c r="K2" t="n">
+        <v>85.78537421927085</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 13.570x + -6843.162</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>438.3739120010454</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>37313480.39081773</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.266813073883723e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8533406657864562</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-178.765</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.74076e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-78.58799999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1198867299119269</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.8053831467700157</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.020858217434877</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.53392835076507</v>
+      </c>
+      <c r="J3" t="n">
+        <v>20.44507927159098</v>
+      </c>
+      <c r="K3" t="n">
+        <v>86.18804292050878</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 15.008x + -7204.231</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>427.9137340466133</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>62432317.69983397</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1.068721946864941e-06</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8779243616846807</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-164.764</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.70895e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-79.021</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.8531281030710763</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.248330204912236</v>
+      </c>
+      <c r="H4" t="n">
+        <v>2.232020104681853</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.207373042269441</v>
+      </c>
+      <c r="J4" t="n">
+        <v>23.57772090874782</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.57986956023579</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 16.733x + -7940.519</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>422.7380480047251</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>191939620.4062985</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9.979548136303341e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.8871396027937497</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-157.039</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.68432e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-79.331</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.9719800631099487</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.764185951249406</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.38583202821234</v>
+      </c>
+      <c r="I5" t="n">
+        <v>3.396476314054961</v>
+      </c>
+      <c r="J5" t="n">
+        <v>25.78162705559582</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.74344256078949</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 17.575x + -8239.343</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>418.2600864407751</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>172998642.9858067</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>9.531497859256004e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.8931999939610994</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-154.919</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.66149e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-79.56999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.3124801425364943</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.8468746452961974</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.848534340910579</v>
+      </c>
+      <c r="I6" t="n">
+        <v>2.664541904079427</v>
+      </c>
+      <c r="J6" t="n">
+        <v>24.38174846657641</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.6698738062922</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 17.186x + -7911.982</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>413.8114836614133</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>340940715.5667116</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>9.194333412358749e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.8978543656938922</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-150.36</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.64535e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-79.794</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.2435525135550979</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.8500694502118552</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.729553403228067</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.494546836641941</v>
+      </c>
+      <c r="J7" t="n">
+        <v>24.98309728818039</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.75137463566472</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 17.618x + -8009.400</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>409.4028202701477</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>449156467.7310114</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>8.916486933032104e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9019026317153118</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>10</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-146.357</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.63123e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-79.994</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.230455214431745</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.7372203931744692</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.983281513832002</v>
+      </c>
+      <c r="I8" t="n">
+        <v>2.643018619430513</v>
+      </c>
+      <c r="J8" t="n">
+        <v>27.01499627703845</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.78347182229572</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 17.794x + -7983.603</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>405.1666236450736</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>170601388.8860681</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>8.676512223636543e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9055252247396053</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-140.483</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.61892e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-80.187</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.8028156818980049</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.475966743823961</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.171522233287315</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.223567482670965</v>
+      </c>
+      <c r="J9" t="n">
+        <v>29.56097891629726</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.9922843357253</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 19.032x + -8475.388</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>401.0661510930278</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>110008698.7541743</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>8.46008907412597e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9089000637390241</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-139.574</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.60773e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-80.339</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3354035625223621</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.7852928017883515</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.030389885209108</v>
+      </c>
+      <c r="I10" t="n">
+        <v>2.896014498207722</v>
+      </c>
+      <c r="J10" t="n">
+        <v>28.73348711450161</v>
+      </c>
+      <c r="K10" t="n">
+        <v>86.92996472219281</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 18.645x + -8181.955</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>397.2817842955411</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>163471712.7856244</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>8.290154829325843e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.911578649492281</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-138.184</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.59828e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-80.47799999999999</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1012091108841455</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.8141289940926068</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.75641338604335</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.644005310281202</v>
+      </c>
+      <c r="J11" t="n">
+        <v>28.03220630902175</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.94504947383524</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.737x + -8129.735</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>393.7836631431049</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>215595680.5163926</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>8.139573087446793e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9140190537441225</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B12" t="n">
+        <v>-135.092</v>
+      </c>
+      <c r="D12" t="n">
+        <v>4.58991e-07</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-80.61199999999999</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1603568218766196</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1.054795122423983</v>
+      </c>
+      <c r="H12" t="n">
+        <v>2.002924902444626</v>
+      </c>
+      <c r="I12" t="n">
+        <v>2.942700943214583</v>
+      </c>
+      <c r="J12" t="n">
+        <v>29.4336183416531</v>
+      </c>
+      <c r="K12" t="n">
+        <v>87.02624608748611</v>
+      </c>
+      <c r="W12" t="n">
+        <v>11</v>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>y = 19.250x + -8281.153</t>
+        </is>
+      </c>
+      <c r="Y12" t="n">
+        <v>390.4954805087149</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>320826921.0744914</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>8.004479004707351e-07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0.9162497946736372</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B13" t="n">
+        <v>-132.969</v>
+      </c>
+      <c r="D13" t="n">
+        <v>4.58185e-07</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-80.72799999999999</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.3643271049418509</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.976858856830971</v>
+      </c>
+      <c r="H13" t="n">
+        <v>1.801837662497254</v>
+      </c>
+      <c r="I13" t="n">
+        <v>2.91016269346947</v>
+      </c>
+      <c r="J13" t="n">
+        <v>30.64638431007635</v>
+      </c>
+      <c r="K13" t="n">
+        <v>87.09347352354551</v>
+      </c>
+      <c r="W13" t="n">
+        <v>12</v>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>y = 19.696x + -8401.525</t>
+        </is>
+      </c>
+      <c r="Y13" t="n">
+        <v>387.380963589799</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>164579411.1256917</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>7.887622345882293e-07</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0.9181883494430608</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B14" t="n">
+        <v>-129.81</v>
+      </c>
+      <c r="D14" t="n">
+        <v>4.57753e-07</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-80.842</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.2737734101181623</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1.226616297558083</v>
+      </c>
+      <c r="H14" t="n">
+        <v>1.989846585499752</v>
+      </c>
+      <c r="I14" t="n">
+        <v>2.891775176486245</v>
+      </c>
+      <c r="J14" t="n">
+        <v>29.95241704508424</v>
+      </c>
+      <c r="K14" t="n">
+        <v>87.18717141016353</v>
+      </c>
+      <c r="W14" t="n">
+        <v>13</v>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>y = 20.353x + -8622.339</t>
+        </is>
+      </c>
+      <c r="Y14" t="n">
+        <v>384.3899998105983</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>225588116.6271352</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>7.789540139398641e-07</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0.9199148681923197</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20</v>
+      </c>
+      <c r="B15" t="n">
+        <v>-127.909</v>
+      </c>
+      <c r="D15" t="n">
+        <v>4.5734e-07</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-80.961</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.37344005728242</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.9597814403458185</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.844441439904753</v>
+      </c>
+      <c r="I15" t="n">
+        <v>2.93608211158811</v>
+      </c>
+      <c r="J15" t="n">
+        <v>30.86579938698311</v>
+      </c>
+      <c r="K15" t="n">
+        <v>87.15478327222786</v>
+      </c>
+      <c r="W15" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>y = 20.121x + -8429.467</t>
+        </is>
+      </c>
+      <c r="Y15" t="n">
+        <v>381.4474402696158</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>156640161.1475782</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>7.685070499554922e-07</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0.9217976267939785</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B16" t="n">
+        <v>-126.046</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4.56802e-07</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-81.039</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.6297353114811841</v>
+      </c>
+      <c r="G16" t="n">
+        <v>1.336810448744086</v>
+      </c>
+      <c r="H16" t="n">
+        <v>1.702099686311896</v>
+      </c>
+      <c r="I16" t="n">
+        <v>3.070800069441218</v>
+      </c>
+      <c r="J16" t="n">
+        <v>31.71038897979813</v>
+      </c>
+      <c r="K16" t="n">
+        <v>87.28882799704577</v>
+      </c>
+      <c r="W16" t="n">
+        <v>15</v>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>y = 21.117x + -8803.437</t>
+        </is>
+      </c>
+      <c r="Y16" t="n">
+        <v>378.5169579094972</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>207228195.8585008</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.613762932077516e-07</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0.9230196628031975</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B17" t="n">
+        <v>-127.987</v>
+      </c>
+      <c r="D17" t="n">
+        <v>4.56379e-07</v>
+      </c>
+      <c r="E17" t="n">
+        <v>-81.13200000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.2766780142113958</v>
+      </c>
+      <c r="H17" t="n">
+        <v>1.543756870255331</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2.740977706870704</v>
+      </c>
+      <c r="J17" t="n">
+        <v>31.60564304574271</v>
+      </c>
+      <c r="K17" t="n">
+        <v>87.00821877162034</v>
+      </c>
+      <c r="W17" t="n">
+        <v>16</v>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>y = 19.134x + -7837.111</t>
+        </is>
+      </c>
+      <c r="Y17" t="n">
+        <v>375.6856700409101</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>256771806.4796622</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>7.534795476309633e-07</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0.9244483286258287</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B18" t="n">
+        <v>-124.0189999999999</v>
+      </c>
+      <c r="D18" t="n">
+        <v>4.55973e-07</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-81.23</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.09677482252185085</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.012815570676912</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.999707488786076</v>
+      </c>
+      <c r="I18" t="n">
+        <v>3.093573834962346</v>
+      </c>
+      <c r="J18" t="n">
+        <v>33.72816077482798</v>
+      </c>
+      <c r="K18" t="n">
+        <v>87.21952144430335</v>
+      </c>
+      <c r="W18" t="n">
+        <v>17</v>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>y = 20.590x + -8408.380</t>
+        </is>
+      </c>
+      <c r="Y18" t="n">
+        <v>372.8719417514002</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>407512057.3213127</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>7.456470208592552e-07</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0.9258764166958136</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B19" t="n">
+        <v>-122.1080000000001</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4.55624e-07</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-81.31999999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.4195969550492009</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.538649390452874</v>
+      </c>
+      <c r="H19" t="n">
+        <v>2.151265977815468</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2.979356815025025</v>
+      </c>
+      <c r="J19" t="n">
+        <v>33.49271493661889</v>
+      </c>
+      <c r="K19" t="n">
+        <v>87.30897587273675</v>
+      </c>
+      <c r="W19" t="n">
+        <v>18</v>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>y = 21.276x + -8633.112</t>
+        </is>
+      </c>
+      <c r="Y19" t="n">
+        <v>370.0935529022672</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>202205481.6304045</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>7.381962876302981e-07</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0.9272713516423379</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B20" t="n">
+        <v>-121.873</v>
+      </c>
+      <c r="D20" t="n">
+        <v>4.55382e-07</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-81.392</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.3598447761619862</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.7282904800313691</v>
+      </c>
+      <c r="H20" t="n">
+        <v>2.081237558101108</v>
+      </c>
+      <c r="I20" t="n">
+        <v>3.301899835515345</v>
+      </c>
+      <c r="J20" t="n">
+        <v>34.47729140310153</v>
+      </c>
+      <c r="K20" t="n">
+        <v>87.28953721596211</v>
+      </c>
+      <c r="W20" t="n">
+        <v>19</v>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>y = 21.123x + -8490.746</t>
+        </is>
+      </c>
+      <c r="Y20" t="n">
+        <v>367.3231930948887</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>125528326.2901103</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>7.326524191337869e-07</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0.9283223804751827</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B21" t="n">
+        <v>-120.841</v>
+      </c>
+      <c r="D21" t="n">
+        <v>4.55044e-07</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-81.479</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.03975724526578119</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.7507491670410263</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.395055773194267</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.806491621768894</v>
+      </c>
+      <c r="J21" t="n">
+        <v>33.47534483144656</v>
+      </c>
+      <c r="K21" t="n">
+        <v>87.28350759337729</v>
+      </c>
+      <c r="W21" t="n">
+        <v>20</v>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>y = 21.076x + -8394.225</t>
+        </is>
+      </c>
+      <c r="Y21" t="n">
+        <v>364.5510236595847</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>199251243.4022189</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>7.259537778530464e-07</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0.9295846152132796</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>30</v>
+      </c>
+      <c r="B22" t="n">
+        <v>-117.864</v>
+      </c>
+      <c r="D22" t="n">
+        <v>4.54982e-07</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-81.562</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.629143386497851</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1.527654774718521</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.35989606077202</v>
+      </c>
+      <c r="I22" t="n">
+        <v>3.261838021127298</v>
+      </c>
+      <c r="J22" t="n">
+        <v>36.5086044093004</v>
+      </c>
+      <c r="K22" t="n">
+        <v>87.45211959884001</v>
+      </c>
+      <c r="W22" t="n">
+        <v>21</v>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>y = 22.473x + -8914.660</t>
+        </is>
+      </c>
+      <c r="Y22" t="n">
+        <v>361.6981794960921</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>218464713.8409812</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>7.201651642019925e-07</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0.9307596279854847</v>
       </c>
     </row>
   </sheetData>
@@ -1754,7 +9276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB1"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,8 +9380,6 @@
           <t>Area Rs-Para</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr"/>
-      <c r="V1" t="inlineStr"/>
       <c r="W1" t="inlineStr">
         <is>
           <t>Cycle</t>
@@ -1889,6 +9409,526 @@
         <is>
           <t>n</t>
         </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B2" t="n">
+        <v>-275.068</v>
+      </c>
+      <c r="D2" t="n">
+        <v>4.77106e-07</v>
+      </c>
+      <c r="E2" t="n">
+        <v>-77.402</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2391220231295112</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.4677179285621796</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1.031620251708121</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.935681700930658</v>
+      </c>
+      <c r="J2" t="n">
+        <v>12.82834797222325</v>
+      </c>
+      <c r="K2" t="n">
+        <v>84.41381906368633</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1</v>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>y = 10.224x + -4547.682</t>
+        </is>
+      </c>
+      <c r="Y2" t="n">
+        <v>381.8066934807066</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>384290012.9981383</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.245415063477581e-06</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.8563738546973015</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B3" t="n">
+        <v>-224.0400000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>4.76293e-07</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-79.16200000000001</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.4616697440533737</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.7660777820712275</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1.48491294348374</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.815396372467346</v>
+      </c>
+      <c r="J3" t="n">
+        <v>16.14121171012069</v>
+      </c>
+      <c r="K3" t="n">
+        <v>85.56221718859311</v>
+      </c>
+      <c r="W3" t="n">
+        <v>2</v>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>y = 12.885x + -5149.400</t>
+        </is>
+      </c>
+      <c r="Y3" t="n">
+        <v>361.0055892513041</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>148254202.694783</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>9.575416816390405e-07</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.8952915193310079</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>9</v>
+      </c>
+      <c r="B4" t="n">
+        <v>-202.367</v>
+      </c>
+      <c r="D4" t="n">
+        <v>4.69554e-07</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-79.904</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.3404743735288339</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1.353293402458386</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.977045484888226</v>
+      </c>
+      <c r="I4" t="n">
+        <v>2.866688355591487</v>
+      </c>
+      <c r="J4" t="n">
+        <v>17.90561527678474</v>
+      </c>
+      <c r="K4" t="n">
+        <v>86.05377117096188</v>
+      </c>
+      <c r="W4" t="n">
+        <v>3</v>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>y = 14.496x + -5636.568</t>
+        </is>
+      </c>
+      <c r="Y4" t="n">
+        <v>354.0310504671017</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>193539432.451957</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>8.694549085997285e-07</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0.9075045683677057</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B5" t="n">
+        <v>-188.856</v>
+      </c>
+      <c r="D5" t="n">
+        <v>4.64099e-07</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-80.376</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.3126867925963355</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1.143332880137172</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.865604262284245</v>
+      </c>
+      <c r="I5" t="n">
+        <v>2.776391343502419</v>
+      </c>
+      <c r="J5" t="n">
+        <v>19.38343415737194</v>
+      </c>
+      <c r="K5" t="n">
+        <v>86.32404876641756</v>
+      </c>
+      <c r="W5" t="n">
+        <v>4</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>y = 15.565x + -5954.809</t>
+        </is>
+      </c>
+      <c r="Y5" t="n">
+        <v>349.329650444781</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>193668420.6884376</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>8.201765853489458e-07</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0.9144184688814156</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>15</v>
+      </c>
+      <c r="B6" t="n">
+        <v>-180.988</v>
+      </c>
+      <c r="D6" t="n">
+        <v>4.5952e-07</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-80.738</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.1657627458050188</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1.200167355316335</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1.732267628032193</v>
+      </c>
+      <c r="I6" t="n">
+        <v>3.13956058229931</v>
+      </c>
+      <c r="J6" t="n">
+        <v>21.20116145234182</v>
+      </c>
+      <c r="K6" t="n">
+        <v>86.43077153242696</v>
+      </c>
+      <c r="W6" t="n">
+        <v>5</v>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>y = 16.032x + -6018.307</t>
+        </is>
+      </c>
+      <c r="Y6" t="n">
+        <v>344.4445793016002</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>195359165.8186222</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>7.845546070895618e-07</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0.9195380809221833</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>18</v>
+      </c>
+      <c r="B7" t="n">
+        <v>-173.04</v>
+      </c>
+      <c r="D7" t="n">
+        <v>4.56141e-07</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-81.06</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.7606699664169325</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.709185618074626</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.616158702049958</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21.85360288835843</v>
+      </c>
+      <c r="K7" t="n">
+        <v>86.55080728929757</v>
+      </c>
+      <c r="W7" t="n">
+        <v>6</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>y = 16.591x + -6123.038</t>
+        </is>
+      </c>
+      <c r="Y7" t="n">
+        <v>339.5606496956183</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>137165222.1105785</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>7.564184407878399e-07</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0.9238620000756955</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>21</v>
+      </c>
+      <c r="B8" t="n">
+        <v>-167.181</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.5332e-07</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-81.285</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1.10418152927704</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1.152327272624091</v>
+      </c>
+      <c r="H8" t="n">
+        <v>2.012381738611669</v>
+      </c>
+      <c r="I8" t="n">
+        <v>3.123012618967273</v>
+      </c>
+      <c r="J8" t="n">
+        <v>23.42290491972876</v>
+      </c>
+      <c r="K8" t="n">
+        <v>86.75641427325557</v>
+      </c>
+      <c r="W8" t="n">
+        <v>7</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>y = 17.645x + -6434.767</t>
+        </is>
+      </c>
+      <c r="Y8" t="n">
+        <v>334.6334579109749</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>182839622.5572596</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>7.361551241341882e-07</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0.9269799310526019</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>-161.647</v>
+      </c>
+      <c r="D9" t="n">
+        <v>4.51184e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-81.535</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.4153092397717863</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.148004031052643</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.044066794046389</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.775124178158655</v>
+      </c>
+      <c r="J9" t="n">
+        <v>24.02169692235111</v>
+      </c>
+      <c r="K9" t="n">
+        <v>86.85473311335363</v>
+      </c>
+      <c r="W9" t="n">
+        <v>8</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>y = 18.198x + -6526.295</t>
+        </is>
+      </c>
+      <c r="Y9" t="n">
+        <v>329.9180126710327</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>144333249.1458964</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>7.1652088650224e-07</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0.9303094907850217</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>27</v>
+      </c>
+      <c r="B10" t="n">
+        <v>-156.297</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.49307e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>-81.727</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.113825854839255</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.280145708246429</v>
+      </c>
+      <c r="H10" t="n">
+        <v>2.251616509255678</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.187998412161114</v>
+      </c>
+      <c r="J10" t="n">
+        <v>25.15029856009681</v>
+      </c>
+      <c r="K10" t="n">
+        <v>87.01209275556037</v>
+      </c>
+      <c r="W10" t="n">
+        <v>9</v>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>y = 19.159x + -6790.271</t>
+        </is>
+      </c>
+      <c r="Y10" t="n">
+        <v>325.4370405855685</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>177303080.3925255</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>7.016495281387601e-07</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0.9328129290911628</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>30</v>
+      </c>
+      <c r="B11" t="n">
+        <v>-154.017</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.47867e-07</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-81.908</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.237363673091897</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1.189953050283336</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.539982400362601</v>
+      </c>
+      <c r="I11" t="n">
+        <v>2.682516985600774</v>
+      </c>
+      <c r="J11" t="n">
+        <v>25.0590033346918</v>
+      </c>
+      <c r="K11" t="n">
+        <v>86.95363110797396</v>
+      </c>
+      <c r="W11" t="n">
+        <v>10</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>y = 18.790x + -6526.385</t>
+        </is>
+      </c>
+      <c r="Y11" t="n">
+        <v>321.2988222282801</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>87504611.61801642</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>6.885139484362863e-07</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0.9351523850912739</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -543,7 +543,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -588,19 +588,19 @@
       <c r="K2" t="n">
         <v>86.49221849863669</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 16.313x + -8303.679</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-8303.678626407043</v>
       </c>
       <c r="Y2" t="n">
         <v>441.8751299021471</v>
       </c>
       <c r="Z2" t="n">
-        <v>245712547.1356277</v>
+        <v>184.19</v>
       </c>
       <c r="AA2" t="n">
         <v>9.077035214013106e-07</v>
@@ -640,19 +640,19 @@
       <c r="K3" t="n">
         <v>86.65194974328436</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.094x + -8487.128</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8487.127595586631</v>
       </c>
       <c r="Y3" t="n">
         <v>434.3481901031161</v>
       </c>
       <c r="Z3" t="n">
-        <v>38491344.48331343</v>
+        <v>171.579</v>
       </c>
       <c r="AA3" t="n">
         <v>8.496679723174884e-07</v>
@@ -692,19 +692,19 @@
       <c r="K4" t="n">
         <v>86.65947280398476</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.132x + -8310.605</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8310.605327035604</v>
       </c>
       <c r="Y4" t="n">
         <v>427.7779039390333</v>
       </c>
       <c r="Z4" t="n">
-        <v>59686438.34264517</v>
+        <v>164.317</v>
       </c>
       <c r="AA4" t="n">
         <v>8.143957286588159e-07</v>
@@ -744,19 +744,19 @@
       <c r="K5" t="n">
         <v>86.8244916387948</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.025x + -8611.818</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8611.818107984484</v>
       </c>
       <c r="Y5" t="n">
         <v>421.5797911742441</v>
       </c>
       <c r="Z5" t="n">
-        <v>63508959.18336506</v>
+        <v>157.765</v>
       </c>
       <c r="AA5" t="n">
         <v>7.892827574397358e-07</v>
@@ -796,19 +796,19 @@
       <c r="K6" t="n">
         <v>86.87144478999733</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 18.296x + -8591.413</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8591.412511777164</v>
       </c>
       <c r="Y6" t="n">
         <v>415.6768547387593</v>
       </c>
       <c r="Z6" t="n">
-        <v>30128315.26671074</v>
+        <v>154.299</v>
       </c>
       <c r="AA6" t="n">
         <v>7.71485166579219e-07</v>
@@ -848,19 +848,19 @@
       <c r="K7" t="n">
         <v>86.92248349849262</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 18.600x + -8596.735</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8596.735331531549</v>
       </c>
       <c r="Y7" t="n">
         <v>409.977589424865</v>
       </c>
       <c r="Z7" t="n">
-        <v>675381081.8686706</v>
+        <v>150.893</v>
       </c>
       <c r="AA7" t="n">
         <v>7.565498516939744e-07</v>
@@ -900,19 +900,19 @@
       <c r="K8" t="n">
         <v>87.01407570627818</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 19.171x + -8740.130</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8740.130202361239</v>
       </c>
       <c r="Y8" t="n">
         <v>404.4319783582843</v>
       </c>
       <c r="Z8" t="n">
-        <v>111313918.0968795</v>
+        <v>147.951</v>
       </c>
       <c r="AA8" t="n">
         <v>7.434343053118211e-07</v>
@@ -952,19 +952,19 @@
       <c r="K9" t="n">
         <v>86.94631826068088</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 18.745x + -8382.359</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8382.359059673714</v>
       </c>
       <c r="Y9" t="n">
         <v>399.2435837759633</v>
       </c>
       <c r="Z9" t="n">
-        <v>164357452.0273654</v>
+        <v>147.2149999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>7.313158604715136e-07</v>
@@ -1004,19 +1004,19 @@
       <c r="K10" t="n">
         <v>86.91908270045455</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.579x + -8177.335</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8177.335005830709</v>
       </c>
       <c r="Y10" t="n">
         <v>394.6339166541012</v>
       </c>
       <c r="Z10" t="n">
-        <v>1081600138.813152</v>
+        <v>145.519</v>
       </c>
       <c r="AA10" t="n">
         <v>7.200036925052079e-07</v>
@@ -1056,19 +1056,19 @@
       <c r="K11" t="n">
         <v>86.93416468923911</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.671x + -8112.778</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8112.777920204778</v>
       </c>
       <c r="Y11" t="n">
         <v>390.5236675824672</v>
       </c>
       <c r="Z11" t="n">
-        <v>121300484.0697669</v>
+        <v>143.198</v>
       </c>
       <c r="AA11" t="n">
         <v>7.10358220782034e-07</v>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -1254,19 +1254,19 @@
       <c r="K2" t="n">
         <v>86.34442876493496</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 15.652x + -7830.369</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7830.369185265049</v>
       </c>
       <c r="Y2" t="n">
         <v>435.0186249382122</v>
       </c>
       <c r="Z2" t="n">
-        <v>79437038.25296503</v>
+        <v>175.045</v>
       </c>
       <c r="AA2" t="n">
         <v>1.008483203030008e-06</v>
@@ -1306,19 +1306,19 @@
       <c r="K3" t="n">
         <v>86.79828850962785</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 17.877x + -8555.250</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8555.250389915491</v>
       </c>
       <c r="Y3" t="n">
         <v>424.1085412556876</v>
       </c>
       <c r="Z3" t="n">
-        <v>103316021.9869039</v>
+        <v>156.492</v>
       </c>
       <c r="AA3" t="n">
         <v>8.943508687437834e-07</v>
@@ -1358,19 +1358,19 @@
       <c r="K4" t="n">
         <v>86.87648169382103</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 18.325x + -8601.813</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8601.813200262834</v>
       </c>
       <c r="Y4" t="n">
         <v>418.9522391080113</v>
       </c>
       <c r="Z4" t="n">
-        <v>37718787.45935754</v>
+        <v>149.898</v>
       </c>
       <c r="AA4" t="n">
         <v>8.557950415430884e-07</v>
@@ -1410,19 +1410,19 @@
       <c r="K5" t="n">
         <v>86.91729452845723</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 18.568x + -8602.648</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8602.648156780922</v>
       </c>
       <c r="Y5" t="n">
         <v>415.0262851245232</v>
       </c>
       <c r="Z5" t="n">
-        <v>341754844.5517014</v>
+        <v>146.881</v>
       </c>
       <c r="AA5" t="n">
         <v>8.321549054307094e-07</v>
@@ -1462,19 +1462,19 @@
       <c r="K6" t="n">
         <v>87.06485746626791</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 19.504x + -8960.891</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8960.890612911184</v>
       </c>
       <c r="Y6" t="n">
         <v>410.983898887697</v>
       </c>
       <c r="Z6" t="n">
-        <v>169185510.2121852</v>
+        <v>142.6010000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>8.130490827824994e-07</v>
@@ -1514,19 +1514,19 @@
       <c r="K7" t="n">
         <v>87.13659687627519</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 19.993x + -9088.720</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-9088.720059306743</v>
       </c>
       <c r="Y7" t="n">
         <v>406.7603474091602</v>
       </c>
       <c r="Z7" t="n">
-        <v>225999761.0266023</v>
+        <v>140.2689999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>7.966910835692676e-07</v>
@@ -1566,19 +1566,19 @@
       <c r="K8" t="n">
         <v>86.99756703532763</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 19.066x + -8516.875</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8516.874534006982</v>
       </c>
       <c r="Y8" t="n">
         <v>402.4949007440025</v>
       </c>
       <c r="Z8" t="n">
-        <v>221187425.3334227</v>
+        <v>140.942</v>
       </c>
       <c r="AA8" t="n">
         <v>7.834205066514079e-07</v>
@@ -1618,19 +1618,19 @@
       <c r="K9" t="n">
         <v>87.14472927873885</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 20.050x + -8878.658</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8878.657663706701</v>
       </c>
       <c r="Y9" t="n">
         <v>398.5084272840842</v>
       </c>
       <c r="Z9" t="n">
-        <v>440368840.7393088</v>
+        <v>136.867</v>
       </c>
       <c r="AA9" t="n">
         <v>7.699376669980727e-07</v>
@@ -1670,19 +1670,19 @@
       <c r="K10" t="n">
         <v>87.12928594521571</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.942x + -8718.879</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8718.879094286116</v>
       </c>
       <c r="Y10" t="n">
         <v>394.7192300493788</v>
       </c>
       <c r="Z10" t="n">
-        <v>216432961.9668211</v>
+        <v>135.136</v>
       </c>
       <c r="AA10" t="n">
         <v>7.579703599375671e-07</v>
@@ -1722,19 +1722,19 @@
       <c r="K11" t="n">
         <v>87.17486865025123</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 20.264x + -8776.357</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8776.357454076953</v>
       </c>
       <c r="Y11" t="n">
         <v>391.2934095908259</v>
       </c>
       <c r="Z11" t="n">
-        <v>164604808.5796399</v>
+        <v>133.176</v>
       </c>
       <c r="AA11" t="n">
         <v>7.476361312322177e-07</v>
@@ -1774,19 +1774,19 @@
       <c r="K12" t="n">
         <v>87.23000221781973</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 20.668x + -8867.960</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-8867.959509423963</v>
       </c>
       <c r="Y12" t="n">
         <v>387.9888220539746</v>
       </c>
       <c r="Z12" t="n">
-        <v>636982177.1051949</v>
+        <v>130.953</v>
       </c>
       <c r="AA12" t="n">
         <v>7.38636039839273e-07</v>
@@ -1826,19 +1826,19 @@
       <c r="K13" t="n">
         <v>87.17390846088941</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 20.257x + -8588.119</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-8588.119164103447</v>
       </c>
       <c r="Y13" t="n">
         <v>384.8544064891893</v>
       </c>
       <c r="Z13" t="n">
-        <v>210467638.5578675</v>
+        <v>131.1779999999999</v>
       </c>
       <c r="AA13" t="n">
         <v>7.313274669477334e-07</v>
@@ -1878,19 +1878,19 @@
       <c r="K14" t="n">
         <v>87.31095941786431</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 21.291x + -8983.087</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-8983.087148939432</v>
       </c>
       <c r="Y14" t="n">
         <v>381.7959252873379</v>
       </c>
       <c r="Z14" t="n">
-        <v>417794686.5864821</v>
+        <v>128.843</v>
       </c>
       <c r="AA14" t="n">
         <v>7.24701217516823e-07</v>
@@ -1930,19 +1930,19 @@
       <c r="K15" t="n">
         <v>87.47135818949879</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 22.644x + -9509.996</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-9509.995708780943</v>
       </c>
       <c r="Y15" t="n">
         <v>378.7175037836427</v>
       </c>
       <c r="Z15" t="n">
-        <v>103760347.6214598</v>
+        <v>124.3559999999999</v>
       </c>
       <c r="AA15" t="n">
         <v>7.16790368695532e-07</v>
@@ -1982,19 +1982,19 @@
       <c r="K16" t="n">
         <v>87.40001507291713</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 22.022x + -9138.471</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-9138.471431213011</v>
       </c>
       <c r="Y16" t="n">
         <v>375.6815895349957</v>
       </c>
       <c r="Z16" t="n">
-        <v>208214067.9970274</v>
+        <v>125.044</v>
       </c>
       <c r="AA16" t="n">
         <v>7.11348877747008e-07</v>
@@ -2034,19 +2034,19 @@
       <c r="K17" t="n">
         <v>87.41102247673675</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 22.116x + -9095.563</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-9095.562659639783</v>
       </c>
       <c r="Y17" t="n">
         <v>372.6977934854936</v>
       </c>
       <c r="Z17" t="n">
-        <v>152890524.945729</v>
+        <v>124.75</v>
       </c>
       <c r="AA17" t="n">
         <v>7.058668754276769e-07</v>
@@ -2086,19 +2086,19 @@
       <c r="K18" t="n">
         <v>87.34533099165118</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 21.568x + -8768.553</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-8768.552856788556</v>
       </c>
       <c r="Y18" t="n">
         <v>369.7578174330148</v>
       </c>
       <c r="Z18" t="n">
-        <v>151738271.3552929</v>
+        <v>125.069</v>
       </c>
       <c r="AA18" t="n">
         <v>7.006918199967112e-07</v>
@@ -2138,19 +2138,19 @@
       <c r="K19" t="n">
         <v>87.44064922809999</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 22.372x + -9033.733</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-9033.73252079194</v>
       </c>
       <c r="Y19" t="n">
         <v>366.856079214409</v>
       </c>
       <c r="Z19" t="n">
-        <v>306931823.3678589</v>
+        <v>121.879</v>
       </c>
       <c r="AA19" t="n">
         <v>6.943042421514423e-07</v>
@@ -2190,19 +2190,19 @@
       <c r="K20" t="n">
         <v>87.50195610308231</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 22.922x + -9187.913</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-9187.912833391589</v>
       </c>
       <c r="Y20" t="n">
         <v>363.8768205576325</v>
       </c>
       <c r="Z20" t="n">
-        <v>199021235.4283823</v>
+        <v>119.655</v>
       </c>
       <c r="AA20" t="n">
         <v>6.88108748222111e-07</v>
@@ -2242,19 +2242,19 @@
       <c r="K21" t="n">
         <v>87.53564373187106</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 23.235x + -9241.637</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-9241.637290420997</v>
       </c>
       <c r="Y21" t="n">
         <v>360.9486237394665</v>
       </c>
       <c r="Z21" t="n">
-        <v>183919532.2370981</v>
+        <v>119.123</v>
       </c>
       <c r="AA21" t="n">
         <v>6.83569896970495e-07</v>
@@ -2294,19 +2294,19 @@
       <c r="K22" t="n">
         <v>87.47095526829668</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 22.640x + -8897.679</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-8897.678884716743</v>
       </c>
       <c r="Y22" t="n">
         <v>357.9682818640612</v>
       </c>
       <c r="Z22" t="n">
-        <v>1270462204.530481</v>
+        <v>120.2</v>
       </c>
       <c r="AA22" t="n">
         <v>6.795181011603263e-07</v>
@@ -2432,12 +2432,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -2492,19 +2492,19 @@
       <c r="K2" t="n">
         <v>86.13945377474806</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 14.819x + -7446.211</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-7446.211464551119</v>
       </c>
       <c r="Y2" t="n">
         <v>433.0755477598454</v>
       </c>
       <c r="Z2" t="n">
-        <v>189294391.1809571</v>
+        <v>196.03</v>
       </c>
       <c r="AA2" t="n">
         <v>9.922148824033418e-07</v>
@@ -2544,19 +2544,19 @@
       <c r="K3" t="n">
         <v>86.61714570465722</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 16.917x + -8081.027</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-8081.026531394899</v>
       </c>
       <c r="Y3" t="n">
         <v>422.2385358405232</v>
       </c>
       <c r="Z3" t="n">
-        <v>59708384.05879393</v>
+        <v>165.46</v>
       </c>
       <c r="AA3" t="n">
         <v>8.529639486165217e-07</v>
@@ -2596,19 +2596,19 @@
       <c r="K4" t="n">
         <v>86.72188768178023</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 17.459x + -8188.276</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-8188.275960781168</v>
       </c>
       <c r="Y4" t="n">
         <v>417.5884862461021</v>
       </c>
       <c r="Z4" t="n">
-        <v>36044888.17761886</v>
+        <v>156.611</v>
       </c>
       <c r="AA4" t="n">
         <v>8.125703972419277e-07</v>
@@ -2648,19 +2648,19 @@
       <c r="K5" t="n">
         <v>87.04977891610596</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 19.404x + -9059.945</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-9059.944754414106</v>
       </c>
       <c r="Y5" t="n">
         <v>413.5496620947689</v>
       </c>
       <c r="Z5" t="n">
-        <v>454790505.9308857</v>
+        <v>146.769</v>
       </c>
       <c r="AA5" t="n">
         <v>7.88163149573542e-07</v>
@@ -2700,19 +2700,19 @@
       <c r="K6" t="n">
         <v>86.87749246948361</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 18.331x + -8396.356</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-8396.355584876788</v>
       </c>
       <c r="Y6" t="n">
         <v>409.3882828900535</v>
       </c>
       <c r="Z6" t="n">
-        <v>449681904.7030554</v>
+        <v>145.914</v>
       </c>
       <c r="AA6" t="n">
         <v>7.704798527426754e-07</v>
@@ -2752,19 +2752,19 @@
       <c r="K7" t="n">
         <v>87.02747491937123</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 19.258x + -8742.079</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8742.078544092812</v>
       </c>
       <c r="Y7" t="n">
         <v>405.0572527687936</v>
       </c>
       <c r="Z7" t="n">
-        <v>222551452.9046378</v>
+        <v>140.85</v>
       </c>
       <c r="AA7" t="n">
         <v>7.550447286602293e-07</v>
@@ -2804,19 +2804,19 @@
       <c r="K8" t="n">
         <v>87.03897266560439</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 19.333x + -8657.705</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-8657.704968765431</v>
       </c>
       <c r="Y8" t="n">
         <v>400.7303388075825</v>
       </c>
       <c r="Z8" t="n">
-        <v>219694685.1342096</v>
+        <v>138.72</v>
       </c>
       <c r="AA8" t="n">
         <v>7.417855691438191e-07</v>
@@ -2856,19 +2856,19 @@
       <c r="K9" t="n">
         <v>87.02591137060513</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 19.248x + -8507.557</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8507.557493821065</v>
       </c>
       <c r="Y9" t="n">
         <v>396.5803041922406</v>
       </c>
       <c r="Z9" t="n">
-        <v>326131378.9680545</v>
+        <v>138.199</v>
       </c>
       <c r="AA9" t="n">
         <v>7.318785446524434e-07</v>
@@ -2908,19 +2908,19 @@
       <c r="K10" t="n">
         <v>87.05236168936062</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.421x + -8480.874</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8480.874046406934</v>
       </c>
       <c r="Y10" t="n">
         <v>392.6631975947702</v>
       </c>
       <c r="Z10" t="n">
-        <v>329255284.1881668</v>
+        <v>135.258</v>
       </c>
       <c r="AA10" t="n">
         <v>7.208276239277801e-07</v>
@@ -2960,19 +2960,19 @@
       <c r="K11" t="n">
         <v>87.22185598824058</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 20.608x + -8937.783</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8937.783194451338</v>
       </c>
       <c r="Y11" t="n">
         <v>388.9439630694364</v>
       </c>
       <c r="Z11" t="n">
-        <v>159855868.3902268</v>
+        <v>131.565</v>
       </c>
       <c r="AA11" t="n">
         <v>7.111089980067962e-07</v>
@@ -3012,19 +3012,19 @@
       <c r="K12" t="n">
         <v>87.15281124632121</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 20.107x + -8607.014</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-8607.0140055543</v>
       </c>
       <c r="Y12" t="n">
         <v>385.4121407138171</v>
       </c>
       <c r="Z12" t="n">
-        <v>116870617.8895902</v>
+        <v>132.447</v>
       </c>
       <c r="AA12" t="n">
         <v>7.044464394495368e-07</v>
@@ -3064,19 +3064,19 @@
       <c r="K13" t="n">
         <v>87.20564446519681</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 20.488x + -8691.976</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-8691.97638429313</v>
       </c>
       <c r="Y13" t="n">
         <v>382.0050234085486</v>
       </c>
       <c r="Z13" t="n">
-        <v>209171369.0694711</v>
+        <v>131.004</v>
       </c>
       <c r="AA13" t="n">
         <v>6.981204294314548e-07</v>
@@ -3116,19 +3116,19 @@
       <c r="K14" t="n">
         <v>87.21069814602048</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 20.525x + -8616.665</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-8616.6647375128</v>
       </c>
       <c r="Y14" t="n">
         <v>378.6541941245881</v>
       </c>
       <c r="Z14" t="n">
-        <v>385677221.7194996</v>
+        <v>129.723</v>
       </c>
       <c r="AA14" t="n">
         <v>6.916289298655832e-07</v>
@@ -3168,19 +3168,19 @@
       <c r="K15" t="n">
         <v>87.21677231629147</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 20.570x + -8548.287</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-8548.286852487357</v>
       </c>
       <c r="Y15" t="n">
         <v>375.5427336321978</v>
       </c>
       <c r="Z15" t="n">
-        <v>154990064.9209351</v>
+        <v>127.657</v>
       </c>
       <c r="AA15" t="n">
         <v>6.85072256865229e-07</v>
@@ -3220,19 +3220,19 @@
       <c r="K16" t="n">
         <v>87.29973932488761</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 21.203x + -8751.373</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-8751.372774631207</v>
       </c>
       <c r="Y16" t="n">
         <v>372.5235151616664</v>
       </c>
       <c r="Z16" t="n">
-        <v>305699367.8179162</v>
+        <v>126.3220000000001</v>
       </c>
       <c r="AA16" t="n">
         <v>6.798831791571903e-07</v>
@@ -3272,19 +3272,19 @@
       <c r="K17" t="n">
         <v>87.20030488207833</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 20.449x + -8336.352</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-8336.351888326819</v>
       </c>
       <c r="Y17" t="n">
         <v>369.5490524095136</v>
       </c>
       <c r="Z17" t="n">
-        <v>112075823.0648189</v>
+        <v>127.994</v>
       </c>
       <c r="AA17" t="n">
         <v>6.754387727039867e-07</v>
@@ -3324,19 +3324,19 @@
       <c r="K18" t="n">
         <v>87.33122650575744</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 21.453x + -8702.471</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-8702.470732248117</v>
       </c>
       <c r="Y18" t="n">
         <v>366.5906727641661</v>
       </c>
       <c r="Z18" t="n">
-        <v>200470441.3851776</v>
+        <v>125.971</v>
       </c>
       <c r="AA18" t="n">
         <v>6.711142224885672e-07</v>
@@ -3376,19 +3376,19 @@
       <c r="K19" t="n">
         <v>87.30840048171451</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 21.271x + -8541.704</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-8541.704394462253</v>
       </c>
       <c r="Y19" t="n">
         <v>363.711147851523</v>
       </c>
       <c r="Z19" t="n">
-        <v>101810104.8653887</v>
+        <v>126.248</v>
       </c>
       <c r="AA19" t="n">
         <v>6.675263665375564e-07</v>
@@ -3428,19 +3428,19 @@
       <c r="K20" t="n">
         <v>87.31407338683741</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 21.316x + -8481.658</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-8481.65815018914</v>
       </c>
       <c r="Y20" t="n">
         <v>360.8848523078199</v>
       </c>
       <c r="Z20" t="n">
-        <v>788563842.0398979</v>
+        <v>125.181</v>
       </c>
       <c r="AA20" t="n">
         <v>6.626457979894738e-07</v>
@@ -3480,19 +3480,19 @@
       <c r="K21" t="n">
         <v>87.31091147042447</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 21.291x + -8392.941</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-8392.940558782655</v>
       </c>
       <c r="Y21" t="n">
         <v>358.1705882762301</v>
       </c>
       <c r="Z21" t="n">
-        <v>294176667.7708919</v>
+        <v>124.092</v>
       </c>
       <c r="AA21" t="n">
         <v>6.582015866471859e-07</v>
@@ -3532,19 +3532,19 @@
       <c r="K22" t="n">
         <v>87.39840699619239</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 22.008x + -8624.156</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-8624.156160304748</v>
       </c>
       <c r="Y22" t="n">
         <v>355.4980297768718</v>
       </c>
       <c r="Z22" t="n">
-        <v>195786323.3136893</v>
+        <v>121.503</v>
       </c>
       <c r="AA22" t="n">
         <v>6.538806611654203e-07</v>
@@ -3670,12 +3670,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -3730,19 +3730,19 @@
       <c r="K2" t="n">
         <v>84.17588870299647</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.804x + -4623.595</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-4623.594987243592</v>
       </c>
       <c r="Y2" t="n">
         <v>399.1107394250932</v>
       </c>
       <c r="Z2" t="n">
-        <v>438446194.1489649</v>
+        <v>293.102</v>
       </c>
       <c r="AA2" t="n">
         <v>1.317512045825061e-06</v>
@@ -3782,19 +3782,19 @@
       <c r="K3" t="n">
         <v>85.33752804804207</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.262x + -5156.461</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-5156.460874532487</v>
       </c>
       <c r="Y3" t="n">
         <v>376.7446016448904</v>
       </c>
       <c r="Z3" t="n">
-        <v>412906226.6559771</v>
+        <v>236.3339999999999</v>
       </c>
       <c r="AA3" t="n">
         <v>9.982360272586506e-07</v>
@@ -3834,19 +3834,19 @@
       <c r="K4" t="n">
         <v>85.77189009505075</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 13.527x + -5514.607</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-5514.607458360963</v>
       </c>
       <c r="Y4" t="n">
         <v>368.9296501274155</v>
       </c>
       <c r="Z4" t="n">
-        <v>202042743.9430597</v>
+        <v>215.6709999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>9.120585127132215e-07</v>
@@ -3886,19 +3886,19 @@
       <c r="K5" t="n">
         <v>85.93663182450629</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.077x + -5623.005</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-5623.004521106845</v>
       </c>
       <c r="Y5" t="n">
         <v>363.7664924369331</v>
       </c>
       <c r="Z5" t="n">
-        <v>200541967.061127</v>
+        <v>204.578</v>
       </c>
       <c r="AA5" t="n">
         <v>8.648920944189094e-07</v>
@@ -3938,19 +3938,19 @@
       <c r="K6" t="n">
         <v>86.16882978339994</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.933x + -5891.785</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-5891.785405700944</v>
       </c>
       <c r="Y6" t="n">
         <v>359.0947097940731</v>
       </c>
       <c r="Z6" t="n">
-        <v>98275559.66834185</v>
+        <v>194.877</v>
       </c>
       <c r="AA6" t="n">
         <v>8.299639251073624e-07</v>
@@ -3990,19 +3990,19 @@
       <c r="K7" t="n">
         <v>86.36335575721175</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 15.734x + -6129.946</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-6129.945738199643</v>
       </c>
       <c r="Y7" t="n">
         <v>354.4718578756008</v>
       </c>
       <c r="Z7" t="n">
-        <v>389018917.1033631</v>
+        <v>186.837</v>
       </c>
       <c r="AA7" t="n">
         <v>8.025533379876564e-07</v>
@@ -4042,19 +4042,19 @@
       <c r="K8" t="n">
         <v>86.44976604876672</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.118x + -6183.843</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-6183.843153199383</v>
       </c>
       <c r="Y8" t="n">
         <v>349.8973545128995</v>
       </c>
       <c r="Z8" t="n">
-        <v>143423329.243043</v>
+        <v>181.823</v>
       </c>
       <c r="AA8" t="n">
         <v>7.800550646503015e-07</v>
@@ -4094,19 +4094,19 @@
       <c r="K9" t="n">
         <v>86.54388671203137</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 16.558x + -6260.835</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-6260.834587116743</v>
       </c>
       <c r="Y9" t="n">
         <v>345.5275287145916</v>
       </c>
       <c r="Z9" t="n">
-        <v>188617771.1430337</v>
+        <v>176.717</v>
       </c>
       <c r="AA9" t="n">
         <v>7.609167513772127e-07</v>
@@ -4146,19 +4146,19 @@
       <c r="K10" t="n">
         <v>86.61620074139398</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 16.913x + -6308.095</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-6308.094701077208</v>
       </c>
       <c r="Y10" t="n">
         <v>341.3931195897867</v>
       </c>
       <c r="Z10" t="n">
-        <v>279365939.1792666</v>
+        <v>173.245</v>
       </c>
       <c r="AA10" t="n">
         <v>7.449007832611085e-07</v>
@@ -4198,19 +4198,19 @@
       <c r="K11" t="n">
         <v>86.76947872918841</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 17.717x + -6541.747</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-6541.747066667391</v>
       </c>
       <c r="Y11" t="n">
         <v>337.5217223839763</v>
       </c>
       <c r="Z11" t="n">
-        <v>184256538.910268</v>
+        <v>166.891</v>
       </c>
       <c r="AA11" t="n">
         <v>7.29545926736977e-07</v>
@@ -4336,12 +4336,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -4396,19 +4396,19 @@
       <c r="K2" t="n">
         <v>85.19589780308293</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.898x + -5928.531</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5928.530747659112</v>
       </c>
       <c r="Y2" t="n">
         <v>430.3375601763885</v>
       </c>
       <c r="Z2" t="n">
-        <v>177345990.1357034</v>
+        <v>236.588</v>
       </c>
       <c r="AA2" t="n">
         <v>1.312691647084753e-06</v>
@@ -4448,19 +4448,19 @@
       <c r="K3" t="n">
         <v>85.93749408650241</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 14.080x + -6692.469</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6692.468863382832</v>
       </c>
       <c r="Y3" t="n">
         <v>419.8009996635196</v>
       </c>
       <c r="Z3" t="n">
-        <v>50360310.56373951</v>
+        <v>199.874</v>
       </c>
       <c r="AA3" t="n">
         <v>1.074401804569402e-06</v>
@@ -4500,19 +4500,19 @@
       <c r="K4" t="n">
         <v>86.11405165353406</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.722x + -6860.358</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6860.358282151244</v>
       </c>
       <c r="Y4" t="n">
         <v>415.1516060485824</v>
       </c>
       <c r="Z4" t="n">
-        <v>161636050.9926125</v>
+        <v>186.5889999999999</v>
       </c>
       <c r="AA4" t="n">
         <v>9.967437724492801e-07</v>
@@ -4552,19 +4552,19 @@
       <c r="K5" t="n">
         <v>86.38286258754704</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.819x + -7310.533</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-7310.533424839303</v>
       </c>
       <c r="Y5" t="n">
         <v>411.1660005968433</v>
       </c>
       <c r="Z5" t="n">
-        <v>171120962.1477516</v>
+        <v>176.016</v>
       </c>
       <c r="AA5" t="n">
         <v>9.500555416419336e-07</v>
@@ -4604,19 +4604,19 @@
       <c r="K6" t="n">
         <v>86.40908360630586</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.935x + -7253.939</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-7253.939141756458</v>
       </c>
       <c r="Y6" t="n">
         <v>407.0124660538758</v>
       </c>
       <c r="Z6" t="n">
-        <v>224782532.1097848</v>
+        <v>170.3299999999999</v>
       </c>
       <c r="AA6" t="n">
         <v>9.148654314970473e-07</v>
@@ -4656,19 +4656,19 @@
       <c r="K7" t="n">
         <v>86.52511975594811</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.468x + -7410.800</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-7410.799510043837</v>
       </c>
       <c r="Y7" t="n">
         <v>402.6703652962622</v>
       </c>
       <c r="Z7" t="n">
-        <v>221444165.4908842</v>
+        <v>164.851</v>
       </c>
       <c r="AA7" t="n">
         <v>8.865235839604954e-07</v>
@@ -4708,19 +4708,19 @@
       <c r="K8" t="n">
         <v>86.66171887850922</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 17.144x + -7632.948</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7632.948425748457</v>
       </c>
       <c r="Y8" t="n">
         <v>398.3747443705986</v>
       </c>
       <c r="Z8" t="n">
-        <v>218891627.6862209</v>
+        <v>159.932</v>
       </c>
       <c r="AA8" t="n">
         <v>8.617305433626118e-07</v>
@@ -4760,19 +4760,19 @@
       <c r="K9" t="n">
         <v>86.73939803914961</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 17.553x + -7727.754</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7727.753523083717</v>
       </c>
       <c r="Y9" t="n">
         <v>394.4347314518075</v>
       </c>
       <c r="Z9" t="n">
-        <v>432269489.553234</v>
+        <v>156.7839999999999</v>
       </c>
       <c r="AA9" t="n">
         <v>8.409253555724308e-07</v>
@@ -4812,19 +4812,19 @@
       <c r="K10" t="n">
         <v>86.76321307466895</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 17.683x + -7688.241</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7688.241306720884</v>
       </c>
       <c r="Y10" t="n">
         <v>390.8375003359115</v>
       </c>
       <c r="Z10" t="n">
-        <v>428395885.152842</v>
+        <v>151.453</v>
       </c>
       <c r="AA10" t="n">
         <v>8.211383059960402e-07</v>
@@ -4864,19 +4864,19 @@
       <c r="K11" t="n">
         <v>86.84478497143563</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.141x + -7815.289</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7815.289419813595</v>
       </c>
       <c r="Y11" t="n">
         <v>387.453420771319</v>
       </c>
       <c r="Z11" t="n">
-        <v>213964053.8038524</v>
+        <v>148.8439999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>8.063701352079936e-07</v>
@@ -4916,19 +4916,19 @@
       <c r="K12" t="n">
         <v>86.96952641648392</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 18.889x + -8081.106</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-8081.105502885852</v>
       </c>
       <c r="Y12" t="n">
         <v>384.2698611246886</v>
       </c>
       <c r="Z12" t="n">
-        <v>211121508.1296392</v>
+        <v>144.881</v>
       </c>
       <c r="AA12" t="n">
         <v>7.926384331754758e-07</v>
@@ -4968,19 +4968,19 @@
       <c r="K13" t="n">
         <v>86.89056668718435</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 18.408x + -7775.949</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-7775.94910073984</v>
       </c>
       <c r="Y13" t="n">
         <v>381.2286649902834</v>
       </c>
       <c r="Z13" t="n">
-        <v>313014959.4294567</v>
+        <v>144.603</v>
       </c>
       <c r="AA13" t="n">
         <v>7.814934457548496e-07</v>
@@ -5020,19 +5020,19 @@
       <c r="K14" t="n">
         <v>86.99326370493998</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 19.038x + -7988.597</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-7988.5966968354</v>
       </c>
       <c r="Y14" t="n">
         <v>378.2434279452024</v>
       </c>
       <c r="Z14" t="n">
-        <v>414211151.969752</v>
+        <v>142.214</v>
       </c>
       <c r="AA14" t="n">
         <v>7.716591258289905e-07</v>
@@ -5072,19 +5072,19 @@
       <c r="K15" t="n">
         <v>87.06119563420363</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 19.479x + -8110.328</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-8110.328318765581</v>
       </c>
       <c r="Y15" t="n">
         <v>375.3233192145844</v>
       </c>
       <c r="Z15" t="n">
-        <v>411216768.2207509</v>
+        <v>139.795</v>
       </c>
       <c r="AA15" t="n">
         <v>7.612174688380247e-07</v>
@@ -5124,19 +5124,19 @@
       <c r="K16" t="n">
         <v>87.06598764755772</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 19.511x + -8048.507</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-8048.507284433118</v>
       </c>
       <c r="Y16" t="n">
         <v>372.4727883082132</v>
       </c>
       <c r="Z16" t="n">
-        <v>305868352.3892522</v>
+        <v>137.646</v>
       </c>
       <c r="AA16" t="n">
         <v>7.530725144062699e-07</v>
@@ -5176,19 +5176,19 @@
       <c r="K17" t="n">
         <v>87.04669351874476</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 19.383x + -7914.748</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-7914.748228115303</v>
       </c>
       <c r="Y17" t="n">
         <v>369.6354063846488</v>
       </c>
       <c r="Z17" t="n">
-        <v>151861490.4505496</v>
+        <v>136.5240000000001</v>
       </c>
       <c r="AA17" t="n">
         <v>7.440256920703068e-07</v>
@@ -5228,19 +5228,19 @@
       <c r="K18" t="n">
         <v>87.12844946748636</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 19.936x + -8083.851</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-8083.850856494796</v>
       </c>
       <c r="Y18" t="n">
         <v>366.8052324291342</v>
       </c>
       <c r="Z18" t="n">
-        <v>301223118.9624547</v>
+        <v>133.609</v>
       </c>
       <c r="AA18" t="n">
         <v>7.358434797363799e-07</v>
@@ -5280,19 +5280,19 @@
       <c r="K19" t="n">
         <v>87.16442505823083</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 20.190x + -8124.669</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-8124.66929687184</v>
       </c>
       <c r="Y19" t="n">
         <v>363.958078806506</v>
       </c>
       <c r="Z19" t="n">
-        <v>896000990.8613718</v>
+        <v>133.562</v>
       </c>
       <c r="AA19" t="n">
         <v>7.300207471263049e-07</v>
@@ -5332,19 +5332,19 @@
       <c r="K20" t="n">
         <v>87.22282850808183</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 20.615x + -8232.125</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-8232.125132821564</v>
       </c>
       <c r="Y20" t="n">
         <v>361.1030437426311</v>
       </c>
       <c r="Z20" t="n">
-        <v>197523750.4443202</v>
+        <v>130.462</v>
       </c>
       <c r="AA20" t="n">
         <v>7.227657215465091e-07</v>
@@ -5384,19 +5384,19 @@
       <c r="K21" t="n">
         <v>87.19541185281336</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 20.413x + -8065.045</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-8065.044971962247</v>
       </c>
       <c r="Y21" t="n">
         <v>358.2517734184513</v>
       </c>
       <c r="Z21" t="n">
-        <v>195866476.6688291</v>
+        <v>129.615</v>
       </c>
       <c r="AA21" t="n">
         <v>7.159869467681006e-07</v>
@@ -5436,19 +5436,19 @@
       <c r="K22" t="n">
         <v>87.21832621275446</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 20.581x + -8061.253</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-8061.252527263254</v>
       </c>
       <c r="Y22" t="n">
         <v>355.4193524940902</v>
       </c>
       <c r="Z22" t="n">
-        <v>388608664.1277252</v>
+        <v>128.767</v>
       </c>
       <c r="AA22" t="n">
         <v>7.103629344653632e-07</v>
@@ -5574,12 +5574,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5589,7 +5589,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -5634,19 +5634,19 @@
       <c r="K2" t="n">
         <v>83.78116345221645</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.177x + -4283.494</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-4283.493809854624</v>
       </c>
       <c r="Y2" t="n">
         <v>396.0480226192574</v>
       </c>
       <c r="Z2" t="n">
-        <v>220341120.03033</v>
+        <v>299.283</v>
       </c>
       <c r="AA2" t="n">
         <v>1.580864204228818e-06</v>
@@ -5686,19 +5686,19 @@
       <c r="K3" t="n">
         <v>84.95858072274089</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.336x + -4759.724</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-4759.723635532172</v>
       </c>
       <c r="Y3" t="n">
         <v>376.1619019626904</v>
       </c>
       <c r="Z3" t="n">
-        <v>206917800.2606733</v>
+        <v>242.703</v>
       </c>
       <c r="AA3" t="n">
         <v>1.167982552580774e-06</v>
@@ -5738,19 +5738,19 @@
       <c r="K4" t="n">
         <v>85.40294984965661</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.437x + -5075.481</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-5075.480918343761</v>
       </c>
       <c r="Y4" t="n">
         <v>369.0674309948403</v>
       </c>
       <c r="Z4" t="n">
-        <v>209377630.0668765</v>
+        <v>222.64</v>
       </c>
       <c r="AA4" t="n">
         <v>1.057263656926392e-06</v>
@@ -5790,19 +5790,19 @@
       <c r="K5" t="n">
         <v>85.68953496840582</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 13.267x + -5329.797</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-5329.797388394029</v>
       </c>
       <c r="Y5" t="n">
         <v>364.1423670579533</v>
       </c>
       <c r="Z5" t="n">
-        <v>697729078.7444665</v>
+        <v>210.065</v>
       </c>
       <c r="AA5" t="n">
         <v>9.933647794257932e-07</v>
@@ -5842,19 +5842,19 @@
       <c r="K6" t="n">
         <v>85.76830569346231</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 13.515x + -5324.501</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-5324.500811857602</v>
       </c>
       <c r="Y6" t="n">
         <v>359.4395566651669</v>
       </c>
       <c r="Z6" t="n">
-        <v>196807789.3057901</v>
+        <v>203.334</v>
       </c>
       <c r="AA6" t="n">
         <v>9.460835482645655e-07</v>
@@ -5894,19 +5894,19 @@
       <c r="K7" t="n">
         <v>85.98534782726016</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 14.248x + -5542.815</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-5542.81532576788</v>
       </c>
       <c r="Y7" t="n">
         <v>354.6544064970562</v>
       </c>
       <c r="Z7" t="n">
-        <v>679380841.0213003</v>
+        <v>195.395</v>
       </c>
       <c r="AA7" t="n">
         <v>9.079446112459932e-07</v>
@@ -5946,19 +5946,19 @@
       <c r="K8" t="n">
         <v>86.1179253403461</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 14.736x + -5645.649</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-5645.649043492897</v>
       </c>
       <c r="Y8" t="n">
         <v>349.9431300454831</v>
       </c>
       <c r="Z8" t="n">
-        <v>143457803.3713763</v>
+        <v>188.716</v>
       </c>
       <c r="AA8" t="n">
         <v>8.75602241623646e-07</v>
@@ -5998,19 +5998,19 @@
       <c r="K9" t="n">
         <v>86.29248315753577</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 15.432x + -5835.432</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-5835.431609975895</v>
       </c>
       <c r="Y9" t="n">
         <v>345.4540720477756</v>
       </c>
       <c r="Z9" t="n">
-        <v>849363057.4685625</v>
+        <v>181.854</v>
       </c>
       <c r="AA9" t="n">
         <v>8.473050545763279e-07</v>
@@ -6050,19 +6050,19 @@
       <c r="K10" t="n">
         <v>86.39895569203611</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 15.890x + -5922.040</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-5922.040076180075</v>
       </c>
       <c r="Y10" t="n">
         <v>341.2259099112376</v>
       </c>
       <c r="Z10" t="n">
-        <v>472832364.0553477</v>
+        <v>176.543</v>
       </c>
       <c r="AA10" t="n">
         <v>8.225130505633036e-07</v>
@@ -6102,19 +6102,19 @@
       <c r="K11" t="n">
         <v>86.39634014755802</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 15.878x + -5821.153</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-5821.152911643883</v>
       </c>
       <c r="Y11" t="n">
         <v>337.3381906520464</v>
       </c>
       <c r="Z11" t="n">
-        <v>261051548.6262453</v>
+        <v>173.7449999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>8.035422719802362e-07</v>
@@ -6240,12 +6240,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -6300,19 +6300,19 @@
       <c r="K2" t="n">
         <v>85.12960059451331</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 11.736x + -5683.332</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-5683.331757794689</v>
       </c>
       <c r="Y2" t="n">
         <v>417.7472076657106</v>
       </c>
       <c r="Z2" t="n">
-        <v>226821460.078298</v>
+        <v>234.4999999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1.44353238429869e-06</v>
@@ -6352,19 +6352,19 @@
       <c r="K3" t="n">
         <v>85.79000605363042</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 13.585x + -6306.152</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-6306.152240210211</v>
       </c>
       <c r="Y3" t="n">
         <v>409.2528650031653</v>
       </c>
       <c r="Z3" t="n">
-        <v>228500177.6122265</v>
+        <v>202.218</v>
       </c>
       <c r="AA3" t="n">
         <v>1.185563077314297e-06</v>
@@ -6404,19 +6404,19 @@
       <c r="K4" t="n">
         <v>86.09604588803867</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.654x + -6706.369</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-6706.368759949533</v>
       </c>
       <c r="Y4" t="n">
         <v>404.9730002838888</v>
       </c>
       <c r="Z4" t="n">
-        <v>224601886.0095915</v>
+        <v>188.469</v>
       </c>
       <c r="AA4" t="n">
         <v>1.096061458687113e-06</v>
@@ -6456,19 +6456,19 @@
       <c r="K5" t="n">
         <v>86.07010806880217</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.557x + -6538.014</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-6538.013673325883</v>
       </c>
       <c r="Y5" t="n">
         <v>400.9688127253339</v>
       </c>
       <c r="Z5" t="n">
-        <v>233810940.7085494</v>
+        <v>181.8340000000001</v>
       </c>
       <c r="AA5" t="n">
         <v>1.038776231899943e-06</v>
@@ -6508,19 +6508,19 @@
       <c r="K6" t="n">
         <v>86.3974213244698</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 15.883x + -7090.955</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-7090.955058926787</v>
       </c>
       <c r="Y6" t="n">
         <v>396.5798434487414</v>
       </c>
       <c r="Z6" t="n">
-        <v>655130097.0375171</v>
+        <v>172.51</v>
       </c>
       <c r="AA6" t="n">
         <v>9.937445627067558e-07</v>
@@ -6560,19 +6560,19 @@
       <c r="K7" t="n">
         <v>86.39990871394555</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 15.894x + -6975.741</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-6975.740533092861</v>
       </c>
       <c r="Y7" t="n">
         <v>391.9445455530394</v>
       </c>
       <c r="Z7" t="n">
-        <v>161931033.7023265</v>
+        <v>168.513</v>
       </c>
       <c r="AA7" t="n">
         <v>9.567497309654283e-07</v>
@@ -6612,19 +6612,19 @@
       <c r="K8" t="n">
         <v>86.52055460344455</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 16.447x + -7128.936</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7128.935944885306</v>
       </c>
       <c r="Y8" t="n">
         <v>387.4690119672044</v>
       </c>
       <c r="Z8" t="n">
-        <v>236660655.3961978</v>
+        <v>164.125</v>
       </c>
       <c r="AA8" t="n">
         <v>9.260766037454285e-07</v>
@@ -6664,19 +6664,19 @@
       <c r="K9" t="n">
         <v>86.61093400004739</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 16.886x + -7229.802</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-7229.801554616858</v>
       </c>
       <c r="Y9" t="n">
         <v>383.2822621587598</v>
       </c>
       <c r="Z9" t="n">
-        <v>210447611.5556608</v>
+        <v>159.772</v>
       </c>
       <c r="AA9" t="n">
         <v>8.986873886286346e-07</v>
@@ -6716,19 +6716,19 @@
       <c r="K10" t="n">
         <v>86.69588850910867</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 17.322x + -7331.279</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-7331.279047687674</v>
       </c>
       <c r="Y10" t="n">
         <v>379.4042988125393</v>
       </c>
       <c r="Z10" t="n">
-        <v>624009656.8922387</v>
+        <v>155.4420000000001</v>
       </c>
       <c r="AA10" t="n">
         <v>8.768879609255373e-07</v>
@@ -6768,19 +6768,19 @@
       <c r="K11" t="n">
         <v>86.74793919765791</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 17.599x + -7361.998</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-7361.997937760949</v>
       </c>
       <c r="Y11" t="n">
         <v>375.7329626332076</v>
       </c>
       <c r="Z11" t="n">
-        <v>159994176.9848319</v>
+        <v>151.945</v>
       </c>
       <c r="AA11" t="n">
         <v>8.561757955896253e-07</v>
@@ -6820,19 +6820,19 @@
       <c r="K12" t="n">
         <v>86.80761449780843</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 17.929x + -7422.985</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-7422.984814473733</v>
       </c>
       <c r="Y12" t="n">
         <v>372.2798102040754</v>
       </c>
       <c r="Z12" t="n">
-        <v>217591330.8219371</v>
+        <v>150.413</v>
       </c>
       <c r="AA12" t="n">
         <v>8.407841750404369e-07</v>
@@ -6872,19 +6872,19 @@
       <c r="K13" t="n">
         <v>86.90405563077231</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 18.489x + -7584.620</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-7584.6203970385</v>
       </c>
       <c r="Y13" t="n">
         <v>368.9567173075583</v>
       </c>
       <c r="Z13" t="n">
-        <v>303843703.1087019</v>
+        <v>145.576</v>
       </c>
       <c r="AA13" t="n">
         <v>8.243302362294342e-07</v>
@@ -6924,19 +6924,19 @@
       <c r="K14" t="n">
         <v>86.85032697074804</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 18.173x + -7356.408</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-7356.407800720732</v>
       </c>
       <c r="Y14" t="n">
         <v>365.7232932991741</v>
       </c>
       <c r="Z14" t="n">
-        <v>200496852.5317627</v>
+        <v>144.2629999999999</v>
       </c>
       <c r="AA14" t="n">
         <v>8.10485472374145e-07</v>
@@ -6976,19 +6976,19 @@
       <c r="K15" t="n">
         <v>86.91608356221145</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 18.561x + -7444.026</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-7444.025720975245</v>
       </c>
       <c r="Y15" t="n">
         <v>362.4449858407583</v>
       </c>
       <c r="Z15" t="n">
-        <v>99398386.45434077</v>
+        <v>142.094</v>
       </c>
       <c r="AA15" t="n">
         <v>7.985641322860091e-07</v>
@@ -7028,19 +7028,19 @@
       <c r="K16" t="n">
         <v>87.04139134951386</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 19.349x + -7707.085</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-7707.084684646431</v>
       </c>
       <c r="Y16" t="n">
         <v>359.2066827937394</v>
       </c>
       <c r="Z16" t="n">
-        <v>150058737.6249207</v>
+        <v>139.393</v>
       </c>
       <c r="AA16" t="n">
         <v>7.872979423758546e-07</v>
@@ -7080,19 +7080,19 @@
       <c r="K17" t="n">
         <v>87.08235123250444</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 19.621x + -7739.443</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-7739.44327589951</v>
       </c>
       <c r="Y17" t="n">
         <v>355.9968355252498</v>
       </c>
       <c r="Z17" t="n">
-        <v>194849446.0354508</v>
+        <v>137.705</v>
       </c>
       <c r="AA17" t="n">
         <v>7.782783084268183e-07</v>
@@ -7132,19 +7132,19 @@
       <c r="K18" t="n">
         <v>87.0904819324337</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 19.676x + -7682.685</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-7682.684802412933</v>
       </c>
       <c r="Y18" t="n">
         <v>352.8422565355276</v>
       </c>
       <c r="Z18" t="n">
-        <v>224647548.3459699</v>
+        <v>137.09</v>
       </c>
       <c r="AA18" t="n">
         <v>7.697054488548521e-07</v>
@@ -7184,19 +7184,19 @@
       <c r="K19" t="n">
         <v>87.12274139930787</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 19.897x + -7687.783</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-7687.78264173453</v>
       </c>
       <c r="Y19" t="n">
         <v>349.6816558741185</v>
       </c>
       <c r="Z19" t="n">
-        <v>143577996.6829306</v>
+        <v>134.0170000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>7.596315165932298e-07</v>
@@ -7236,19 +7236,19 @@
       <c r="K20" t="n">
         <v>87.14911157335852</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 20.081x + -7681.191</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-7681.19113117973</v>
       </c>
       <c r="Y20" t="n">
         <v>346.5167564290449</v>
       </c>
       <c r="Z20" t="n">
-        <v>378870519.4103824</v>
+        <v>132.952</v>
       </c>
       <c r="AA20" t="n">
         <v>7.51514431538005e-07</v>
@@ -7288,19 +7288,19 @@
       <c r="K21" t="n">
         <v>87.22916975012306</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 20.662x + -7841.170</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-7841.170060151584</v>
       </c>
       <c r="Y21" t="n">
         <v>343.3036977339311</v>
       </c>
       <c r="Z21" t="n">
-        <v>187752679.7979519</v>
+        <v>131.369</v>
       </c>
       <c r="AA21" t="n">
         <v>7.447306624467331e-07</v>
@@ -7340,19 +7340,19 @@
       <c r="K22" t="n">
         <v>87.21428760940691</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 20.552x + -7703.352</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-7703.352265908799</v>
       </c>
       <c r="Y22" t="n">
         <v>340.0849493883837</v>
       </c>
       <c r="Z22" t="n">
-        <v>743855828.3581824</v>
+        <v>129.769</v>
       </c>
       <c r="AA22" t="n">
         <v>7.359385478192486e-07</v>
@@ -7478,12 +7478,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7493,7 +7493,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -7538,19 +7538,19 @@
       <c r="K2" t="n">
         <v>84.13590972262895</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 9.736x + -4706.862</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-4706.862100501113</v>
       </c>
       <c r="Y2" t="n">
         <v>409.5966677084947</v>
       </c>
       <c r="Z2" t="n">
-        <v>23643246.47042691</v>
+        <v>276.889</v>
       </c>
       <c r="AA2" t="n">
         <v>1.680464557764971e-06</v>
@@ -7590,19 +7590,19 @@
       <c r="K3" t="n">
         <v>85.06619720273187</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 11.584x + -4976.356</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-4976.356265492807</v>
       </c>
       <c r="Y3" t="n">
         <v>387.9620306346272</v>
       </c>
       <c r="Z3" t="n">
-        <v>425516878.9159348</v>
+        <v>229.763</v>
       </c>
       <c r="AA3" t="n">
         <v>1.17313974285562e-06</v>
@@ -7642,19 +7642,19 @@
       <c r="K4" t="n">
         <v>85.58516677937202</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 12.952x + -5411.810</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-5411.809530377352</v>
       </c>
       <c r="Y4" t="n">
         <v>380.4854366236969</v>
       </c>
       <c r="Z4" t="n">
-        <v>156286969.7261375</v>
+        <v>209.499</v>
       </c>
       <c r="AA4" t="n">
         <v>1.042702286983623e-06</v>
@@ -7694,19 +7694,19 @@
       <c r="K5" t="n">
         <v>85.99007229705575</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 14.265x + -5882.446</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-5882.445877498227</v>
       </c>
       <c r="Y5" t="n">
         <v>375.3988591102163</v>
       </c>
       <c r="Z5" t="n">
-        <v>411004768.3896478</v>
+        <v>194.066</v>
       </c>
       <c r="AA5" t="n">
         <v>9.667632009195438e-07</v>
@@ -7746,19 +7746,19 @@
       <c r="K6" t="n">
         <v>86.08654354099457</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 14.618x + -5912.551</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-5912.550917972069</v>
       </c>
       <c r="Y6" t="n">
         <v>370.5521640097273</v>
       </c>
       <c r="Z6" t="n">
-        <v>252678220.7777854</v>
+        <v>187.0000000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>9.154067010114607e-07</v>
@@ -7798,19 +7798,19 @@
       <c r="K7" t="n">
         <v>86.33257021576475</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 15.602x + -6235.442</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-6235.442365587123</v>
       </c>
       <c r="Y7" t="n">
         <v>365.6591788806057</v>
       </c>
       <c r="Z7" t="n">
-        <v>199763291.0778566</v>
+        <v>178.0450000000001</v>
       </c>
       <c r="AA7" t="n">
         <v>8.743835325129439e-07</v>
@@ -7850,19 +7850,19 @@
       <c r="K8" t="n">
         <v>86.34633725051124</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 15.660x + -6135.529</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-6135.528995056597</v>
       </c>
       <c r="Y8" t="n">
         <v>360.6028353008273</v>
       </c>
       <c r="Z8" t="n">
-        <v>393828248.638447</v>
+        <v>173.8440000000001</v>
       </c>
       <c r="AA8" t="n">
         <v>8.417608574416963e-07</v>
@@ -7902,19 +7902,19 @@
       <c r="K9" t="n">
         <v>86.62592367176711</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 16.962x + -6578.014</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-6578.014354393819</v>
       </c>
       <c r="Y9" t="n">
         <v>355.5571271536988</v>
       </c>
       <c r="Z9" t="n">
-        <v>291080314.3059894</v>
+        <v>165.977</v>
       </c>
       <c r="AA9" t="n">
         <v>8.130776909525363e-07</v>
@@ -7954,19 +7954,19 @@
       <c r="K10" t="n">
         <v>86.60634163310644</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 16.863x + -6410.810</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-6410.809512081318</v>
       </c>
       <c r="Y10" t="n">
         <v>350.7256056046506</v>
       </c>
       <c r="Z10" t="n">
-        <v>202197978.6934312</v>
+        <v>162.939</v>
       </c>
       <c r="AA10" t="n">
         <v>7.900417733723573e-07</v>
@@ -8006,19 +8006,19 @@
       <c r="K11" t="n">
         <v>86.73447448770771</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 17.527x + -6576.717</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-6576.716637615972</v>
       </c>
       <c r="Y11" t="n">
         <v>346.2620188885043</v>
       </c>
       <c r="Z11" t="n">
-        <v>283062746.1524704</v>
+        <v>158.1829999999999</v>
       </c>
       <c r="AA11" t="n">
         <v>7.698221397174921e-07</v>
@@ -8144,12 +8144,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8159,7 +8159,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -8204,19 +8204,19 @@
       <c r="K2" t="n">
         <v>85.78537421927085</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 13.570x + -6843.162</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-6843.161697481773</v>
       </c>
       <c r="Y2" t="n">
         <v>438.3739120010454</v>
       </c>
       <c r="Z2" t="n">
-        <v>37313480.39081773</v>
+        <v>202.537</v>
       </c>
       <c r="AA2" t="n">
         <v>1.266813073883723e-06</v>
@@ -8256,19 +8256,19 @@
       <c r="K3" t="n">
         <v>86.18804292050878</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 15.008x + -7204.231</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-7204.231455318031</v>
       </c>
       <c r="Y3" t="n">
         <v>427.9137340466133</v>
       </c>
       <c r="Z3" t="n">
-        <v>62432317.69983397</v>
+        <v>178.765</v>
       </c>
       <c r="AA3" t="n">
         <v>1.068721946864941e-06</v>
@@ -8308,19 +8308,19 @@
       <c r="K4" t="n">
         <v>86.57986956023579</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 16.733x + -7940.519</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-7940.519382880433</v>
       </c>
       <c r="Y4" t="n">
         <v>422.7380480047251</v>
       </c>
       <c r="Z4" t="n">
-        <v>191939620.4062985</v>
+        <v>164.764</v>
       </c>
       <c r="AA4" t="n">
         <v>9.979548136303341e-07</v>
@@ -8360,19 +8360,19 @@
       <c r="K5" t="n">
         <v>86.74344256078949</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 17.575x + -8239.343</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-8239.342518949676</v>
       </c>
       <c r="Y5" t="n">
         <v>418.2600864407751</v>
       </c>
       <c r="Z5" t="n">
-        <v>172998642.9858067</v>
+        <v>157.039</v>
       </c>
       <c r="AA5" t="n">
         <v>9.531497859256004e-07</v>
@@ -8412,19 +8412,19 @@
       <c r="K6" t="n">
         <v>86.6698738062922</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 17.186x + -7911.982</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-7911.982102012559</v>
       </c>
       <c r="Y6" t="n">
         <v>413.8114836614133</v>
       </c>
       <c r="Z6" t="n">
-        <v>340940715.5667116</v>
+        <v>154.919</v>
       </c>
       <c r="AA6" t="n">
         <v>9.194333412358749e-07</v>
@@ -8464,19 +8464,19 @@
       <c r="K7" t="n">
         <v>86.75137463566472</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 17.618x + -8009.400</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-8009.399682345235</v>
       </c>
       <c r="Y7" t="n">
         <v>409.4028202701477</v>
       </c>
       <c r="Z7" t="n">
-        <v>449156467.7310114</v>
+        <v>150.36</v>
       </c>
       <c r="AA7" t="n">
         <v>8.916486933032104e-07</v>
@@ -8516,19 +8516,19 @@
       <c r="K8" t="n">
         <v>86.78347182229572</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 17.794x + -7983.603</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-7983.603048873175</v>
       </c>
       <c r="Y8" t="n">
         <v>405.1666236450736</v>
       </c>
       <c r="Z8" t="n">
-        <v>170601388.8860681</v>
+        <v>146.357</v>
       </c>
       <c r="AA8" t="n">
         <v>8.676512223636543e-07</v>
@@ -8568,19 +8568,19 @@
       <c r="K9" t="n">
         <v>86.9922843357253</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 19.032x + -8475.388</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-8475.388206199019</v>
       </c>
       <c r="Y9" t="n">
         <v>401.0661510930278</v>
       </c>
       <c r="Z9" t="n">
-        <v>110008698.7541743</v>
+        <v>140.483</v>
       </c>
       <c r="AA9" t="n">
         <v>8.46008907412597e-07</v>
@@ -8620,19 +8620,19 @@
       <c r="K10" t="n">
         <v>86.92996472219281</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 18.645x + -8181.955</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-8181.955223618737</v>
       </c>
       <c r="Y10" t="n">
         <v>397.2817842955411</v>
       </c>
       <c r="Z10" t="n">
-        <v>163471712.7856244</v>
+        <v>139.574</v>
       </c>
       <c r="AA10" t="n">
         <v>8.290154829325843e-07</v>
@@ -8672,19 +8672,19 @@
       <c r="K11" t="n">
         <v>86.94504947383524</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.737x + -8129.735</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-8129.735377625187</v>
       </c>
       <c r="Y11" t="n">
         <v>393.7836631431049</v>
       </c>
       <c r="Z11" t="n">
-        <v>215595680.5163926</v>
+        <v>138.184</v>
       </c>
       <c r="AA11" t="n">
         <v>8.139573087446793e-07</v>
@@ -8724,19 +8724,19 @@
       <c r="K12" t="n">
         <v>87.02624608748611</v>
       </c>
-      <c r="W12" t="n">
-        <v>11</v>
-      </c>
-      <c r="X12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>y = 19.250x + -8281.153</t>
         </is>
+      </c>
+      <c r="X12" t="n">
+        <v>-8281.152765069404</v>
       </c>
       <c r="Y12" t="n">
         <v>390.4954805087149</v>
       </c>
       <c r="Z12" t="n">
-        <v>320826921.0744914</v>
+        <v>135.092</v>
       </c>
       <c r="AA12" t="n">
         <v>8.004479004707351e-07</v>
@@ -8776,19 +8776,19 @@
       <c r="K13" t="n">
         <v>87.09347352354551</v>
       </c>
-      <c r="W13" t="n">
-        <v>12</v>
-      </c>
-      <c r="X13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>y = 19.696x + -8401.525</t>
         </is>
+      </c>
+      <c r="X13" t="n">
+        <v>-8401.525297760061</v>
       </c>
       <c r="Y13" t="n">
         <v>387.380963589799</v>
       </c>
       <c r="Z13" t="n">
-        <v>164579411.1256917</v>
+        <v>132.969</v>
       </c>
       <c r="AA13" t="n">
         <v>7.887622345882293e-07</v>
@@ -8828,19 +8828,19 @@
       <c r="K14" t="n">
         <v>87.18717141016353</v>
       </c>
-      <c r="W14" t="n">
-        <v>13</v>
-      </c>
-      <c r="X14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>y = 20.353x + -8622.339</t>
         </is>
+      </c>
+      <c r="X14" t="n">
+        <v>-8622.338619069558</v>
       </c>
       <c r="Y14" t="n">
         <v>384.3899998105983</v>
       </c>
       <c r="Z14" t="n">
-        <v>225588116.6271352</v>
+        <v>129.81</v>
       </c>
       <c r="AA14" t="n">
         <v>7.789540139398641e-07</v>
@@ -8880,19 +8880,19 @@
       <c r="K15" t="n">
         <v>87.15478327222786</v>
       </c>
-      <c r="W15" t="n">
-        <v>14</v>
-      </c>
-      <c r="X15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>y = 20.121x + -8429.467</t>
         </is>
+      </c>
+      <c r="X15" t="n">
+        <v>-8429.467215093911</v>
       </c>
       <c r="Y15" t="n">
         <v>381.4474402696158</v>
       </c>
       <c r="Z15" t="n">
-        <v>156640161.1475782</v>
+        <v>127.909</v>
       </c>
       <c r="AA15" t="n">
         <v>7.685070499554922e-07</v>
@@ -8932,19 +8932,19 @@
       <c r="K16" t="n">
         <v>87.28882799704577</v>
       </c>
-      <c r="W16" t="n">
-        <v>15</v>
-      </c>
-      <c r="X16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>y = 21.117x + -8803.437</t>
         </is>
+      </c>
+      <c r="X16" t="n">
+        <v>-8803.436857199689</v>
       </c>
       <c r="Y16" t="n">
         <v>378.5169579094972</v>
       </c>
       <c r="Z16" t="n">
-        <v>207228195.8585008</v>
+        <v>126.046</v>
       </c>
       <c r="AA16" t="n">
         <v>7.613762932077516e-07</v>
@@ -8984,19 +8984,19 @@
       <c r="K17" t="n">
         <v>87.00821877162034</v>
       </c>
-      <c r="W17" t="n">
-        <v>16</v>
-      </c>
-      <c r="X17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>y = 19.134x + -7837.111</t>
         </is>
+      </c>
+      <c r="X17" t="n">
+        <v>-7837.110899560415</v>
       </c>
       <c r="Y17" t="n">
         <v>375.6856700409101</v>
       </c>
       <c r="Z17" t="n">
-        <v>256771806.4796622</v>
+        <v>127.987</v>
       </c>
       <c r="AA17" t="n">
         <v>7.534795476309633e-07</v>
@@ -9036,19 +9036,19 @@
       <c r="K18" t="n">
         <v>87.21952144430335</v>
       </c>
-      <c r="W18" t="n">
-        <v>17</v>
-      </c>
-      <c r="X18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>y = 20.590x + -8408.380</t>
         </is>
+      </c>
+      <c r="X18" t="n">
+        <v>-8408.379533294215</v>
       </c>
       <c r="Y18" t="n">
         <v>372.8719417514002</v>
       </c>
       <c r="Z18" t="n">
-        <v>407512057.3213127</v>
+        <v>124.0189999999999</v>
       </c>
       <c r="AA18" t="n">
         <v>7.456470208592552e-07</v>
@@ -9088,19 +9088,19 @@
       <c r="K19" t="n">
         <v>87.30897587273675</v>
       </c>
-      <c r="W19" t="n">
-        <v>18</v>
-      </c>
-      <c r="X19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>y = 21.276x + -8633.112</t>
         </is>
+      </c>
+      <c r="X19" t="n">
+        <v>-8633.112353307812</v>
       </c>
       <c r="Y19" t="n">
         <v>370.0935529022672</v>
       </c>
       <c r="Z19" t="n">
-        <v>202205481.6304045</v>
+        <v>122.1080000000001</v>
       </c>
       <c r="AA19" t="n">
         <v>7.381962876302981e-07</v>
@@ -9140,19 +9140,19 @@
       <c r="K20" t="n">
         <v>87.28953721596211</v>
       </c>
-      <c r="W20" t="n">
-        <v>19</v>
-      </c>
-      <c r="X20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>y = 21.123x + -8490.746</t>
         </is>
+      </c>
+      <c r="X20" t="n">
+        <v>-8490.745996283242</v>
       </c>
       <c r="Y20" t="n">
         <v>367.3231930948887</v>
       </c>
       <c r="Z20" t="n">
-        <v>125528326.2901103</v>
+        <v>121.873</v>
       </c>
       <c r="AA20" t="n">
         <v>7.326524191337869e-07</v>
@@ -9192,19 +9192,19 @@
       <c r="K21" t="n">
         <v>87.28350759337729</v>
       </c>
-      <c r="W21" t="n">
-        <v>20</v>
-      </c>
-      <c r="X21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>y = 21.076x + -8394.225</t>
         </is>
+      </c>
+      <c r="X21" t="n">
+        <v>-8394.224795684553</v>
       </c>
       <c r="Y21" t="n">
         <v>364.5510236595847</v>
       </c>
       <c r="Z21" t="n">
-        <v>199251243.4022189</v>
+        <v>120.841</v>
       </c>
       <c r="AA21" t="n">
         <v>7.259537778530464e-07</v>
@@ -9244,19 +9244,19 @@
       <c r="K22" t="n">
         <v>87.45211959884001</v>
       </c>
-      <c r="W22" t="n">
-        <v>21</v>
-      </c>
-      <c r="X22" t="inlineStr">
+      <c r="W22" t="inlineStr">
         <is>
           <t>y = 22.473x + -8914.660</t>
         </is>
+      </c>
+      <c r="X22" t="n">
+        <v>-8914.659985291592</v>
       </c>
       <c r="Y22" t="n">
         <v>361.6981794960921</v>
       </c>
       <c r="Z22" t="n">
-        <v>218464713.8409812</v>
+        <v>117.864</v>
       </c>
       <c r="AA22" t="n">
         <v>7.201651642019925e-07</v>
@@ -9382,12 +9382,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Cycle</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9397,7 +9397,7 @@
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>Rp</t>
+          <t>delta Rct-i</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
@@ -9442,19 +9442,19 @@
       <c r="K2" t="n">
         <v>84.41381906368633</v>
       </c>
-      <c r="W2" t="n">
-        <v>1</v>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>y = 10.224x + -4547.682</t>
         </is>
+      </c>
+      <c r="X2" t="n">
+        <v>-4547.682375547115</v>
       </c>
       <c r="Y2" t="n">
         <v>381.8066934807066</v>
       </c>
       <c r="Z2" t="n">
-        <v>384290012.9981383</v>
+        <v>275.068</v>
       </c>
       <c r="AA2" t="n">
         <v>1.245415063477581e-06</v>
@@ -9494,19 +9494,19 @@
       <c r="K3" t="n">
         <v>85.56221718859311</v>
       </c>
-      <c r="W3" t="n">
-        <v>2</v>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>y = 12.885x + -5149.400</t>
         </is>
+      </c>
+      <c r="X3" t="n">
+        <v>-5149.39981701879</v>
       </c>
       <c r="Y3" t="n">
         <v>361.0055892513041</v>
       </c>
       <c r="Z3" t="n">
-        <v>148254202.694783</v>
+        <v>224.0400000000001</v>
       </c>
       <c r="AA3" t="n">
         <v>9.575416816390405e-07</v>
@@ -9546,19 +9546,19 @@
       <c r="K4" t="n">
         <v>86.05377117096188</v>
       </c>
-      <c r="W4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>y = 14.496x + -5636.568</t>
         </is>
+      </c>
+      <c r="X4" t="n">
+        <v>-5636.568039942341</v>
       </c>
       <c r="Y4" t="n">
         <v>354.0310504671017</v>
       </c>
       <c r="Z4" t="n">
-        <v>193539432.451957</v>
+        <v>202.367</v>
       </c>
       <c r="AA4" t="n">
         <v>8.694549085997285e-07</v>
@@ -9598,19 +9598,19 @@
       <c r="K5" t="n">
         <v>86.32404876641756</v>
       </c>
-      <c r="W5" t="n">
-        <v>4</v>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>y = 15.565x + -5954.809</t>
         </is>
+      </c>
+      <c r="X5" t="n">
+        <v>-5954.809487507271</v>
       </c>
       <c r="Y5" t="n">
         <v>349.329650444781</v>
       </c>
       <c r="Z5" t="n">
-        <v>193668420.6884376</v>
+        <v>188.856</v>
       </c>
       <c r="AA5" t="n">
         <v>8.201765853489458e-07</v>
@@ -9650,19 +9650,19 @@
       <c r="K6" t="n">
         <v>86.43077153242696</v>
       </c>
-      <c r="W6" t="n">
-        <v>5</v>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>y = 16.032x + -6018.307</t>
         </is>
+      </c>
+      <c r="X6" t="n">
+        <v>-6018.307491526186</v>
       </c>
       <c r="Y6" t="n">
         <v>344.4445793016002</v>
       </c>
       <c r="Z6" t="n">
-        <v>195359165.8186222</v>
+        <v>180.988</v>
       </c>
       <c r="AA6" t="n">
         <v>7.845546070895618e-07</v>
@@ -9702,19 +9702,19 @@
       <c r="K7" t="n">
         <v>86.55080728929757</v>
       </c>
-      <c r="W7" t="n">
-        <v>6</v>
-      </c>
-      <c r="X7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>y = 16.591x + -6123.038</t>
         </is>
+      </c>
+      <c r="X7" t="n">
+        <v>-6123.038141008891</v>
       </c>
       <c r="Y7" t="n">
         <v>339.5606496956183</v>
       </c>
       <c r="Z7" t="n">
-        <v>137165222.1105785</v>
+        <v>173.04</v>
       </c>
       <c r="AA7" t="n">
         <v>7.564184407878399e-07</v>
@@ -9754,19 +9754,19 @@
       <c r="K8" t="n">
         <v>86.75641427325557</v>
       </c>
-      <c r="W8" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>y = 17.645x + -6434.767</t>
         </is>
+      </c>
+      <c r="X8" t="n">
+        <v>-6434.766853772477</v>
       </c>
       <c r="Y8" t="n">
         <v>334.6334579109749</v>
       </c>
       <c r="Z8" t="n">
-        <v>182839622.5572596</v>
+        <v>167.181</v>
       </c>
       <c r="AA8" t="n">
         <v>7.361551241341882e-07</v>
@@ -9806,19 +9806,19 @@
       <c r="K9" t="n">
         <v>86.85473311335363</v>
       </c>
-      <c r="W9" t="n">
-        <v>8</v>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>y = 18.198x + -6526.295</t>
         </is>
+      </c>
+      <c r="X9" t="n">
+        <v>-6526.29454549875</v>
       </c>
       <c r="Y9" t="n">
         <v>329.9180126710327</v>
       </c>
       <c r="Z9" t="n">
-        <v>144333249.1458964</v>
+        <v>161.647</v>
       </c>
       <c r="AA9" t="n">
         <v>7.1652088650224e-07</v>
@@ -9858,19 +9858,19 @@
       <c r="K10" t="n">
         <v>87.01209275556037</v>
       </c>
-      <c r="W10" t="n">
-        <v>9</v>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>y = 19.159x + -6790.271</t>
         </is>
+      </c>
+      <c r="X10" t="n">
+        <v>-6790.270708425777</v>
       </c>
       <c r="Y10" t="n">
         <v>325.4370405855685</v>
       </c>
       <c r="Z10" t="n">
-        <v>177303080.3925255</v>
+        <v>156.297</v>
       </c>
       <c r="AA10" t="n">
         <v>7.016495281387601e-07</v>
@@ -9910,19 +9910,19 @@
       <c r="K11" t="n">
         <v>86.95363110797396</v>
       </c>
-      <c r="W11" t="n">
-        <v>10</v>
-      </c>
-      <c r="X11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>y = 18.790x + -6526.385</t>
         </is>
+      </c>
+      <c r="X11" t="n">
+        <v>-6526.385286717029</v>
       </c>
       <c r="Y11" t="n">
         <v>321.2988222282801</v>
       </c>
       <c r="Z11" t="n">
-        <v>87504611.61801642</v>
+        <v>154.017</v>
       </c>
       <c r="AA11" t="n">
         <v>6.885139484362863e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
@@ -528,12 +528,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -588,10 +588,8 @@
       <c r="K2" t="n">
         <v>86.49221849863669</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 16.313x + -8303.679</t>
-        </is>
+      <c r="W2" t="n">
+        <v>16.31349522111721</v>
       </c>
       <c r="X2" t="n">
         <v>-8303.678626407043</v>
@@ -600,7 +598,7 @@
         <v>441.8751299021471</v>
       </c>
       <c r="Z2" t="n">
-        <v>184.19</v>
+        <v>245712547.1356277</v>
       </c>
       <c r="AA2" t="n">
         <v>9.077035214013106e-07</v>
@@ -640,10 +638,8 @@
       <c r="K3" t="n">
         <v>86.65194974328436</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.094x + -8487.128</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.0936952534511</v>
       </c>
       <c r="X3" t="n">
         <v>-8487.127595586631</v>
@@ -652,7 +648,7 @@
         <v>434.3481901031161</v>
       </c>
       <c r="Z3" t="n">
-        <v>171.579</v>
+        <v>38491344.48331343</v>
       </c>
       <c r="AA3" t="n">
         <v>8.496679723174884e-07</v>
@@ -692,10 +688,8 @@
       <c r="K4" t="n">
         <v>86.65947280398476</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.132x + -8310.605</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.13227891826376</v>
       </c>
       <c r="X4" t="n">
         <v>-8310.605327035604</v>
@@ -704,7 +698,7 @@
         <v>427.7779039390333</v>
       </c>
       <c r="Z4" t="n">
-        <v>164.317</v>
+        <v>59686438.34264517</v>
       </c>
       <c r="AA4" t="n">
         <v>8.143957286588159e-07</v>
@@ -744,10 +738,8 @@
       <c r="K5" t="n">
         <v>86.8244916387948</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.025x + -8611.818</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.02454772737477</v>
       </c>
       <c r="X5" t="n">
         <v>-8611.818107984484</v>
@@ -756,7 +748,7 @@
         <v>421.5797911742441</v>
       </c>
       <c r="Z5" t="n">
-        <v>157.765</v>
+        <v>63508959.18336506</v>
       </c>
       <c r="AA5" t="n">
         <v>7.892827574397358e-07</v>
@@ -796,10 +788,8 @@
       <c r="K6" t="n">
         <v>86.87144478999733</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.296x + -8591.413</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.29560960290341</v>
       </c>
       <c r="X6" t="n">
         <v>-8591.412511777164</v>
@@ -808,7 +798,7 @@
         <v>415.6768547387593</v>
       </c>
       <c r="Z6" t="n">
-        <v>154.299</v>
+        <v>30128315.26671074</v>
       </c>
       <c r="AA6" t="n">
         <v>7.71485166579219e-07</v>
@@ -848,10 +838,8 @@
       <c r="K7" t="n">
         <v>86.92248349849262</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 18.600x + -8596.735</t>
-        </is>
+      <c r="W7" t="n">
+        <v>18.59962999790918</v>
       </c>
       <c r="X7" t="n">
         <v>-8596.735331531549</v>
@@ -860,7 +848,7 @@
         <v>409.977589424865</v>
       </c>
       <c r="Z7" t="n">
-        <v>150.893</v>
+        <v>675381081.8686706</v>
       </c>
       <c r="AA7" t="n">
         <v>7.565498516939744e-07</v>
@@ -900,10 +888,8 @@
       <c r="K8" t="n">
         <v>87.01407570627818</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 19.171x + -8740.130</t>
-        </is>
+      <c r="W8" t="n">
+        <v>19.17124976817003</v>
       </c>
       <c r="X8" t="n">
         <v>-8740.130202361239</v>
@@ -912,7 +898,7 @@
         <v>404.4319783582843</v>
       </c>
       <c r="Z8" t="n">
-        <v>147.951</v>
+        <v>111313918.0968795</v>
       </c>
       <c r="AA8" t="n">
         <v>7.434343053118211e-07</v>
@@ -952,10 +938,8 @@
       <c r="K9" t="n">
         <v>86.94631826068088</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 18.745x + -8382.359</t>
-        </is>
+      <c r="W9" t="n">
+        <v>18.74508335655008</v>
       </c>
       <c r="X9" t="n">
         <v>-8382.359059673714</v>
@@ -964,7 +948,7 @@
         <v>399.2435837759633</v>
       </c>
       <c r="Z9" t="n">
-        <v>147.2149999999999</v>
+        <v>164357452.0273654</v>
       </c>
       <c r="AA9" t="n">
         <v>7.313158604715136e-07</v>
@@ -1004,10 +988,8 @@
       <c r="K10" t="n">
         <v>86.91908270045455</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.579x + -8177.335</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.57905967068162</v>
       </c>
       <c r="X10" t="n">
         <v>-8177.335005830709</v>
@@ -1016,7 +998,7 @@
         <v>394.6339166541012</v>
       </c>
       <c r="Z10" t="n">
-        <v>145.519</v>
+        <v>1081600138.813152</v>
       </c>
       <c r="AA10" t="n">
         <v>7.200036925052079e-07</v>
@@ -1056,10 +1038,8 @@
       <c r="K11" t="n">
         <v>86.93416468923911</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.671x + -8112.778</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.67063298934583</v>
       </c>
       <c r="X11" t="n">
         <v>-8112.777920204778</v>
@@ -1068,7 +1048,7 @@
         <v>390.5236675824672</v>
       </c>
       <c r="Z11" t="n">
-        <v>143.198</v>
+        <v>121300484.0697669</v>
       </c>
       <c r="AA11" t="n">
         <v>7.10358220782034e-07</v>
@@ -1194,12 +1174,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -1254,10 +1234,8 @@
       <c r="K2" t="n">
         <v>86.34442876493496</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 15.652x + -7830.369</t>
-        </is>
+      <c r="W2" t="n">
+        <v>15.6522772434987</v>
       </c>
       <c r="X2" t="n">
         <v>-7830.369185265049</v>
@@ -1266,7 +1244,7 @@
         <v>435.0186249382122</v>
       </c>
       <c r="Z2" t="n">
-        <v>175.045</v>
+        <v>79437038.25296503</v>
       </c>
       <c r="AA2" t="n">
         <v>1.008483203030008e-06</v>
@@ -1306,10 +1284,8 @@
       <c r="K3" t="n">
         <v>86.79828850962785</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 17.877x + -8555.250</t>
-        </is>
+      <c r="W3" t="n">
+        <v>17.87672924908356</v>
       </c>
       <c r="X3" t="n">
         <v>-8555.250389915491</v>
@@ -1318,7 +1294,7 @@
         <v>424.1085412556876</v>
       </c>
       <c r="Z3" t="n">
-        <v>156.492</v>
+        <v>103316021.9869039</v>
       </c>
       <c r="AA3" t="n">
         <v>8.943508687437834e-07</v>
@@ -1358,10 +1334,8 @@
       <c r="K4" t="n">
         <v>86.87648169382103</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 18.325x + -8601.813</t>
-        </is>
+      <c r="W4" t="n">
+        <v>18.32517130141567</v>
       </c>
       <c r="X4" t="n">
         <v>-8601.813200262834</v>
@@ -1370,7 +1344,7 @@
         <v>418.9522391080113</v>
       </c>
       <c r="Z4" t="n">
-        <v>149.898</v>
+        <v>37718787.45935754</v>
       </c>
       <c r="AA4" t="n">
         <v>8.557950415430884e-07</v>
@@ -1410,10 +1384,8 @@
       <c r="K5" t="n">
         <v>86.91729452845723</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 18.568x + -8602.648</t>
-        </is>
+      <c r="W5" t="n">
+        <v>18.56826178536179</v>
       </c>
       <c r="X5" t="n">
         <v>-8602.648156780922</v>
@@ -1422,7 +1394,7 @@
         <v>415.0262851245232</v>
       </c>
       <c r="Z5" t="n">
-        <v>146.881</v>
+        <v>341754844.5517014</v>
       </c>
       <c r="AA5" t="n">
         <v>8.321549054307094e-07</v>
@@ -1462,10 +1434,8 @@
       <c r="K6" t="n">
         <v>87.06485746626791</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 19.504x + -8960.891</t>
-        </is>
+      <c r="W6" t="n">
+        <v>19.50353336746041</v>
       </c>
       <c r="X6" t="n">
         <v>-8960.890612911184</v>
@@ -1474,7 +1444,7 @@
         <v>410.983898887697</v>
       </c>
       <c r="Z6" t="n">
-        <v>142.6010000000001</v>
+        <v>169185510.2121852</v>
       </c>
       <c r="AA6" t="n">
         <v>8.130490827824994e-07</v>
@@ -1514,10 +1484,8 @@
       <c r="K7" t="n">
         <v>87.13659687627519</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 19.993x + -9088.720</t>
-        </is>
+      <c r="W7" t="n">
+        <v>19.99301837574501</v>
       </c>
       <c r="X7" t="n">
         <v>-9088.720059306743</v>
@@ -1526,7 +1494,7 @@
         <v>406.7603474091602</v>
       </c>
       <c r="Z7" t="n">
-        <v>140.2689999999999</v>
+        <v>225999761.0266023</v>
       </c>
       <c r="AA7" t="n">
         <v>7.966910835692676e-07</v>
@@ -1566,10 +1534,8 @@
       <c r="K8" t="n">
         <v>86.99756703532763</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 19.066x + -8516.875</t>
-        </is>
+      <c r="W8" t="n">
+        <v>19.0656463423861</v>
       </c>
       <c r="X8" t="n">
         <v>-8516.874534006982</v>
@@ -1578,7 +1544,7 @@
         <v>402.4949007440025</v>
       </c>
       <c r="Z8" t="n">
-        <v>140.942</v>
+        <v>221187425.3334227</v>
       </c>
       <c r="AA8" t="n">
         <v>7.834205066514079e-07</v>
@@ -1618,10 +1584,8 @@
       <c r="K9" t="n">
         <v>87.14472927873885</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 20.050x + -8878.658</t>
-        </is>
+      <c r="W9" t="n">
+        <v>20.0500574245267</v>
       </c>
       <c r="X9" t="n">
         <v>-8878.657663706701</v>
@@ -1630,7 +1594,7 @@
         <v>398.5084272840842</v>
       </c>
       <c r="Z9" t="n">
-        <v>136.867</v>
+        <v>440368840.7393088</v>
       </c>
       <c r="AA9" t="n">
         <v>7.699376669980727e-07</v>
@@ -1670,10 +1634,8 @@
       <c r="K10" t="n">
         <v>87.12928594521571</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.942x + -8718.879</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.94201658718402</v>
       </c>
       <c r="X10" t="n">
         <v>-8718.879094286116</v>
@@ -1682,7 +1644,7 @@
         <v>394.7192300493788</v>
       </c>
       <c r="Z10" t="n">
-        <v>135.136</v>
+        <v>216432961.9668211</v>
       </c>
       <c r="AA10" t="n">
         <v>7.579703599375671e-07</v>
@@ -1722,10 +1684,8 @@
       <c r="K11" t="n">
         <v>87.17486865025123</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 20.264x + -8776.357</t>
-        </is>
+      <c r="W11" t="n">
+        <v>20.26431028717905</v>
       </c>
       <c r="X11" t="n">
         <v>-8776.357454076953</v>
@@ -1734,7 +1694,7 @@
         <v>391.2934095908259</v>
       </c>
       <c r="Z11" t="n">
-        <v>133.176</v>
+        <v>164604808.5796399</v>
       </c>
       <c r="AA11" t="n">
         <v>7.476361312322177e-07</v>
@@ -1774,10 +1734,8 @@
       <c r="K12" t="n">
         <v>87.23000221781973</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 20.668x + -8867.960</t>
-        </is>
+      <c r="W12" t="n">
+        <v>20.66829579176916</v>
       </c>
       <c r="X12" t="n">
         <v>-8867.959509423963</v>
@@ -1786,7 +1744,7 @@
         <v>387.9888220539746</v>
       </c>
       <c r="Z12" t="n">
-        <v>130.953</v>
+        <v>636982177.1051949</v>
       </c>
       <c r="AA12" t="n">
         <v>7.38636039839273e-07</v>
@@ -1826,10 +1784,8 @@
       <c r="K13" t="n">
         <v>87.17390846088941</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 20.257x + -8588.119</t>
-        </is>
+      <c r="W13" t="n">
+        <v>20.25741413617275</v>
       </c>
       <c r="X13" t="n">
         <v>-8588.119164103447</v>
@@ -1838,7 +1794,7 @@
         <v>384.8544064891893</v>
       </c>
       <c r="Z13" t="n">
-        <v>131.1779999999999</v>
+        <v>210467638.5578675</v>
       </c>
       <c r="AA13" t="n">
         <v>7.313274669477334e-07</v>
@@ -1878,10 +1834,8 @@
       <c r="K14" t="n">
         <v>87.31095941786431</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 21.291x + -8983.087</t>
-        </is>
+      <c r="W14" t="n">
+        <v>21.29149921179159</v>
       </c>
       <c r="X14" t="n">
         <v>-8983.087148939432</v>
@@ -1890,7 +1844,7 @@
         <v>381.7959252873379</v>
       </c>
       <c r="Z14" t="n">
-        <v>128.843</v>
+        <v>417794686.5864821</v>
       </c>
       <c r="AA14" t="n">
         <v>7.24701217516823e-07</v>
@@ -1930,10 +1884,8 @@
       <c r="K15" t="n">
         <v>87.47135818949879</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 22.644x + -9509.996</t>
-        </is>
+      <c r="W15" t="n">
+        <v>22.64400418001273</v>
       </c>
       <c r="X15" t="n">
         <v>-9509.995708780943</v>
@@ -1942,7 +1894,7 @@
         <v>378.7175037836427</v>
       </c>
       <c r="Z15" t="n">
-        <v>124.3559999999999</v>
+        <v>103760347.6214598</v>
       </c>
       <c r="AA15" t="n">
         <v>7.16790368695532e-07</v>
@@ -1982,10 +1934,8 @@
       <c r="K16" t="n">
         <v>87.40001507291713</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 22.022x + -9138.471</t>
-        </is>
+      <c r="W16" t="n">
+        <v>22.02183785256468</v>
       </c>
       <c r="X16" t="n">
         <v>-9138.471431213011</v>
@@ -1994,7 +1944,7 @@
         <v>375.6815895349957</v>
       </c>
       <c r="Z16" t="n">
-        <v>125.044</v>
+        <v>208214067.9970274</v>
       </c>
       <c r="AA16" t="n">
         <v>7.11348877747008e-07</v>
@@ -2034,10 +1984,8 @@
       <c r="K17" t="n">
         <v>87.41102247673675</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 22.116x + -9095.563</t>
-        </is>
+      <c r="W17" t="n">
+        <v>22.11559519269355</v>
       </c>
       <c r="X17" t="n">
         <v>-9095.562659639783</v>
@@ -2046,7 +1994,7 @@
         <v>372.6977934854936</v>
       </c>
       <c r="Z17" t="n">
-        <v>124.75</v>
+        <v>152890524.945729</v>
       </c>
       <c r="AA17" t="n">
         <v>7.058668754276769e-07</v>
@@ -2086,10 +2034,8 @@
       <c r="K18" t="n">
         <v>87.34533099165118</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 21.568x + -8768.553</t>
-        </is>
+      <c r="W18" t="n">
+        <v>21.56757551452696</v>
       </c>
       <c r="X18" t="n">
         <v>-8768.552856788556</v>
@@ -2098,7 +2044,7 @@
         <v>369.7578174330148</v>
       </c>
       <c r="Z18" t="n">
-        <v>125.069</v>
+        <v>151738271.3552929</v>
       </c>
       <c r="AA18" t="n">
         <v>7.006918199967112e-07</v>
@@ -2138,10 +2084,8 @@
       <c r="K19" t="n">
         <v>87.44064922809999</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 22.372x + -9033.733</t>
-        </is>
+      <c r="W19" t="n">
+        <v>22.37194960079927</v>
       </c>
       <c r="X19" t="n">
         <v>-9033.73252079194</v>
@@ -2150,7 +2094,7 @@
         <v>366.856079214409</v>
       </c>
       <c r="Z19" t="n">
-        <v>121.879</v>
+        <v>306931823.3678589</v>
       </c>
       <c r="AA19" t="n">
         <v>6.943042421514423e-07</v>
@@ -2190,10 +2134,8 @@
       <c r="K20" t="n">
         <v>87.50195610308231</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 22.922x + -9187.913</t>
-        </is>
+      <c r="W20" t="n">
+        <v>22.92172320695897</v>
       </c>
       <c r="X20" t="n">
         <v>-9187.912833391589</v>
@@ -2202,7 +2144,7 @@
         <v>363.8768205576325</v>
       </c>
       <c r="Z20" t="n">
-        <v>119.655</v>
+        <v>199021235.4283823</v>
       </c>
       <c r="AA20" t="n">
         <v>6.88108748222111e-07</v>
@@ -2242,10 +2184,8 @@
       <c r="K21" t="n">
         <v>87.53564373187106</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 23.235x + -9241.637</t>
-        </is>
+      <c r="W21" t="n">
+        <v>23.23545678525143</v>
       </c>
       <c r="X21" t="n">
         <v>-9241.637290420997</v>
@@ -2254,7 +2194,7 @@
         <v>360.9486237394665</v>
       </c>
       <c r="Z21" t="n">
-        <v>119.123</v>
+        <v>183919532.2370981</v>
       </c>
       <c r="AA21" t="n">
         <v>6.83569896970495e-07</v>
@@ -2294,10 +2234,8 @@
       <c r="K22" t="n">
         <v>87.47095526829668</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 22.640x + -8897.679</t>
-        </is>
+      <c r="W22" t="n">
+        <v>22.640391903774</v>
       </c>
       <c r="X22" t="n">
         <v>-8897.678884716743</v>
@@ -2306,7 +2244,7 @@
         <v>357.9682818640612</v>
       </c>
       <c r="Z22" t="n">
-        <v>120.2</v>
+        <v>1270462204.530481</v>
       </c>
       <c r="AA22" t="n">
         <v>6.795181011603263e-07</v>
@@ -2432,12 +2370,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -2492,10 +2430,8 @@
       <c r="K2" t="n">
         <v>86.13945377474806</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 14.819x + -7446.211</t>
-        </is>
+      <c r="W2" t="n">
+        <v>14.81889945804878</v>
       </c>
       <c r="X2" t="n">
         <v>-7446.211464551119</v>
@@ -2504,7 +2440,7 @@
         <v>433.0755477598454</v>
       </c>
       <c r="Z2" t="n">
-        <v>196.03</v>
+        <v>189294391.1809571</v>
       </c>
       <c r="AA2" t="n">
         <v>9.922148824033418e-07</v>
@@ -2544,10 +2480,8 @@
       <c r="K3" t="n">
         <v>86.61714570465722</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 16.917x + -8081.027</t>
-        </is>
+      <c r="W3" t="n">
+        <v>16.91742601746587</v>
       </c>
       <c r="X3" t="n">
         <v>-8081.026531394899</v>
@@ -2556,7 +2490,7 @@
         <v>422.2385358405232</v>
       </c>
       <c r="Z3" t="n">
-        <v>165.46</v>
+        <v>59708384.05879393</v>
       </c>
       <c r="AA3" t="n">
         <v>8.529639486165217e-07</v>
@@ -2596,10 +2530,8 @@
       <c r="K4" t="n">
         <v>86.72188768178023</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 17.459x + -8188.276</t>
-        </is>
+      <c r="W4" t="n">
+        <v>17.45920898904154</v>
       </c>
       <c r="X4" t="n">
         <v>-8188.275960781168</v>
@@ -2608,7 +2540,7 @@
         <v>417.5884862461021</v>
       </c>
       <c r="Z4" t="n">
-        <v>156.611</v>
+        <v>36044888.17761886</v>
       </c>
       <c r="AA4" t="n">
         <v>8.125703972419277e-07</v>
@@ -2648,10 +2580,8 @@
       <c r="K5" t="n">
         <v>87.04977891610596</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 19.404x + -9059.945</t>
-        </is>
+      <c r="W5" t="n">
+        <v>19.40367594529323</v>
       </c>
       <c r="X5" t="n">
         <v>-9059.944754414106</v>
@@ -2660,7 +2590,7 @@
         <v>413.5496620947689</v>
       </c>
       <c r="Z5" t="n">
-        <v>146.769</v>
+        <v>454790505.9308857</v>
       </c>
       <c r="AA5" t="n">
         <v>7.88163149573542e-07</v>
@@ -2700,10 +2630,8 @@
       <c r="K6" t="n">
         <v>86.87749246948361</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 18.331x + -8396.356</t>
-        </is>
+      <c r="W6" t="n">
+        <v>18.33111504406767</v>
       </c>
       <c r="X6" t="n">
         <v>-8396.355584876788</v>
@@ -2712,7 +2640,7 @@
         <v>409.3882828900535</v>
       </c>
       <c r="Z6" t="n">
-        <v>145.914</v>
+        <v>449681904.7030554</v>
       </c>
       <c r="AA6" t="n">
         <v>7.704798527426754e-07</v>
@@ -2752,10 +2680,8 @@
       <c r="K7" t="n">
         <v>87.02747491937123</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 19.258x + -8742.079</t>
-        </is>
+      <c r="W7" t="n">
+        <v>19.25782407896265</v>
       </c>
       <c r="X7" t="n">
         <v>-8742.078544092812</v>
@@ -2764,7 +2690,7 @@
         <v>405.0572527687936</v>
       </c>
       <c r="Z7" t="n">
-        <v>140.85</v>
+        <v>222551452.9046378</v>
       </c>
       <c r="AA7" t="n">
         <v>7.550447286602293e-07</v>
@@ -2804,10 +2730,8 @@
       <c r="K8" t="n">
         <v>87.03897266560439</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 19.333x + -8657.705</t>
-        </is>
+      <c r="W8" t="n">
+        <v>19.33273680129014</v>
       </c>
       <c r="X8" t="n">
         <v>-8657.704968765431</v>
@@ -2816,7 +2740,7 @@
         <v>400.7303388075825</v>
       </c>
       <c r="Z8" t="n">
-        <v>138.72</v>
+        <v>219694685.1342096</v>
       </c>
       <c r="AA8" t="n">
         <v>7.417855691438191e-07</v>
@@ -2856,10 +2780,8 @@
       <c r="K9" t="n">
         <v>87.02591137060513</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 19.248x + -8507.557</t>
-        </is>
+      <c r="W9" t="n">
+        <v>19.24768159069383</v>
       </c>
       <c r="X9" t="n">
         <v>-8507.557493821065</v>
@@ -2868,7 +2790,7 @@
         <v>396.5803041922406</v>
       </c>
       <c r="Z9" t="n">
-        <v>138.199</v>
+        <v>326131378.9680545</v>
       </c>
       <c r="AA9" t="n">
         <v>7.318785446524434e-07</v>
@@ -2908,10 +2830,8 @@
       <c r="K10" t="n">
         <v>87.05236168936062</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.421x + -8480.874</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.42070786791356</v>
       </c>
       <c r="X10" t="n">
         <v>-8480.874046406934</v>
@@ -2920,7 +2840,7 @@
         <v>392.6631975947702</v>
       </c>
       <c r="Z10" t="n">
-        <v>135.258</v>
+        <v>329255284.1881668</v>
       </c>
       <c r="AA10" t="n">
         <v>7.208276239277801e-07</v>
@@ -2960,10 +2880,8 @@
       <c r="K11" t="n">
         <v>87.22185598824058</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 20.608x + -8937.783</t>
-        </is>
+      <c r="W11" t="n">
+        <v>20.60759638013381</v>
       </c>
       <c r="X11" t="n">
         <v>-8937.783194451338</v>
@@ -2972,7 +2890,7 @@
         <v>388.9439630694364</v>
       </c>
       <c r="Z11" t="n">
-        <v>131.565</v>
+        <v>159855868.3902268</v>
       </c>
       <c r="AA11" t="n">
         <v>7.111089980067962e-07</v>
@@ -3012,10 +2930,8 @@
       <c r="K12" t="n">
         <v>87.15281124632121</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 20.107x + -8607.014</t>
-        </is>
+      <c r="W12" t="n">
+        <v>20.10706528054541</v>
       </c>
       <c r="X12" t="n">
         <v>-8607.0140055543</v>
@@ -3024,7 +2940,7 @@
         <v>385.4121407138171</v>
       </c>
       <c r="Z12" t="n">
-        <v>132.447</v>
+        <v>116870617.8895902</v>
       </c>
       <c r="AA12" t="n">
         <v>7.044464394495368e-07</v>
@@ -3064,10 +2980,8 @@
       <c r="K13" t="n">
         <v>87.20564446519681</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 20.488x + -8691.976</t>
-        </is>
+      <c r="W13" t="n">
+        <v>20.48785275607478</v>
       </c>
       <c r="X13" t="n">
         <v>-8691.97638429313</v>
@@ -3076,7 +2990,7 @@
         <v>382.0050234085486</v>
       </c>
       <c r="Z13" t="n">
-        <v>131.004</v>
+        <v>209171369.0694711</v>
       </c>
       <c r="AA13" t="n">
         <v>6.981204294314548e-07</v>
@@ -3116,10 +3030,8 @@
       <c r="K14" t="n">
         <v>87.21069814602048</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 20.525x + -8616.665</t>
-        </is>
+      <c r="W14" t="n">
+        <v>20.52503169611332</v>
       </c>
       <c r="X14" t="n">
         <v>-8616.6647375128</v>
@@ -3128,7 +3040,7 @@
         <v>378.6541941245881</v>
       </c>
       <c r="Z14" t="n">
-        <v>129.723</v>
+        <v>385677221.7194996</v>
       </c>
       <c r="AA14" t="n">
         <v>6.916289298655832e-07</v>
@@ -3168,10 +3080,8 @@
       <c r="K15" t="n">
         <v>87.21677231629147</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 20.570x + -8548.287</t>
-        </is>
+      <c r="W15" t="n">
+        <v>20.56989670041561</v>
       </c>
       <c r="X15" t="n">
         <v>-8548.286852487357</v>
@@ -3180,7 +3090,7 @@
         <v>375.5427336321978</v>
       </c>
       <c r="Z15" t="n">
-        <v>127.657</v>
+        <v>154990064.9209351</v>
       </c>
       <c r="AA15" t="n">
         <v>6.85072256865229e-07</v>
@@ -3220,10 +3130,8 @@
       <c r="K16" t="n">
         <v>87.29973932488761</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 21.203x + -8751.373</t>
-        </is>
+      <c r="W16" t="n">
+        <v>21.20289869332894</v>
       </c>
       <c r="X16" t="n">
         <v>-8751.372774631207</v>
@@ -3232,7 +3140,7 @@
         <v>372.5235151616664</v>
       </c>
       <c r="Z16" t="n">
-        <v>126.3220000000001</v>
+        <v>305699367.8179162</v>
       </c>
       <c r="AA16" t="n">
         <v>6.798831791571903e-07</v>
@@ -3272,10 +3180,8 @@
       <c r="K17" t="n">
         <v>87.20030488207833</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 20.449x + -8336.352</t>
-        </is>
+      <c r="W17" t="n">
+        <v>20.44871620035842</v>
       </c>
       <c r="X17" t="n">
         <v>-8336.351888326819</v>
@@ -3284,7 +3190,7 @@
         <v>369.5490524095136</v>
       </c>
       <c r="Z17" t="n">
-        <v>127.994</v>
+        <v>112075823.0648189</v>
       </c>
       <c r="AA17" t="n">
         <v>6.754387727039867e-07</v>
@@ -3324,10 +3230,8 @@
       <c r="K18" t="n">
         <v>87.33122650575744</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 21.453x + -8702.471</t>
-        </is>
+      <c r="W18" t="n">
+        <v>21.45342700606522</v>
       </c>
       <c r="X18" t="n">
         <v>-8702.470732248117</v>
@@ -3336,7 +3240,7 @@
         <v>366.5906727641661</v>
       </c>
       <c r="Z18" t="n">
-        <v>125.971</v>
+        <v>200470441.3851776</v>
       </c>
       <c r="AA18" t="n">
         <v>6.711142224885672e-07</v>
@@ -3376,10 +3280,8 @@
       <c r="K19" t="n">
         <v>87.30840048171451</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 21.271x + -8541.704</t>
-        </is>
+      <c r="W19" t="n">
+        <v>21.27122735732923</v>
       </c>
       <c r="X19" t="n">
         <v>-8541.704394462253</v>
@@ -3388,7 +3290,7 @@
         <v>363.711147851523</v>
       </c>
       <c r="Z19" t="n">
-        <v>126.248</v>
+        <v>101810104.8653887</v>
       </c>
       <c r="AA19" t="n">
         <v>6.675263665375564e-07</v>
@@ -3428,10 +3330,8 @@
       <c r="K20" t="n">
         <v>87.31407338683741</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 21.316x + -8481.658</t>
-        </is>
+      <c r="W20" t="n">
+        <v>21.31622009243743</v>
       </c>
       <c r="X20" t="n">
         <v>-8481.65815018914</v>
@@ -3440,7 +3340,7 @@
         <v>360.8848523078199</v>
       </c>
       <c r="Z20" t="n">
-        <v>125.181</v>
+        <v>788563842.0398979</v>
       </c>
       <c r="AA20" t="n">
         <v>6.626457979894738e-07</v>
@@ -3480,10 +3380,8 @@
       <c r="K21" t="n">
         <v>87.31091147042447</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 21.291x + -8392.941</t>
-        </is>
+      <c r="W21" t="n">
+        <v>21.29111901845852</v>
       </c>
       <c r="X21" t="n">
         <v>-8392.940558782655</v>
@@ -3492,7 +3390,7 @@
         <v>358.1705882762301</v>
       </c>
       <c r="Z21" t="n">
-        <v>124.092</v>
+        <v>294176667.7708919</v>
       </c>
       <c r="AA21" t="n">
         <v>6.582015866471859e-07</v>
@@ -3532,10 +3430,8 @@
       <c r="K22" t="n">
         <v>87.39840699619239</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 22.008x + -8624.156</t>
-        </is>
+      <c r="W22" t="n">
+        <v>22.00820717278198</v>
       </c>
       <c r="X22" t="n">
         <v>-8624.156160304748</v>
@@ -3544,7 +3440,7 @@
         <v>355.4980297768718</v>
       </c>
       <c r="Z22" t="n">
-        <v>121.503</v>
+        <v>195786323.3136893</v>
       </c>
       <c r="AA22" t="n">
         <v>6.538806611654203e-07</v>
@@ -3670,12 +3566,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -3730,10 +3626,8 @@
       <c r="K2" t="n">
         <v>84.17588870299647</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.804x + -4623.595</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.803779561330455</v>
       </c>
       <c r="X2" t="n">
         <v>-4623.594987243592</v>
@@ -3742,7 +3636,7 @@
         <v>399.1107394250932</v>
       </c>
       <c r="Z2" t="n">
-        <v>293.102</v>
+        <v>438446194.1489649</v>
       </c>
       <c r="AA2" t="n">
         <v>1.317512045825061e-06</v>
@@ -3782,10 +3676,8 @@
       <c r="K3" t="n">
         <v>85.33752804804207</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.262x + -5156.461</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.26157581781073</v>
       </c>
       <c r="X3" t="n">
         <v>-5156.460874532487</v>
@@ -3794,7 +3686,7 @@
         <v>376.7446016448904</v>
       </c>
       <c r="Z3" t="n">
-        <v>236.3339999999999</v>
+        <v>412906226.6559771</v>
       </c>
       <c r="AA3" t="n">
         <v>9.982360272586506e-07</v>
@@ -3834,10 +3726,8 @@
       <c r="K4" t="n">
         <v>85.77189009505075</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 13.527x + -5514.607</t>
-        </is>
+      <c r="W4" t="n">
+        <v>13.52654953524155</v>
       </c>
       <c r="X4" t="n">
         <v>-5514.607458360963</v>
@@ -3846,7 +3736,7 @@
         <v>368.9296501274155</v>
       </c>
       <c r="Z4" t="n">
-        <v>215.6709999999999</v>
+        <v>202042743.9430597</v>
       </c>
       <c r="AA4" t="n">
         <v>9.120585127132215e-07</v>
@@ -3886,10 +3776,8 @@
       <c r="K5" t="n">
         <v>85.93663182450629</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.077x + -5623.005</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.07691549036024</v>
       </c>
       <c r="X5" t="n">
         <v>-5623.004521106845</v>
@@ -3898,7 +3786,7 @@
         <v>363.7664924369331</v>
       </c>
       <c r="Z5" t="n">
-        <v>204.578</v>
+        <v>200541967.061127</v>
       </c>
       <c r="AA5" t="n">
         <v>8.648920944189094e-07</v>
@@ -3938,10 +3826,8 @@
       <c r="K6" t="n">
         <v>86.16882978339994</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.933x + -5891.785</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.93286866830128</v>
       </c>
       <c r="X6" t="n">
         <v>-5891.785405700944</v>
@@ -3950,7 +3836,7 @@
         <v>359.0947097940731</v>
       </c>
       <c r="Z6" t="n">
-        <v>194.877</v>
+        <v>98275559.66834185</v>
       </c>
       <c r="AA6" t="n">
         <v>8.299639251073624e-07</v>
@@ -3990,10 +3876,8 @@
       <c r="K7" t="n">
         <v>86.36335575721175</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.734x + -6129.946</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.73396077110964</v>
       </c>
       <c r="X7" t="n">
         <v>-6129.945738199643</v>
@@ -4002,7 +3886,7 @@
         <v>354.4718578756008</v>
       </c>
       <c r="Z7" t="n">
-        <v>186.837</v>
+        <v>389018917.1033631</v>
       </c>
       <c r="AA7" t="n">
         <v>8.025533379876564e-07</v>
@@ -4042,10 +3926,8 @@
       <c r="K8" t="n">
         <v>86.44976604876672</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.118x + -6183.843</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.11793292668291</v>
       </c>
       <c r="X8" t="n">
         <v>-6183.843153199383</v>
@@ -4054,7 +3936,7 @@
         <v>349.8973545128995</v>
       </c>
       <c r="Z8" t="n">
-        <v>181.823</v>
+        <v>143423329.243043</v>
       </c>
       <c r="AA8" t="n">
         <v>7.800550646503015e-07</v>
@@ -4094,10 +3976,8 @@
       <c r="K9" t="n">
         <v>86.54388671203137</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.558x + -6260.835</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.55798474291716</v>
       </c>
       <c r="X9" t="n">
         <v>-6260.834587116743</v>
@@ -4106,7 +3986,7 @@
         <v>345.5275287145916</v>
       </c>
       <c r="Z9" t="n">
-        <v>176.717</v>
+        <v>188617771.1430337</v>
       </c>
       <c r="AA9" t="n">
         <v>7.609167513772127e-07</v>
@@ -4146,10 +4026,8 @@
       <c r="K10" t="n">
         <v>86.61620074139398</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 16.913x + -6308.095</t>
-        </is>
+      <c r="W10" t="n">
+        <v>16.91269064094116</v>
       </c>
       <c r="X10" t="n">
         <v>-6308.094701077208</v>
@@ -4158,7 +4036,7 @@
         <v>341.3931195897867</v>
       </c>
       <c r="Z10" t="n">
-        <v>173.245</v>
+        <v>279365939.1792666</v>
       </c>
       <c r="AA10" t="n">
         <v>7.449007832611085e-07</v>
@@ -4198,10 +4076,8 @@
       <c r="K11" t="n">
         <v>86.76947872918841</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.717x + -6541.747</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.71697076076464</v>
       </c>
       <c r="X11" t="n">
         <v>-6541.747066667391</v>
@@ -4210,7 +4086,7 @@
         <v>337.5217223839763</v>
       </c>
       <c r="Z11" t="n">
-        <v>166.891</v>
+        <v>184256538.910268</v>
       </c>
       <c r="AA11" t="n">
         <v>7.29545926736977e-07</v>
@@ -4336,12 +4212,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -4396,10 +4272,8 @@
       <c r="K2" t="n">
         <v>85.19589780308293</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.898x + -5928.531</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.89846587395262</v>
       </c>
       <c r="X2" t="n">
         <v>-5928.530747659112</v>
@@ -4408,7 +4282,7 @@
         <v>430.3375601763885</v>
       </c>
       <c r="Z2" t="n">
-        <v>236.588</v>
+        <v>177345990.1357034</v>
       </c>
       <c r="AA2" t="n">
         <v>1.312691647084753e-06</v>
@@ -4448,10 +4322,8 @@
       <c r="K3" t="n">
         <v>85.93749408650241</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 14.080x + -6692.469</t>
-        </is>
+      <c r="W3" t="n">
+        <v>14.07991333942035</v>
       </c>
       <c r="X3" t="n">
         <v>-6692.468863382832</v>
@@ -4460,7 +4332,7 @@
         <v>419.8009996635196</v>
       </c>
       <c r="Z3" t="n">
-        <v>199.874</v>
+        <v>50360310.56373951</v>
       </c>
       <c r="AA3" t="n">
         <v>1.074401804569402e-06</v>
@@ -4500,10 +4372,8 @@
       <c r="K4" t="n">
         <v>86.11405165353406</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.722x + -6860.358</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.72173476384452</v>
       </c>
       <c r="X4" t="n">
         <v>-6860.358282151244</v>
@@ -4512,7 +4382,7 @@
         <v>415.1516060485824</v>
       </c>
       <c r="Z4" t="n">
-        <v>186.5889999999999</v>
+        <v>161636050.9926125</v>
       </c>
       <c r="AA4" t="n">
         <v>9.967437724492801e-07</v>
@@ -4552,10 +4422,8 @@
       <c r="K5" t="n">
         <v>86.38286258754704</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.819x + -7310.533</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.81904002354427</v>
       </c>
       <c r="X5" t="n">
         <v>-7310.533424839303</v>
@@ -4564,7 +4432,7 @@
         <v>411.1660005968433</v>
       </c>
       <c r="Z5" t="n">
-        <v>176.016</v>
+        <v>171120962.1477516</v>
       </c>
       <c r="AA5" t="n">
         <v>9.500555416419336e-07</v>
@@ -4604,10 +4472,8 @@
       <c r="K6" t="n">
         <v>86.40908360630586</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.935x + -7253.939</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.93485767343772</v>
       </c>
       <c r="X6" t="n">
         <v>-7253.939141756458</v>
@@ -4616,7 +4482,7 @@
         <v>407.0124660538758</v>
       </c>
       <c r="Z6" t="n">
-        <v>170.3299999999999</v>
+        <v>224782532.1097848</v>
       </c>
       <c r="AA6" t="n">
         <v>9.148654314970473e-07</v>
@@ -4656,10 +4522,8 @@
       <c r="K7" t="n">
         <v>86.52511975594811</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.468x + -7410.800</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.46834134292472</v>
       </c>
       <c r="X7" t="n">
         <v>-7410.799510043837</v>
@@ -4668,7 +4532,7 @@
         <v>402.6703652962622</v>
       </c>
       <c r="Z7" t="n">
-        <v>164.851</v>
+        <v>221444165.4908842</v>
       </c>
       <c r="AA7" t="n">
         <v>8.865235839604954e-07</v>
@@ -4708,10 +4572,8 @@
       <c r="K8" t="n">
         <v>86.66171887850922</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.144x + -7632.948</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.1438320757833</v>
       </c>
       <c r="X8" t="n">
         <v>-7632.948425748457</v>
@@ -4720,7 +4582,7 @@
         <v>398.3747443705986</v>
       </c>
       <c r="Z8" t="n">
-        <v>159.932</v>
+        <v>218891627.6862209</v>
       </c>
       <c r="AA8" t="n">
         <v>8.617305433626118e-07</v>
@@ -4760,10 +4622,8 @@
       <c r="K9" t="n">
         <v>86.73939803914961</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 17.553x + -7727.754</t>
-        </is>
+      <c r="W9" t="n">
+        <v>17.55317427152207</v>
       </c>
       <c r="X9" t="n">
         <v>-7727.753523083717</v>
@@ -4772,7 +4632,7 @@
         <v>394.4347314518075</v>
       </c>
       <c r="Z9" t="n">
-        <v>156.7839999999999</v>
+        <v>432269489.553234</v>
       </c>
       <c r="AA9" t="n">
         <v>8.409253555724308e-07</v>
@@ -4812,10 +4672,8 @@
       <c r="K10" t="n">
         <v>86.76321307466895</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.683x + -7688.241</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.68260202793824</v>
       </c>
       <c r="X10" t="n">
         <v>-7688.241306720884</v>
@@ -4824,7 +4682,7 @@
         <v>390.8375003359115</v>
       </c>
       <c r="Z10" t="n">
-        <v>151.453</v>
+        <v>428395885.152842</v>
       </c>
       <c r="AA10" t="n">
         <v>8.211383059960402e-07</v>
@@ -4864,10 +4722,8 @@
       <c r="K11" t="n">
         <v>86.84478497143563</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.141x + -7815.289</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.14071282561955</v>
       </c>
       <c r="X11" t="n">
         <v>-7815.289419813595</v>
@@ -4876,7 +4732,7 @@
         <v>387.453420771319</v>
       </c>
       <c r="Z11" t="n">
-        <v>148.8439999999999</v>
+        <v>213964053.8038524</v>
       </c>
       <c r="AA11" t="n">
         <v>8.063701352079936e-07</v>
@@ -4916,10 +4772,8 @@
       <c r="K12" t="n">
         <v>86.96952641648392</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 18.889x + -8081.106</t>
-        </is>
+      <c r="W12" t="n">
+        <v>18.88890926099844</v>
       </c>
       <c r="X12" t="n">
         <v>-8081.105502885852</v>
@@ -4928,7 +4782,7 @@
         <v>384.2698611246886</v>
       </c>
       <c r="Z12" t="n">
-        <v>144.881</v>
+        <v>211121508.1296392</v>
       </c>
       <c r="AA12" t="n">
         <v>7.926384331754758e-07</v>
@@ -4968,10 +4822,8 @@
       <c r="K13" t="n">
         <v>86.89056668718435</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 18.408x + -7775.949</t>
-        </is>
+      <c r="W13" t="n">
+        <v>18.40834429132125</v>
       </c>
       <c r="X13" t="n">
         <v>-7775.94910073984</v>
@@ -4980,7 +4832,7 @@
         <v>381.2286649902834</v>
       </c>
       <c r="Z13" t="n">
-        <v>144.603</v>
+        <v>313014959.4294567</v>
       </c>
       <c r="AA13" t="n">
         <v>7.814934457548496e-07</v>
@@ -5020,10 +4872,8 @@
       <c r="K14" t="n">
         <v>86.99326370493998</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 19.038x + -7988.597</t>
-        </is>
+      <c r="W14" t="n">
+        <v>19.03830896839971</v>
       </c>
       <c r="X14" t="n">
         <v>-7988.5966968354</v>
@@ -5032,7 +4882,7 @@
         <v>378.2434279452024</v>
       </c>
       <c r="Z14" t="n">
-        <v>142.214</v>
+        <v>414211151.969752</v>
       </c>
       <c r="AA14" t="n">
         <v>7.716591258289905e-07</v>
@@ -5072,10 +4922,8 @@
       <c r="K15" t="n">
         <v>87.06119563420363</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 19.479x + -8110.328</t>
-        </is>
+      <c r="W15" t="n">
+        <v>19.47918882612264</v>
       </c>
       <c r="X15" t="n">
         <v>-8110.328318765581</v>
@@ -5084,7 +4932,7 @@
         <v>375.3233192145844</v>
       </c>
       <c r="Z15" t="n">
-        <v>139.795</v>
+        <v>411216768.2207509</v>
       </c>
       <c r="AA15" t="n">
         <v>7.612174688380247e-07</v>
@@ -5124,10 +4972,8 @@
       <c r="K16" t="n">
         <v>87.06598764755772</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 19.511x + -8048.507</t>
-        </is>
+      <c r="W16" t="n">
+        <v>19.51105928412112</v>
       </c>
       <c r="X16" t="n">
         <v>-8048.507284433118</v>
@@ -5136,7 +4982,7 @@
         <v>372.4727883082132</v>
       </c>
       <c r="Z16" t="n">
-        <v>137.646</v>
+        <v>305868352.3892522</v>
       </c>
       <c r="AA16" t="n">
         <v>7.530725144062699e-07</v>
@@ -5176,10 +5022,8 @@
       <c r="K17" t="n">
         <v>87.04669351874476</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 19.383x + -7914.748</t>
-        </is>
+      <c r="W17" t="n">
+        <v>19.38336851785602</v>
       </c>
       <c r="X17" t="n">
         <v>-7914.748228115303</v>
@@ -5188,7 +5032,7 @@
         <v>369.6354063846488</v>
       </c>
       <c r="Z17" t="n">
-        <v>136.5240000000001</v>
+        <v>151861490.4505496</v>
       </c>
       <c r="AA17" t="n">
         <v>7.440256920703068e-07</v>
@@ -5228,10 +5072,8 @@
       <c r="K18" t="n">
         <v>87.12844946748636</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 19.936x + -8083.851</t>
-        </is>
+      <c r="W18" t="n">
+        <v>19.9361977773622</v>
       </c>
       <c r="X18" t="n">
         <v>-8083.850856494796</v>
@@ -5240,7 +5082,7 @@
         <v>366.8052324291342</v>
       </c>
       <c r="Z18" t="n">
-        <v>133.609</v>
+        <v>301223118.9624547</v>
       </c>
       <c r="AA18" t="n">
         <v>7.358434797363799e-07</v>
@@ -5280,10 +5122,8 @@
       <c r="K19" t="n">
         <v>87.16442505823083</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 20.190x + -8124.669</t>
-        </is>
+      <c r="W19" t="n">
+        <v>20.18955428858366</v>
       </c>
       <c r="X19" t="n">
         <v>-8124.66929687184</v>
@@ -5292,7 +5132,7 @@
         <v>363.958078806506</v>
       </c>
       <c r="Z19" t="n">
-        <v>133.562</v>
+        <v>896000990.8613718</v>
       </c>
       <c r="AA19" t="n">
         <v>7.300207471263049e-07</v>
@@ -5332,10 +5172,8 @@
       <c r="K20" t="n">
         <v>87.22282850808183</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 20.615x + -8232.125</t>
-        </is>
+      <c r="W20" t="n">
+        <v>20.61482414321637</v>
       </c>
       <c r="X20" t="n">
         <v>-8232.125132821564</v>
@@ -5344,7 +5182,7 @@
         <v>361.1030437426311</v>
       </c>
       <c r="Z20" t="n">
-        <v>130.462</v>
+        <v>197523750.4443202</v>
       </c>
       <c r="AA20" t="n">
         <v>7.227657215465091e-07</v>
@@ -5384,10 +5222,8 @@
       <c r="K21" t="n">
         <v>87.19541185281336</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 20.413x + -8065.045</t>
-        </is>
+      <c r="W21" t="n">
+        <v>20.41298341297195</v>
       </c>
       <c r="X21" t="n">
         <v>-8065.044971962247</v>
@@ -5396,7 +5232,7 @@
         <v>358.2517734184513</v>
       </c>
       <c r="Z21" t="n">
-        <v>129.615</v>
+        <v>195866476.6688291</v>
       </c>
       <c r="AA21" t="n">
         <v>7.159869467681006e-07</v>
@@ -5436,10 +5272,8 @@
       <c r="K22" t="n">
         <v>87.21832621275446</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 20.581x + -8061.253</t>
-        </is>
+      <c r="W22" t="n">
+        <v>20.58140553137124</v>
       </c>
       <c r="X22" t="n">
         <v>-8061.252527263254</v>
@@ -5448,7 +5282,7 @@
         <v>355.4193524940902</v>
       </c>
       <c r="Z22" t="n">
-        <v>128.767</v>
+        <v>388608664.1277252</v>
       </c>
       <c r="AA22" t="n">
         <v>7.103629344653632e-07</v>
@@ -5574,12 +5408,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -5634,10 +5468,8 @@
       <c r="K2" t="n">
         <v>83.78116345221645</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.177x + -4283.494</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.177055286031266</v>
       </c>
       <c r="X2" t="n">
         <v>-4283.493809854624</v>
@@ -5646,7 +5478,7 @@
         <v>396.0480226192574</v>
       </c>
       <c r="Z2" t="n">
-        <v>299.283</v>
+        <v>220341120.03033</v>
       </c>
       <c r="AA2" t="n">
         <v>1.580864204228818e-06</v>
@@ -5686,10 +5518,8 @@
       <c r="K3" t="n">
         <v>84.95858072274089</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.336x + -4759.724</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.33566486623271</v>
       </c>
       <c r="X3" t="n">
         <v>-4759.723635532172</v>
@@ -5698,7 +5528,7 @@
         <v>376.1619019626904</v>
       </c>
       <c r="Z3" t="n">
-        <v>242.703</v>
+        <v>206917800.2606733</v>
       </c>
       <c r="AA3" t="n">
         <v>1.167982552580774e-06</v>
@@ -5738,10 +5568,8 @@
       <c r="K4" t="n">
         <v>85.40294984965661</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.437x + -5075.481</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.4368407549619</v>
       </c>
       <c r="X4" t="n">
         <v>-5075.480918343761</v>
@@ -5750,7 +5578,7 @@
         <v>369.0674309948403</v>
       </c>
       <c r="Z4" t="n">
-        <v>222.64</v>
+        <v>209377630.0668765</v>
       </c>
       <c r="AA4" t="n">
         <v>1.057263656926392e-06</v>
@@ -5790,10 +5618,8 @@
       <c r="K5" t="n">
         <v>85.68953496840582</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 13.267x + -5329.797</t>
-        </is>
+      <c r="W5" t="n">
+        <v>13.26716342533937</v>
       </c>
       <c r="X5" t="n">
         <v>-5329.797388394029</v>
@@ -5802,7 +5628,7 @@
         <v>364.1423670579533</v>
       </c>
       <c r="Z5" t="n">
-        <v>210.065</v>
+        <v>697729078.7444665</v>
       </c>
       <c r="AA5" t="n">
         <v>9.933647794257932e-07</v>
@@ -5842,10 +5668,8 @@
       <c r="K6" t="n">
         <v>85.76830569346231</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 13.515x + -5324.501</t>
-        </is>
+      <c r="W6" t="n">
+        <v>13.51505032843908</v>
       </c>
       <c r="X6" t="n">
         <v>-5324.500811857602</v>
@@ -5854,7 +5678,7 @@
         <v>359.4395566651669</v>
       </c>
       <c r="Z6" t="n">
-        <v>203.334</v>
+        <v>196807789.3057901</v>
       </c>
       <c r="AA6" t="n">
         <v>9.460835482645655e-07</v>
@@ -5894,10 +5718,8 @@
       <c r="K7" t="n">
         <v>85.98534782726016</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 14.248x + -5542.815</t>
-        </is>
+      <c r="W7" t="n">
+        <v>14.2483031972898</v>
       </c>
       <c r="X7" t="n">
         <v>-5542.81532576788</v>
@@ -5906,7 +5728,7 @@
         <v>354.6544064970562</v>
       </c>
       <c r="Z7" t="n">
-        <v>195.395</v>
+        <v>679380841.0213003</v>
       </c>
       <c r="AA7" t="n">
         <v>9.079446112459932e-07</v>
@@ -5946,10 +5768,8 @@
       <c r="K8" t="n">
         <v>86.1179253403461</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 14.736x + -5645.649</t>
-        </is>
+      <c r="W8" t="n">
+        <v>14.73646981245748</v>
       </c>
       <c r="X8" t="n">
         <v>-5645.649043492897</v>
@@ -5958,7 +5778,7 @@
         <v>349.9431300454831</v>
       </c>
       <c r="Z8" t="n">
-        <v>188.716</v>
+        <v>143457803.3713763</v>
       </c>
       <c r="AA8" t="n">
         <v>8.75602241623646e-07</v>
@@ -5998,10 +5818,8 @@
       <c r="K9" t="n">
         <v>86.29248315753577</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 15.432x + -5835.432</t>
-        </is>
+      <c r="W9" t="n">
+        <v>15.43237441152464</v>
       </c>
       <c r="X9" t="n">
         <v>-5835.431609975895</v>
@@ -6010,7 +5828,7 @@
         <v>345.4540720477756</v>
       </c>
       <c r="Z9" t="n">
-        <v>181.854</v>
+        <v>849363057.4685625</v>
       </c>
       <c r="AA9" t="n">
         <v>8.473050545763279e-07</v>
@@ -6050,10 +5868,8 @@
       <c r="K10" t="n">
         <v>86.39895569203611</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 15.890x + -5922.040</t>
-        </is>
+      <c r="W10" t="n">
+        <v>15.88992324757191</v>
       </c>
       <c r="X10" t="n">
         <v>-5922.040076180075</v>
@@ -6062,7 +5878,7 @@
         <v>341.2259099112376</v>
       </c>
       <c r="Z10" t="n">
-        <v>176.543</v>
+        <v>472832364.0553477</v>
       </c>
       <c r="AA10" t="n">
         <v>8.225130505633036e-07</v>
@@ -6102,10 +5918,8 @@
       <c r="K11" t="n">
         <v>86.39634014755802</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 15.878x + -5821.153</t>
-        </is>
+      <c r="W11" t="n">
+        <v>15.87835986706932</v>
       </c>
       <c r="X11" t="n">
         <v>-5821.152911643883</v>
@@ -6114,7 +5928,7 @@
         <v>337.3381906520464</v>
       </c>
       <c r="Z11" t="n">
-        <v>173.7449999999999</v>
+        <v>261051548.6262453</v>
       </c>
       <c r="AA11" t="n">
         <v>8.035422719802362e-07</v>
@@ -6240,12 +6054,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -6300,10 +6114,8 @@
       <c r="K2" t="n">
         <v>85.12960059451331</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 11.736x + -5683.332</t>
-        </is>
+      <c r="W2" t="n">
+        <v>11.73573382103866</v>
       </c>
       <c r="X2" t="n">
         <v>-5683.331757794689</v>
@@ -6312,7 +6124,7 @@
         <v>417.7472076657106</v>
       </c>
       <c r="Z2" t="n">
-        <v>234.4999999999999</v>
+        <v>226821460.078298</v>
       </c>
       <c r="AA2" t="n">
         <v>1.44353238429869e-06</v>
@@ -6352,10 +6164,8 @@
       <c r="K3" t="n">
         <v>85.79000605363042</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 13.585x + -6306.152</t>
-        </is>
+      <c r="W3" t="n">
+        <v>13.58496681241171</v>
       </c>
       <c r="X3" t="n">
         <v>-6306.152240210211</v>
@@ -6364,7 +6174,7 @@
         <v>409.2528650031653</v>
       </c>
       <c r="Z3" t="n">
-        <v>202.218</v>
+        <v>228500177.6122265</v>
       </c>
       <c r="AA3" t="n">
         <v>1.185563077314297e-06</v>
@@ -6404,10 +6214,8 @@
       <c r="K4" t="n">
         <v>86.09604588803867</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.654x + -6706.369</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.65362622124289</v>
       </c>
       <c r="X4" t="n">
         <v>-6706.368759949533</v>
@@ -6416,7 +6224,7 @@
         <v>404.9730002838888</v>
       </c>
       <c r="Z4" t="n">
-        <v>188.469</v>
+        <v>224601886.0095915</v>
       </c>
       <c r="AA4" t="n">
         <v>1.096061458687113e-06</v>
@@ -6456,10 +6264,8 @@
       <c r="K5" t="n">
         <v>86.07010806880217</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.557x + -6538.014</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.55660931081341</v>
       </c>
       <c r="X5" t="n">
         <v>-6538.013673325883</v>
@@ -6468,7 +6274,7 @@
         <v>400.9688127253339</v>
       </c>
       <c r="Z5" t="n">
-        <v>181.8340000000001</v>
+        <v>233810940.7085494</v>
       </c>
       <c r="AA5" t="n">
         <v>1.038776231899943e-06</v>
@@ -6508,10 +6314,8 @@
       <c r="K6" t="n">
         <v>86.3974213244698</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 15.883x + -7090.955</t>
-        </is>
+      <c r="W6" t="n">
+        <v>15.88313774120423</v>
       </c>
       <c r="X6" t="n">
         <v>-7090.955058926787</v>
@@ -6520,7 +6324,7 @@
         <v>396.5798434487414</v>
       </c>
       <c r="Z6" t="n">
-        <v>172.51</v>
+        <v>655130097.0375171</v>
       </c>
       <c r="AA6" t="n">
         <v>9.937445627067558e-07</v>
@@ -6560,10 +6364,8 @@
       <c r="K7" t="n">
         <v>86.39990871394555</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.894x + -6975.741</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.89414074963146</v>
       </c>
       <c r="X7" t="n">
         <v>-6975.740533092861</v>
@@ -6572,7 +6374,7 @@
         <v>391.9445455530394</v>
       </c>
       <c r="Z7" t="n">
-        <v>168.513</v>
+        <v>161931033.7023265</v>
       </c>
       <c r="AA7" t="n">
         <v>9.567497309654283e-07</v>
@@ -6612,10 +6414,8 @@
       <c r="K8" t="n">
         <v>86.52055460344455</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 16.447x + -7128.936</t>
-        </is>
+      <c r="W8" t="n">
+        <v>16.44668120124397</v>
       </c>
       <c r="X8" t="n">
         <v>-7128.935944885306</v>
@@ -6624,7 +6424,7 @@
         <v>387.4690119672044</v>
       </c>
       <c r="Z8" t="n">
-        <v>164.125</v>
+        <v>236660655.3961978</v>
       </c>
       <c r="AA8" t="n">
         <v>9.260766037454285e-07</v>
@@ -6664,10 +6464,8 @@
       <c r="K9" t="n">
         <v>86.61093400004739</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.886x + -7229.802</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.88634639481359</v>
       </c>
       <c r="X9" t="n">
         <v>-7229.801554616858</v>
@@ -6676,7 +6474,7 @@
         <v>383.2822621587598</v>
       </c>
       <c r="Z9" t="n">
-        <v>159.772</v>
+        <v>210447611.5556608</v>
       </c>
       <c r="AA9" t="n">
         <v>8.986873886286346e-07</v>
@@ -6716,10 +6514,8 @@
       <c r="K10" t="n">
         <v>86.69588850910867</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 17.322x + -7331.279</t>
-        </is>
+      <c r="W10" t="n">
+        <v>17.32152567040469</v>
       </c>
       <c r="X10" t="n">
         <v>-7331.279047687674</v>
@@ -6728,7 +6524,7 @@
         <v>379.4042988125393</v>
       </c>
       <c r="Z10" t="n">
-        <v>155.4420000000001</v>
+        <v>624009656.8922387</v>
       </c>
       <c r="AA10" t="n">
         <v>8.768879609255373e-07</v>
@@ -6768,10 +6564,8 @@
       <c r="K11" t="n">
         <v>86.74793919765791</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.599x + -7361.998</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.59937519132789</v>
       </c>
       <c r="X11" t="n">
         <v>-7361.997937760949</v>
@@ -6780,7 +6574,7 @@
         <v>375.7329626332076</v>
       </c>
       <c r="Z11" t="n">
-        <v>151.945</v>
+        <v>159994176.9848319</v>
       </c>
       <c r="AA11" t="n">
         <v>8.561757955896253e-07</v>
@@ -6820,10 +6614,8 @@
       <c r="K12" t="n">
         <v>86.80761449780843</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 17.929x + -7422.985</t>
-        </is>
+      <c r="W12" t="n">
+        <v>17.92906166017158</v>
       </c>
       <c r="X12" t="n">
         <v>-7422.984814473733</v>
@@ -6832,7 +6624,7 @@
         <v>372.2798102040754</v>
       </c>
       <c r="Z12" t="n">
-        <v>150.413</v>
+        <v>217591330.8219371</v>
       </c>
       <c r="AA12" t="n">
         <v>8.407841750404369e-07</v>
@@ -6872,10 +6664,8 @@
       <c r="K13" t="n">
         <v>86.90405563077231</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 18.489x + -7584.620</t>
-        </is>
+      <c r="W13" t="n">
+        <v>18.48870629030299</v>
       </c>
       <c r="X13" t="n">
         <v>-7584.6203970385</v>
@@ -6884,7 +6674,7 @@
         <v>368.9567173075583</v>
       </c>
       <c r="Z13" t="n">
-        <v>145.576</v>
+        <v>303843703.1087019</v>
       </c>
       <c r="AA13" t="n">
         <v>8.243302362294342e-07</v>
@@ -6924,10 +6714,8 @@
       <c r="K14" t="n">
         <v>86.85032697074804</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 18.173x + -7356.408</t>
-        </is>
+      <c r="W14" t="n">
+        <v>18.17269683844975</v>
       </c>
       <c r="X14" t="n">
         <v>-7356.407800720732</v>
@@ -6936,7 +6724,7 @@
         <v>365.7232932991741</v>
       </c>
       <c r="Z14" t="n">
-        <v>144.2629999999999</v>
+        <v>200496852.5317627</v>
       </c>
       <c r="AA14" t="n">
         <v>8.10485472374145e-07</v>
@@ -6976,10 +6764,8 @@
       <c r="K15" t="n">
         <v>86.91608356221145</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 18.561x + -7444.026</t>
-        </is>
+      <c r="W15" t="n">
+        <v>18.5609564643298</v>
       </c>
       <c r="X15" t="n">
         <v>-7444.025720975245</v>
@@ -6988,7 +6774,7 @@
         <v>362.4449858407583</v>
       </c>
       <c r="Z15" t="n">
-        <v>142.094</v>
+        <v>99398386.45434077</v>
       </c>
       <c r="AA15" t="n">
         <v>7.985641322860091e-07</v>
@@ -7028,10 +6814,8 @@
       <c r="K16" t="n">
         <v>87.04139134951386</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 19.349x + -7707.085</t>
-        </is>
+      <c r="W16" t="n">
+        <v>19.34856961724427</v>
       </c>
       <c r="X16" t="n">
         <v>-7707.084684646431</v>
@@ -7040,7 +6824,7 @@
         <v>359.2066827937394</v>
       </c>
       <c r="Z16" t="n">
-        <v>139.393</v>
+        <v>150058737.6249207</v>
       </c>
       <c r="AA16" t="n">
         <v>7.872979423758546e-07</v>
@@ -7080,10 +6864,8 @@
       <c r="K17" t="n">
         <v>87.08235123250444</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 19.621x + -7739.443</t>
-        </is>
+      <c r="W17" t="n">
+        <v>19.62067773731119</v>
       </c>
       <c r="X17" t="n">
         <v>-7739.44327589951</v>
@@ -7092,7 +6874,7 @@
         <v>355.9968355252498</v>
       </c>
       <c r="Z17" t="n">
-        <v>137.705</v>
+        <v>194849446.0354508</v>
       </c>
       <c r="AA17" t="n">
         <v>7.782783084268183e-07</v>
@@ -7132,10 +6914,8 @@
       <c r="K18" t="n">
         <v>87.0904819324337</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 19.676x + -7682.685</t>
-        </is>
+      <c r="W18" t="n">
+        <v>19.67560283967531</v>
       </c>
       <c r="X18" t="n">
         <v>-7682.684802412933</v>
@@ -7144,7 +6924,7 @@
         <v>352.8422565355276</v>
       </c>
       <c r="Z18" t="n">
-        <v>137.09</v>
+        <v>224647548.3459699</v>
       </c>
       <c r="AA18" t="n">
         <v>7.697054488548521e-07</v>
@@ -7184,10 +6964,8 @@
       <c r="K19" t="n">
         <v>87.12274139930787</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 19.897x + -7687.783</t>
-        </is>
+      <c r="W19" t="n">
+        <v>19.89658084902466</v>
       </c>
       <c r="X19" t="n">
         <v>-7687.78264173453</v>
@@ -7196,7 +6974,7 @@
         <v>349.6816558741185</v>
       </c>
       <c r="Z19" t="n">
-        <v>134.0170000000001</v>
+        <v>143577996.6829306</v>
       </c>
       <c r="AA19" t="n">
         <v>7.596315165932298e-07</v>
@@ -7236,10 +7014,8 @@
       <c r="K20" t="n">
         <v>87.14911157335852</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 20.081x + -7681.191</t>
-        </is>
+      <c r="W20" t="n">
+        <v>20.0809287786944</v>
       </c>
       <c r="X20" t="n">
         <v>-7681.19113117973</v>
@@ -7248,7 +7024,7 @@
         <v>346.5167564290449</v>
       </c>
       <c r="Z20" t="n">
-        <v>132.952</v>
+        <v>378870519.4103824</v>
       </c>
       <c r="AA20" t="n">
         <v>7.51514431538005e-07</v>
@@ -7288,10 +7064,8 @@
       <c r="K21" t="n">
         <v>87.22916975012306</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 20.662x + -7841.170</t>
-        </is>
+      <c r="W21" t="n">
+        <v>20.66207652526992</v>
       </c>
       <c r="X21" t="n">
         <v>-7841.170060151584</v>
@@ -7300,7 +7074,7 @@
         <v>343.3036977339311</v>
       </c>
       <c r="Z21" t="n">
-        <v>131.369</v>
+        <v>187752679.7979519</v>
       </c>
       <c r="AA21" t="n">
         <v>7.447306624467331e-07</v>
@@ -7340,10 +7114,8 @@
       <c r="K22" t="n">
         <v>87.21428760940691</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 20.552x + -7703.352</t>
-        </is>
+      <c r="W22" t="n">
+        <v>20.55152054250722</v>
       </c>
       <c r="X22" t="n">
         <v>-7703.352265908799</v>
@@ -7352,7 +7124,7 @@
         <v>340.0849493883837</v>
       </c>
       <c r="Z22" t="n">
-        <v>129.769</v>
+        <v>743855828.3581824</v>
       </c>
       <c r="AA22" t="n">
         <v>7.359385478192486e-07</v>
@@ -7478,12 +7250,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -7538,10 +7310,8 @@
       <c r="K2" t="n">
         <v>84.13590972262895</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 9.736x + -4706.862</t>
-        </is>
+      <c r="W2" t="n">
+        <v>9.736477148276787</v>
       </c>
       <c r="X2" t="n">
         <v>-4706.862100501113</v>
@@ -7550,7 +7320,7 @@
         <v>409.5966677084947</v>
       </c>
       <c r="Z2" t="n">
-        <v>276.889</v>
+        <v>23643246.47042691</v>
       </c>
       <c r="AA2" t="n">
         <v>1.680464557764971e-06</v>
@@ -7590,10 +7360,8 @@
       <c r="K3" t="n">
         <v>85.06619720273187</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 11.584x + -4976.356</t>
-        </is>
+      <c r="W3" t="n">
+        <v>11.58418635750227</v>
       </c>
       <c r="X3" t="n">
         <v>-4976.356265492807</v>
@@ -7602,7 +7370,7 @@
         <v>387.9620306346272</v>
       </c>
       <c r="Z3" t="n">
-        <v>229.763</v>
+        <v>425516878.9159348</v>
       </c>
       <c r="AA3" t="n">
         <v>1.17313974285562e-06</v>
@@ -7642,10 +7410,8 @@
       <c r="K4" t="n">
         <v>85.58516677937202</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 12.952x + -5411.810</t>
-        </is>
+      <c r="W4" t="n">
+        <v>12.95232212560322</v>
       </c>
       <c r="X4" t="n">
         <v>-5411.809530377352</v>
@@ -7654,7 +7420,7 @@
         <v>380.4854366236969</v>
       </c>
       <c r="Z4" t="n">
-        <v>209.499</v>
+        <v>156286969.7261375</v>
       </c>
       <c r="AA4" t="n">
         <v>1.042702286983623e-06</v>
@@ -7694,10 +7460,8 @@
       <c r="K5" t="n">
         <v>85.99007229705575</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 14.265x + -5882.446</t>
-        </is>
+      <c r="W5" t="n">
+        <v>14.26514549216907</v>
       </c>
       <c r="X5" t="n">
         <v>-5882.445877498227</v>
@@ -7706,7 +7470,7 @@
         <v>375.3988591102163</v>
       </c>
       <c r="Z5" t="n">
-        <v>194.066</v>
+        <v>411004768.3896478</v>
       </c>
       <c r="AA5" t="n">
         <v>9.667632009195438e-07</v>
@@ -7746,10 +7510,8 @@
       <c r="K6" t="n">
         <v>86.08654354099457</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 14.618x + -5912.551</t>
-        </is>
+      <c r="W6" t="n">
+        <v>14.61793493990395</v>
       </c>
       <c r="X6" t="n">
         <v>-5912.550917972069</v>
@@ -7758,7 +7520,7 @@
         <v>370.5521640097273</v>
       </c>
       <c r="Z6" t="n">
-        <v>187.0000000000001</v>
+        <v>252678220.7777854</v>
       </c>
       <c r="AA6" t="n">
         <v>9.154067010114607e-07</v>
@@ -7798,10 +7560,8 @@
       <c r="K7" t="n">
         <v>86.33257021576475</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 15.602x + -6235.442</t>
-        </is>
+      <c r="W7" t="n">
+        <v>15.60152813550097</v>
       </c>
       <c r="X7" t="n">
         <v>-6235.442365587123</v>
@@ -7810,7 +7570,7 @@
         <v>365.6591788806057</v>
       </c>
       <c r="Z7" t="n">
-        <v>178.0450000000001</v>
+        <v>199763291.0778566</v>
       </c>
       <c r="AA7" t="n">
         <v>8.743835325129439e-07</v>
@@ -7850,10 +7610,8 @@
       <c r="K8" t="n">
         <v>86.34633725051124</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 15.660x + -6135.529</t>
-        </is>
+      <c r="W8" t="n">
+        <v>15.66047541250164</v>
       </c>
       <c r="X8" t="n">
         <v>-6135.528995056597</v>
@@ -7862,7 +7620,7 @@
         <v>360.6028353008273</v>
       </c>
       <c r="Z8" t="n">
-        <v>173.8440000000001</v>
+        <v>393828248.638447</v>
       </c>
       <c r="AA8" t="n">
         <v>8.417608574416963e-07</v>
@@ -7902,10 +7660,8 @@
       <c r="K9" t="n">
         <v>86.62592367176711</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 16.962x + -6578.014</t>
-        </is>
+      <c r="W9" t="n">
+        <v>16.96154055982626</v>
       </c>
       <c r="X9" t="n">
         <v>-6578.014354393819</v>
@@ -7914,7 +7670,7 @@
         <v>355.5571271536988</v>
       </c>
       <c r="Z9" t="n">
-        <v>165.977</v>
+        <v>291080314.3059894</v>
       </c>
       <c r="AA9" t="n">
         <v>8.130776909525363e-07</v>
@@ -7954,10 +7710,8 @@
       <c r="K10" t="n">
         <v>86.60634163310644</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 16.863x + -6410.810</t>
-        </is>
+      <c r="W10" t="n">
+        <v>16.8634420269123</v>
       </c>
       <c r="X10" t="n">
         <v>-6410.809512081318</v>
@@ -7966,7 +7720,7 @@
         <v>350.7256056046506</v>
       </c>
       <c r="Z10" t="n">
-        <v>162.939</v>
+        <v>202197978.6934312</v>
       </c>
       <c r="AA10" t="n">
         <v>7.900417733723573e-07</v>
@@ -8006,10 +7760,8 @@
       <c r="K11" t="n">
         <v>86.73447448770771</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 17.527x + -6576.717</t>
-        </is>
+      <c r="W11" t="n">
+        <v>17.52665144331503</v>
       </c>
       <c r="X11" t="n">
         <v>-6576.716637615972</v>
@@ -8018,7 +7770,7 @@
         <v>346.2620188885043</v>
       </c>
       <c r="Z11" t="n">
-        <v>158.1829999999999</v>
+        <v>283062746.1524704</v>
       </c>
       <c r="AA11" t="n">
         <v>7.698221397174921e-07</v>
@@ -8144,12 +7896,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -8204,10 +7956,8 @@
       <c r="K2" t="n">
         <v>85.78537421927085</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 13.570x + -6843.162</t>
-        </is>
+      <c r="W2" t="n">
+        <v>13.56998315772325</v>
       </c>
       <c r="X2" t="n">
         <v>-6843.161697481773</v>
@@ -8216,7 +7966,7 @@
         <v>438.3739120010454</v>
       </c>
       <c r="Z2" t="n">
-        <v>202.537</v>
+        <v>37313480.39081773</v>
       </c>
       <c r="AA2" t="n">
         <v>1.266813073883723e-06</v>
@@ -8256,10 +8006,8 @@
       <c r="K3" t="n">
         <v>86.18804292050878</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 15.008x + -7204.231</t>
-        </is>
+      <c r="W3" t="n">
+        <v>15.0083579993464</v>
       </c>
       <c r="X3" t="n">
         <v>-7204.231455318031</v>
@@ -8268,7 +8016,7 @@
         <v>427.9137340466133</v>
       </c>
       <c r="Z3" t="n">
-        <v>178.765</v>
+        <v>62432317.69983397</v>
       </c>
       <c r="AA3" t="n">
         <v>1.068721946864941e-06</v>
@@ -8308,10 +8056,8 @@
       <c r="K4" t="n">
         <v>86.57986956023579</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 16.733x + -7940.519</t>
-        </is>
+      <c r="W4" t="n">
+        <v>16.73261071831124</v>
       </c>
       <c r="X4" t="n">
         <v>-7940.519382880433</v>
@@ -8320,7 +8066,7 @@
         <v>422.7380480047251</v>
       </c>
       <c r="Z4" t="n">
-        <v>164.764</v>
+        <v>191939620.4062985</v>
       </c>
       <c r="AA4" t="n">
         <v>9.979548136303341e-07</v>
@@ -8360,10 +8106,8 @@
       <c r="K5" t="n">
         <v>86.74344256078949</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 17.575x + -8239.343</t>
-        </is>
+      <c r="W5" t="n">
+        <v>17.57502176229121</v>
       </c>
       <c r="X5" t="n">
         <v>-8239.342518949676</v>
@@ -8372,7 +8116,7 @@
         <v>418.2600864407751</v>
       </c>
       <c r="Z5" t="n">
-        <v>157.039</v>
+        <v>172998642.9858067</v>
       </c>
       <c r="AA5" t="n">
         <v>9.531497859256004e-07</v>
@@ -8412,10 +8156,8 @@
       <c r="K6" t="n">
         <v>86.6698738062922</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 17.186x + -7911.982</t>
-        </is>
+      <c r="W6" t="n">
+        <v>17.18590952855711</v>
       </c>
       <c r="X6" t="n">
         <v>-7911.982102012559</v>
@@ -8424,7 +8166,7 @@
         <v>413.8114836614133</v>
       </c>
       <c r="Z6" t="n">
-        <v>154.919</v>
+        <v>340940715.5667116</v>
       </c>
       <c r="AA6" t="n">
         <v>9.194333412358749e-07</v>
@@ -8464,10 +8206,8 @@
       <c r="K7" t="n">
         <v>86.75137463566472</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 17.618x + -8009.400</t>
-        </is>
+      <c r="W7" t="n">
+        <v>17.61802663241954</v>
       </c>
       <c r="X7" t="n">
         <v>-8009.399682345235</v>
@@ -8476,7 +8216,7 @@
         <v>409.4028202701477</v>
       </c>
       <c r="Z7" t="n">
-        <v>150.36</v>
+        <v>449156467.7310114</v>
       </c>
       <c r="AA7" t="n">
         <v>8.916486933032104e-07</v>
@@ -8516,10 +8256,8 @@
       <c r="K8" t="n">
         <v>86.78347182229572</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.794x + -7983.603</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.79420940878632</v>
       </c>
       <c r="X8" t="n">
         <v>-7983.603048873175</v>
@@ -8528,7 +8266,7 @@
         <v>405.1666236450736</v>
       </c>
       <c r="Z8" t="n">
-        <v>146.357</v>
+        <v>170601388.8860681</v>
       </c>
       <c r="AA8" t="n">
         <v>8.676512223636543e-07</v>
@@ -8568,10 +8306,8 @@
       <c r="K9" t="n">
         <v>86.9922843357253</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 19.032x + -8475.388</t>
-        </is>
+      <c r="W9" t="n">
+        <v>19.03209833642563</v>
       </c>
       <c r="X9" t="n">
         <v>-8475.388206199019</v>
@@ -8580,7 +8316,7 @@
         <v>401.0661510930278</v>
       </c>
       <c r="Z9" t="n">
-        <v>140.483</v>
+        <v>110008698.7541743</v>
       </c>
       <c r="AA9" t="n">
         <v>8.46008907412597e-07</v>
@@ -8620,10 +8356,8 @@
       <c r="K10" t="n">
         <v>86.92996472219281</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 18.645x + -8181.955</t>
-        </is>
+      <c r="W10" t="n">
+        <v>18.64504174366195</v>
       </c>
       <c r="X10" t="n">
         <v>-8181.955223618737</v>
@@ -8632,7 +8366,7 @@
         <v>397.2817842955411</v>
       </c>
       <c r="Z10" t="n">
-        <v>139.574</v>
+        <v>163471712.7856244</v>
       </c>
       <c r="AA10" t="n">
         <v>8.290154829325843e-07</v>
@@ -8672,10 +8406,8 @@
       <c r="K11" t="n">
         <v>86.94504947383524</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.737x + -8129.735</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.73728335358576</v>
       </c>
       <c r="X11" t="n">
         <v>-8129.735377625187</v>
@@ -8684,7 +8416,7 @@
         <v>393.7836631431049</v>
       </c>
       <c r="Z11" t="n">
-        <v>138.184</v>
+        <v>215595680.5163926</v>
       </c>
       <c r="AA11" t="n">
         <v>8.139573087446793e-07</v>
@@ -8724,10 +8456,8 @@
       <c r="K12" t="n">
         <v>87.02624608748611</v>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>y = 19.250x + -8281.153</t>
-        </is>
+      <c r="W12" t="n">
+        <v>19.24985194861765</v>
       </c>
       <c r="X12" t="n">
         <v>-8281.152765069404</v>
@@ -8736,7 +8466,7 @@
         <v>390.4954805087149</v>
       </c>
       <c r="Z12" t="n">
-        <v>135.092</v>
+        <v>320826921.0744914</v>
       </c>
       <c r="AA12" t="n">
         <v>8.004479004707351e-07</v>
@@ -8776,10 +8506,8 @@
       <c r="K13" t="n">
         <v>87.09347352354551</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>y = 19.696x + -8401.525</t>
-        </is>
+      <c r="W13" t="n">
+        <v>19.69588912243694</v>
       </c>
       <c r="X13" t="n">
         <v>-8401.525297760061</v>
@@ -8788,7 +8516,7 @@
         <v>387.380963589799</v>
       </c>
       <c r="Z13" t="n">
-        <v>132.969</v>
+        <v>164579411.1256917</v>
       </c>
       <c r="AA13" t="n">
         <v>7.887622345882293e-07</v>
@@ -8828,10 +8556,8 @@
       <c r="K14" t="n">
         <v>87.18717141016353</v>
       </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>y = 20.353x + -8622.339</t>
-        </is>
+      <c r="W14" t="n">
+        <v>20.35308590966891</v>
       </c>
       <c r="X14" t="n">
         <v>-8622.338619069558</v>
@@ -8840,7 +8566,7 @@
         <v>384.3899998105983</v>
       </c>
       <c r="Z14" t="n">
-        <v>129.81</v>
+        <v>225588116.6271352</v>
       </c>
       <c r="AA14" t="n">
         <v>7.789540139398641e-07</v>
@@ -8880,10 +8606,8 @@
       <c r="K15" t="n">
         <v>87.15478327222786</v>
       </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>y = 20.121x + -8429.467</t>
-        </is>
+      <c r="W15" t="n">
+        <v>20.12102449232445</v>
       </c>
       <c r="X15" t="n">
         <v>-8429.467215093911</v>
@@ -8892,7 +8616,7 @@
         <v>381.4474402696158</v>
       </c>
       <c r="Z15" t="n">
-        <v>127.909</v>
+        <v>156640161.1475782</v>
       </c>
       <c r="AA15" t="n">
         <v>7.685070499554922e-07</v>
@@ -8932,10 +8656,8 @@
       <c r="K16" t="n">
         <v>87.28882799704577</v>
       </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>y = 21.117x + -8803.437</t>
-        </is>
+      <c r="W16" t="n">
+        <v>21.11743919611612</v>
       </c>
       <c r="X16" t="n">
         <v>-8803.436857199689</v>
@@ -8944,7 +8666,7 @@
         <v>378.5169579094972</v>
       </c>
       <c r="Z16" t="n">
-        <v>126.046</v>
+        <v>207228195.8585008</v>
       </c>
       <c r="AA16" t="n">
         <v>7.613762932077516e-07</v>
@@ -8984,10 +8706,8 @@
       <c r="K17" t="n">
         <v>87.00821877162034</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>y = 19.134x + -7837.111</t>
-        </is>
+      <c r="W17" t="n">
+        <v>19.1336505894647</v>
       </c>
       <c r="X17" t="n">
         <v>-7837.110899560415</v>
@@ -8996,7 +8716,7 @@
         <v>375.6856700409101</v>
       </c>
       <c r="Z17" t="n">
-        <v>127.987</v>
+        <v>256771806.4796622</v>
       </c>
       <c r="AA17" t="n">
         <v>7.534795476309633e-07</v>
@@ -9036,10 +8756,8 @@
       <c r="K18" t="n">
         <v>87.21952144430335</v>
       </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>y = 20.590x + -8408.380</t>
-        </is>
+      <c r="W18" t="n">
+        <v>20.59026668016892</v>
       </c>
       <c r="X18" t="n">
         <v>-8408.379533294215</v>
@@ -9048,7 +8766,7 @@
         <v>372.8719417514002</v>
       </c>
       <c r="Z18" t="n">
-        <v>124.0189999999999</v>
+        <v>407512057.3213127</v>
       </c>
       <c r="AA18" t="n">
         <v>7.456470208592552e-07</v>
@@ -9088,10 +8806,8 @@
       <c r="K19" t="n">
         <v>87.30897587273675</v>
       </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>y = 21.276x + -8633.112</t>
-        </is>
+      <c r="W19" t="n">
+        <v>21.27578223913298</v>
       </c>
       <c r="X19" t="n">
         <v>-8633.112353307812</v>
@@ -9100,7 +8816,7 @@
         <v>370.0935529022672</v>
       </c>
       <c r="Z19" t="n">
-        <v>122.1080000000001</v>
+        <v>202205481.6304045</v>
       </c>
       <c r="AA19" t="n">
         <v>7.381962876302981e-07</v>
@@ -9140,10 +8856,8 @@
       <c r="K20" t="n">
         <v>87.28953721596211</v>
       </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>y = 21.123x + -8490.746</t>
-        </is>
+      <c r="W20" t="n">
+        <v>21.12297303489289</v>
       </c>
       <c r="X20" t="n">
         <v>-8490.745996283242</v>
@@ -9152,7 +8866,7 @@
         <v>367.3231930948887</v>
       </c>
       <c r="Z20" t="n">
-        <v>121.873</v>
+        <v>125528326.2901103</v>
       </c>
       <c r="AA20" t="n">
         <v>7.326524191337869e-07</v>
@@ -9192,10 +8906,8 @@
       <c r="K21" t="n">
         <v>87.28350759337729</v>
       </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>y = 21.076x + -8394.225</t>
-        </is>
+      <c r="W21" t="n">
+        <v>21.07601763621516</v>
       </c>
       <c r="X21" t="n">
         <v>-8394.224795684553</v>
@@ -9204,7 +8916,7 @@
         <v>364.5510236595847</v>
       </c>
       <c r="Z21" t="n">
-        <v>120.841</v>
+        <v>199251243.4022189</v>
       </c>
       <c r="AA21" t="n">
         <v>7.259537778530464e-07</v>
@@ -9244,10 +8956,8 @@
       <c r="K22" t="n">
         <v>87.45211959884001</v>
       </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>y = 22.473x + -8914.660</t>
-        </is>
+      <c r="W22" t="n">
+        <v>22.47280027713964</v>
       </c>
       <c r="X22" t="n">
         <v>-8914.659985291592</v>
@@ -9256,7 +8966,7 @@
         <v>361.6981794960921</v>
       </c>
       <c r="Z22" t="n">
-        <v>117.864</v>
+        <v>218464713.8409812</v>
       </c>
       <c r="AA22" t="n">
         <v>7.201651642019925e-07</v>
@@ -9382,12 +9092,12 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Model</t>
+          <t>linear_eq_m</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>b</t>
+          <t>linear_eq_b</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -9442,10 +9152,8 @@
       <c r="K2" t="n">
         <v>84.41381906368633</v>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>y = 10.224x + -4547.682</t>
-        </is>
+      <c r="W2" t="n">
+        <v>10.22417985599863</v>
       </c>
       <c r="X2" t="n">
         <v>-4547.682375547115</v>
@@ -9454,7 +9162,7 @@
         <v>381.8066934807066</v>
       </c>
       <c r="Z2" t="n">
-        <v>275.068</v>
+        <v>384290012.9981383</v>
       </c>
       <c r="AA2" t="n">
         <v>1.245415063477581e-06</v>
@@ -9494,10 +9202,8 @@
       <c r="K3" t="n">
         <v>85.56221718859311</v>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>y = 12.885x + -5149.400</t>
-        </is>
+      <c r="W3" t="n">
+        <v>12.8850738157596</v>
       </c>
       <c r="X3" t="n">
         <v>-5149.39981701879</v>
@@ -9506,7 +9212,7 @@
         <v>361.0055892513041</v>
       </c>
       <c r="Z3" t="n">
-        <v>224.0400000000001</v>
+        <v>148254202.694783</v>
       </c>
       <c r="AA3" t="n">
         <v>9.575416816390405e-07</v>
@@ -9546,10 +9252,8 @@
       <c r="K4" t="n">
         <v>86.05377117096188</v>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>y = 14.496x + -5636.568</t>
-        </is>
+      <c r="W4" t="n">
+        <v>14.49615693941547</v>
       </c>
       <c r="X4" t="n">
         <v>-5636.568039942341</v>
@@ -9558,7 +9262,7 @@
         <v>354.0310504671017</v>
       </c>
       <c r="Z4" t="n">
-        <v>202.367</v>
+        <v>193539432.451957</v>
       </c>
       <c r="AA4" t="n">
         <v>8.694549085997285e-07</v>
@@ -9598,10 +9302,8 @@
       <c r="K5" t="n">
         <v>86.32404876641756</v>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>y = 15.565x + -5954.809</t>
-        </is>
+      <c r="W5" t="n">
+        <v>15.56526217967302</v>
       </c>
       <c r="X5" t="n">
         <v>-5954.809487507271</v>
@@ -9610,7 +9312,7 @@
         <v>349.329650444781</v>
       </c>
       <c r="Z5" t="n">
-        <v>188.856</v>
+        <v>193668420.6884376</v>
       </c>
       <c r="AA5" t="n">
         <v>8.201765853489458e-07</v>
@@ -9650,10 +9352,8 @@
       <c r="K6" t="n">
         <v>86.43077153242696</v>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>y = 16.032x + -6018.307</t>
-        </is>
+      <c r="W6" t="n">
+        <v>16.03193689452932</v>
       </c>
       <c r="X6" t="n">
         <v>-6018.307491526186</v>
@@ -9662,7 +9362,7 @@
         <v>344.4445793016002</v>
       </c>
       <c r="Z6" t="n">
-        <v>180.988</v>
+        <v>195359165.8186222</v>
       </c>
       <c r="AA6" t="n">
         <v>7.845546070895618e-07</v>
@@ -9702,10 +9402,8 @@
       <c r="K7" t="n">
         <v>86.55080728929757</v>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>y = 16.591x + -6123.038</t>
-        </is>
+      <c r="W7" t="n">
+        <v>16.59128788962701</v>
       </c>
       <c r="X7" t="n">
         <v>-6123.038141008891</v>
@@ -9714,7 +9412,7 @@
         <v>339.5606496956183</v>
       </c>
       <c r="Z7" t="n">
-        <v>173.04</v>
+        <v>137165222.1105785</v>
       </c>
       <c r="AA7" t="n">
         <v>7.564184407878399e-07</v>
@@ -9754,10 +9452,8 @@
       <c r="K8" t="n">
         <v>86.75641427325557</v>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>y = 17.645x + -6434.767</t>
-        </is>
+      <c r="W8" t="n">
+        <v>17.64545889602354</v>
       </c>
       <c r="X8" t="n">
         <v>-6434.766853772477</v>
@@ -9766,7 +9462,7 @@
         <v>334.6334579109749</v>
       </c>
       <c r="Z8" t="n">
-        <v>167.181</v>
+        <v>182839622.5572596</v>
       </c>
       <c r="AA8" t="n">
         <v>7.361551241341882e-07</v>
@@ -9806,10 +9502,8 @@
       <c r="K9" t="n">
         <v>86.85473311335363</v>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>y = 18.198x + -6526.295</t>
-        </is>
+      <c r="W9" t="n">
+        <v>18.19820593688107</v>
       </c>
       <c r="X9" t="n">
         <v>-6526.29454549875</v>
@@ -9818,7 +9512,7 @@
         <v>329.9180126710327</v>
       </c>
       <c r="Z9" t="n">
-        <v>161.647</v>
+        <v>144333249.1458964</v>
       </c>
       <c r="AA9" t="n">
         <v>7.1652088650224e-07</v>
@@ -9858,10 +9552,8 @@
       <c r="K10" t="n">
         <v>87.01209275556037</v>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>y = 19.159x + -6790.271</t>
-        </is>
+      <c r="W10" t="n">
+        <v>19.15850352757258</v>
       </c>
       <c r="X10" t="n">
         <v>-6790.270708425777</v>
@@ -9870,7 +9562,7 @@
         <v>325.4370405855685</v>
       </c>
       <c r="Z10" t="n">
-        <v>156.297</v>
+        <v>177303080.3925255</v>
       </c>
       <c r="AA10" t="n">
         <v>7.016495281387601e-07</v>
@@ -9910,10 +9602,8 @@
       <c r="K11" t="n">
         <v>86.95363110797396</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>y = 18.790x + -6526.385</t>
-        </is>
+      <c r="W11" t="n">
+        <v>18.79016639086698</v>
       </c>
       <c r="X11" t="n">
         <v>-6526.385286717029</v>
@@ -9922,7 +9612,7 @@
         <v>321.2988222282801</v>
       </c>
       <c r="Z11" t="n">
-        <v>154.017</v>
+        <v>87504611.61801642</v>
       </c>
       <c r="AA11" t="n">
         <v>6.885139484362863e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
@@ -428,7 +428,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -559,7 +559,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-184.19</v>
@@ -609,7 +609,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-171.579</v>
@@ -659,7 +659,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-164.317</v>
@@ -709,7 +709,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-157.765</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-154.299</v>
@@ -809,7 +809,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-150.893</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-147.951</v>
@@ -909,7 +909,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-147.2149999999999</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-145.519</v>
@@ -1009,7 +1009,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-143.198</v>
@@ -1074,7 +1074,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -2270,7 +2270,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -3597,7 +3597,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-293.102</v>
@@ -3647,7 +3647,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-236.3339999999999</v>
@@ -3697,7 +3697,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-215.6709999999999</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-204.578</v>
@@ -3797,7 +3797,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-194.877</v>
@@ -3847,7 +3847,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-186.837</v>
@@ -3897,7 +3897,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-181.823</v>
@@ -3947,7 +3947,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-176.717</v>
@@ -3997,7 +3997,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-173.245</v>
@@ -4047,7 +4047,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-166.891</v>
@@ -4112,7 +4112,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5308,7 +5308,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-299.283</v>
@@ -5489,7 +5489,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-242.703</v>
@@ -5539,7 +5539,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-222.64</v>
@@ -5589,7 +5589,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-210.065</v>
@@ -5639,7 +5639,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-203.334</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-195.395</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-188.716</v>
@@ -5789,7 +5789,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-181.854</v>
@@ -5839,7 +5839,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-176.543</v>
@@ -5889,7 +5889,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-173.7449999999999</v>
@@ -5954,7 +5954,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7150,7 +7150,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -7281,7 +7281,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-276.889</v>
@@ -7331,7 +7331,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-229.763</v>
@@ -7381,7 +7381,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-209.499</v>
@@ -7431,7 +7431,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-194.066</v>
@@ -7481,7 +7481,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-187.0000000000001</v>
@@ -7531,7 +7531,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-178.0450000000001</v>
@@ -7581,7 +7581,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-173.8440000000001</v>
@@ -7631,7 +7631,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-165.977</v>
@@ -7681,7 +7681,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-162.939</v>
@@ -7731,7 +7731,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-158.1829999999999</v>
@@ -7796,7 +7796,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -8992,7 +8992,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>time(s)</t>
+          <t>time(mins)</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -9123,7 +9123,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="B2" t="n">
         <v>-275.068</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B3" t="n">
         <v>-224.0400000000001</v>
@@ -9223,7 +9223,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="B4" t="n">
         <v>-202.367</v>
@@ -9273,7 +9273,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B5" t="n">
         <v>-188.856</v>
@@ -9323,7 +9323,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>15</v>
+        <v>7.5</v>
       </c>
       <c r="B6" t="n">
         <v>-180.988</v>
@@ -9373,7 +9373,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B7" t="n">
         <v>-173.04</v>
@@ -9423,7 +9423,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>21</v>
+        <v>10.5</v>
       </c>
       <c r="B8" t="n">
         <v>-167.181</v>
@@ -9473,7 +9473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="B9" t="n">
         <v>-161.647</v>
@@ -9523,7 +9523,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>27</v>
+        <v>13.5</v>
       </c>
       <c r="B10" t="n">
         <v>-156.297</v>
@@ -9573,7 +9573,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="B11" t="n">
         <v>-154.017</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
@@ -562,7 +562,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-184.19</v>
+        <v>129.816</v>
       </c>
       <c r="D2" t="n">
         <v>4.11386e-07</v>
@@ -612,7 +612,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-171.579</v>
+        <v>121.697</v>
       </c>
       <c r="D3" t="n">
         <v>4.11095e-07</v>
@@ -662,7 +662,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-164.317</v>
+        <v>114.407</v>
       </c>
       <c r="D4" t="n">
         <v>4.11214e-07</v>
@@ -712,7 +712,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-157.765</v>
+        <v>110.61</v>
       </c>
       <c r="D5" t="n">
         <v>4.11614e-07</v>
@@ -762,7 +762,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-154.299</v>
+        <v>106.412</v>
       </c>
       <c r="D6" t="n">
         <v>4.12326e-07</v>
@@ -812,7 +812,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-150.893</v>
+        <v>102.859</v>
       </c>
       <c r="D7" t="n">
         <v>4.12857e-07</v>
@@ -862,7 +862,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-147.951</v>
+        <v>99.90499999999997</v>
       </c>
       <c r="D8" t="n">
         <v>4.13321e-07</v>
@@ -912,7 +912,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-147.2149999999999</v>
+        <v>94.87300000000005</v>
       </c>
       <c r="D9" t="n">
         <v>4.13835e-07</v>
@@ -962,7 +962,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-145.519</v>
+        <v>91.20000000000005</v>
       </c>
       <c r="D10" t="n">
         <v>4.14111e-07</v>
@@ -1012,7 +1012,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-143.198</v>
+        <v>88.26299999999998</v>
       </c>
       <c r="D11" t="n">
         <v>4.14408e-07</v>
@@ -1208,7 +1208,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-175.045</v>
+        <v>123.017</v>
       </c>
       <c r="D2" t="n">
         <v>4.45364e-07</v>
@@ -1258,7 +1258,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-156.492</v>
+        <v>106.605</v>
       </c>
       <c r="D3" t="n">
         <v>4.44371e-07</v>
@@ -1308,7 +1308,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-149.898</v>
+        <v>100.546</v>
       </c>
       <c r="D4" t="n">
         <v>4.43179e-07</v>
@@ -1358,7 +1358,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-146.881</v>
+        <v>96.899</v>
       </c>
       <c r="D5" t="n">
         <v>4.41995e-07</v>
@@ -1408,7 +1408,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-142.6010000000001</v>
+        <v>96.03699999999998</v>
       </c>
       <c r="D6" t="n">
         <v>4.40925e-07</v>
@@ -1458,7 +1458,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-140.2689999999999</v>
+        <v>93.70499999999998</v>
       </c>
       <c r="D7" t="n">
         <v>4.40216e-07</v>
@@ -1508,7 +1508,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-140.942</v>
+        <v>89.05399999999997</v>
       </c>
       <c r="D8" t="n">
         <v>4.39602e-07</v>
@@ -1558,7 +1558,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-136.867</v>
+        <v>88.11700000000002</v>
       </c>
       <c r="D9" t="n">
         <v>4.39295e-07</v>
@@ -1608,7 +1608,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-135.136</v>
+        <v>84.762</v>
       </c>
       <c r="D10" t="n">
         <v>4.38897e-07</v>
@@ -1658,7 +1658,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-133.176</v>
+        <v>83.26099999999997</v>
       </c>
       <c r="D11" t="n">
         <v>4.38463e-07</v>
@@ -1708,7 +1708,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-130.953</v>
+        <v>82.06399999999996</v>
       </c>
       <c r="D12" t="n">
         <v>4.38079e-07</v>
@@ -1758,7 +1758,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-131.1779999999999</v>
+        <v>78.935</v>
       </c>
       <c r="D13" t="n">
         <v>4.38024e-07</v>
@@ -1808,7 +1808,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-128.843</v>
+        <v>79.26299999999998</v>
       </c>
       <c r="D14" t="n">
         <v>4.3775e-07</v>
@@ -1858,7 +1858,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-124.3559999999999</v>
+        <v>79.89800000000002</v>
       </c>
       <c r="D15" t="n">
         <v>4.37654e-07</v>
@@ -1908,7 +1908,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-125.044</v>
+        <v>77.23200000000003</v>
       </c>
       <c r="D16" t="n">
         <v>4.3758e-07</v>
@@ -1958,7 +1958,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-124.75</v>
+        <v>75.50099999999998</v>
       </c>
       <c r="D17" t="n">
         <v>4.37357e-07</v>
@@ -2008,7 +2008,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-125.069</v>
+        <v>73.53300000000002</v>
       </c>
       <c r="D18" t="n">
         <v>4.37256e-07</v>
@@ -2058,7 +2058,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-121.879</v>
+        <v>73.10199999999998</v>
       </c>
       <c r="D19" t="n">
         <v>4.37343e-07</v>
@@ -2108,7 +2108,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-119.655</v>
+        <v>72.32600000000002</v>
       </c>
       <c r="D20" t="n">
         <v>4.37165e-07</v>
@@ -2158,7 +2158,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-119.123</v>
+        <v>71.55400000000003</v>
       </c>
       <c r="D21" t="n">
         <v>4.37066e-07</v>
@@ -2208,7 +2208,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-120.2</v>
+        <v>69.53000000000003</v>
       </c>
       <c r="D22" t="n">
         <v>4.36996e-07</v>
@@ -2404,7 +2404,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-196.03</v>
+        <v>129.108</v>
       </c>
       <c r="D2" t="n">
         <v>4.28239e-07</v>
@@ -2454,7 +2454,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-165.46</v>
+        <v>109.101</v>
       </c>
       <c r="D3" t="n">
         <v>4.26096e-07</v>
@@ -2504,7 +2504,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-156.611</v>
+        <v>103.232</v>
       </c>
       <c r="D4" t="n">
         <v>4.2453e-07</v>
@@ -2554,7 +2554,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-146.769</v>
+        <v>103.322</v>
       </c>
       <c r="D5" t="n">
         <v>4.23514e-07</v>
@@ -2604,7 +2604,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-145.914</v>
+        <v>97.82499999999999</v>
       </c>
       <c r="D6" t="n">
         <v>4.22845e-07</v>
@@ -2654,7 +2654,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-140.85</v>
+        <v>96.84500000000003</v>
       </c>
       <c r="D7" t="n">
         <v>4.22367e-07</v>
@@ -2704,7 +2704,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-138.72</v>
+        <v>93.31200000000001</v>
       </c>
       <c r="D8" t="n">
         <v>4.2209e-07</v>
@@ -2754,7 +2754,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-138.199</v>
+        <v>90.22899999999998</v>
       </c>
       <c r="D9" t="n">
         <v>4.22084e-07</v>
@@ -2804,7 +2804,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-135.258</v>
+        <v>88.00999999999999</v>
       </c>
       <c r="D10" t="n">
         <v>4.21893e-07</v>
@@ -2854,7 +2854,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-131.565</v>
+        <v>87.58699999999999</v>
       </c>
       <c r="D11" t="n">
         <v>4.21756e-07</v>
@@ -2904,7 +2904,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-132.447</v>
+        <v>84.745</v>
       </c>
       <c r="D12" t="n">
         <v>4.21658e-07</v>
@@ -2954,7 +2954,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-131.004</v>
+        <v>83.46300000000002</v>
       </c>
       <c r="D13" t="n">
         <v>4.21741e-07</v>
@@ -3004,7 +3004,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-129.723</v>
+        <v>81.57900000000001</v>
       </c>
       <c r="D14" t="n">
         <v>4.21776e-07</v>
@@ -3054,7 +3054,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-127.657</v>
+        <v>79.45000000000005</v>
       </c>
       <c r="D15" t="n">
         <v>4.21873e-07</v>
@@ -3104,7 +3104,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-126.3220000000001</v>
+        <v>78.75599999999997</v>
       </c>
       <c r="D16" t="n">
         <v>4.21857e-07</v>
@@ -3154,7 +3154,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-127.994</v>
+        <v>76.27600000000001</v>
       </c>
       <c r="D17" t="n">
         <v>4.21774e-07</v>
@@ -3204,7 +3204,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-125.971</v>
+        <v>75.935</v>
       </c>
       <c r="D18" t="n">
         <v>4.21905e-07</v>
@@ -3254,7 +3254,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-126.248</v>
+        <v>74.28999999999996</v>
       </c>
       <c r="D19" t="n">
         <v>4.22086e-07</v>
@@ -3304,7 +3304,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-125.181</v>
+        <v>72.767</v>
       </c>
       <c r="D20" t="n">
         <v>4.22095e-07</v>
@@ -3354,7 +3354,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-124.092</v>
+        <v>71.50700000000001</v>
       </c>
       <c r="D21" t="n">
         <v>4.22186e-07</v>
@@ -3404,7 +3404,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-121.503</v>
+        <v>71.55099999999999</v>
       </c>
       <c r="D22" t="n">
         <v>4.22288e-07</v>
@@ -3600,7 +3600,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-293.102</v>
+        <v>124.143</v>
       </c>
       <c r="D2" t="n">
         <v>4.58367e-07</v>
@@ -3650,7 +3650,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-236.3339999999999</v>
+        <v>84.48000000000002</v>
       </c>
       <c r="D3" t="n">
         <v>4.64888e-07</v>
@@ -3700,7 +3700,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-215.6709999999999</v>
+        <v>75.40500000000003</v>
       </c>
       <c r="D4" t="n">
         <v>4.62057e-07</v>
@@ -3750,7 +3750,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-204.578</v>
+        <v>70.87700000000001</v>
       </c>
       <c r="D5" t="n">
         <v>4.58705e-07</v>
@@ -3800,7 +3800,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-194.877</v>
+        <v>69.327</v>
       </c>
       <c r="D6" t="n">
         <v>4.5565e-07</v>
@@ -3850,7 +3850,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-186.837</v>
+        <v>67.33199999999999</v>
       </c>
       <c r="D7" t="n">
         <v>4.53261e-07</v>
@@ -3900,7 +3900,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-181.823</v>
+        <v>64.70999999999998</v>
       </c>
       <c r="D8" t="n">
         <v>4.51167e-07</v>
@@ -3950,7 +3950,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-176.717</v>
+        <v>62.04999999999995</v>
       </c>
       <c r="D9" t="n">
         <v>4.49551e-07</v>
@@ -4000,7 +4000,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-173.245</v>
+        <v>60.31</v>
       </c>
       <c r="D10" t="n">
         <v>4.47803e-07</v>
@@ -4050,7 +4050,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-166.891</v>
+        <v>59.291</v>
       </c>
       <c r="D11" t="n">
         <v>4.46535e-07</v>
@@ -4246,7 +4246,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-236.588</v>
+        <v>126.633</v>
       </c>
       <c r="D2" t="n">
         <v>4.62212e-07</v>
@@ -4296,7 +4296,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-199.874</v>
+        <v>109.67</v>
       </c>
       <c r="D3" t="n">
         <v>4.59991e-07</v>
@@ -4346,7 +4346,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-186.5889999999999</v>
+        <v>102.344</v>
       </c>
       <c r="D4" t="n">
         <v>4.57266e-07</v>
@@ -4396,7 +4396,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-176.016</v>
+        <v>101.124</v>
       </c>
       <c r="D5" t="n">
         <v>4.54742e-07</v>
@@ -4446,7 +4446,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-170.3299999999999</v>
+        <v>97.53200000000004</v>
       </c>
       <c r="D6" t="n">
         <v>4.52903e-07</v>
@@ -4496,7 +4496,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-164.851</v>
+        <v>94.90600000000001</v>
       </c>
       <c r="D7" t="n">
         <v>4.51503e-07</v>
@@ -4546,7 +4546,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-159.932</v>
+        <v>93.04000000000002</v>
       </c>
       <c r="D8" t="n">
         <v>4.50016e-07</v>
@@ -4596,7 +4596,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-156.7839999999999</v>
+        <v>90.173</v>
       </c>
       <c r="D9" t="n">
         <v>4.48717e-07</v>
@@ -4646,7 +4646,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-151.453</v>
+        <v>87.74800000000005</v>
       </c>
       <c r="D10" t="n">
         <v>4.47817e-07</v>
@@ -4696,7 +4696,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-148.8439999999999</v>
+        <v>86.12</v>
       </c>
       <c r="D11" t="n">
         <v>4.46873e-07</v>
@@ -4746,7 +4746,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-144.881</v>
+        <v>85.72300000000001</v>
       </c>
       <c r="D12" t="n">
         <v>4.45936e-07</v>
@@ -4796,7 +4796,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-144.603</v>
+        <v>82.25900000000001</v>
       </c>
       <c r="D13" t="n">
         <v>4.45247e-07</v>
@@ -4846,7 +4846,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-142.214</v>
+        <v>82.39699999999999</v>
       </c>
       <c r="D14" t="n">
         <v>4.44504e-07</v>
@@ -4896,7 +4896,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-139.795</v>
+        <v>80.50900000000001</v>
       </c>
       <c r="D15" t="n">
         <v>4.43868e-07</v>
@@ -4946,7 +4946,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-137.646</v>
+        <v>79.62600000000003</v>
       </c>
       <c r="D16" t="n">
         <v>4.4356e-07</v>
@@ -4996,7 +4996,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-136.5240000000001</v>
+        <v>77.30199999999996</v>
       </c>
       <c r="D17" t="n">
         <v>4.42902e-07</v>
@@ -5046,7 +5046,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-133.609</v>
+        <v>76.89300000000003</v>
       </c>
       <c r="D18" t="n">
         <v>4.42504e-07</v>
@@ -5096,7 +5096,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-133.562</v>
+        <v>75.31400000000002</v>
       </c>
       <c r="D19" t="n">
         <v>4.42194e-07</v>
@@ -5146,7 +5146,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-130.462</v>
+        <v>75.01399999999995</v>
       </c>
       <c r="D20" t="n">
         <v>4.41998e-07</v>
@@ -5196,7 +5196,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-129.615</v>
+        <v>73.20400000000001</v>
       </c>
       <c r="D21" t="n">
         <v>4.41749e-07</v>
@@ -5246,7 +5246,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-128.767</v>
+        <v>71.86399999999998</v>
       </c>
       <c r="D22" t="n">
         <v>4.4155e-07</v>
@@ -5442,7 +5442,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-299.283</v>
+        <v>121.092</v>
       </c>
       <c r="D2" t="n">
         <v>4.8887e-07</v>
@@ -5492,7 +5492,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-242.703</v>
+        <v>83.94799999999998</v>
       </c>
       <c r="D3" t="n">
         <v>4.96942e-07</v>
@@ -5542,7 +5542,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-222.64</v>
+        <v>76.423</v>
       </c>
       <c r="D4" t="n">
         <v>4.93326e-07</v>
@@ -5592,7 +5592,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-210.065</v>
+        <v>73.19899999999996</v>
       </c>
       <c r="D5" t="n">
         <v>4.891439999999999e-07</v>
@@ -5642,7 +5642,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-203.334</v>
+        <v>68.11800000000005</v>
       </c>
       <c r="D6" t="n">
         <v>4.85406e-07</v>
@@ -5692,7 +5692,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-195.395</v>
+        <v>66.875</v>
       </c>
       <c r="D7" t="n">
         <v>4.8182e-07</v>
@@ -5742,7 +5742,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-188.716</v>
+        <v>64.42599999999999</v>
       </c>
       <c r="D8" t="n">
         <v>4.78968e-07</v>
@@ -5792,7 +5792,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-181.854</v>
+        <v>62.57499999999999</v>
       </c>
       <c r="D9" t="n">
         <v>4.76339e-07</v>
@@ -5842,7 +5842,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-176.543</v>
+        <v>60.048</v>
       </c>
       <c r="D10" t="n">
         <v>4.73825e-07</v>
@@ -5892,7 +5892,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-173.7449999999999</v>
+        <v>57.11200000000002</v>
       </c>
       <c r="D11" t="n">
         <v>4.71744e-07</v>
@@ -6088,7 +6088,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-234.4999999999999</v>
+        <v>123.676</v>
       </c>
       <c r="D2" t="n">
         <v>4.84296e-07</v>
@@ -6138,7 +6138,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-202.218</v>
+        <v>107.541</v>
       </c>
       <c r="D3" t="n">
         <v>4.81725e-07</v>
@@ -6188,7 +6188,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-188.469</v>
+        <v>103.253</v>
       </c>
       <c r="D4" t="n">
         <v>4.78223e-07</v>
@@ -6238,7 +6238,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-181.8340000000001</v>
+        <v>98.27499999999998</v>
       </c>
       <c r="D5" t="n">
         <v>4.75225e-07</v>
@@ -6288,7 +6288,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-172.51</v>
+        <v>98.31</v>
       </c>
       <c r="D6" t="n">
         <v>4.7266e-07</v>
@@ -6338,7 +6338,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-168.513</v>
+        <v>94.524</v>
       </c>
       <c r="D7" t="n">
         <v>4.7051e-07</v>
@@ -6388,7 +6388,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-164.125</v>
+        <v>91.20700000000005</v>
       </c>
       <c r="D8" t="n">
         <v>4.68669e-07</v>
@@ -6438,7 +6438,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-159.772</v>
+        <v>88.71699999999998</v>
       </c>
       <c r="D9" t="n">
         <v>4.66931e-07</v>
@@ -6488,7 +6488,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-155.4420000000001</v>
+        <v>86.673</v>
       </c>
       <c r="D10" t="n">
         <v>4.65709e-07</v>
@@ -6538,7 +6538,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-151.945</v>
+        <v>84.81299999999999</v>
       </c>
       <c r="D11" t="n">
         <v>4.64191e-07</v>
@@ -6588,7 +6588,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-150.413</v>
+        <v>82.91899999999998</v>
       </c>
       <c r="D12" t="n">
         <v>4.63033e-07</v>
@@ -6638,7 +6638,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-145.576</v>
+        <v>81.91500000000002</v>
       </c>
       <c r="D13" t="n">
         <v>4.62104e-07</v>
@@ -6688,7 +6688,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-144.2629999999999</v>
+        <v>78.851</v>
       </c>
       <c r="D14" t="n">
         <v>4.61169e-07</v>
@@ -6738,7 +6738,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-142.094</v>
+        <v>77.49299999999999</v>
       </c>
       <c r="D15" t="n">
         <v>4.6039e-07</v>
@@ -6788,7 +6788,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-139.393</v>
+        <v>76.70600000000002</v>
       </c>
       <c r="D16" t="n">
         <v>4.59584e-07</v>
@@ -6838,7 +6838,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-137.705</v>
+        <v>75.99000000000001</v>
       </c>
       <c r="D17" t="n">
         <v>4.5913e-07</v>
@@ -6888,7 +6888,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-137.09</v>
+        <v>74.08100000000002</v>
       </c>
       <c r="D18" t="n">
         <v>4.58504e-07</v>
@@ -6938,7 +6938,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-134.0170000000001</v>
+        <v>72.64999999999998</v>
       </c>
       <c r="D19" t="n">
         <v>4.5813e-07</v>
@@ -6988,7 +6988,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-132.952</v>
+        <v>71.572</v>
       </c>
       <c r="D20" t="n">
         <v>4.5765e-07</v>
@@ -7038,7 +7038,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-131.369</v>
+        <v>70.94</v>
       </c>
       <c r="D21" t="n">
         <v>4.57344e-07</v>
@@ -7088,7 +7088,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-129.769</v>
+        <v>68.702</v>
       </c>
       <c r="D22" t="n">
         <v>4.57011e-07</v>
@@ -7284,7 +7284,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-276.889</v>
+        <v>124.192</v>
       </c>
       <c r="D2" t="n">
         <v>5.06168e-07</v>
@@ -7334,7 +7334,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-229.763</v>
+        <v>80.36900000000003</v>
       </c>
       <c r="D3" t="n">
         <v>5.05983e-07</v>
@@ -7384,7 +7384,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-209.499</v>
+        <v>72.76999999999998</v>
       </c>
       <c r="D4" t="n">
         <v>4.98707e-07</v>
@@ -7434,7 +7434,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-194.066</v>
+        <v>71.12</v>
       </c>
       <c r="D5" t="n">
         <v>4.91899e-07</v>
@@ -7484,7 +7484,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-187.0000000000001</v>
+        <v>66.69199999999995</v>
       </c>
       <c r="D6" t="n">
         <v>4.86304e-07</v>
@@ -7534,7 +7534,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-178.0450000000001</v>
+        <v>65.197</v>
       </c>
       <c r="D7" t="n">
         <v>4.81797e-07</v>
@@ -7584,7 +7584,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-173.8440000000001</v>
+        <v>61.40999999999997</v>
       </c>
       <c r="D8" t="n">
         <v>4.7786e-07</v>
@@ -7634,7 +7634,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-165.977</v>
+        <v>61.18799999999999</v>
       </c>
       <c r="D9" t="n">
         <v>4.74438e-07</v>
@@ -7684,7 +7684,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-162.939</v>
+        <v>57.14799999999997</v>
       </c>
       <c r="D10" t="n">
         <v>4.71805e-07</v>
@@ -7734,7 +7734,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-158.1829999999999</v>
+        <v>55.91800000000001</v>
       </c>
       <c r="D11" t="n">
         <v>4.69256e-07</v>
@@ -7930,7 +7930,7 @@
         <v>1.428571428571429</v>
       </c>
       <c r="B2" t="n">
-        <v>-202.537</v>
+        <v>121.722</v>
       </c>
       <c r="D2" t="n">
         <v>4.76632e-07</v>
@@ -7980,7 +7980,7 @@
         <v>2.857142857142857</v>
       </c>
       <c r="B3" t="n">
-        <v>-178.765</v>
+        <v>102.705</v>
       </c>
       <c r="D3" t="n">
         <v>4.74076e-07</v>
@@ -8030,7 +8030,7 @@
         <v>4.285714285714286</v>
       </c>
       <c r="B4" t="n">
-        <v>-164.764</v>
+        <v>100.697</v>
       </c>
       <c r="D4" t="n">
         <v>4.70895e-07</v>
@@ -8080,7 +8080,7 @@
         <v>5.714285714285714</v>
       </c>
       <c r="B5" t="n">
-        <v>-157.039</v>
+        <v>97.654</v>
       </c>
       <c r="D5" t="n">
         <v>4.68432e-07</v>
@@ -8130,7 +8130,7 @@
         <v>7.142857142857143</v>
       </c>
       <c r="B6" t="n">
-        <v>-154.919</v>
+        <v>92.14100000000002</v>
       </c>
       <c r="D6" t="n">
         <v>4.66149e-07</v>
@@ -8180,7 +8180,7 @@
         <v>8.571428571428571</v>
       </c>
       <c r="B7" t="n">
-        <v>-150.36</v>
+        <v>89.60300000000001</v>
       </c>
       <c r="D7" t="n">
         <v>4.64535e-07</v>
@@ -8230,7 +8230,7 @@
         <v>10</v>
       </c>
       <c r="B8" t="n">
-        <v>-146.357</v>
+        <v>87.36600000000004</v>
       </c>
       <c r="D8" t="n">
         <v>4.63123e-07</v>
@@ -8280,7 +8280,7 @@
         <v>11.42857142857143</v>
       </c>
       <c r="B9" t="n">
-        <v>-140.483</v>
+        <v>86.68400000000003</v>
       </c>
       <c r="D9" t="n">
         <v>4.61892e-07</v>
@@ -8330,7 +8330,7 @@
         <v>12.85714285714286</v>
       </c>
       <c r="B10" t="n">
-        <v>-139.574</v>
+        <v>82.69300000000004</v>
       </c>
       <c r="D10" t="n">
         <v>4.60773e-07</v>
@@ -8380,7 +8380,7 @@
         <v>14.28571428571429</v>
       </c>
       <c r="B11" t="n">
-        <v>-138.184</v>
+        <v>80.03100000000001</v>
       </c>
       <c r="D11" t="n">
         <v>4.59828e-07</v>
@@ -8430,7 +8430,7 @@
         <v>15.71428571428572</v>
       </c>
       <c r="B12" t="n">
-        <v>-135.092</v>
+        <v>78.76499999999999</v>
       </c>
       <c r="D12" t="n">
         <v>4.58991e-07</v>
@@ -8480,7 +8480,7 @@
         <v>17.14285714285714</v>
       </c>
       <c r="B13" t="n">
-        <v>-132.969</v>
+        <v>77.476</v>
       </c>
       <c r="D13" t="n">
         <v>4.58185e-07</v>
@@ -8530,7 +8530,7 @@
         <v>18.57142857142857</v>
       </c>
       <c r="B14" t="n">
-        <v>-129.81</v>
+        <v>77.07600000000002</v>
       </c>
       <c r="D14" t="n">
         <v>4.57753e-07</v>
@@ -8580,7 +8580,7 @@
         <v>20</v>
       </c>
       <c r="B15" t="n">
-        <v>-127.909</v>
+        <v>74.57299999999998</v>
       </c>
       <c r="D15" t="n">
         <v>4.5734e-07</v>
@@ -8630,7 +8630,7 @@
         <v>21.42857142857143</v>
       </c>
       <c r="B16" t="n">
-        <v>-126.046</v>
+        <v>74.93699999999995</v>
       </c>
       <c r="D16" t="n">
         <v>4.56802e-07</v>
@@ -8680,7 +8680,7 @@
         <v>22.85714285714286</v>
       </c>
       <c r="B17" t="n">
-        <v>-127.987</v>
+        <v>70.38400000000001</v>
       </c>
       <c r="D17" t="n">
         <v>4.56379e-07</v>
@@ -8730,7 +8730,7 @@
         <v>24.28571428571428</v>
       </c>
       <c r="B18" t="n">
-        <v>-124.0189999999999</v>
+        <v>71.27600000000001</v>
       </c>
       <c r="D18" t="n">
         <v>4.55973e-07</v>
@@ -8780,7 +8780,7 @@
         <v>25.71428571428572</v>
       </c>
       <c r="B19" t="n">
-        <v>-122.1080000000001</v>
+        <v>70.56200000000001</v>
       </c>
       <c r="D19" t="n">
         <v>4.55624e-07</v>
@@ -8830,7 +8830,7 @@
         <v>27.14285714285714</v>
       </c>
       <c r="B20" t="n">
-        <v>-121.873</v>
+        <v>69.02999999999997</v>
       </c>
       <c r="D20" t="n">
         <v>4.55382e-07</v>
@@ -8880,7 +8880,7 @@
         <v>28.57142857142857</v>
       </c>
       <c r="B21" t="n">
-        <v>-120.841</v>
+        <v>67.68700000000001</v>
       </c>
       <c r="D21" t="n">
         <v>4.55044e-07</v>
@@ -8930,7 +8930,7 @@
         <v>30</v>
       </c>
       <c r="B22" t="n">
-        <v>-117.864</v>
+        <v>67.94100000000003</v>
       </c>
       <c r="D22" t="n">
         <v>4.54982e-07</v>
@@ -9126,7 +9126,7 @@
         <v>1.5</v>
       </c>
       <c r="B2" t="n">
-        <v>-275.068</v>
+        <v>108.78</v>
       </c>
       <c r="D2" t="n">
         <v>4.77106e-07</v>
@@ -9176,7 +9176,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>-224.0400000000001</v>
+        <v>73.56599999999997</v>
       </c>
       <c r="D3" t="n">
         <v>4.76293e-07</v>
@@ -9226,7 +9226,7 @@
         <v>4.5</v>
       </c>
       <c r="B4" t="n">
-        <v>-202.367</v>
+        <v>66.85599999999999</v>
       </c>
       <c r="D4" t="n">
         <v>4.69554e-07</v>
@@ -9276,7 +9276,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="n">
-        <v>-188.856</v>
+        <v>63.73900000000003</v>
       </c>
       <c r="D5" t="n">
         <v>4.64099e-07</v>
@@ -9326,7 +9326,7 @@
         <v>7.5</v>
       </c>
       <c r="B6" t="n">
-        <v>-180.988</v>
+        <v>60.34499999999997</v>
       </c>
       <c r="D6" t="n">
         <v>4.5952e-07</v>
@@ -9376,7 +9376,7 @@
         <v>9</v>
       </c>
       <c r="B7" t="n">
-        <v>-173.04</v>
+        <v>57.44199999999995</v>
       </c>
       <c r="D7" t="n">
         <v>4.56141e-07</v>
@@ -9426,7 +9426,7 @@
         <v>10.5</v>
       </c>
       <c r="B8" t="n">
-        <v>-167.181</v>
+        <v>57.26400000000001</v>
       </c>
       <c r="D8" t="n">
         <v>4.5332e-07</v>
@@ -9476,7 +9476,7 @@
         <v>12</v>
       </c>
       <c r="B9" t="n">
-        <v>-161.647</v>
+        <v>54.125</v>
       </c>
       <c r="D9" t="n">
         <v>4.51184e-07</v>
@@ -9526,7 +9526,7 @@
         <v>13.5</v>
       </c>
       <c r="B10" t="n">
-        <v>-156.297</v>
+        <v>53.63499999999999</v>
       </c>
       <c r="D10" t="n">
         <v>4.49307e-07</v>
@@ -9576,7 +9576,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="n">
-        <v>-154.017</v>
+        <v>49.94299999999998</v>
       </c>
       <c r="D11" t="n">
         <v>4.47867e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
@@ -438,7 +438,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -564,6 +564,9 @@
       <c r="B2" t="n">
         <v>129.816</v>
       </c>
+      <c r="C2" t="n">
+        <v>720.8500140358487</v>
+      </c>
       <c r="D2" t="n">
         <v>4.11386e-07</v>
       </c>
@@ -614,6 +617,9 @@
       <c r="B3" t="n">
         <v>121.697</v>
       </c>
+      <c r="C3" t="n">
+        <v>701.4909254470725</v>
+      </c>
       <c r="D3" t="n">
         <v>4.11095e-07</v>
       </c>
@@ -664,6 +670,9 @@
       <c r="B4" t="n">
         <v>114.407</v>
       </c>
+      <c r="C4" t="n">
+        <v>673.0864825838983</v>
+      </c>
       <c r="D4" t="n">
         <v>4.11214e-07</v>
       </c>
@@ -714,6 +723,9 @@
       <c r="B5" t="n">
         <v>110.61</v>
       </c>
+      <c r="C5" t="n">
+        <v>689.7480281658251</v>
+      </c>
       <c r="D5" t="n">
         <v>4.11614e-07</v>
       </c>
@@ -764,6 +776,9 @@
       <c r="B6" t="n">
         <v>106.412</v>
       </c>
+      <c r="C6" t="n">
+        <v>684.6802186902963</v>
+      </c>
       <c r="D6" t="n">
         <v>4.12326e-07</v>
       </c>
@@ -814,6 +829,9 @@
       <c r="B7" t="n">
         <v>102.859</v>
       </c>
+      <c r="C7" t="n">
+        <v>673.2755063606371</v>
+      </c>
       <c r="D7" t="n">
         <v>4.12857e-07</v>
       </c>
@@ -864,6 +882,9 @@
       <c r="B8" t="n">
         <v>99.90499999999997</v>
       </c>
+      <c r="C8" t="n">
+        <v>684.5060485352931</v>
+      </c>
       <c r="D8" t="n">
         <v>4.13321e-07</v>
       </c>
@@ -914,6 +935,9 @@
       <c r="B9" t="n">
         <v>94.87300000000005</v>
       </c>
+      <c r="C9" t="n">
+        <v>659.5085506342015</v>
+      </c>
       <c r="D9" t="n">
         <v>4.13835e-07</v>
       </c>
@@ -964,6 +988,9 @@
       <c r="B10" t="n">
         <v>91.20000000000005</v>
       </c>
+      <c r="C10" t="n">
+        <v>654.560846845185</v>
+      </c>
       <c r="D10" t="n">
         <v>4.14111e-07</v>
       </c>
@@ -1013,6 +1040,9 @@
       </c>
       <c r="B11" t="n">
         <v>88.26299999999998</v>
+      </c>
+      <c r="C11" t="n">
+        <v>636.5813516903087</v>
       </c>
       <c r="D11" t="n">
         <v>4.14408e-07</v>
@@ -1084,7 +1114,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -1210,6 +1240,9 @@
       <c r="B2" t="n">
         <v>123.017</v>
       </c>
+      <c r="C2" t="n">
+        <v>899.340445288763</v>
+      </c>
       <c r="D2" t="n">
         <v>4.45364e-07</v>
       </c>
@@ -1260,6 +1293,9 @@
       <c r="B3" t="n">
         <v>106.605</v>
       </c>
+      <c r="C3" t="n">
+        <v>713.6497531870107</v>
+      </c>
       <c r="D3" t="n">
         <v>4.44371e-07</v>
       </c>
@@ -1310,6 +1346,9 @@
       <c r="B4" t="n">
         <v>100.546</v>
       </c>
+      <c r="C4" t="n">
+        <v>667.6738638327722</v>
+      </c>
       <c r="D4" t="n">
         <v>4.43179e-07</v>
       </c>
@@ -1360,6 +1399,9 @@
       <c r="B5" t="n">
         <v>96.899</v>
       </c>
+      <c r="C5" t="n">
+        <v>656.4302997640609</v>
+      </c>
       <c r="D5" t="n">
         <v>4.41995e-07</v>
       </c>
@@ -1410,6 +1452,9 @@
       <c r="B6" t="n">
         <v>96.03699999999998</v>
       </c>
+      <c r="C6" t="n">
+        <v>680.090879666216</v>
+      </c>
       <c r="D6" t="n">
         <v>4.40925e-07</v>
       </c>
@@ -1460,6 +1505,9 @@
       <c r="B7" t="n">
         <v>93.70499999999998</v>
       </c>
+      <c r="C7" t="n">
+        <v>686.111655797867</v>
+      </c>
       <c r="D7" t="n">
         <v>4.40216e-07</v>
       </c>
@@ -1510,6 +1558,9 @@
       <c r="B8" t="n">
         <v>89.05399999999997</v>
       </c>
+      <c r="C8" t="n">
+        <v>649.7944101664943</v>
+      </c>
       <c r="D8" t="n">
         <v>4.39602e-07</v>
       </c>
@@ -1560,6 +1611,9 @@
       <c r="B9" t="n">
         <v>88.11700000000002</v>
       </c>
+      <c r="C9" t="n">
+        <v>656.3595523498944</v>
+      </c>
       <c r="D9" t="n">
         <v>4.39295e-07</v>
       </c>
@@ -1610,6 +1664,9 @@
       <c r="B10" t="n">
         <v>84.762</v>
       </c>
+      <c r="C10" t="n">
+        <v>648.4239826662224</v>
+      </c>
       <c r="D10" t="n">
         <v>4.38897e-07</v>
       </c>
@@ -1660,6 +1717,9 @@
       <c r="B11" t="n">
         <v>83.26099999999997</v>
       </c>
+      <c r="C11" t="n">
+        <v>648.2540632578232</v>
+      </c>
       <c r="D11" t="n">
         <v>4.38463e-07</v>
       </c>
@@ -1710,6 +1770,9 @@
       <c r="B12" t="n">
         <v>82.06399999999996</v>
       </c>
+      <c r="C12" t="n">
+        <v>647.03948546486</v>
+      </c>
       <c r="D12" t="n">
         <v>4.38079e-07</v>
       </c>
@@ -1760,6 +1823,9 @@
       <c r="B13" t="n">
         <v>78.935</v>
       </c>
+      <c r="C13" t="n">
+        <v>641.8487406465758</v>
+      </c>
       <c r="D13" t="n">
         <v>4.38024e-07</v>
       </c>
@@ -1810,6 +1876,9 @@
       <c r="B14" t="n">
         <v>79.26299999999998</v>
       </c>
+      <c r="C14" t="n">
+        <v>643.6944774244892</v>
+      </c>
       <c r="D14" t="n">
         <v>4.3775e-07</v>
       </c>
@@ -1860,6 +1929,9 @@
       <c r="B15" t="n">
         <v>79.89800000000002</v>
       </c>
+      <c r="C15" t="n">
+        <v>684.8597005079682</v>
+      </c>
       <c r="D15" t="n">
         <v>4.37654e-07</v>
       </c>
@@ -1910,6 +1982,9 @@
       <c r="B16" t="n">
         <v>77.23200000000003</v>
       </c>
+      <c r="C16" t="n">
+        <v>641.376145921137</v>
+      </c>
       <c r="D16" t="n">
         <v>4.3758e-07</v>
       </c>
@@ -1960,6 +2035,9 @@
       <c r="B17" t="n">
         <v>75.50099999999998</v>
       </c>
+      <c r="C17" t="n">
+        <v>657.9721710545239</v>
+      </c>
       <c r="D17" t="n">
         <v>4.37357e-07</v>
       </c>
@@ -2010,6 +2088,9 @@
       <c r="B18" t="n">
         <v>73.53300000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>630.6661161990052</v>
+      </c>
       <c r="D18" t="n">
         <v>4.37256e-07</v>
       </c>
@@ -2060,6 +2141,9 @@
       <c r="B19" t="n">
         <v>73.10199999999998</v>
       </c>
+      <c r="C19" t="n">
+        <v>641.3960193748983</v>
+      </c>
       <c r="D19" t="n">
         <v>4.37343e-07</v>
       </c>
@@ -2110,6 +2194,9 @@
       <c r="B20" t="n">
         <v>72.32600000000002</v>
       </c>
+      <c r="C20" t="n">
+        <v>668.3984943511233</v>
+      </c>
       <c r="D20" t="n">
         <v>4.37165e-07</v>
       </c>
@@ -2160,6 +2247,9 @@
       <c r="B21" t="n">
         <v>71.55400000000003</v>
       </c>
+      <c r="C21" t="n">
+        <v>684.1803828341108</v>
+      </c>
       <c r="D21" t="n">
         <v>4.37066e-07</v>
       </c>
@@ -2209,6 +2299,9 @@
       </c>
       <c r="B22" t="n">
         <v>69.53000000000003</v>
+      </c>
+      <c r="C22" t="n">
+        <v>631.3314001309458</v>
       </c>
       <c r="D22" t="n">
         <v>4.36996e-07</v>
@@ -2280,7 +2373,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -2406,6 +2499,9 @@
       <c r="B2" t="n">
         <v>129.108</v>
       </c>
+      <c r="C2" t="n">
+        <v>936.2287021263882</v>
+      </c>
       <c r="D2" t="n">
         <v>4.28239e-07</v>
       </c>
@@ -2456,6 +2552,9 @@
       <c r="B3" t="n">
         <v>109.101</v>
       </c>
+      <c r="C3" t="n">
+        <v>688.9215461118637</v>
+      </c>
       <c r="D3" t="n">
         <v>4.26096e-07</v>
       </c>
@@ -2506,6 +2605,9 @@
       <c r="B4" t="n">
         <v>103.232</v>
       </c>
+      <c r="C4" t="n">
+        <v>658.6159919993078</v>
+      </c>
       <c r="D4" t="n">
         <v>4.2453e-07</v>
       </c>
@@ -2556,6 +2658,9 @@
       <c r="B5" t="n">
         <v>103.322</v>
       </c>
+      <c r="C5" t="n">
+        <v>701.300580316535</v>
+      </c>
       <c r="D5" t="n">
         <v>4.23514e-07</v>
       </c>
@@ -2606,6 +2711,9 @@
       <c r="B6" t="n">
         <v>97.82499999999999</v>
       </c>
+      <c r="C6" t="n">
+        <v>647.1263633350176</v>
+      </c>
       <c r="D6" t="n">
         <v>4.22845e-07</v>
       </c>
@@ -2656,6 +2764,9 @@
       <c r="B7" t="n">
         <v>96.84500000000003</v>
       </c>
+      <c r="C7" t="n">
+        <v>667.8147788170378</v>
+      </c>
       <c r="D7" t="n">
         <v>4.22367e-07</v>
       </c>
@@ -2706,6 +2817,9 @@
       <c r="B8" t="n">
         <v>93.31200000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>664.9233432644954</v>
+      </c>
       <c r="D8" t="n">
         <v>4.2209e-07</v>
       </c>
@@ -2756,6 +2870,9 @@
       <c r="B9" t="n">
         <v>90.22899999999998</v>
       </c>
+      <c r="C9" t="n">
+        <v>651.8200565219901</v>
+      </c>
       <c r="D9" t="n">
         <v>4.22084e-07</v>
       </c>
@@ -2806,6 +2923,9 @@
       <c r="B10" t="n">
         <v>88.00999999999999</v>
       </c>
+      <c r="C10" t="n">
+        <v>646.0487812634905</v>
+      </c>
       <c r="D10" t="n">
         <v>4.21893e-07</v>
       </c>
@@ -2856,6 +2976,9 @@
       <c r="B11" t="n">
         <v>87.58699999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>668.9647490216912</v>
+      </c>
       <c r="D11" t="n">
         <v>4.21756e-07</v>
       </c>
@@ -2906,6 +3029,9 @@
       <c r="B12" t="n">
         <v>84.745</v>
       </c>
+      <c r="C12" t="n">
+        <v>651.3164943036192</v>
+      </c>
       <c r="D12" t="n">
         <v>4.21658e-07</v>
       </c>
@@ -2956,6 +3082,9 @@
       <c r="B13" t="n">
         <v>83.46300000000002</v>
       </c>
+      <c r="C13" t="n">
+        <v>657.5202472954152</v>
+      </c>
       <c r="D13" t="n">
         <v>4.21741e-07</v>
       </c>
@@ -3006,6 +3135,9 @@
       <c r="B14" t="n">
         <v>81.57900000000001</v>
       </c>
+      <c r="C14" t="n">
+        <v>660.0897678654854</v>
+      </c>
       <c r="D14" t="n">
         <v>4.21776e-07</v>
       </c>
@@ -3056,6 +3188,9 @@
       <c r="B15" t="n">
         <v>79.45000000000005</v>
       </c>
+      <c r="C15" t="n">
+        <v>659.0192601933589</v>
+      </c>
       <c r="D15" t="n">
         <v>4.21873e-07</v>
       </c>
@@ -3106,6 +3241,9 @@
       <c r="B16" t="n">
         <v>78.75599999999997</v>
       </c>
+      <c r="C16" t="n">
+        <v>660.6303099470944</v>
+      </c>
       <c r="D16" t="n">
         <v>4.21857e-07</v>
       </c>
@@ -3156,6 +3294,9 @@
       <c r="B17" t="n">
         <v>76.27600000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>623.7645572957276</v>
+      </c>
       <c r="D17" t="n">
         <v>4.21774e-07</v>
       </c>
@@ -3206,6 +3347,9 @@
       <c r="B18" t="n">
         <v>75.935</v>
       </c>
+      <c r="C18" t="n">
+        <v>652.7246587300516</v>
+      </c>
       <c r="D18" t="n">
         <v>4.21905e-07</v>
       </c>
@@ -3256,6 +3400,9 @@
       <c r="B19" t="n">
         <v>74.28999999999996</v>
       </c>
+      <c r="C19" t="n">
+        <v>657.5764947682455</v>
+      </c>
       <c r="D19" t="n">
         <v>4.22086e-07</v>
       </c>
@@ -3306,6 +3453,9 @@
       <c r="B20" t="n">
         <v>72.767</v>
       </c>
+      <c r="C20" t="n">
+        <v>651.8143057081736</v>
+      </c>
       <c r="D20" t="n">
         <v>4.22095e-07</v>
       </c>
@@ -3356,6 +3506,9 @@
       <c r="B21" t="n">
         <v>71.50700000000001</v>
       </c>
+      <c r="C21" t="n">
+        <v>620.0701320100694</v>
+      </c>
       <c r="D21" t="n">
         <v>4.22186e-07</v>
       </c>
@@ -3405,6 +3558,9 @@
       </c>
       <c r="B22" t="n">
         <v>71.55099999999999</v>
+      </c>
+      <c r="C22" t="n">
+        <v>649.3861581990768</v>
       </c>
       <c r="D22" t="n">
         <v>4.22288e-07</v>
@@ -3476,7 +3632,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -3602,6 +3758,9 @@
       <c r="B2" t="n">
         <v>124.143</v>
       </c>
+      <c r="C2" t="n">
+        <v>3155.63806226789</v>
+      </c>
       <c r="D2" t="n">
         <v>4.58367e-07</v>
       </c>
@@ -3652,6 +3811,9 @@
       <c r="B3" t="n">
         <v>84.48000000000002</v>
       </c>
+      <c r="C3" t="n">
+        <v>803.0206544290256</v>
+      </c>
       <c r="D3" t="n">
         <v>4.64888e-07</v>
       </c>
@@ -3702,6 +3864,9 @@
       <c r="B4" t="n">
         <v>75.40500000000003</v>
       </c>
+      <c r="C4" t="n">
+        <v>703.1211463154615</v>
+      </c>
       <c r="D4" t="n">
         <v>4.62057e-07</v>
       </c>
@@ -3752,6 +3917,9 @@
       <c r="B5" t="n">
         <v>70.87700000000001</v>
       </c>
+      <c r="C5" t="n">
+        <v>641.5032125678089</v>
+      </c>
       <c r="D5" t="n">
         <v>4.58705e-07</v>
       </c>
@@ -3802,6 +3970,9 @@
       <c r="B6" t="n">
         <v>69.327</v>
       </c>
+      <c r="C6" t="n">
+        <v>689.5297847975535</v>
+      </c>
       <c r="D6" t="n">
         <v>4.5565e-07</v>
       </c>
@@ -3852,6 +4023,9 @@
       <c r="B7" t="n">
         <v>67.33199999999999</v>
       </c>
+      <c r="C7" t="n">
+        <v>704.5177030422943</v>
+      </c>
       <c r="D7" t="n">
         <v>4.53261e-07</v>
       </c>
@@ -3902,6 +4076,9 @@
       <c r="B8" t="n">
         <v>64.70999999999998</v>
       </c>
+      <c r="C8" t="n">
+        <v>710.6261843403965</v>
+      </c>
       <c r="D8" t="n">
         <v>4.51167e-07</v>
       </c>
@@ -3952,6 +4129,9 @@
       <c r="B9" t="n">
         <v>62.04999999999995</v>
       </c>
+      <c r="C9" t="n">
+        <v>716.8243195581902</v>
+      </c>
       <c r="D9" t="n">
         <v>4.49551e-07</v>
       </c>
@@ -4002,6 +4182,9 @@
       <c r="B10" t="n">
         <v>60.31</v>
       </c>
+      <c r="C10" t="n">
+        <v>727.123993983589</v>
+      </c>
       <c r="D10" t="n">
         <v>4.47803e-07</v>
       </c>
@@ -4051,6 +4234,9 @@
       </c>
       <c r="B11" t="n">
         <v>59.291</v>
+      </c>
+      <c r="C11" t="n">
+        <v>817.7970237542532</v>
       </c>
       <c r="D11" t="n">
         <v>4.46535e-07</v>
@@ -4122,7 +4308,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -4248,6 +4434,9 @@
       <c r="B2" t="n">
         <v>126.633</v>
       </c>
+      <c r="C2" t="n">
+        <v>874.8576373914515</v>
+      </c>
       <c r="D2" t="n">
         <v>4.62212e-07</v>
       </c>
@@ -4298,6 +4487,9 @@
       <c r="B3" t="n">
         <v>109.67</v>
       </c>
+      <c r="C3" t="n">
+        <v>685.0452487694256</v>
+      </c>
       <c r="D3" t="n">
         <v>4.59991e-07</v>
       </c>
@@ -4348,6 +4540,9 @@
       <c r="B4" t="n">
         <v>102.344</v>
       </c>
+      <c r="C4" t="n">
+        <v>635.0165402559239</v>
+      </c>
       <c r="D4" t="n">
         <v>4.57266e-07</v>
       </c>
@@ -4398,6 +4593,9 @@
       <c r="B5" t="n">
         <v>101.124</v>
       </c>
+      <c r="C5" t="n">
+        <v>654.1365810640671</v>
+      </c>
       <c r="D5" t="n">
         <v>4.54742e-07</v>
       </c>
@@ -4448,6 +4646,9 @@
       <c r="B6" t="n">
         <v>97.53200000000004</v>
       </c>
+      <c r="C6" t="n">
+        <v>639.3980852990893</v>
+      </c>
       <c r="D6" t="n">
         <v>4.52903e-07</v>
       </c>
@@ -4498,6 +4699,9 @@
       <c r="B7" t="n">
         <v>94.90600000000001</v>
       </c>
+      <c r="C7" t="n">
+        <v>644.8802155549746</v>
+      </c>
       <c r="D7" t="n">
         <v>4.51503e-07</v>
       </c>
@@ -4548,6 +4752,9 @@
       <c r="B8" t="n">
         <v>93.04000000000002</v>
       </c>
+      <c r="C8" t="n">
+        <v>653.4046936808984</v>
+      </c>
       <c r="D8" t="n">
         <v>4.50016e-07</v>
       </c>
@@ -4598,6 +4805,9 @@
       <c r="B9" t="n">
         <v>90.173</v>
       </c>
+      <c r="C9" t="n">
+        <v>649.3640530642965</v>
+      </c>
       <c r="D9" t="n">
         <v>4.48717e-07</v>
       </c>
@@ -4648,6 +4858,9 @@
       <c r="B10" t="n">
         <v>87.74800000000005</v>
       </c>
+      <c r="C10" t="n">
+        <v>632.6456809622277</v>
+      </c>
       <c r="D10" t="n">
         <v>4.47817e-07</v>
       </c>
@@ -4698,6 +4911,9 @@
       <c r="B11" t="n">
         <v>86.12</v>
       </c>
+      <c r="C11" t="n">
+        <v>636.3638549313672</v>
+      </c>
       <c r="D11" t="n">
         <v>4.46873e-07</v>
       </c>
@@ -4748,6 +4964,9 @@
       <c r="B12" t="n">
         <v>85.72300000000001</v>
       </c>
+      <c r="C12" t="n">
+        <v>646.27187925997</v>
+      </c>
       <c r="D12" t="n">
         <v>4.45936e-07</v>
       </c>
@@ -4798,6 +5017,9 @@
       <c r="B13" t="n">
         <v>82.25900000000001</v>
       </c>
+      <c r="C13" t="n">
+        <v>624.494009119665</v>
+      </c>
       <c r="D13" t="n">
         <v>4.45247e-07</v>
       </c>
@@ -4848,6 +5070,9 @@
       <c r="B14" t="n">
         <v>82.39699999999999</v>
       </c>
+      <c r="C14" t="n">
+        <v>619.9636012446135</v>
+      </c>
       <c r="D14" t="n">
         <v>4.44504e-07</v>
       </c>
@@ -4898,6 +5123,9 @@
       <c r="B15" t="n">
         <v>80.50900000000001</v>
       </c>
+      <c r="C15" t="n">
+        <v>632.1873959688705</v>
+      </c>
       <c r="D15" t="n">
         <v>4.43868e-07</v>
       </c>
@@ -4948,6 +5176,9 @@
       <c r="B16" t="n">
         <v>79.62600000000003</v>
       </c>
+      <c r="C16" t="n">
+        <v>626.3976481946423</v>
+      </c>
       <c r="D16" t="n">
         <v>4.4356e-07</v>
       </c>
@@ -4998,6 +5229,9 @@
       <c r="B17" t="n">
         <v>77.30199999999996</v>
       </c>
+      <c r="C17" t="n">
+        <v>623.2343674445448</v>
+      </c>
       <c r="D17" t="n">
         <v>4.42902e-07</v>
       </c>
@@ -5048,6 +5282,9 @@
       <c r="B18" t="n">
         <v>76.89300000000003</v>
       </c>
+      <c r="C18" t="n">
+        <v>631.4652882350346</v>
+      </c>
       <c r="D18" t="n">
         <v>4.42504e-07</v>
       </c>
@@ -5098,6 +5335,9 @@
       <c r="B19" t="n">
         <v>75.31400000000002</v>
       </c>
+      <c r="C19" t="n">
+        <v>631.3232973719903</v>
+      </c>
       <c r="D19" t="n">
         <v>4.42194e-07</v>
       </c>
@@ -5148,6 +5388,9 @@
       <c r="B20" t="n">
         <v>75.01399999999995</v>
       </c>
+      <c r="C20" t="n">
+        <v>632.7211897132238</v>
+      </c>
       <c r="D20" t="n">
         <v>4.41998e-07</v>
       </c>
@@ -5198,6 +5441,9 @@
       <c r="B21" t="n">
         <v>73.20400000000001</v>
       </c>
+      <c r="C21" t="n">
+        <v>619.383539465166</v>
+      </c>
       <c r="D21" t="n">
         <v>4.41749e-07</v>
       </c>
@@ -5247,6 +5493,9 @@
       </c>
       <c r="B22" t="n">
         <v>71.86399999999998</v>
+      </c>
+      <c r="C22" t="n">
+        <v>616.3638810461654</v>
       </c>
       <c r="D22" t="n">
         <v>4.4155e-07</v>
@@ -5318,7 +5567,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -5444,6 +5693,9 @@
       <c r="B2" t="n">
         <v>121.092</v>
       </c>
+      <c r="C2" t="n">
+        <v>2352.192109664631</v>
+      </c>
       <c r="D2" t="n">
         <v>4.8887e-07</v>
       </c>
@@ -5494,6 +5746,9 @@
       <c r="B3" t="n">
         <v>83.94799999999998</v>
       </c>
+      <c r="C3" t="n">
+        <v>780.5008265319979</v>
+      </c>
       <c r="D3" t="n">
         <v>4.96942e-07</v>
       </c>
@@ -5544,6 +5799,9 @@
       <c r="B4" t="n">
         <v>76.423</v>
       </c>
+      <c r="C4" t="n">
+        <v>718.0817293895909</v>
+      </c>
       <c r="D4" t="n">
         <v>4.93326e-07</v>
       </c>
@@ -5594,6 +5852,9 @@
       <c r="B5" t="n">
         <v>73.19899999999996</v>
       </c>
+      <c r="C5" t="n">
+        <v>690.233042440539</v>
+      </c>
       <c r="D5" t="n">
         <v>4.891439999999999e-07</v>
       </c>
@@ -5644,6 +5905,9 @@
       <c r="B6" t="n">
         <v>68.11800000000005</v>
       </c>
+      <c r="C6" t="n">
+        <v>642.9533744546808</v>
+      </c>
       <c r="D6" t="n">
         <v>4.85406e-07</v>
       </c>
@@ -5694,6 +5958,9 @@
       <c r="B7" t="n">
         <v>66.875</v>
       </c>
+      <c r="C7" t="n">
+        <v>672.3777381407684</v>
+      </c>
       <c r="D7" t="n">
         <v>4.8182e-07</v>
       </c>
@@ -5744,6 +6011,9 @@
       <c r="B8" t="n">
         <v>64.42599999999999</v>
       </c>
+      <c r="C8" t="n">
+        <v>688.5220718046609</v>
+      </c>
       <c r="D8" t="n">
         <v>4.78968e-07</v>
       </c>
@@ -5794,6 +6064,9 @@
       <c r="B9" t="n">
         <v>62.57499999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>720.7280887885386</v>
+      </c>
       <c r="D9" t="n">
         <v>4.76339e-07</v>
       </c>
@@ -5844,6 +6117,9 @@
       <c r="B10" t="n">
         <v>60.048</v>
       </c>
+      <c r="C10" t="n">
+        <v>722.9162690896277</v>
+      </c>
       <c r="D10" t="n">
         <v>4.73825e-07</v>
       </c>
@@ -5893,6 +6169,9 @@
       </c>
       <c r="B11" t="n">
         <v>57.11200000000002</v>
+      </c>
+      <c r="C11" t="n">
+        <v>672.0805246375523</v>
       </c>
       <c r="D11" t="n">
         <v>4.71744e-07</v>
@@ -5964,7 +6243,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -6090,6 +6369,9 @@
       <c r="B2" t="n">
         <v>123.676</v>
       </c>
+      <c r="C2" t="n">
+        <v>855.0935304239182</v>
+      </c>
       <c r="D2" t="n">
         <v>4.84296e-07</v>
       </c>
@@ -6140,6 +6422,9 @@
       <c r="B3" t="n">
         <v>107.541</v>
       </c>
+      <c r="C3" t="n">
+        <v>660.00640754248</v>
+      </c>
       <c r="D3" t="n">
         <v>4.81725e-07</v>
       </c>
@@ -6190,6 +6475,9 @@
       <c r="B4" t="n">
         <v>103.253</v>
       </c>
+      <c r="C4" t="n">
+        <v>647.1063874525702</v>
+      </c>
       <c r="D4" t="n">
         <v>4.78223e-07</v>
       </c>
@@ -6240,6 +6528,9 @@
       <c r="B5" t="n">
         <v>98.27499999999998</v>
       </c>
+      <c r="C5" t="n">
+        <v>606.3516184835494</v>
+      </c>
       <c r="D5" t="n">
         <v>4.75225e-07</v>
       </c>
@@ -6290,6 +6581,9 @@
       <c r="B6" t="n">
         <v>98.31</v>
       </c>
+      <c r="C6" t="n">
+        <v>644.455040605251</v>
+      </c>
       <c r="D6" t="n">
         <v>4.7266e-07</v>
       </c>
@@ -6340,6 +6634,9 @@
       <c r="B7" t="n">
         <v>94.524</v>
       </c>
+      <c r="C7" t="n">
+        <v>624.3059440724148</v>
+      </c>
       <c r="D7" t="n">
         <v>4.7051e-07</v>
       </c>
@@ -6390,6 +6687,9 @@
       <c r="B8" t="n">
         <v>91.20700000000005</v>
       </c>
+      <c r="C8" t="n">
+        <v>623.6591506195338</v>
+      </c>
       <c r="D8" t="n">
         <v>4.68669e-07</v>
       </c>
@@ -6440,6 +6740,9 @@
       <c r="B9" t="n">
         <v>88.71699999999998</v>
       </c>
+      <c r="C9" t="n">
+        <v>625.0399832623575</v>
+      </c>
       <c r="D9" t="n">
         <v>4.66931e-07</v>
       </c>
@@ -6490,6 +6793,9 @@
       <c r="B10" t="n">
         <v>86.673</v>
       </c>
+      <c r="C10" t="n">
+        <v>625.0284769351979</v>
+      </c>
       <c r="D10" t="n">
         <v>4.65709e-07</v>
       </c>
@@ -6540,6 +6846,9 @@
       <c r="B11" t="n">
         <v>84.81299999999999</v>
       </c>
+      <c r="C11" t="n">
+        <v>614.7888387354366</v>
+      </c>
       <c r="D11" t="n">
         <v>4.64191e-07</v>
       </c>
@@ -6590,6 +6899,9 @@
       <c r="B12" t="n">
         <v>82.91899999999998</v>
       </c>
+      <c r="C12" t="n">
+        <v>618.3077314025624</v>
+      </c>
       <c r="D12" t="n">
         <v>4.63033e-07</v>
       </c>
@@ -6640,6 +6952,9 @@
       <c r="B13" t="n">
         <v>81.91500000000002</v>
       </c>
+      <c r="C13" t="n">
+        <v>624.0160376637402</v>
+      </c>
       <c r="D13" t="n">
         <v>4.62104e-07</v>
       </c>
@@ -6690,6 +7005,9 @@
       <c r="B14" t="n">
         <v>78.851</v>
       </c>
+      <c r="C14" t="n">
+        <v>591.2716895676103</v>
+      </c>
       <c r="D14" t="n">
         <v>4.61169e-07</v>
       </c>
@@ -6740,6 +7058,9 @@
       <c r="B15" t="n">
         <v>77.49299999999999</v>
       </c>
+      <c r="C15" t="n">
+        <v>605.5053367880757</v>
+      </c>
       <c r="D15" t="n">
         <v>4.6039e-07</v>
       </c>
@@ -6790,6 +7111,9 @@
       <c r="B16" t="n">
         <v>76.70600000000002</v>
       </c>
+      <c r="C16" t="n">
+        <v>600.3030966411289</v>
+      </c>
       <c r="D16" t="n">
         <v>4.59584e-07</v>
       </c>
@@ -6840,6 +7164,9 @@
       <c r="B17" t="n">
         <v>75.99000000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>614.5939996018349</v>
+      </c>
       <c r="D17" t="n">
         <v>4.5913e-07</v>
       </c>
@@ -6890,6 +7217,9 @@
       <c r="B18" t="n">
         <v>74.08100000000002</v>
       </c>
+      <c r="C18" t="n">
+        <v>616.4352711789447</v>
+      </c>
       <c r="D18" t="n">
         <v>4.58504e-07</v>
       </c>
@@ -6940,6 +7270,9 @@
       <c r="B19" t="n">
         <v>72.64999999999998</v>
       </c>
+      <c r="C19" t="n">
+        <v>597.4550291658081</v>
+      </c>
       <c r="D19" t="n">
         <v>4.5813e-07</v>
       </c>
@@ -6990,6 +7323,9 @@
       <c r="B20" t="n">
         <v>71.572</v>
       </c>
+      <c r="C20" t="n">
+        <v>613.6934895008891</v>
+      </c>
       <c r="D20" t="n">
         <v>4.5765e-07</v>
       </c>
@@ -7040,6 +7376,9 @@
       <c r="B21" t="n">
         <v>70.94</v>
       </c>
+      <c r="C21" t="n">
+        <v>617.9120102830822</v>
+      </c>
       <c r="D21" t="n">
         <v>4.57344e-07</v>
       </c>
@@ -7089,6 +7428,9 @@
       </c>
       <c r="B22" t="n">
         <v>68.702</v>
+      </c>
+      <c r="C22" t="n">
+        <v>603.6641862080721</v>
       </c>
       <c r="D22" t="n">
         <v>4.57011e-07</v>
@@ -7160,7 +7502,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7286,6 +7628,9 @@
       <c r="B2" t="n">
         <v>124.192</v>
       </c>
+      <c r="C2" t="n">
+        <v>5980.700868795026</v>
+      </c>
       <c r="D2" t="n">
         <v>5.06168e-07</v>
       </c>
@@ -7336,6 +7681,9 @@
       <c r="B3" t="n">
         <v>80.36900000000003</v>
       </c>
+      <c r="C3" t="n">
+        <v>806.7452303954329</v>
+      </c>
       <c r="D3" t="n">
         <v>5.05983e-07</v>
       </c>
@@ -7386,6 +7734,9 @@
       <c r="B4" t="n">
         <v>72.76999999999998</v>
       </c>
+      <c r="C4" t="n">
+        <v>714.9821143343383</v>
+      </c>
       <c r="D4" t="n">
         <v>4.98707e-07</v>
       </c>
@@ -7436,6 +7787,9 @@
       <c r="B5" t="n">
         <v>71.12</v>
       </c>
+      <c r="C5" t="n">
+        <v>735.9533274710844</v>
+      </c>
       <c r="D5" t="n">
         <v>4.91899e-07</v>
       </c>
@@ -7486,6 +7840,9 @@
       <c r="B6" t="n">
         <v>66.69199999999995</v>
       </c>
+      <c r="C6" t="n">
+        <v>698.6683701258029</v>
+      </c>
       <c r="D6" t="n">
         <v>4.86304e-07</v>
       </c>
@@ -7536,6 +7893,9 @@
       <c r="B7" t="n">
         <v>65.197</v>
       </c>
+      <c r="C7" t="n">
+        <v>742.4617405958196</v>
+      </c>
       <c r="D7" t="n">
         <v>4.81797e-07</v>
       </c>
@@ -7586,6 +7946,9 @@
       <c r="B8" t="n">
         <v>61.40999999999997</v>
       </c>
+      <c r="C8" t="n">
+        <v>702.5996257553236</v>
+      </c>
       <c r="D8" t="n">
         <v>4.7786e-07</v>
       </c>
@@ -7636,6 +7999,9 @@
       <c r="B9" t="n">
         <v>61.18799999999999</v>
       </c>
+      <c r="C9" t="n">
+        <v>813.59184294638</v>
+      </c>
       <c r="D9" t="n">
         <v>4.74438e-07</v>
       </c>
@@ -7686,6 +8052,9 @@
       <c r="B10" t="n">
         <v>57.14799999999997</v>
       </c>
+      <c r="C10" t="n">
+        <v>699.5582381900427</v>
+      </c>
       <c r="D10" t="n">
         <v>4.71805e-07</v>
       </c>
@@ -7735,6 +8104,9 @@
       </c>
       <c r="B11" t="n">
         <v>55.91800000000001</v>
+      </c>
+      <c r="C11" t="n">
+        <v>759.8787056198097</v>
       </c>
       <c r="D11" t="n">
         <v>4.69256e-07</v>
@@ -7806,7 +8178,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -7932,6 +8304,9 @@
       <c r="B2" t="n">
         <v>121.722</v>
       </c>
+      <c r="C2" t="n">
+        <v>948.1853691536838</v>
+      </c>
       <c r="D2" t="n">
         <v>4.76632e-07</v>
       </c>
@@ -7982,6 +8357,9 @@
       <c r="B3" t="n">
         <v>102.705</v>
       </c>
+      <c r="C3" t="n">
+        <v>698.6712925382575</v>
+      </c>
       <c r="D3" t="n">
         <v>4.74076e-07</v>
       </c>
@@ -8032,6 +8410,9 @@
       <c r="B4" t="n">
         <v>100.697</v>
       </c>
+      <c r="C4" t="n">
+        <v>702.1433860803539</v>
+      </c>
       <c r="D4" t="n">
         <v>4.70895e-07</v>
       </c>
@@ -8082,6 +8463,9 @@
       <c r="B5" t="n">
         <v>97.654</v>
       </c>
+      <c r="C5" t="n">
+        <v>704.2764532471296</v>
+      </c>
       <c r="D5" t="n">
         <v>4.68432e-07</v>
       </c>
@@ -8132,6 +8516,9 @@
       <c r="B6" t="n">
         <v>92.14100000000002</v>
       </c>
+      <c r="C6" t="n">
+        <v>668.5654964052603</v>
+      </c>
       <c r="D6" t="n">
         <v>4.66149e-07</v>
       </c>
@@ -8182,6 +8569,9 @@
       <c r="B7" t="n">
         <v>89.60300000000001</v>
       </c>
+      <c r="C7" t="n">
+        <v>665.7111109225192</v>
+      </c>
       <c r="D7" t="n">
         <v>4.64535e-07</v>
       </c>
@@ -8232,6 +8622,9 @@
       <c r="B8" t="n">
         <v>87.36600000000004</v>
       </c>
+      <c r="C8" t="n">
+        <v>665.1209670161586</v>
+      </c>
       <c r="D8" t="n">
         <v>4.63123e-07</v>
       </c>
@@ -8282,6 +8675,9 @@
       <c r="B9" t="n">
         <v>86.68400000000003</v>
       </c>
+      <c r="C9" t="n">
+        <v>686.1986494497235</v>
+      </c>
       <c r="D9" t="n">
         <v>4.61892e-07</v>
       </c>
@@ -8332,6 +8728,9 @@
       <c r="B10" t="n">
         <v>82.69300000000004</v>
       </c>
+      <c r="C10" t="n">
+        <v>658.1838017767451</v>
+      </c>
       <c r="D10" t="n">
         <v>4.60773e-07</v>
       </c>
@@ -8382,6 +8781,9 @@
       <c r="B11" t="n">
         <v>80.03100000000001</v>
       </c>
+      <c r="C11" t="n">
+        <v>648.640927757444</v>
+      </c>
       <c r="D11" t="n">
         <v>4.59828e-07</v>
       </c>
@@ -8432,6 +8834,9 @@
       <c r="B12" t="n">
         <v>78.76499999999999</v>
       </c>
+      <c r="C12" t="n">
+        <v>642.2704761402231</v>
+      </c>
       <c r="D12" t="n">
         <v>4.58991e-07</v>
       </c>
@@ -8482,6 +8887,9 @@
       <c r="B13" t="n">
         <v>77.476</v>
       </c>
+      <c r="C13" t="n">
+        <v>651.8495718293996</v>
+      </c>
       <c r="D13" t="n">
         <v>4.58185e-07</v>
       </c>
@@ -8532,6 +8940,9 @@
       <c r="B14" t="n">
         <v>77.07600000000002</v>
       </c>
+      <c r="C14" t="n">
+        <v>665.140710871394</v>
+      </c>
       <c r="D14" t="n">
         <v>4.57753e-07</v>
       </c>
@@ -8582,6 +8993,9 @@
       <c r="B15" t="n">
         <v>74.57299999999998</v>
       </c>
+      <c r="C15" t="n">
+        <v>638.3980420905522</v>
+      </c>
       <c r="D15" t="n">
         <v>4.5734e-07</v>
       </c>
@@ -8632,6 +9046,9 @@
       <c r="B16" t="n">
         <v>74.93699999999995</v>
       </c>
+      <c r="C16" t="n">
+        <v>672.2953890029386</v>
+      </c>
       <c r="D16" t="n">
         <v>4.56802e-07</v>
       </c>
@@ -8682,6 +9099,9 @@
       <c r="B17" t="n">
         <v>70.38400000000001</v>
       </c>
+      <c r="C17" t="n">
+        <v>615.1259437577935</v>
+      </c>
       <c r="D17" t="n">
         <v>4.56379e-07</v>
       </c>
@@ -8732,6 +9152,9 @@
       <c r="B18" t="n">
         <v>71.27600000000001</v>
       </c>
+      <c r="C18" t="n">
+        <v>635.017655928022</v>
+      </c>
       <c r="D18" t="n">
         <v>4.55973e-07</v>
       </c>
@@ -8782,6 +9205,9 @@
       <c r="B19" t="n">
         <v>70.56200000000001</v>
       </c>
+      <c r="C19" t="n">
+        <v>653.5020778912087</v>
+      </c>
       <c r="D19" t="n">
         <v>4.55624e-07</v>
       </c>
@@ -8832,6 +9258,9 @@
       <c r="B20" t="n">
         <v>69.02999999999997</v>
       </c>
+      <c r="C20" t="n">
+        <v>633.7453654911785</v>
+      </c>
       <c r="D20" t="n">
         <v>4.55382e-07</v>
       </c>
@@ -8882,6 +9311,9 @@
       <c r="B21" t="n">
         <v>67.68700000000001</v>
       </c>
+      <c r="C21" t="n">
+        <v>606.1986498566346</v>
+      </c>
       <c r="D21" t="n">
         <v>4.55044e-07</v>
       </c>
@@ -8931,6 +9363,9 @@
       </c>
       <c r="B22" t="n">
         <v>67.94100000000003</v>
+      </c>
+      <c r="C22" t="n">
+        <v>666.7210812738267</v>
       </c>
       <c r="D22" t="n">
         <v>4.54982e-07</v>
@@ -9002,7 +9437,7 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Rct-d</t>
+          <t>delta Rct-d</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -9128,6 +9563,9 @@
       <c r="B2" t="n">
         <v>108.78</v>
       </c>
+      <c r="C2" t="n">
+        <v>5331.214363815037</v>
+      </c>
       <c r="D2" t="n">
         <v>4.77106e-07</v>
       </c>
@@ -9178,6 +9616,9 @@
       <c r="B3" t="n">
         <v>73.56599999999997</v>
       </c>
+      <c r="C3" t="n">
+        <v>838.479423475485</v>
+      </c>
       <c r="D3" t="n">
         <v>4.76293e-07</v>
       </c>
@@ -9228,6 +9669,9 @@
       <c r="B4" t="n">
         <v>66.85599999999999</v>
       </c>
+      <c r="C4" t="n">
+        <v>748.7821376145343</v>
+      </c>
       <c r="D4" t="n">
         <v>4.69554e-07</v>
       </c>
@@ -9278,6 +9722,9 @@
       <c r="B5" t="n">
         <v>63.73900000000003</v>
       </c>
+      <c r="C5" t="n">
+        <v>714.7246854044275</v>
+      </c>
       <c r="D5" t="n">
         <v>4.64099e-07</v>
       </c>
@@ -9328,6 +9775,9 @@
       <c r="B6" t="n">
         <v>60.34499999999997</v>
       </c>
+      <c r="C6" t="n">
+        <v>673.2092925799028</v>
+      </c>
       <c r="D6" t="n">
         <v>4.5952e-07</v>
       </c>
@@ -9378,6 +9828,9 @@
       <c r="B7" t="n">
         <v>57.44199999999995</v>
       </c>
+      <c r="C7" t="n">
+        <v>668.8933833379225</v>
+      </c>
       <c r="D7" t="n">
         <v>4.56141e-07</v>
       </c>
@@ -9428,6 +9881,9 @@
       <c r="B8" t="n">
         <v>57.26400000000001</v>
       </c>
+      <c r="C8" t="n">
+        <v>815.2509216250455</v>
+      </c>
       <c r="D8" t="n">
         <v>4.5332e-07</v>
       </c>
@@ -9478,6 +9934,9 @@
       <c r="B9" t="n">
         <v>54.125</v>
       </c>
+      <c r="C9" t="n">
+        <v>761.3173879387413</v>
+      </c>
       <c r="D9" t="n">
         <v>4.51184e-07</v>
       </c>
@@ -9528,6 +9987,9 @@
       <c r="B10" t="n">
         <v>53.63499999999999</v>
       </c>
+      <c r="C10" t="n">
+        <v>853.5517679089754</v>
+      </c>
       <c r="D10" t="n">
         <v>4.49307e-07</v>
       </c>
@@ -9577,6 +10039,9 @@
       </c>
       <c r="B11" t="n">
         <v>49.94299999999998</v>
+      </c>
+      <c r="C11" t="n">
+        <v>772.1021096614774</v>
       </c>
       <c r="D11" t="n">
         <v>4.47867e-07</v>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
@@ -565,7 +565,7 @@
         <v>129.816</v>
       </c>
       <c r="C2" t="n">
-        <v>720.8500140358487</v>
+        <v>129.816</v>
       </c>
       <c r="D2" t="n">
         <v>4.11386e-07</v>
@@ -597,11 +597,10 @@
       <c r="X2" t="n">
         <v>-8303.678626407043</v>
       </c>
-      <c r="Y2" t="n">
-        <v>441.8751299021471</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>245712547.1356277</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>9.077035214013106e-07</v>
@@ -618,7 +617,7 @@
         <v>121.697</v>
       </c>
       <c r="C3" t="n">
-        <v>701.4909254470725</v>
+        <v>277.5030697948743</v>
       </c>
       <c r="D3" t="n">
         <v>4.11095e-07</v>
@@ -651,16 +650,13 @@
         <v>-8487.127595586631</v>
       </c>
       <c r="Y3" t="n">
-        <v>434.3481901031161</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>38491344.48331343</v>
+        <v>205.2434374351851</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.496679723174884e-07</v>
+        <v>7.425467691008536e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8899859477585453</v>
+        <v>0.9084181236155583</v>
       </c>
     </row>
     <row r="4">
@@ -671,7 +667,7 @@
         <v>114.407</v>
       </c>
       <c r="C4" t="n">
-        <v>673.0864825838983</v>
+        <v>271.6157510356171</v>
       </c>
       <c r="D4" t="n">
         <v>4.11214e-07</v>
@@ -704,16 +700,13 @@
         <v>-8310.605327035604</v>
       </c>
       <c r="Y4" t="n">
-        <v>427.7779039390333</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>59686438.34264517</v>
+        <v>202.1209045214844</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.143957286588159e-07</v>
+        <v>7.013632258779919e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8964225003084479</v>
+        <v>0.912565941959113</v>
       </c>
     </row>
     <row r="5">
@@ -724,7 +717,7 @@
         <v>110.61</v>
       </c>
       <c r="C5" t="n">
-        <v>689.7480281658251</v>
+        <v>110.61</v>
       </c>
       <c r="D5" t="n">
         <v>4.11614e-07</v>
@@ -756,11 +749,10 @@
       <c r="X5" t="n">
         <v>-8611.818107984484</v>
       </c>
-      <c r="Y5" t="n">
-        <v>421.5797911742441</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>63508959.18336506</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>7.892827574397358e-07</v>
@@ -777,7 +769,7 @@
         <v>106.412</v>
       </c>
       <c r="C6" t="n">
-        <v>684.6802186902963</v>
+        <v>254.3360098940687</v>
       </c>
       <c r="D6" t="n">
         <v>4.12326e-07</v>
@@ -810,16 +802,13 @@
         <v>-8591.412511777164</v>
       </c>
       <c r="Y6" t="n">
-        <v>415.6768547387593</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>30128315.26671074</v>
+        <v>205.1256587110798</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.71485166579219e-07</v>
+        <v>6.965753217997821e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9050139365760173</v>
+        <v>0.9206336757676614</v>
       </c>
     </row>
     <row r="7">
@@ -830,7 +819,7 @@
         <v>102.859</v>
       </c>
       <c r="C7" t="n">
-        <v>673.2755063606371</v>
+        <v>253.9813166457417</v>
       </c>
       <c r="D7" t="n">
         <v>4.12857e-07</v>
@@ -863,16 +852,13 @@
         <v>-8596.735331531549</v>
       </c>
       <c r="Y7" t="n">
-        <v>409.977589424865</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>675381081.8686706</v>
+        <v>198.6453905757892</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.565498516939744e-07</v>
+        <v>6.640844184341245e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.908154540578976</v>
+        <v>0.9231169070881019</v>
       </c>
     </row>
     <row r="8">
@@ -883,7 +869,7 @@
         <v>99.90499999999997</v>
       </c>
       <c r="C8" t="n">
-        <v>684.5060485352931</v>
+        <v>99.90499999999997</v>
       </c>
       <c r="D8" t="n">
         <v>4.13321e-07</v>
@@ -915,11 +901,10 @@
       <c r="X8" t="n">
         <v>-8740.130202361239</v>
       </c>
-      <c r="Y8" t="n">
-        <v>404.4319783582843</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>111313918.0968795</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>7.434343053118211e-07</v>
@@ -936,7 +921,7 @@
         <v>94.87300000000005</v>
       </c>
       <c r="C9" t="n">
-        <v>659.5085506342015</v>
+        <v>242.8186302388395</v>
       </c>
       <c r="D9" t="n">
         <v>4.13835e-07</v>
@@ -969,16 +954,13 @@
         <v>-8382.359059673714</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.2435837759633</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>164357452.0273654</v>
+        <v>196.5290441894363</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.313158604715136e-07</v>
+        <v>6.344140673819727e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9136482768902352</v>
+        <v>0.9297443489512175</v>
       </c>
     </row>
     <row r="10">
@@ -989,7 +971,7 @@
         <v>91.20000000000005</v>
       </c>
       <c r="C10" t="n">
-        <v>654.560846845185</v>
+        <v>237.7342602469007</v>
       </c>
       <c r="D10" t="n">
         <v>4.14111e-07</v>
@@ -1022,16 +1004,13 @@
         <v>-8177.335005830709</v>
       </c>
       <c r="Y10" t="n">
-        <v>394.6339166541012</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1081600138.813152</v>
+        <v>196.5612627273072</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.200036925052079e-07</v>
+        <v>6.588650813622219e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.916102328578133</v>
+        <v>0.9289504209002936</v>
       </c>
     </row>
     <row r="11">
@@ -1042,7 +1021,7 @@
         <v>88.26299999999998</v>
       </c>
       <c r="C11" t="n">
-        <v>636.5813516903087</v>
+        <v>234.273109870991</v>
       </c>
       <c r="D11" t="n">
         <v>4.14408e-07</v>
@@ -1075,16 +1054,13 @@
         <v>-8112.777920204778</v>
       </c>
       <c r="Y11" t="n">
-        <v>390.5236675824672</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>121300484.0697669</v>
+        <v>194.4008623820646</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.10358220782034e-07</v>
+        <v>6.156628456846852e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9182480339726223</v>
+        <v>0.9338513810270599</v>
       </c>
     </row>
   </sheetData>
@@ -1241,7 +1217,7 @@
         <v>123.017</v>
       </c>
       <c r="C2" t="n">
-        <v>899.340445288763</v>
+        <v>277.6421253937257</v>
       </c>
       <c r="D2" t="n">
         <v>4.45364e-07</v>
@@ -1274,16 +1250,13 @@
         <v>-7830.369185265049</v>
       </c>
       <c r="Y2" t="n">
-        <v>435.0186249382122</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>79437038.25296503</v>
+        <v>201.9640346955541</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.008483203030008e-06</v>
+        <v>6.656450658599064e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8768153250799705</v>
+        <v>0.9109589162388128</v>
       </c>
     </row>
     <row r="3">
@@ -1294,7 +1267,7 @@
         <v>106.605</v>
       </c>
       <c r="C3" t="n">
-        <v>713.6497531870107</v>
+        <v>106.605</v>
       </c>
       <c r="D3" t="n">
         <v>4.44371e-07</v>
@@ -1326,11 +1299,10 @@
       <c r="X3" t="n">
         <v>-8555.250389915491</v>
       </c>
-      <c r="Y3" t="n">
-        <v>424.1085412556876</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>103316021.9869039</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>8.943508687437834e-07</v>
@@ -1347,7 +1319,7 @@
         <v>100.546</v>
       </c>
       <c r="C4" t="n">
-        <v>667.6738638327722</v>
+        <v>100.546</v>
       </c>
       <c r="D4" t="n">
         <v>4.43179e-07</v>
@@ -1379,11 +1351,10 @@
       <c r="X4" t="n">
         <v>-8601.813200262834</v>
       </c>
-      <c r="Y4" t="n">
-        <v>418.9522391080113</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>37718787.45935754</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>8.557950415430884e-07</v>
@@ -1400,7 +1371,7 @@
         <v>96.899</v>
       </c>
       <c r="C5" t="n">
-        <v>656.4302997640609</v>
+        <v>247.368800616263</v>
       </c>
       <c r="D5" t="n">
         <v>4.41995e-07</v>
@@ -1433,16 +1404,13 @@
         <v>-8602.648156780922</v>
       </c>
       <c r="Y5" t="n">
-        <v>415.0262851245232</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>341754844.5517014</v>
+        <v>211.1371387748853</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.321549054307094e-07</v>
+        <v>8.70856003276709e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.9045421916477052</v>
+        <v>0.9061782386821448</v>
       </c>
     </row>
     <row r="6">
@@ -1453,7 +1421,7 @@
         <v>96.03699999999998</v>
       </c>
       <c r="C6" t="n">
-        <v>680.090879666216</v>
+        <v>243.3782657960244</v>
       </c>
       <c r="D6" t="n">
         <v>4.40925e-07</v>
@@ -1486,16 +1454,13 @@
         <v>-8960.890612911184</v>
       </c>
       <c r="Y6" t="n">
-        <v>410.983898887697</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>169185510.2121852</v>
+        <v>210.6621087180095</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.130490827824994e-07</v>
+        <v>8.635171779451237e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.9076742869282133</v>
+        <v>0.9086359202899976</v>
       </c>
     </row>
     <row r="7">
@@ -1506,7 +1471,7 @@
         <v>93.70499999999998</v>
       </c>
       <c r="C7" t="n">
-        <v>686.111655797867</v>
+        <v>93.70499999999998</v>
       </c>
       <c r="D7" t="n">
         <v>4.40216e-07</v>
@@ -1538,11 +1503,10 @@
       <c r="X7" t="n">
         <v>-9088.720059306743</v>
       </c>
-      <c r="Y7" t="n">
-        <v>406.7603474091602</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>225999761.0266023</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>7.966910835692676e-07</v>
@@ -1559,7 +1523,7 @@
         <v>89.05399999999997</v>
       </c>
       <c r="C8" t="n">
-        <v>649.7944101664943</v>
+        <v>234.2609221833207</v>
       </c>
       <c r="D8" t="n">
         <v>4.39602e-07</v>
@@ -1592,16 +1556,13 @@
         <v>-8516.874534006982</v>
       </c>
       <c r="Y8" t="n">
-        <v>402.4949007440025</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>221187425.3334227</v>
+        <v>208.1186091778975</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.834205066514079e-07</v>
+        <v>7.77696123214339e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.912799689768508</v>
+        <v>0.917581784304662</v>
       </c>
     </row>
     <row r="9">
@@ -1612,7 +1573,7 @@
         <v>88.11700000000002</v>
       </c>
       <c r="C9" t="n">
-        <v>656.3595523498944</v>
+        <v>88.11700000000002</v>
       </c>
       <c r="D9" t="n">
         <v>4.39295e-07</v>
@@ -1644,11 +1605,10 @@
       <c r="X9" t="n">
         <v>-8878.657663706701</v>
       </c>
-      <c r="Y9" t="n">
-        <v>398.5084272840842</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>440368840.7393088</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>7.699376669980727e-07</v>
@@ -1665,7 +1625,7 @@
         <v>84.762</v>
       </c>
       <c r="C10" t="n">
-        <v>648.4239826662224</v>
+        <v>227.1751801631002</v>
       </c>
       <c r="D10" t="n">
         <v>4.38897e-07</v>
@@ -1698,16 +1658,13 @@
         <v>-8718.879094286116</v>
       </c>
       <c r="Y10" t="n">
-        <v>394.7192300493788</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>216432961.9668211</v>
+        <v>206.1021147971382</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.579703599375671e-07</v>
+        <v>7.523955252822934e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9175166126156107</v>
+        <v>0.9230486778464599</v>
       </c>
     </row>
     <row r="11">
@@ -1718,7 +1675,7 @@
         <v>83.26099999999997</v>
       </c>
       <c r="C11" t="n">
-        <v>648.2540632578232</v>
+        <v>227.067305054051</v>
       </c>
       <c r="D11" t="n">
         <v>4.38463e-07</v>
@@ -1751,16 +1708,13 @@
         <v>-8776.357454076953</v>
       </c>
       <c r="Y11" t="n">
-        <v>391.2934095908259</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>164604808.5796399</v>
+        <v>201.7966502155279</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.476361312322177e-07</v>
+        <v>7.138624498424078e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9194328954308543</v>
+        <v>0.9257464047725557</v>
       </c>
     </row>
     <row r="12">
@@ -1771,7 +1725,7 @@
         <v>82.06399999999996</v>
       </c>
       <c r="C12" t="n">
-        <v>647.03948546486</v>
+        <v>82.06399999999996</v>
       </c>
       <c r="D12" t="n">
         <v>4.38079e-07</v>
@@ -1803,11 +1757,10 @@
       <c r="X12" t="n">
         <v>-8867.959509423963</v>
       </c>
-      <c r="Y12" t="n">
-        <v>387.9888220539746</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>636982177.1051949</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>7.38636039839273e-07</v>
@@ -1824,7 +1777,7 @@
         <v>78.935</v>
       </c>
       <c r="C13" t="n">
-        <v>641.8487406465758</v>
+        <v>221.5780166290493</v>
       </c>
       <c r="D13" t="n">
         <v>4.38024e-07</v>
@@ -1857,16 +1810,13 @@
         <v>-8588.119164103447</v>
       </c>
       <c r="Y13" t="n">
-        <v>384.8544064891893</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>210467638.5578675</v>
+        <v>199.9152313334998</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.313274669477334e-07</v>
+        <v>6.948828566441212e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9225964107236322</v>
+        <v>0.9303378268640712</v>
       </c>
     </row>
     <row r="14">
@@ -1877,7 +1827,7 @@
         <v>79.26299999999998</v>
       </c>
       <c r="C14" t="n">
-        <v>643.6944774244892</v>
+        <v>222.3128939110321</v>
       </c>
       <c r="D14" t="n">
         <v>4.3775e-07</v>
@@ -1910,16 +1860,13 @@
         <v>-8983.087148939432</v>
       </c>
       <c r="Y14" t="n">
-        <v>381.7959252873379</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>417794686.5864821</v>
+        <v>195.192741020245</v>
       </c>
       <c r="AA14" t="n">
-        <v>7.24701217516823e-07</v>
+        <v>6.654680186982608e-09</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.9238740285267643</v>
+        <v>0.9315570754346812</v>
       </c>
     </row>
     <row r="15">
@@ -1930,7 +1877,7 @@
         <v>79.89800000000002</v>
       </c>
       <c r="C15" t="n">
-        <v>684.8597005079682</v>
+        <v>79.89800000000002</v>
       </c>
       <c r="D15" t="n">
         <v>4.37654e-07</v>
@@ -1962,11 +1909,10 @@
       <c r="X15" t="n">
         <v>-9509.995708780943</v>
       </c>
-      <c r="Y15" t="n">
-        <v>378.7175037836427</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>103760347.6214598</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>7.16790368695532e-07</v>
@@ -1983,7 +1929,7 @@
         <v>77.23200000000003</v>
       </c>
       <c r="C16" t="n">
-        <v>641.376145921137</v>
+        <v>77.23200000000003</v>
       </c>
       <c r="D16" t="n">
         <v>4.3758e-07</v>
@@ -2015,11 +1961,10 @@
       <c r="X16" t="n">
         <v>-9138.471431213011</v>
       </c>
-      <c r="Y16" t="n">
-        <v>375.6815895349957</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>208214067.9970274</v>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA16" t="n">
         <v>7.11348877747008e-07</v>
@@ -2036,7 +1981,7 @@
         <v>75.50099999999998</v>
       </c>
       <c r="C17" t="n">
-        <v>657.9721710545239</v>
+        <v>75.50099999999998</v>
       </c>
       <c r="D17" t="n">
         <v>4.37357e-07</v>
@@ -2068,11 +2013,10 @@
       <c r="X17" t="n">
         <v>-9095.562659639783</v>
       </c>
-      <c r="Y17" t="n">
-        <v>372.6977934854936</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>152890524.945729</v>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA17" t="n">
         <v>7.058668754276769e-07</v>
@@ -2089,7 +2033,7 @@
         <v>73.53300000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>630.6661161990052</v>
+        <v>73.53300000000002</v>
       </c>
       <c r="D18" t="n">
         <v>4.37256e-07</v>
@@ -2121,11 +2065,10 @@
       <c r="X18" t="n">
         <v>-8768.552856788556</v>
       </c>
-      <c r="Y18" t="n">
-        <v>369.7578174330148</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>151738271.3552929</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>7.006918199967112e-07</v>
@@ -2142,7 +2085,7 @@
         <v>73.10199999999998</v>
       </c>
       <c r="C19" t="n">
-        <v>641.3960193748983</v>
+        <v>73.10199999999998</v>
       </c>
       <c r="D19" t="n">
         <v>4.37343e-07</v>
@@ -2174,11 +2117,10 @@
       <c r="X19" t="n">
         <v>-9033.73252079194</v>
       </c>
-      <c r="Y19" t="n">
-        <v>366.856079214409</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>306931823.3678589</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>6.943042421514423e-07</v>
@@ -2195,7 +2137,7 @@
         <v>72.32600000000002</v>
       </c>
       <c r="C20" t="n">
-        <v>668.3984943511233</v>
+        <v>72.32600000000002</v>
       </c>
       <c r="D20" t="n">
         <v>4.37165e-07</v>
@@ -2227,11 +2169,10 @@
       <c r="X20" t="n">
         <v>-9187.912833391589</v>
       </c>
-      <c r="Y20" t="n">
-        <v>363.8768205576325</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>199021235.4283823</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>6.88108748222111e-07</v>
@@ -2248,7 +2189,7 @@
         <v>71.55400000000003</v>
       </c>
       <c r="C21" t="n">
-        <v>684.1803828341108</v>
+        <v>71.55400000000003</v>
       </c>
       <c r="D21" t="n">
         <v>4.37066e-07</v>
@@ -2280,11 +2221,10 @@
       <c r="X21" t="n">
         <v>-9241.637290420997</v>
       </c>
-      <c r="Y21" t="n">
-        <v>360.9486237394665</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>183919532.2370981</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>6.83569896970495e-07</v>
@@ -2301,7 +2241,7 @@
         <v>69.53000000000003</v>
       </c>
       <c r="C22" t="n">
-        <v>631.3314001309458</v>
+        <v>196.4027710076599</v>
       </c>
       <c r="D22" t="n">
         <v>4.36996e-07</v>
@@ -2334,16 +2274,13 @@
         <v>-8897.678884716743</v>
       </c>
       <c r="Y22" t="n">
-        <v>357.9682818640612</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>1270462204.530481</v>
+        <v>193.7208211975801</v>
       </c>
       <c r="AA22" t="n">
-        <v>6.795181011603263e-07</v>
+        <v>5.980132610953426e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.9332925960956555</v>
+        <v>0.952124785920649</v>
       </c>
     </row>
   </sheetData>
@@ -2500,7 +2437,7 @@
         <v>129.108</v>
       </c>
       <c r="C2" t="n">
-        <v>936.2287021263882</v>
+        <v>275.5655255490741</v>
       </c>
       <c r="D2" t="n">
         <v>4.28239e-07</v>
@@ -2533,16 +2470,13 @@
         <v>-7446.211464551119</v>
       </c>
       <c r="Y2" t="n">
-        <v>433.0755477598454</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>189294391.1809571</v>
+        <v>202.9437112974075</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.922148824033418e-07</v>
+        <v>6.08970210150385e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8731068589040796</v>
+        <v>0.9199403696720266</v>
       </c>
     </row>
     <row r="3">
@@ -2553,7 +2487,7 @@
         <v>109.101</v>
       </c>
       <c r="C3" t="n">
-        <v>688.9215461118637</v>
+        <v>266.3502819996833</v>
       </c>
       <c r="D3" t="n">
         <v>4.26096e-07</v>
@@ -2586,16 +2520,13 @@
         <v>-8081.026531394899</v>
       </c>
       <c r="Y3" t="n">
-        <v>422.2385358405232</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>59708384.05879393</v>
+        <v>200.4105928440121</v>
       </c>
       <c r="AA3" t="n">
-        <v>8.529639486165217e-07</v>
+        <v>7.286214905198477e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8950227877615352</v>
+        <v>0.9099976673560036</v>
       </c>
     </row>
     <row r="4">
@@ -2606,7 +2537,7 @@
         <v>103.232</v>
       </c>
       <c r="C4" t="n">
-        <v>658.6159919993078</v>
+        <v>255.6053204444733</v>
       </c>
       <c r="D4" t="n">
         <v>4.2453e-07</v>
@@ -2639,16 +2570,13 @@
         <v>-8188.275960781168</v>
       </c>
       <c r="Y4" t="n">
-        <v>417.5884862461021</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>36044888.17761886</v>
+        <v>206.2777581694981</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.125703972419277e-07</v>
+        <v>7.759352731808683e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9017663342807797</v>
+        <v>0.9111705615664077</v>
       </c>
     </row>
     <row r="5">
@@ -2659,7 +2587,7 @@
         <v>103.322</v>
       </c>
       <c r="C5" t="n">
-        <v>701.300580316535</v>
+        <v>103.322</v>
       </c>
       <c r="D5" t="n">
         <v>4.23514e-07</v>
@@ -2691,11 +2619,10 @@
       <c r="X5" t="n">
         <v>-9059.944754414106</v>
       </c>
-      <c r="Y5" t="n">
-        <v>413.5496620947689</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>454790505.9308857</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>7.88163149573542e-07</v>
@@ -2712,7 +2639,7 @@
         <v>97.82499999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>647.1263633350176</v>
+        <v>97.82499999999999</v>
       </c>
       <c r="D6" t="n">
         <v>4.22845e-07</v>
@@ -2744,11 +2671,10 @@
       <c r="X6" t="n">
         <v>-8396.355584876788</v>
       </c>
-      <c r="Y6" t="n">
-        <v>409.3882828900535</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>449681904.7030554</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>7.704798527426754e-07</v>
@@ -2765,7 +2691,7 @@
         <v>96.84500000000003</v>
       </c>
       <c r="C7" t="n">
-        <v>667.8147788170378</v>
+        <v>242.0069366893809</v>
       </c>
       <c r="D7" t="n">
         <v>4.22367e-07</v>
@@ -2798,16 +2724,13 @@
         <v>-8742.078544092812</v>
       </c>
       <c r="Y7" t="n">
-        <v>405.0572527687936</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>222551452.9046378</v>
+        <v>204.421604371853</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.550447286602293e-07</v>
+        <v>7.156815113785817e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.912034098651431</v>
+        <v>0.922358655680706</v>
       </c>
     </row>
     <row r="8">
@@ -2818,7 +2741,7 @@
         <v>93.31200000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>664.9233432644954</v>
+        <v>237.6826588629553</v>
       </c>
       <c r="D8" t="n">
         <v>4.2209e-07</v>
@@ -2851,16 +2774,13 @@
         <v>-8657.704968765431</v>
       </c>
       <c r="Y8" t="n">
-        <v>400.7303388075825</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>219694685.1342096</v>
+        <v>203.5705765274378</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.417855691438191e-07</v>
+        <v>7.01105350765427e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9145978154303235</v>
+        <v>0.9255452667453306</v>
       </c>
     </row>
     <row r="9">
@@ -2871,7 +2791,7 @@
         <v>90.22899999999998</v>
       </c>
       <c r="C9" t="n">
-        <v>651.8200565219901</v>
+        <v>239.7648567154045</v>
       </c>
       <c r="D9" t="n">
         <v>4.22084e-07</v>
@@ -2904,16 +2824,13 @@
         <v>-8507.557493821065</v>
       </c>
       <c r="Y9" t="n">
-        <v>396.5803041922406</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>326131378.9680545</v>
+        <v>195.7460909798888</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.318785446524434e-07</v>
+        <v>6.497247260086743e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9166306031253019</v>
+        <v>0.9275324301334351</v>
       </c>
     </row>
     <row r="10">
@@ -2924,7 +2841,7 @@
         <v>88.00999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>646.0487812634905</v>
+        <v>237.3749855686762</v>
       </c>
       <c r="D10" t="n">
         <v>4.21893e-07</v>
@@ -2957,16 +2874,13 @@
         <v>-8480.874046406934</v>
       </c>
       <c r="Y10" t="n">
-        <v>392.6631975947702</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>329255284.1881668</v>
+        <v>194.844878419513</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.208276239277801e-07</v>
+        <v>6.976810579612623e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9188212921463067</v>
+        <v>0.9243891143278269</v>
       </c>
     </row>
     <row r="11">
@@ -2977,7 +2891,7 @@
         <v>87.58699999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>668.9647490216912</v>
+        <v>232.5327358408306</v>
       </c>
       <c r="D11" t="n">
         <v>4.21756e-07</v>
@@ -3010,16 +2924,13 @@
         <v>-8937.783194451338</v>
       </c>
       <c r="Y11" t="n">
-        <v>388.9439630694364</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>159855868.3902268</v>
+        <v>193.8885735047691</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.111089980067962e-07</v>
+        <v>6.410457504076683e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9208507833971519</v>
+        <v>0.9316138086931188</v>
       </c>
     </row>
     <row r="12">
@@ -3030,7 +2941,7 @@
         <v>84.745</v>
       </c>
       <c r="C12" t="n">
-        <v>651.3164943036192</v>
+        <v>229.2680158066162</v>
       </c>
       <c r="D12" t="n">
         <v>4.21658e-07</v>
@@ -3063,16 +2974,13 @@
         <v>-8607.0140055543</v>
       </c>
       <c r="Y12" t="n">
-        <v>385.4121407138171</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>116870617.8895902</v>
+        <v>193.5584586127191</v>
       </c>
       <c r="AA12" t="n">
-        <v>7.044464394495368e-07</v>
+        <v>6.295954443507889e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9222454363731062</v>
+        <v>0.9347964997087718</v>
       </c>
     </row>
     <row r="13">
@@ -3083,7 +2991,7 @@
         <v>83.46300000000002</v>
       </c>
       <c r="C13" t="n">
-        <v>657.5202472954152</v>
+        <v>83.46300000000002</v>
       </c>
       <c r="D13" t="n">
         <v>4.21741e-07</v>
@@ -3115,11 +3023,10 @@
       <c r="X13" t="n">
         <v>-8691.97638429313</v>
       </c>
-      <c r="Y13" t="n">
-        <v>382.0050234085486</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>209171369.0694711</v>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>6.981204294314548e-07</v>
@@ -3136,7 +3043,7 @@
         <v>81.57900000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>660.0897678654854</v>
+        <v>81.57900000000001</v>
       </c>
       <c r="D14" t="n">
         <v>4.21776e-07</v>
@@ -3168,11 +3075,10 @@
       <c r="X14" t="n">
         <v>-8616.6647375128</v>
       </c>
-      <c r="Y14" t="n">
-        <v>378.6541941245881</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>385677221.7194996</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>6.916289298655832e-07</v>
@@ -3189,7 +3095,7 @@
         <v>79.45000000000005</v>
       </c>
       <c r="C15" t="n">
-        <v>659.0192601933589</v>
+        <v>79.45000000000005</v>
       </c>
       <c r="D15" t="n">
         <v>4.21873e-07</v>
@@ -3221,11 +3127,10 @@
       <c r="X15" t="n">
         <v>-8548.286852487357</v>
       </c>
-      <c r="Y15" t="n">
-        <v>375.5427336321978</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>154990064.9209351</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>6.85072256865229e-07</v>
@@ -3242,7 +3147,7 @@
         <v>78.75599999999997</v>
       </c>
       <c r="C16" t="n">
-        <v>660.6303099470944</v>
+        <v>219.2425627884013</v>
       </c>
       <c r="D16" t="n">
         <v>4.21857e-07</v>
@@ -3275,16 +3180,13 @@
         <v>-8751.372774631207</v>
       </c>
       <c r="Y16" t="n">
-        <v>372.5235151616664</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>305699367.8179162</v>
+        <v>187.7688367414725</v>
       </c>
       <c r="AA16" t="n">
-        <v>6.798831791571903e-07</v>
+        <v>5.753606834109308e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9276594653105199</v>
+        <v>0.943271659348526</v>
       </c>
     </row>
     <row r="17">
@@ -3295,7 +3197,7 @@
         <v>76.27600000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>623.7645572957276</v>
+        <v>210.7766813308193</v>
       </c>
       <c r="D17" t="n">
         <v>4.21774e-07</v>
@@ -3328,16 +3230,13 @@
         <v>-8336.351888326819</v>
       </c>
       <c r="Y17" t="n">
-        <v>369.5490524095136</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>112075823.0648189</v>
+        <v>193.0628066167137</v>
       </c>
       <c r="AA17" t="n">
-        <v>6.754387727039867e-07</v>
+        <v>5.919204777074212e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9286325555176161</v>
+        <v>0.9462978745148412</v>
       </c>
     </row>
     <row r="18">
@@ -3348,7 +3247,7 @@
         <v>75.935</v>
       </c>
       <c r="C18" t="n">
-        <v>652.7246587300516</v>
+        <v>207.595951035287</v>
       </c>
       <c r="D18" t="n">
         <v>4.21905e-07</v>
@@ -3381,16 +3280,13 @@
         <v>-8702.470732248117</v>
       </c>
       <c r="Y18" t="n">
-        <v>366.5906727641661</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>200470441.3851776</v>
+        <v>192.4724842113749</v>
       </c>
       <c r="AA18" t="n">
-        <v>6.711142224885672e-07</v>
+        <v>5.843044654466032e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9296439902348186</v>
+        <v>0.9486937319333727</v>
       </c>
     </row>
     <row r="19">
@@ -3401,7 +3297,7 @@
         <v>74.28999999999996</v>
       </c>
       <c r="C19" t="n">
-        <v>657.5764947682455</v>
+        <v>74.28999999999996</v>
       </c>
       <c r="D19" t="n">
         <v>4.22086e-07</v>
@@ -3433,11 +3329,10 @@
       <c r="X19" t="n">
         <v>-8541.704394462253</v>
       </c>
-      <c r="Y19" t="n">
-        <v>363.711147851523</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>101810104.8653887</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>6.675263665375564e-07</v>
@@ -3454,7 +3349,7 @@
         <v>72.767</v>
       </c>
       <c r="C20" t="n">
-        <v>651.8143057081736</v>
+        <v>202.4280925725969</v>
       </c>
       <c r="D20" t="n">
         <v>4.22095e-07</v>
@@ -3487,16 +3382,13 @@
         <v>-8481.65815018914</v>
       </c>
       <c r="Y20" t="n">
-        <v>360.8848523078199</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>788563842.0398979</v>
+        <v>191.0946508489662</v>
       </c>
       <c r="AA20" t="n">
-        <v>6.626457979894738e-07</v>
+        <v>5.766129595894874e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9316335793742081</v>
+        <v>0.9505672338172825</v>
       </c>
     </row>
     <row r="21">
@@ -3507,7 +3399,7 @@
         <v>71.50700000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>620.0701320100694</v>
+        <v>214.4581025039486</v>
       </c>
       <c r="D21" t="n">
         <v>4.22186e-07</v>
@@ -3540,16 +3432,13 @@
         <v>-8392.940558782655</v>
       </c>
       <c r="Y21" t="n">
-        <v>358.1705882762301</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>294176667.7708919</v>
+        <v>175.2570568119838</v>
       </c>
       <c r="AA21" t="n">
-        <v>6.582015866471859e-07</v>
+        <v>5.061090396981637e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.932678957115012</v>
+        <v>0.9514787801854225</v>
       </c>
     </row>
     <row r="22">
@@ -3560,7 +3449,7 @@
         <v>71.55099999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>649.3861581990768</v>
+        <v>71.55099999999999</v>
       </c>
       <c r="D22" t="n">
         <v>4.22288e-07</v>
@@ -3592,11 +3481,10 @@
       <c r="X22" t="n">
         <v>-8624.156160304748</v>
       </c>
-      <c r="Y22" t="n">
-        <v>355.4980297768718</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>195786323.3136893</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>6.538806611654203e-07</v>
@@ -3759,7 +3647,7 @@
         <v>124.143</v>
       </c>
       <c r="C2" t="n">
-        <v>3155.63806226789</v>
+        <v>241.0606047039136</v>
       </c>
       <c r="D2" t="n">
         <v>4.58367e-07</v>
@@ -3792,16 +3680,13 @@
         <v>-4623.594987243592</v>
       </c>
       <c r="Y2" t="n">
-        <v>399.1107394250932</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>438446194.1489649</v>
+        <v>192.8857394327653</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.317512045825061e-06</v>
+        <v>3.596573730614208e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8416291881512713</v>
+        <v>0.9610827027210566</v>
       </c>
     </row>
     <row r="3">
@@ -3812,7 +3697,7 @@
         <v>84.48000000000002</v>
       </c>
       <c r="C3" t="n">
-        <v>803.0206544290256</v>
+        <v>227.3804331116178</v>
       </c>
       <c r="D3" t="n">
         <v>4.64888e-07</v>
@@ -3845,16 +3730,13 @@
         <v>-5156.460874532487</v>
       </c>
       <c r="Y3" t="n">
-        <v>376.7446016448904</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>412906226.6559771</v>
+        <v>183.4356467706833</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.982360272586506e-07</v>
+        <v>5.322457169672815e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8852216569213783</v>
+        <v>0.9397109688727332</v>
       </c>
     </row>
     <row r="4">
@@ -3865,7 +3747,7 @@
         <v>75.40500000000003</v>
       </c>
       <c r="C4" t="n">
-        <v>703.1211463154615</v>
+        <v>216.020504572917</v>
       </c>
       <c r="D4" t="n">
         <v>4.62057e-07</v>
@@ -3898,16 +3780,13 @@
         <v>-5514.607458360963</v>
       </c>
       <c r="Y4" t="n">
-        <v>368.9296501274155</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>202042743.9430597</v>
+        <v>186.9894452589869</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.120585127132215e-07</v>
+        <v>5.787887666859605e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8977624772184749</v>
+        <v>0.9422926536231049</v>
       </c>
     </row>
     <row r="5">
@@ -3918,7 +3797,7 @@
         <v>70.87700000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>641.5032125678089</v>
+        <v>70.87700000000001</v>
       </c>
       <c r="D5" t="n">
         <v>4.58705e-07</v>
@@ -3950,11 +3829,10 @@
       <c r="X5" t="n">
         <v>-5623.004521106845</v>
       </c>
-      <c r="Y5" t="n">
-        <v>363.7664924369331</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>200541967.061127</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>8.648920944189094e-07</v>
@@ -3971,7 +3849,7 @@
         <v>69.327</v>
       </c>
       <c r="C6" t="n">
-        <v>689.5297847975535</v>
+        <v>69.327</v>
       </c>
       <c r="D6" t="n">
         <v>4.5565e-07</v>
@@ -4003,11 +3881,10 @@
       <c r="X6" t="n">
         <v>-5891.785405700944</v>
       </c>
-      <c r="Y6" t="n">
-        <v>359.0947097940731</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>98275559.66834185</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>8.299639251073624e-07</v>
@@ -4024,7 +3901,7 @@
         <v>67.33199999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>704.5177030422943</v>
+        <v>191.3212056045977</v>
       </c>
       <c r="D7" t="n">
         <v>4.53261e-07</v>
@@ -4057,16 +3934,13 @@
         <v>-6129.945738199643</v>
       </c>
       <c r="Y7" t="n">
-        <v>354.4718578756008</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>389018917.1033631</v>
+        <v>193.9300349269734</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.025533379876564e-07</v>
+        <v>5.508591414903618e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.913935640009838</v>
+        <v>0.9575336978485482</v>
       </c>
     </row>
     <row r="8">
@@ -4077,7 +3951,7 @@
         <v>64.70999999999998</v>
       </c>
       <c r="C8" t="n">
-        <v>710.6261843403965</v>
+        <v>186.8229641419788</v>
       </c>
       <c r="D8" t="n">
         <v>4.51167e-07</v>
@@ -4110,16 +3984,13 @@
         <v>-6183.843153199383</v>
       </c>
       <c r="Y8" t="n">
-        <v>349.8973545128995</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>143423329.243043</v>
+        <v>192.6397309088283</v>
       </c>
       <c r="AA8" t="n">
-        <v>7.800550646503015e-07</v>
+        <v>5.29163594265999e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9174801160845886</v>
+        <v>0.9614743675959011</v>
       </c>
     </row>
     <row r="9">
@@ -4130,7 +4001,7 @@
         <v>62.04999999999995</v>
       </c>
       <c r="C9" t="n">
-        <v>716.8243195581902</v>
+        <v>182.7962413544894</v>
       </c>
       <c r="D9" t="n">
         <v>4.49551e-07</v>
@@ -4163,16 +4034,13 @@
         <v>-6260.834587116743</v>
       </c>
       <c r="Y9" t="n">
-        <v>345.5275287145916</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>188617771.1430337</v>
+        <v>191.5574509019321</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.609167513772127e-07</v>
+        <v>5.15139789568654e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9206359726549826</v>
+        <v>0.9667532698500895</v>
       </c>
     </row>
     <row r="10">
@@ -4183,7 +4051,7 @@
         <v>60.31</v>
       </c>
       <c r="C10" t="n">
-        <v>727.123993983589</v>
+        <v>179.4135770871539</v>
       </c>
       <c r="D10" t="n">
         <v>4.47803e-07</v>
@@ -4216,16 +4084,13 @@
         <v>-6308.094701077208</v>
       </c>
       <c r="Y10" t="n">
-        <v>341.3931195897867</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>279365939.1792666</v>
+        <v>191.0573368184867</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.449007832611085e-07</v>
+        <v>5.294583681977069e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9232423324097968</v>
+        <v>0.9672571694859677</v>
       </c>
     </row>
     <row r="11">
@@ -4236,7 +4101,7 @@
         <v>59.291</v>
       </c>
       <c r="C11" t="n">
-        <v>817.7970237542532</v>
+        <v>59.291</v>
       </c>
       <c r="D11" t="n">
         <v>4.46535e-07</v>
@@ -4268,11 +4133,10 @@
       <c r="X11" t="n">
         <v>-6541.747066667391</v>
       </c>
-      <c r="Y11" t="n">
-        <v>337.5217223839763</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>184256538.910268</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>7.29545926736977e-07</v>
@@ -4435,7 +4299,7 @@
         <v>126.633</v>
       </c>
       <c r="C2" t="n">
-        <v>874.8576373914515</v>
+        <v>279.2424657648739</v>
       </c>
       <c r="D2" t="n">
         <v>4.62212e-07</v>
@@ -4468,16 +4332,13 @@
         <v>-5928.530747659112</v>
       </c>
       <c r="Y2" t="n">
-        <v>430.3375601763885</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>177345990.1357034</v>
+        <v>198.5942584296369</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.312691647084753e-06</v>
+        <v>7.20594163508478e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8430872232040106</v>
+        <v>0.9045325966477242</v>
       </c>
     </row>
     <row r="3">
@@ -4488,7 +4349,7 @@
         <v>109.67</v>
       </c>
       <c r="C3" t="n">
-        <v>685.0452487694256</v>
+        <v>109.67</v>
       </c>
       <c r="D3" t="n">
         <v>4.59991e-07</v>
@@ -4520,11 +4381,10 @@
       <c r="X3" t="n">
         <v>-6692.468863382832</v>
       </c>
-      <c r="Y3" t="n">
-        <v>419.8009996635196</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>50360310.56373951</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.074401804569402e-06</v>
@@ -4541,7 +4401,7 @@
         <v>102.344</v>
       </c>
       <c r="C4" t="n">
-        <v>635.0165402559239</v>
+        <v>102.344</v>
       </c>
       <c r="D4" t="n">
         <v>4.57266e-07</v>
@@ -4573,11 +4433,10 @@
       <c r="X4" t="n">
         <v>-6860.358282151244</v>
       </c>
-      <c r="Y4" t="n">
-        <v>415.1516060485824</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>161636050.9926125</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>9.967437724492801e-07</v>
@@ -4594,7 +4453,7 @@
         <v>101.124</v>
       </c>
       <c r="C5" t="n">
-        <v>654.1365810640671</v>
+        <v>101.124</v>
       </c>
       <c r="D5" t="n">
         <v>4.54742e-07</v>
@@ -4626,11 +4485,10 @@
       <c r="X5" t="n">
         <v>-7310.533424839303</v>
       </c>
-      <c r="Y5" t="n">
-        <v>411.1660005968433</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>171120962.1477516</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>9.500555416419336e-07</v>
@@ -4647,7 +4505,7 @@
         <v>97.53200000000004</v>
       </c>
       <c r="C6" t="n">
-        <v>639.3980852990893</v>
+        <v>248.5452233132899</v>
       </c>
       <c r="D6" t="n">
         <v>4.52903e-07</v>
@@ -4680,16 +4538,13 @@
         <v>-7253.939141756458</v>
       </c>
       <c r="Y6" t="n">
-        <v>407.0124660538758</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>224782532.1097848</v>
+        <v>203.1453744155297</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.148654314970473e-07</v>
+        <v>9.228282304198647e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8939534840873773</v>
+        <v>0.9013686247386464</v>
       </c>
     </row>
     <row r="7">
@@ -4700,7 +4555,7 @@
         <v>94.90600000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>644.8802155549746</v>
+        <v>94.90600000000001</v>
       </c>
       <c r="D7" t="n">
         <v>4.51503e-07</v>
@@ -4732,11 +4587,10 @@
       <c r="X7" t="n">
         <v>-7410.799510043837</v>
       </c>
-      <c r="Y7" t="n">
-        <v>402.6703652962622</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>221444165.4908842</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>8.865235839604954e-07</v>
@@ -4753,7 +4607,7 @@
         <v>93.04000000000002</v>
       </c>
       <c r="C8" t="n">
-        <v>653.4046936808984</v>
+        <v>239.9253285367745</v>
       </c>
       <c r="D8" t="n">
         <v>4.50016e-07</v>
@@ -4786,16 +4640,13 @@
         <v>-7632.948425748457</v>
       </c>
       <c r="Y8" t="n">
-        <v>398.3747443705986</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>218891627.6862209</v>
+        <v>199.1465416720376</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.617305433626118e-07</v>
+        <v>7.568427278182528e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9019582986173899</v>
+        <v>0.9175165454323739</v>
       </c>
     </row>
     <row r="9">
@@ -4806,7 +4657,7 @@
         <v>90.173</v>
       </c>
       <c r="C9" t="n">
-        <v>649.3640530642965</v>
+        <v>236.706033163049</v>
       </c>
       <c r="D9" t="n">
         <v>4.48717e-07</v>
@@ -4839,16 +4690,13 @@
         <v>-7727.753523083717</v>
       </c>
       <c r="Y9" t="n">
-        <v>394.4347314518075</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>432269489.553234</v>
+        <v>199.5846839255638</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.409253555724308e-07</v>
+        <v>8.710646255187705e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9051804329360816</v>
+        <v>0.9093208606775804</v>
       </c>
     </row>
     <row r="10">
@@ -4859,7 +4707,7 @@
         <v>87.74800000000005</v>
       </c>
       <c r="C10" t="n">
-        <v>632.6456809622277</v>
+        <v>87.74800000000005</v>
       </c>
       <c r="D10" t="n">
         <v>4.47817e-07</v>
@@ -4891,11 +4739,10 @@
       <c r="X10" t="n">
         <v>-7688.241306720884</v>
       </c>
-      <c r="Y10" t="n">
-        <v>390.8375003359115</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>428395885.152842</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>8.211383059960402e-07</v>
@@ -4912,7 +4759,7 @@
         <v>86.12</v>
       </c>
       <c r="C11" t="n">
-        <v>636.3638549313672</v>
+        <v>228.6077702989032</v>
       </c>
       <c r="D11" t="n">
         <v>4.46873e-07</v>
@@ -4945,16 +4792,13 @@
         <v>-7815.289419813595</v>
       </c>
       <c r="Y11" t="n">
-        <v>387.453420771319</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>213964053.8038524</v>
+        <v>196.5247794935082</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.063701352079936e-07</v>
+        <v>7.092012356981486e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9108344549519343</v>
+        <v>0.9258002019853316</v>
       </c>
     </row>
     <row r="12">
@@ -4965,7 +4809,7 @@
         <v>85.72300000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>646.27187925997</v>
+        <v>85.72300000000001</v>
       </c>
       <c r="D12" t="n">
         <v>4.45936e-07</v>
@@ -4997,11 +4841,10 @@
       <c r="X12" t="n">
         <v>-8081.105502885852</v>
       </c>
-      <c r="Y12" t="n">
-        <v>384.2698611246886</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>211121508.1296392</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>7.926384331754758e-07</v>
@@ -5018,7 +4861,7 @@
         <v>82.25900000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>624.494009119665</v>
+        <v>221.7127420251749</v>
       </c>
       <c r="D13" t="n">
         <v>4.45247e-07</v>
@@ -5051,16 +4894,13 @@
         <v>-7775.94910073984</v>
       </c>
       <c r="Y13" t="n">
-        <v>381.2286649902834</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>313014959.4294567</v>
+        <v>196.1691927514078</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.814934457548496e-07</v>
+        <v>6.844952951873025e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9149875159325446</v>
+        <v>0.9303169105542378</v>
       </c>
     </row>
     <row r="14">
@@ -5071,7 +4911,7 @@
         <v>82.39699999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>619.9636012446135</v>
+        <v>82.39699999999999</v>
       </c>
       <c r="D14" t="n">
         <v>4.44504e-07</v>
@@ -5103,11 +4943,10 @@
       <c r="X14" t="n">
         <v>-7988.5966968354</v>
       </c>
-      <c r="Y14" t="n">
-        <v>378.2434279452024</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>414211151.969752</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>7.716591258289905e-07</v>
@@ -5124,7 +4963,7 @@
         <v>80.50900000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>632.1873959688705</v>
+        <v>216.6182829945408</v>
       </c>
       <c r="D15" t="n">
         <v>4.43868e-07</v>
@@ -5157,16 +4996,13 @@
         <v>-8110.328318765581</v>
       </c>
       <c r="Y15" t="n">
-        <v>375.3233192145844</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>411216768.2207509</v>
+        <v>195.079223028552</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.612174688380247e-07</v>
+        <v>7.033344260110918e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9184570620464072</v>
+        <v>0.9317285796499265</v>
       </c>
     </row>
     <row r="16">
@@ -5177,7 +5013,7 @@
         <v>79.62600000000003</v>
       </c>
       <c r="C16" t="n">
-        <v>626.3976481946423</v>
+        <v>215.0545883123891</v>
       </c>
       <c r="D16" t="n">
         <v>4.4356e-07</v>
@@ -5210,16 +5046,13 @@
         <v>-8048.507284433118</v>
       </c>
       <c r="Y16" t="n">
-        <v>372.4727883082132</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>305868352.3892522</v>
+        <v>194.0396353469861</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.530725144062699e-07</v>
+        <v>7.23713027630956e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9199711053264399</v>
+        <v>0.930640602349788</v>
       </c>
     </row>
     <row r="17">
@@ -5230,7 +5063,7 @@
         <v>77.30199999999996</v>
       </c>
       <c r="C17" t="n">
-        <v>623.2343674445448</v>
+        <v>211.478924595072</v>
       </c>
       <c r="D17" t="n">
         <v>4.42902e-07</v>
@@ -5263,16 +5096,13 @@
         <v>-7914.748228115303</v>
       </c>
       <c r="Y17" t="n">
-        <v>369.6354063846488</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>151861490.4505496</v>
+        <v>192.8751660086514</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.440256920703068e-07</v>
+        <v>6.420916030009866e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9215555928106822</v>
+        <v>0.9395505185278595</v>
       </c>
     </row>
     <row r="18">
@@ -5283,7 +5113,7 @@
         <v>76.89300000000003</v>
       </c>
       <c r="C18" t="n">
-        <v>631.4652882350346</v>
+        <v>209.8732662696822</v>
       </c>
       <c r="D18" t="n">
         <v>4.42504e-07</v>
@@ -5316,16 +5146,13 @@
         <v>-8083.850856494796</v>
       </c>
       <c r="Y18" t="n">
-        <v>366.8052324291342</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>301223118.9624547</v>
+        <v>192.3417753934907</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.358434797363799e-07</v>
+        <v>6.943320981695139e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9230799910191222</v>
+        <v>0.9355425319482937</v>
       </c>
     </row>
     <row r="19">
@@ -5336,7 +5163,7 @@
         <v>75.31400000000002</v>
       </c>
       <c r="C19" t="n">
-        <v>631.3232973719903</v>
+        <v>75.31400000000002</v>
       </c>
       <c r="D19" t="n">
         <v>4.42194e-07</v>
@@ -5368,11 +5195,10 @@
       <c r="X19" t="n">
         <v>-8124.66929687184</v>
       </c>
-      <c r="Y19" t="n">
-        <v>363.958078806506</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>896000990.8613718</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>7.300207471263049e-07</v>
@@ -5389,7 +5215,7 @@
         <v>75.01399999999995</v>
       </c>
       <c r="C20" t="n">
-        <v>632.7211897132238</v>
+        <v>231.7888822108527</v>
       </c>
       <c r="D20" t="n">
         <v>4.41998e-07</v>
@@ -5422,16 +5248,13 @@
         <v>-8232.125132821564</v>
       </c>
       <c r="Y20" t="n">
-        <v>361.1030437426311</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>197523750.4443202</v>
+        <v>161.2958078449766</v>
       </c>
       <c r="AA20" t="n">
-        <v>7.227657215465091e-07</v>
+        <v>5.188665915908253e-09</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.9255939660528533</v>
+        <v>0.9390423625561429</v>
       </c>
     </row>
     <row r="21">
@@ -5442,7 +5265,7 @@
         <v>73.20400000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>619.383539465166</v>
+        <v>227.5321982882519</v>
       </c>
       <c r="D21" t="n">
         <v>4.41749e-07</v>
@@ -5475,16 +5298,13 @@
         <v>-8065.044971962247</v>
       </c>
       <c r="Y21" t="n">
-        <v>358.2517734184513</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>195866476.6688291</v>
+        <v>162.3422856760035</v>
       </c>
       <c r="AA21" t="n">
-        <v>7.159869467681006e-07</v>
+        <v>5.186213708453722e-09</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.9269266376916596</v>
+        <v>0.9410912153147036</v>
       </c>
     </row>
     <row r="22">
@@ -5495,7 +5315,7 @@
         <v>71.86399999999998</v>
       </c>
       <c r="C22" t="n">
-        <v>616.3638810461654</v>
+        <v>220.7819084093204</v>
       </c>
       <c r="D22" t="n">
         <v>4.4155e-07</v>
@@ -5528,16 +5348,13 @@
         <v>-8061.252527263254</v>
       </c>
       <c r="Y22" t="n">
-        <v>355.4193524940902</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>388608664.1277252</v>
+        <v>166.1503667362745</v>
       </c>
       <c r="AA22" t="n">
-        <v>7.103629344653632e-07</v>
+        <v>5.245986962020285e-09</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.928042798095171</v>
+        <v>0.9444726707771707</v>
       </c>
     </row>
   </sheetData>
@@ -5694,7 +5511,7 @@
         <v>121.092</v>
       </c>
       <c r="C2" t="n">
-        <v>2352.192109664631</v>
+        <v>121.092</v>
       </c>
       <c r="D2" t="n">
         <v>4.8887e-07</v>
@@ -5726,11 +5543,10 @@
       <c r="X2" t="n">
         <v>-4283.493809854624</v>
       </c>
-      <c r="Y2" t="n">
-        <v>396.0480226192574</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>220341120.03033</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>1.580864204228818e-06</v>
@@ -5747,7 +5563,7 @@
         <v>83.94799999999998</v>
       </c>
       <c r="C3" t="n">
-        <v>780.5008265319979</v>
+        <v>224.8636392676889</v>
       </c>
       <c r="D3" t="n">
         <v>4.96942e-07</v>
@@ -5780,16 +5596,13 @@
         <v>-4759.723635532172</v>
       </c>
       <c r="Y3" t="n">
-        <v>376.1619019626904</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>206917800.2606733</v>
+        <v>187.0411817459277</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.167982552580774e-06</v>
+        <v>6.470234707193539e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8720335294883568</v>
+        <v>0.9283169440138738</v>
       </c>
     </row>
     <row r="4">
@@ -5800,7 +5613,7 @@
         <v>76.423</v>
       </c>
       <c r="C4" t="n">
-        <v>718.0817293895909</v>
+        <v>218.0339700704828</v>
       </c>
       <c r="D4" t="n">
         <v>4.93326e-07</v>
@@ -5833,16 +5646,13 @@
         <v>-5075.480918343761</v>
       </c>
       <c r="Y4" t="n">
-        <v>369.0674309948403</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>209377630.0668765</v>
+        <v>186.2089461164162</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.057263656926392e-06</v>
+        <v>6.922280780300548e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8857564486800935</v>
+        <v>0.9273957833527938</v>
       </c>
     </row>
     <row r="5">
@@ -5853,7 +5663,7 @@
         <v>73.19899999999996</v>
       </c>
       <c r="C5" t="n">
-        <v>690.233042440539</v>
+        <v>73.19899999999996</v>
       </c>
       <c r="D5" t="n">
         <v>4.891439999999999e-07</v>
@@ -5885,11 +5695,10 @@
       <c r="X5" t="n">
         <v>-5329.797388394029</v>
       </c>
-      <c r="Y5" t="n">
-        <v>364.1423670579533</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>697729078.7444665</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>9.933647794257932e-07</v>
@@ -5906,7 +5715,7 @@
         <v>68.11800000000005</v>
       </c>
       <c r="C6" t="n">
-        <v>642.9533744546808</v>
+        <v>68.11800000000005</v>
       </c>
       <c r="D6" t="n">
         <v>4.85406e-07</v>
@@ -5938,11 +5747,10 @@
       <c r="X6" t="n">
         <v>-5324.500811857602</v>
       </c>
-      <c r="Y6" t="n">
-        <v>359.4395566651669</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>196807789.3057901</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>9.460835482645655e-07</v>
@@ -5959,7 +5767,7 @@
         <v>66.875</v>
       </c>
       <c r="C7" t="n">
-        <v>672.3777381407684</v>
+        <v>198.4859029987728</v>
       </c>
       <c r="D7" t="n">
         <v>4.8182e-07</v>
@@ -5992,16 +5800,13 @@
         <v>-5542.81532576788</v>
       </c>
       <c r="Y7" t="n">
-        <v>354.6544064970562</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>679380841.0213003</v>
+        <v>186.963249240652</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.079446112459932e-07</v>
+        <v>5.854462630753068e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.904846474563714</v>
+        <v>0.9468316214655962</v>
       </c>
     </row>
     <row r="8">
@@ -6012,7 +5817,7 @@
         <v>64.42599999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>688.5220718046609</v>
+        <v>64.42599999999999</v>
       </c>
       <c r="D8" t="n">
         <v>4.78968e-07</v>
@@ -6044,11 +5849,10 @@
       <c r="X8" t="n">
         <v>-5645.649043492897</v>
       </c>
-      <c r="Y8" t="n">
-        <v>349.9431300454831</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>143457803.3713763</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>8.75602241623646e-07</v>
@@ -6065,7 +5869,7 @@
         <v>62.57499999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>720.7280887885386</v>
+        <v>62.57499999999999</v>
       </c>
       <c r="D9" t="n">
         <v>4.76339e-07</v>
@@ -6097,11 +5901,10 @@
       <c r="X9" t="n">
         <v>-5835.431609975895</v>
       </c>
-      <c r="Y9" t="n">
-        <v>345.4540720477756</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>849363057.4685625</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>8.473050545763279e-07</v>
@@ -6118,7 +5921,7 @@
         <v>60.048</v>
       </c>
       <c r="C10" t="n">
-        <v>722.9162690896277</v>
+        <v>178.438436763826</v>
       </c>
       <c r="D10" t="n">
         <v>4.73825e-07</v>
@@ -6151,16 +5954,13 @@
         <v>-5922.040076180075</v>
       </c>
       <c r="Y10" t="n">
-        <v>341.2259099112376</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>472832364.0553477</v>
+        <v>191.6733948033734</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.225130505633036e-07</v>
+        <v>5.791894355854565e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9170265949096936</v>
+        <v>0.9598284397630543</v>
       </c>
     </row>
     <row r="11">
@@ -6171,7 +5971,7 @@
         <v>57.11200000000002</v>
       </c>
       <c r="C11" t="n">
-        <v>672.0805246375523</v>
+        <v>57.11200000000002</v>
       </c>
       <c r="D11" t="n">
         <v>4.71744e-07</v>
@@ -6203,11 +6003,10 @@
       <c r="X11" t="n">
         <v>-5821.152911643883</v>
       </c>
-      <c r="Y11" t="n">
-        <v>337.3381906520464</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>261051548.6262453</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>8.035422719802362e-07</v>
@@ -6370,7 +6169,7 @@
         <v>123.676</v>
       </c>
       <c r="C2" t="n">
-        <v>855.0935304239182</v>
+        <v>270.2112226044484</v>
       </c>
       <c r="D2" t="n">
         <v>4.84296e-07</v>
@@ -6403,16 +6202,13 @@
         <v>-5683.331757794689</v>
       </c>
       <c r="Y2" t="n">
-        <v>417.7472076657106</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>226821460.078298</v>
+        <v>194.0361020894284</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.44353238429869e-06</v>
+        <v>7.499672239711494e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8359661112213421</v>
+        <v>0.9045129300789467</v>
       </c>
     </row>
     <row r="3">
@@ -6423,7 +6219,7 @@
         <v>107.541</v>
       </c>
       <c r="C3" t="n">
-        <v>660.00640754248</v>
+        <v>107.541</v>
       </c>
       <c r="D3" t="n">
         <v>4.81725e-07</v>
@@ -6455,11 +6251,10 @@
       <c r="X3" t="n">
         <v>-6306.152240210211</v>
       </c>
-      <c r="Y3" t="n">
-        <v>409.2528650031653</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>228500177.6122265</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.185563077314297e-06</v>
@@ -6476,7 +6271,7 @@
         <v>103.253</v>
       </c>
       <c r="C4" t="n">
-        <v>647.1063874525702</v>
+        <v>258.9537930511639</v>
       </c>
       <c r="D4" t="n">
         <v>4.78223e-07</v>
@@ -6509,16 +6304,13 @@
         <v>-6706.368759949533</v>
       </c>
       <c r="Y4" t="n">
-        <v>404.9730002838888</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>224601886.0095915</v>
+        <v>190.4878928210352</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.096061458687113e-06</v>
+        <v>8.754750453842761e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8751476842042138</v>
+        <v>0.8988145872048803</v>
       </c>
     </row>
     <row r="5">
@@ -6529,7 +6321,7 @@
         <v>98.27499999999998</v>
       </c>
       <c r="C5" t="n">
-        <v>606.3516184835494</v>
+        <v>98.27499999999998</v>
       </c>
       <c r="D5" t="n">
         <v>4.75225e-07</v>
@@ -6561,11 +6353,10 @@
       <c r="X5" t="n">
         <v>-6538.013673325883</v>
       </c>
-      <c r="Y5" t="n">
-        <v>400.9688127253339</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>233810940.7085494</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>1.038776231899943e-06</v>
@@ -6582,7 +6373,7 @@
         <v>98.31</v>
       </c>
       <c r="C6" t="n">
-        <v>644.455040605251</v>
+        <v>254.5078813203409</v>
       </c>
       <c r="D6" t="n">
         <v>4.7266e-07</v>
@@ -6615,16 +6406,13 @@
         <v>-7090.955058926787</v>
       </c>
       <c r="Y6" t="n">
-        <v>396.5798434487414</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>655130097.0375171</v>
+        <v>183.1305726645157</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.937445627067558e-07</v>
+        <v>7.639348268424465e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8880242328620667</v>
+        <v>0.9077159995584154</v>
       </c>
     </row>
     <row r="7">
@@ -6635,7 +6423,7 @@
         <v>94.524</v>
       </c>
       <c r="C7" t="n">
-        <v>624.3059440724148</v>
+        <v>94.524</v>
       </c>
       <c r="D7" t="n">
         <v>4.7051e-07</v>
@@ -6667,11 +6455,10 @@
       <c r="X7" t="n">
         <v>-6975.740533092861</v>
       </c>
-      <c r="Y7" t="n">
-        <v>391.9445455530394</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>161931033.7023265</v>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA7" t="n">
         <v>9.567497309654283e-07</v>
@@ -6688,7 +6475,7 @@
         <v>91.20700000000005</v>
       </c>
       <c r="C8" t="n">
-        <v>623.6591506195338</v>
+        <v>91.20700000000005</v>
       </c>
       <c r="D8" t="n">
         <v>4.68669e-07</v>
@@ -6720,11 +6507,10 @@
       <c r="X8" t="n">
         <v>-7128.935944885306</v>
       </c>
-      <c r="Y8" t="n">
-        <v>387.4690119672044</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>236660655.3961978</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>9.260766037454285e-07</v>
@@ -6741,7 +6527,7 @@
         <v>88.71699999999998</v>
       </c>
       <c r="C9" t="n">
-        <v>625.0399832623575</v>
+        <v>88.71699999999998</v>
       </c>
       <c r="D9" t="n">
         <v>4.66931e-07</v>
@@ -6773,11 +6559,10 @@
       <c r="X9" t="n">
         <v>-7229.801554616858</v>
       </c>
-      <c r="Y9" t="n">
-        <v>383.2822621587598</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>210447611.5556608</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>8.986873886286346e-07</v>
@@ -6794,7 +6579,7 @@
         <v>86.673</v>
       </c>
       <c r="C10" t="n">
-        <v>625.0284769351979</v>
+        <v>86.673</v>
       </c>
       <c r="D10" t="n">
         <v>4.65709e-07</v>
@@ -6826,11 +6611,10 @@
       <c r="X10" t="n">
         <v>-7331.279047687674</v>
       </c>
-      <c r="Y10" t="n">
-        <v>379.4042988125393</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>624009656.8922387</v>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>8.768879609255373e-07</v>
@@ -6847,7 +6631,7 @@
         <v>84.81299999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>614.7888387354366</v>
+        <v>84.81299999999999</v>
       </c>
       <c r="D11" t="n">
         <v>4.64191e-07</v>
@@ -6879,11 +6663,10 @@
       <c r="X11" t="n">
         <v>-7361.997937760949</v>
       </c>
-      <c r="Y11" t="n">
-        <v>375.7329626332076</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>159994176.9848319</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>8.561757955896253e-07</v>
@@ -6900,7 +6683,7 @@
         <v>82.91899999999998</v>
       </c>
       <c r="C12" t="n">
-        <v>618.3077314025624</v>
+        <v>230.1833017190559</v>
       </c>
       <c r="D12" t="n">
         <v>4.63033e-07</v>
@@ -6933,16 +6716,13 @@
         <v>-7422.984814473733</v>
       </c>
       <c r="Y12" t="n">
-        <v>372.2798102040754</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>217591330.8219371</v>
+        <v>177.7627121658531</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.407841750404369e-07</v>
+        <v>6.640615622686976e-09</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.9099342884053379</v>
+        <v>0.9255661891080427</v>
       </c>
     </row>
     <row r="13">
@@ -6953,7 +6733,7 @@
         <v>81.91500000000002</v>
       </c>
       <c r="C13" t="n">
-        <v>624.0160376637402</v>
+        <v>225.9353660824801</v>
       </c>
       <c r="D13" t="n">
         <v>4.62104e-07</v>
@@ -6986,16 +6766,13 @@
         <v>-7584.6203970385</v>
       </c>
       <c r="Y13" t="n">
-        <v>368.9567173075583</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>303843703.1087019</v>
+        <v>178.0186987663812</v>
       </c>
       <c r="AA13" t="n">
-        <v>8.243302362294342e-07</v>
+        <v>6.517868117771895e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9125830831068515</v>
+        <v>0.9287286684766042</v>
       </c>
     </row>
     <row r="14">
@@ -7006,7 +6783,7 @@
         <v>78.851</v>
       </c>
       <c r="C14" t="n">
-        <v>591.2716895676103</v>
+        <v>78.851</v>
       </c>
       <c r="D14" t="n">
         <v>4.61169e-07</v>
@@ -7038,11 +6815,10 @@
       <c r="X14" t="n">
         <v>-7356.407800720732</v>
       </c>
-      <c r="Y14" t="n">
-        <v>365.7232932991741</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>200496852.5317627</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>8.10485472374145e-07</v>
@@ -7059,7 +6835,7 @@
         <v>77.49299999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>605.5053367880757</v>
+        <v>218.2288829005245</v>
       </c>
       <c r="D15" t="n">
         <v>4.6039e-07</v>
@@ -7092,16 +6868,13 @@
         <v>-7444.025720975245</v>
       </c>
       <c r="Y15" t="n">
-        <v>362.4449858407583</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>99398386.45434077</v>
+        <v>178.227614977141</v>
       </c>
       <c r="AA15" t="n">
-        <v>7.985641322860091e-07</v>
+        <v>6.510347789544165e-09</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.9167876429668199</v>
+        <v>0.9321568164517519</v>
       </c>
     </row>
     <row r="16">
@@ -7112,7 +6885,7 @@
         <v>76.70600000000002</v>
       </c>
       <c r="C16" t="n">
-        <v>600.3030966411289</v>
+        <v>214.8440734871376</v>
       </c>
       <c r="D16" t="n">
         <v>4.59584e-07</v>
@@ -7145,16 +6918,13 @@
         <v>-7707.084684646431</v>
       </c>
       <c r="Y16" t="n">
-        <v>359.2066827937394</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>150058737.6249207</v>
+        <v>178.2506876942566</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.872979423758546e-07</v>
+        <v>6.52469133729794e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9186516067912844</v>
+        <v>0.9346211752099332</v>
       </c>
     </row>
     <row r="17">
@@ -7165,7 +6935,7 @@
         <v>75.99000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>614.5939996018349</v>
+        <v>229.2540065397584</v>
       </c>
       <c r="D17" t="n">
         <v>4.5913e-07</v>
@@ -7198,16 +6968,13 @@
         <v>-7739.44327589951</v>
       </c>
       <c r="Y17" t="n">
-        <v>355.9968355252498</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>194849446.0354508</v>
+        <v>159.7344083357879</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.782783084268183e-07</v>
+        <v>5.801000649856903e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9202361608546163</v>
+        <v>0.9333709736685065</v>
       </c>
     </row>
     <row r="18">
@@ -7218,7 +6985,7 @@
         <v>74.08100000000002</v>
       </c>
       <c r="C18" t="n">
-        <v>616.4352711789447</v>
+        <v>220.7166799045308</v>
       </c>
       <c r="D18" t="n">
         <v>4.58504e-07</v>
@@ -7251,16 +7018,13 @@
         <v>-7682.684802412933</v>
       </c>
       <c r="Y18" t="n">
-        <v>352.8422565355276</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>224647548.3459699</v>
+        <v>164.8779909115576</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.697054488548521e-07</v>
+        <v>5.953831647480189e-09</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.9216871260833548</v>
+        <v>0.9361383426142577</v>
       </c>
     </row>
     <row r="19">
@@ -7271,7 +7035,7 @@
         <v>72.64999999999998</v>
       </c>
       <c r="C19" t="n">
-        <v>597.4550291658081</v>
+        <v>216.3048788997761</v>
       </c>
       <c r="D19" t="n">
         <v>4.5813e-07</v>
@@ -7304,16 +7068,13 @@
         <v>-7687.78264173453</v>
       </c>
       <c r="Y19" t="n">
-        <v>349.6816558741185</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>143577996.6829306</v>
+        <v>165.0888049623329</v>
       </c>
       <c r="AA19" t="n">
-        <v>7.596315165932298e-07</v>
+        <v>5.691254663960773e-09</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.9235366745520968</v>
+        <v>0.9410884397916405</v>
       </c>
     </row>
     <row r="20">
@@ -7324,7 +7085,7 @@
         <v>71.572</v>
       </c>
       <c r="C20" t="n">
-        <v>613.6934895008891</v>
+        <v>71.572</v>
       </c>
       <c r="D20" t="n">
         <v>4.5765e-07</v>
@@ -7356,11 +7117,10 @@
       <c r="X20" t="n">
         <v>-7681.19113117973</v>
       </c>
-      <c r="Y20" t="n">
-        <v>346.5167564290449</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>378870519.4103824</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>7.51514431538005e-07</v>
@@ -7377,7 +7137,7 @@
         <v>70.94</v>
       </c>
       <c r="C21" t="n">
-        <v>617.9120102830822</v>
+        <v>70.94</v>
       </c>
       <c r="D21" t="n">
         <v>4.57344e-07</v>
@@ -7409,11 +7169,10 @@
       <c r="X21" t="n">
         <v>-7841.170060151584</v>
       </c>
-      <c r="Y21" t="n">
-        <v>343.3036977339311</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>187752679.7979519</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>7.447306624467331e-07</v>
@@ -7430,7 +7189,7 @@
         <v>68.702</v>
       </c>
       <c r="C22" t="n">
-        <v>603.6641862080721</v>
+        <v>68.702</v>
       </c>
       <c r="D22" t="n">
         <v>4.57011e-07</v>
@@ -7462,11 +7221,10 @@
       <c r="X22" t="n">
         <v>-7703.352265908799</v>
       </c>
-      <c r="Y22" t="n">
-        <v>340.0849493883837</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>743855828.3581824</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>7.359385478192486e-07</v>
@@ -7629,7 +7387,7 @@
         <v>124.192</v>
       </c>
       <c r="C2" t="n">
-        <v>5980.700868795026</v>
+        <v>263.3623335045764</v>
       </c>
       <c r="D2" t="n">
         <v>5.06168e-07</v>
@@ -7662,16 +7420,13 @@
         <v>-4706.862100501113</v>
       </c>
       <c r="Y2" t="n">
-        <v>409.5966677084947</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>23643246.47042691</v>
+        <v>181.7227949464663</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.680464557764971e-06</v>
+        <v>3.804388133672855e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8210742518935598</v>
+        <v>0.9436007953100107</v>
       </c>
     </row>
     <row r="3">
@@ -7682,7 +7437,7 @@
         <v>80.36900000000003</v>
       </c>
       <c r="C3" t="n">
-        <v>806.7452303954329</v>
+        <v>80.36900000000003</v>
       </c>
       <c r="D3" t="n">
         <v>5.05983e-07</v>
@@ -7714,11 +7469,10 @@
       <c r="X3" t="n">
         <v>-4976.356265492807</v>
       </c>
-      <c r="Y3" t="n">
-        <v>387.9620306346272</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>425516878.9159348</v>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA3" t="n">
         <v>1.17313974285562e-06</v>
@@ -7735,7 +7489,7 @@
         <v>72.76999999999998</v>
       </c>
       <c r="C4" t="n">
-        <v>714.9821143343383</v>
+        <v>218.6153902914114</v>
       </c>
       <c r="D4" t="n">
         <v>4.98707e-07</v>
@@ -7768,16 +7522,13 @@
         <v>-5411.809530377352</v>
       </c>
       <c r="Y4" t="n">
-        <v>380.4854366236969</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>156286969.7261375</v>
+        <v>196.5026778282235</v>
       </c>
       <c r="AA4" t="n">
-        <v>1.042702286983623e-06</v>
+        <v>7.034091301029507e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.8897456183513072</v>
+        <v>0.9251239300060898</v>
       </c>
     </row>
     <row r="5">
@@ -7788,7 +7539,7 @@
         <v>71.12</v>
       </c>
       <c r="C5" t="n">
-        <v>735.9533274710844</v>
+        <v>216.0833796245709</v>
       </c>
       <c r="D5" t="n">
         <v>4.91899e-07</v>
@@ -7821,16 +7572,13 @@
         <v>-5882.445877498227</v>
       </c>
       <c r="Y5" t="n">
-        <v>375.3988591102163</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>411004768.3896478</v>
+        <v>192.8881811048317</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.667632009195438e-07</v>
+        <v>6.684310545934836e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8988976992951779</v>
+        <v>0.9299928997458926</v>
       </c>
     </row>
     <row r="6">
@@ -7841,7 +7589,7 @@
         <v>66.69199999999995</v>
       </c>
       <c r="C6" t="n">
-        <v>698.6683701258029</v>
+        <v>205.2750852601087</v>
       </c>
       <c r="D6" t="n">
         <v>4.86304e-07</v>
@@ -7874,16 +7622,13 @@
         <v>-5912.550917972069</v>
       </c>
       <c r="Y6" t="n">
-        <v>370.5521640097273</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>252678220.7777854</v>
+        <v>197.5957630211251</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.154067010114607e-07</v>
+        <v>6.533211546703765e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.905276494417247</v>
+        <v>0.9368118768263525</v>
       </c>
     </row>
     <row r="7">
@@ -7894,7 +7639,7 @@
         <v>65.197</v>
       </c>
       <c r="C7" t="n">
-        <v>742.4617405958196</v>
+        <v>200.2068105174158</v>
       </c>
       <c r="D7" t="n">
         <v>4.81797e-07</v>
@@ -7927,16 +7672,13 @@
         <v>-6235.442365587123</v>
       </c>
       <c r="Y7" t="n">
-        <v>365.6591788806057</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>199763291.0778566</v>
+        <v>197.0140186358144</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.743835325129439e-07</v>
+        <v>6.294220337676299e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9106807515897078</v>
+        <v>0.9425425446462324</v>
       </c>
     </row>
     <row r="8">
@@ -7947,7 +7689,7 @@
         <v>61.40999999999997</v>
       </c>
       <c r="C8" t="n">
-        <v>702.5996257553236</v>
+        <v>61.40999999999997</v>
       </c>
       <c r="D8" t="n">
         <v>4.7786e-07</v>
@@ -7979,11 +7721,10 @@
       <c r="X8" t="n">
         <v>-6135.528995056597</v>
       </c>
-      <c r="Y8" t="n">
-        <v>360.6028353008273</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>393828248.638447</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>8.417608574416963e-07</v>
@@ -8000,7 +7741,7 @@
         <v>61.18799999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>813.59184294638</v>
+        <v>181.8366541326277</v>
       </c>
       <c r="D9" t="n">
         <v>4.74438e-07</v>
@@ -8033,16 +7774,13 @@
         <v>-6578.014354393819</v>
       </c>
       <c r="Y9" t="n">
-        <v>355.5571271536988</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>291080314.3059894</v>
+        <v>202.850677811816</v>
       </c>
       <c r="AA9" t="n">
-        <v>8.130776909525363e-07</v>
+        <v>6.000738930463012e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9191796398091944</v>
+        <v>0.9559042743097818</v>
       </c>
     </row>
     <row r="10">
@@ -8053,7 +7791,7 @@
         <v>57.14799999999997</v>
       </c>
       <c r="C10" t="n">
-        <v>699.5582381900427</v>
+        <v>177.9717112145793</v>
       </c>
       <c r="D10" t="n">
         <v>4.71805e-07</v>
@@ -8086,16 +7824,13 @@
         <v>-6410.809512081318</v>
       </c>
       <c r="Y10" t="n">
-        <v>350.7256056046506</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>202197978.6934312</v>
+        <v>201.0437067497458</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.900417733723573e-07</v>
+        <v>5.723800018500904e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9225975243207039</v>
+        <v>0.9601672865330738</v>
       </c>
     </row>
     <row r="11">
@@ -8106,7 +7841,7 @@
         <v>55.91800000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>759.8787056198097</v>
+        <v>174.4403836254837</v>
       </c>
       <c r="D11" t="n">
         <v>4.69256e-07</v>
@@ -8139,16 +7874,13 @@
         <v>-6576.716637615972</v>
       </c>
       <c r="Y11" t="n">
-        <v>346.2620188885043</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>283062746.1524704</v>
+        <v>199.133434264249</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.698221397174921e-07</v>
+        <v>5.525084248568512e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.925669087504264</v>
+        <v>0.9635529431301783</v>
       </c>
     </row>
   </sheetData>
@@ -8305,7 +8037,7 @@
         <v>121.722</v>
       </c>
       <c r="C2" t="n">
-        <v>948.1853691536838</v>
+        <v>273.3023440086084</v>
       </c>
       <c r="D2" t="n">
         <v>4.76632e-07</v>
@@ -8338,16 +8070,13 @@
         <v>-6843.161697481773</v>
       </c>
       <c r="Y2" t="n">
-        <v>438.3739120010454</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>37313480.39081773</v>
+        <v>210.8431312137974</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.266813073883723e-06</v>
+        <v>7.831284396802856e-09</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.8533406657864562</v>
+        <v>0.8996406680179438</v>
       </c>
     </row>
     <row r="3">
@@ -8358,7 +8087,7 @@
         <v>102.705</v>
       </c>
       <c r="C3" t="n">
-        <v>698.6712925382575</v>
+        <v>273.7305877642011</v>
       </c>
       <c r="D3" t="n">
         <v>4.74076e-07</v>
@@ -8391,16 +8120,13 @@
         <v>-7204.231455318031</v>
       </c>
       <c r="Y3" t="n">
-        <v>427.9137340466133</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>62432317.69983397</v>
+        <v>201.4817372966018</v>
       </c>
       <c r="AA3" t="n">
-        <v>1.068721946864941e-06</v>
+        <v>1.040843026416149e-08</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8779243616846807</v>
+        <v>0.8807668742243131</v>
       </c>
     </row>
     <row r="4">
@@ -8411,7 +8137,7 @@
         <v>100.697</v>
       </c>
       <c r="C4" t="n">
-        <v>702.1433860803539</v>
+        <v>100.697</v>
       </c>
       <c r="D4" t="n">
         <v>4.70895e-07</v>
@@ -8443,11 +8169,10 @@
       <c r="X4" t="n">
         <v>-7940.519382880433</v>
       </c>
-      <c r="Y4" t="n">
-        <v>422.7380480047251</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>191939620.4062985</v>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA4" t="n">
         <v>9.979548136303341e-07</v>
@@ -8464,7 +8189,7 @@
         <v>97.654</v>
       </c>
       <c r="C5" t="n">
-        <v>704.2764532471296</v>
+        <v>458.5375214825285</v>
       </c>
       <c r="D5" t="n">
         <v>4.68432e-07</v>
@@ -8497,16 +8222,13 @@
         <v>-8239.342518949676</v>
       </c>
       <c r="Y5" t="n">
-        <v>418.2600864407751</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>172998642.9858067</v>
+        <v>0.01733331055770637</v>
       </c>
       <c r="AA5" t="n">
-        <v>9.531497859256004e-07</v>
+        <v>4.303191777567681e-09</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.8931999939610994</v>
+        <v>0.866566081980971</v>
       </c>
     </row>
     <row r="6">
@@ -8517,7 +8239,7 @@
         <v>92.14100000000002</v>
       </c>
       <c r="C6" t="n">
-        <v>668.5654964052603</v>
+        <v>452.9360387702655</v>
       </c>
       <c r="D6" t="n">
         <v>4.66149e-07</v>
@@ -8550,16 +8272,13 @@
         <v>-7911.982102012559</v>
       </c>
       <c r="Y6" t="n">
-        <v>413.8114836614133</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>340940715.5667116</v>
+        <v>0.04448160698170284</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.194333412358749e-07</v>
+        <v>4.143252193951067e-09</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.8978543656938922</v>
+        <v>0.8700672050138953</v>
       </c>
     </row>
     <row r="7">
@@ -8570,7 +8289,7 @@
         <v>89.60300000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>665.7111109225192</v>
+        <v>239.8368930125294</v>
       </c>
       <c r="D7" t="n">
         <v>4.64535e-07</v>
@@ -8603,16 +8322,13 @@
         <v>-8009.399682345235</v>
       </c>
       <c r="Y7" t="n">
-        <v>409.4028202701477</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>449156467.7310114</v>
+        <v>211.3853586285381</v>
       </c>
       <c r="AA7" t="n">
-        <v>8.916486933032104e-07</v>
+        <v>9.040235019042626e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9019026317153118</v>
+        <v>0.9050738033458443</v>
       </c>
     </row>
     <row r="8">
@@ -8623,7 +8339,7 @@
         <v>87.36600000000004</v>
       </c>
       <c r="C8" t="n">
-        <v>665.1209670161586</v>
+        <v>236.6831420986686</v>
       </c>
       <c r="D8" t="n">
         <v>4.63123e-07</v>
@@ -8656,16 +8372,13 @@
         <v>-7983.603048873175</v>
       </c>
       <c r="Y8" t="n">
-        <v>405.1666236450736</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>170601388.8860681</v>
+        <v>209.6968041714887</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.676512223636543e-07</v>
+        <v>8.939045588452896e-09</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.9055252247396053</v>
+        <v>0.9069586951751444</v>
       </c>
     </row>
     <row r="9">
@@ -8676,7 +8389,7 @@
         <v>86.68400000000003</v>
       </c>
       <c r="C9" t="n">
-        <v>686.1986494497235</v>
+        <v>86.68400000000003</v>
       </c>
       <c r="D9" t="n">
         <v>4.61892e-07</v>
@@ -8708,11 +8421,10 @@
       <c r="X9" t="n">
         <v>-8475.388206199019</v>
       </c>
-      <c r="Y9" t="n">
-        <v>401.0661510930278</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>110008698.7541743</v>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA9" t="n">
         <v>8.46008907412597e-07</v>
@@ -8729,7 +8441,7 @@
         <v>82.69300000000004</v>
       </c>
       <c r="C10" t="n">
-        <v>658.1838017767451</v>
+        <v>229.6960297950307</v>
       </c>
       <c r="D10" t="n">
         <v>4.60773e-07</v>
@@ -8762,16 +8474,13 @@
         <v>-8181.955223618737</v>
       </c>
       <c r="Y10" t="n">
-        <v>397.2817842955411</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>163471712.7856244</v>
+        <v>207.4256815407371</v>
       </c>
       <c r="AA10" t="n">
-        <v>8.290154829325843e-07</v>
+        <v>9.087739963741833e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.911578649492281</v>
+        <v>0.9079690268471692</v>
       </c>
     </row>
     <row r="11">
@@ -8782,7 +8491,7 @@
         <v>80.03100000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>648.640927757444</v>
+        <v>80.03100000000001</v>
       </c>
       <c r="D11" t="n">
         <v>4.59828e-07</v>
@@ -8814,11 +8523,10 @@
       <c r="X11" t="n">
         <v>-8129.735377625187</v>
       </c>
-      <c r="Y11" t="n">
-        <v>393.7836631431049</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>215595680.5163926</v>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA11" t="n">
         <v>8.139573087446793e-07</v>
@@ -8835,7 +8543,7 @@
         <v>78.76499999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>642.2704761402231</v>
+        <v>78.76499999999999</v>
       </c>
       <c r="D12" t="n">
         <v>4.58991e-07</v>
@@ -8867,11 +8575,10 @@
       <c r="X12" t="n">
         <v>-8281.152765069404</v>
       </c>
-      <c r="Y12" t="n">
-        <v>390.4954805087149</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>320826921.0744914</v>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA12" t="n">
         <v>8.004479004707351e-07</v>
@@ -8888,7 +8595,7 @@
         <v>77.476</v>
       </c>
       <c r="C13" t="n">
-        <v>651.8495718293996</v>
+        <v>219.7183525159547</v>
       </c>
       <c r="D13" t="n">
         <v>4.58185e-07</v>
@@ -8921,16 +8628,13 @@
         <v>-8401.525297760061</v>
       </c>
       <c r="Y13" t="n">
-        <v>387.380963589799</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>164579411.1256917</v>
+        <v>204.4536867245711</v>
       </c>
       <c r="AA13" t="n">
-        <v>7.887622345882293e-07</v>
+        <v>7.710147381987403e-09</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.9181883494430608</v>
+        <v>0.9232106074294792</v>
       </c>
     </row>
     <row r="14">
@@ -8941,7 +8645,7 @@
         <v>77.07600000000002</v>
       </c>
       <c r="C14" t="n">
-        <v>665.140710871394</v>
+        <v>77.07600000000002</v>
       </c>
       <c r="D14" t="n">
         <v>4.57753e-07</v>
@@ -8973,11 +8677,10 @@
       <c r="X14" t="n">
         <v>-8622.338619069558</v>
       </c>
-      <c r="Y14" t="n">
-        <v>384.3899998105983</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>225588116.6271352</v>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA14" t="n">
         <v>7.789540139398641e-07</v>
@@ -8994,7 +8697,7 @@
         <v>74.57299999999998</v>
       </c>
       <c r="C15" t="n">
-        <v>638.3980420905522</v>
+        <v>74.57299999999998</v>
       </c>
       <c r="D15" t="n">
         <v>4.5734e-07</v>
@@ -9026,11 +8729,10 @@
       <c r="X15" t="n">
         <v>-8429.467215093911</v>
       </c>
-      <c r="Y15" t="n">
-        <v>381.4474402696158</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>156640161.1475782</v>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA15" t="n">
         <v>7.685070499554922e-07</v>
@@ -9047,7 +8749,7 @@
         <v>74.93699999999995</v>
       </c>
       <c r="C16" t="n">
-        <v>672.2953890029386</v>
+        <v>211.8288328815496</v>
       </c>
       <c r="D16" t="n">
         <v>4.56802e-07</v>
@@ -9080,16 +8782,13 @@
         <v>-8803.436857199689</v>
       </c>
       <c r="Y16" t="n">
-        <v>378.5169579094972</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>207228195.8585008</v>
+        <v>201.8578954209279</v>
       </c>
       <c r="AA16" t="n">
-        <v>7.613762932077516e-07</v>
+        <v>7.278182438699546e-09</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.9230196628031975</v>
+        <v>0.9306448632110641</v>
       </c>
     </row>
     <row r="17">
@@ -9100,7 +8799,7 @@
         <v>70.38400000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>615.1259437577935</v>
+        <v>209.3719665077789</v>
       </c>
       <c r="D17" t="n">
         <v>4.56379e-07</v>
@@ -9133,16 +8832,13 @@
         <v>-7837.110899560415</v>
       </c>
       <c r="Y17" t="n">
-        <v>375.6856700409101</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>256771806.4796622</v>
+        <v>200.6168621951835</v>
       </c>
       <c r="AA17" t="n">
-        <v>7.534795476309633e-07</v>
+        <v>7.061840733253742e-09</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.9244483286258287</v>
+        <v>0.9329280798614948</v>
       </c>
     </row>
     <row r="18">
@@ -9153,7 +8849,7 @@
         <v>71.27600000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>635.017655928022</v>
+        <v>71.27600000000001</v>
       </c>
       <c r="D18" t="n">
         <v>4.55973e-07</v>
@@ -9185,11 +8881,10 @@
       <c r="X18" t="n">
         <v>-8408.379533294215</v>
       </c>
-      <c r="Y18" t="n">
-        <v>372.8719417514002</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>407512057.3213127</v>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA18" t="n">
         <v>7.456470208592552e-07</v>
@@ -9206,7 +8901,7 @@
         <v>70.56200000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>653.5020778912087</v>
+        <v>70.56200000000001</v>
       </c>
       <c r="D19" t="n">
         <v>4.55624e-07</v>
@@ -9238,11 +8933,10 @@
       <c r="X19" t="n">
         <v>-8633.112353307812</v>
       </c>
-      <c r="Y19" t="n">
-        <v>370.0935529022672</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>202205481.6304045</v>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA19" t="n">
         <v>7.381962876302981e-07</v>
@@ -9259,7 +8953,7 @@
         <v>69.02999999999997</v>
       </c>
       <c r="C20" t="n">
-        <v>633.7453654911785</v>
+        <v>69.02999999999997</v>
       </c>
       <c r="D20" t="n">
         <v>4.55382e-07</v>
@@ -9291,11 +8985,10 @@
       <c r="X20" t="n">
         <v>-8490.745996283242</v>
       </c>
-      <c r="Y20" t="n">
-        <v>367.3231930948887</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>125528326.2901103</v>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA20" t="n">
         <v>7.326524191337869e-07</v>
@@ -9312,7 +9005,7 @@
         <v>67.68700000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>606.1986498566346</v>
+        <v>67.68700000000001</v>
       </c>
       <c r="D21" t="n">
         <v>4.55044e-07</v>
@@ -9344,11 +9037,10 @@
       <c r="X21" t="n">
         <v>-8394.224795684553</v>
       </c>
-      <c r="Y21" t="n">
-        <v>364.5510236595847</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>199251243.4022189</v>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA21" t="n">
         <v>7.259537778530464e-07</v>
@@ -9365,7 +9057,7 @@
         <v>67.94100000000003</v>
       </c>
       <c r="C22" t="n">
-        <v>666.7210812738267</v>
+        <v>67.94100000000003</v>
       </c>
       <c r="D22" t="n">
         <v>4.54982e-07</v>
@@ -9397,11 +9089,10 @@
       <c r="X22" t="n">
         <v>-8914.659985291592</v>
       </c>
-      <c r="Y22" t="n">
-        <v>361.6981794960921</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>218464713.8409812</v>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA22" t="n">
         <v>7.201651642019925e-07</v>
@@ -9564,7 +9255,7 @@
         <v>108.78</v>
       </c>
       <c r="C2" t="n">
-        <v>5331.214363815037</v>
+        <v>108.78</v>
       </c>
       <c r="D2" t="n">
         <v>4.77106e-07</v>
@@ -9596,11 +9287,10 @@
       <c r="X2" t="n">
         <v>-4547.682375547115</v>
       </c>
-      <c r="Y2" t="n">
-        <v>381.8066934807066</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>384290012.9981383</v>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA2" t="n">
         <v>1.245415063477581e-06</v>
@@ -9617,7 +9307,7 @@
         <v>73.56599999999997</v>
       </c>
       <c r="C3" t="n">
-        <v>838.479423475485</v>
+        <v>203.1483492998353</v>
       </c>
       <c r="D3" t="n">
         <v>4.76293e-07</v>
@@ -9650,16 +9340,13 @@
         <v>-5149.39981701879</v>
       </c>
       <c r="Y3" t="n">
-        <v>361.0055892513041</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>148254202.694783</v>
+        <v>188.8552790610317</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.575416816390405e-07</v>
+        <v>5.388050384690532e-09</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.8952915193310079</v>
+        <v>0.95097016648232</v>
       </c>
     </row>
     <row r="4">
@@ -9670,7 +9357,7 @@
         <v>66.85599999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>748.7821376145343</v>
+        <v>204.9126876181511</v>
       </c>
       <c r="D4" t="n">
         <v>4.69554e-07</v>
@@ -9703,16 +9390,13 @@
         <v>-5636.568039942341</v>
       </c>
       <c r="Y4" t="n">
-        <v>354.0310504671017</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>193539432.451957</v>
+        <v>180.4362841189411</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.694549085997285e-07</v>
+        <v>5.724325909229528e-09</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.9075045683677057</v>
+        <v>0.9456756531990098</v>
       </c>
     </row>
     <row r="5">
@@ -9723,7 +9407,7 @@
         <v>63.73900000000003</v>
       </c>
       <c r="C5" t="n">
-        <v>714.7246854044275</v>
+        <v>63.73900000000003</v>
       </c>
       <c r="D5" t="n">
         <v>4.64099e-07</v>
@@ -9755,11 +9439,10 @@
       <c r="X5" t="n">
         <v>-5954.809487507271</v>
       </c>
-      <c r="Y5" t="n">
-        <v>349.329650444781</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>193668420.6884376</v>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA5" t="n">
         <v>8.201765853489458e-07</v>
@@ -9776,7 +9459,7 @@
         <v>60.34499999999997</v>
       </c>
       <c r="C6" t="n">
-        <v>673.2092925799028</v>
+        <v>60.34499999999997</v>
       </c>
       <c r="D6" t="n">
         <v>4.5952e-07</v>
@@ -9808,11 +9491,10 @@
       <c r="X6" t="n">
         <v>-6018.307491526186</v>
       </c>
-      <c r="Y6" t="n">
-        <v>344.4445793016002</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>195359165.8186222</v>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA6" t="n">
         <v>7.845546070895618e-07</v>
@@ -9829,7 +9511,7 @@
         <v>57.44199999999995</v>
       </c>
       <c r="C7" t="n">
-        <v>668.8933833379225</v>
+        <v>175.4733547437569</v>
       </c>
       <c r="D7" t="n">
         <v>4.56141e-07</v>
@@ -9862,16 +9544,13 @@
         <v>-6123.038141008891</v>
       </c>
       <c r="Y7" t="n">
-        <v>339.5606496956183</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>137165222.1105785</v>
+        <v>192.4132770086032</v>
       </c>
       <c r="AA7" t="n">
-        <v>7.564184407878399e-07</v>
+        <v>5.227206363448354e-09</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.9238620000756955</v>
+        <v>0.9698971955213928</v>
       </c>
     </row>
     <row r="8">
@@ -9882,7 +9561,7 @@
         <v>57.26400000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>815.2509216250455</v>
+        <v>57.26400000000001</v>
       </c>
       <c r="D8" t="n">
         <v>4.5332e-07</v>
@@ -9914,11 +9593,10 @@
       <c r="X8" t="n">
         <v>-6434.766853772477</v>
       </c>
-      <c r="Y8" t="n">
-        <v>334.6334579109749</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>182839622.5572596</v>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>delta Rct-a</t>
+        </is>
       </c>
       <c r="AA8" t="n">
         <v>7.361551241341882e-07</v>
@@ -9935,7 +9613,7 @@
         <v>54.125</v>
       </c>
       <c r="C9" t="n">
-        <v>761.3173879387413</v>
+        <v>168.3619012892958</v>
       </c>
       <c r="D9" t="n">
         <v>4.51184e-07</v>
@@ -9968,16 +9646,13 @@
         <v>-6526.29454549875</v>
       </c>
       <c r="Y9" t="n">
-        <v>329.9180126710327</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>144333249.1458964</v>
+        <v>187.2072106462534</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.1652088650224e-07</v>
+        <v>4.631906103408947e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.9303094907850217</v>
+        <v>0.9796127135666235</v>
       </c>
     </row>
     <row r="10">
@@ -9988,7 +9663,7 @@
         <v>53.63499999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>853.5517679089754</v>
+        <v>163.4587948558183</v>
       </c>
       <c r="D10" t="n">
         <v>4.49307e-07</v>
@@ -10021,16 +9696,13 @@
         <v>-6790.270708425777</v>
       </c>
       <c r="Y10" t="n">
-        <v>325.4370405855685</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>177303080.3925255</v>
+        <v>187.2111884093287</v>
       </c>
       <c r="AA10" t="n">
-        <v>7.016495281387601e-07</v>
+        <v>4.660884098423892e-09</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.9328129290911628</v>
+        <v>0.9822859473911348</v>
       </c>
     </row>
     <row r="11">
@@ -10041,7 +9713,7 @@
         <v>49.94299999999998</v>
       </c>
       <c r="C11" t="n">
-        <v>772.1021096614774</v>
+        <v>165.6733047909108</v>
       </c>
       <c r="D11" t="n">
         <v>4.47867e-07</v>
@@ -10074,16 +9746,13 @@
         <v>-6526.385286717029</v>
       </c>
       <c r="Y11" t="n">
-        <v>321.2988222282801</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>87504611.61801642</v>
+        <v>179.9675721385721</v>
       </c>
       <c r="AA11" t="n">
-        <v>6.885139484362863e-07</v>
+        <v>4.334688072888576e-09</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.9351523850912739</v>
+        <v>0.9844656758406392</v>
       </c>
     </row>
   </sheetData>

--- a/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
+++ b/BioSensorAnalysisSrcCode/EIS_Analysis/Austin_EIS/MegaExcel/Processed Chips for PCAI1ia/Chip 27.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1124,6 +1124,566 @@
         <v>7.10358220782034e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9182480339726223</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>129.816</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>720.6323626475281</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.11386e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-79.643</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5681574138265125</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1.60227503578306</v>
+      </c>
+      <c r="J12" t="n">
+        <v>2.231673111673855</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.797836423690727</v>
+      </c>
+      <c r="L12" t="n">
+        <v>23.9320108645923</v>
+      </c>
+      <c r="M12" t="n">
+        <v>86.49221849863669</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>16.31349522111721</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-8303.678626407043</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>-190.7193208737768</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>9.077035214013106e-07</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.8801445757784034</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>121.697</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.9374576323411596</v>
+      </c>
+      <c r="D13" t="n">
+        <v>696.6740502786434</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.9667537657053531</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.11095e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-80.05</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6696596687227759</v>
+      </c>
+      <c r="I13" t="n">
+        <v>1.352601367110984</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.973355036064676</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.727283138734068</v>
+      </c>
+      <c r="L13" t="n">
+        <v>24.85426467531383</v>
+      </c>
+      <c r="M13" t="n">
+        <v>86.65194974328436</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>17.0936952534511</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-8487.127595586631</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-181.3388792208428</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.496679723174884e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8899859477585453</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>114.407</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.8813012263511433</v>
+      </c>
+      <c r="D14" t="n">
+        <v>668.6544586307722</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.9278718154902251</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.11214e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-80.32899999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.4615968870788024</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7885838132438485</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.773394018974194</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.567804572679223</v>
+      </c>
+      <c r="L14" t="n">
+        <v>25.55340974527982</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.65947280398476</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>17.13227891826376</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-8310.605327035604</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-166.2299322425594</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.143957286588159e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8964225003084479</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>110.61</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.8520521353300055</v>
+      </c>
+      <c r="D15" t="n">
+        <v>679.0607470844898</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.9423123110786913</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.11614e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-80.542</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.4229508573827554</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.145149732712472</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.948587885801673</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.867653758616919</v>
+      </c>
+      <c r="L15" t="n">
+        <v>28.98402889414337</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.8244916387948</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>18.02454772737477</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-8611.818107984484</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-183.5123001001468</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>7.892827574397358e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9013032144441889</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106.412</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.8197140568188822</v>
+      </c>
+      <c r="D16" t="n">
+        <v>673.9287058144672</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.9351907307333845</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.12326e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-80.705</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.6560948736901148</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.007303162440803</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.697363023508245</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.811289985461836</v>
+      </c>
+      <c r="L16" t="n">
+        <v>28.92607989266839</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.87144478999733</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>18.29560960290341</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-8591.412511777164</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-186.5145605573098</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.71485166579219e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9050139365760173</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>102.859</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.7923445492081096</v>
+      </c>
+      <c r="D17" t="n">
+        <v>673.390710920641</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.9344441712923824</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.12857e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-80.86</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.4710873013870996</v>
+      </c>
+      <c r="I17" t="n">
+        <v>1.019647458260897</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.96940584744119</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.802398690124514</v>
+      </c>
+      <c r="L17" t="n">
+        <v>29.65413701388699</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.92248349849262</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>18.59962999790918</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-8596.735331531549</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-193.130408405672</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.565498516939744e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.908154540578976</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99.90499999999997</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.7695892648055705</v>
+      </c>
+      <c r="D18" t="n">
+        <v>684.0105659492361</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.9491810268362812</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.13321e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-80.992</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.131237450091643</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.329791949651252</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.231570477672867</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.148310726445605</v>
+      </c>
+      <c r="L18" t="n">
+        <v>32.04423865046279</v>
+      </c>
+      <c r="M18" t="n">
+        <v>87.01407570627818</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>19.17124976817003</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-8740.130202361239</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-209.2633309598944</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.434343053118211e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9109785219444676</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>94.87300000000005</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.7308267085721331</v>
+      </c>
+      <c r="D19" t="n">
+        <v>659.3131498989064</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.914909160444389</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.13835e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-81.125</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.32748020843396</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.226352510236725</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.846409623918039</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.028512578551965</v>
+      </c>
+      <c r="L19" t="n">
+        <v>30.52725586883264</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.94631826068088</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>18.74508335655008</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-8382.359059673714</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-194.2358141286062</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.313158604715136e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9136482768902352</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91.20000000000005</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.7025328156775746</v>
+      </c>
+      <c r="D20" t="n">
+        <v>640.4649207659123</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.8887540359871031</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.14111e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-81.253</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.06517366898170843</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.6834135199323136</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.566144438550274</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.716166197388699</v>
+      </c>
+      <c r="L20" t="n">
+        <v>28.76978189435176</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.91908270045455</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>18.57905967068162</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-8177.335005830709</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-183.4385713815567</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.200036925052079e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.916102328578133</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>88.26299999999998</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.6799084858569048</v>
+      </c>
+      <c r="D21" t="n">
+        <v>631.9825645463151</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.8769833236804369</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.14408e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-81.367</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.3891260344940065</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.7575077114716539</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.732859411402087</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.090234913222961</v>
+      </c>
+      <c r="L21" t="n">
+        <v>31.89528338918303</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.93416468923911</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18.67063298934583</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-8112.777920204778</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-181.256331680823</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.10358220782034e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9182480339726223</v>
       </c>
     </row>
@@ -1138,7 +1698,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2456,6 +3016,1182 @@
         <v>5.980132610953426e-09</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.952124785920649</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>123.017</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>890.8128666857568</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.45364e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-79.059</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.3035305152156914</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.742721446445516</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.720964612167591</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.565547367885113</v>
+      </c>
+      <c r="L23" t="n">
+        <v>23.73392580872853</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.34442876493496</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>15.6522772434987</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7830.369185265049</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-346.043719911943</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.008483203030008e-06</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8768153250799705</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>106.605</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.86658754481088</v>
+      </c>
+      <c r="D24" t="n">
+        <v>701.4668021527762</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7874457457743766</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.44371e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-79.75</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5308606703994583</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.066643470228123</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.847287116683712</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.467681376095283</v>
+      </c>
+      <c r="L24" t="n">
+        <v>25.30733145970917</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.79828850962785</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>17.87672924908356</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-8555.250389915491</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-205.0070511661788</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.943508687437834e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8945247794697502</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100.546</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8173341895835534</v>
+      </c>
+      <c r="D25" t="n">
+        <v>657.3390925589714</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7379092928962535</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.43179e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-80.03700000000001</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.4177912602354802</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.283337904151673</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.91558603773612</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.826168263619314</v>
+      </c>
+      <c r="L25" t="n">
+        <v>27.39830601857852</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.87648169382103</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>18.32517130141567</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8601.813200262834</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-174.3126957241175</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.557950415430884e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9007270019340107</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>96.899</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7876878805368364</v>
+      </c>
+      <c r="D26" t="n">
+        <v>647.0804078807662</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7263931989310054</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.41995e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-80.22</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.3600575886295302</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.239001315439677</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.53561362418326</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.724795416656296</v>
+      </c>
+      <c r="L26" t="n">
+        <v>27.02533422649617</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.91729452845723</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>18.56826178536179</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8602.648156780922</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-170.2773698105996</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>8.321549054307094e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9045421916477052</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>96.03699999999998</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7806807189250264</v>
+      </c>
+      <c r="D27" t="n">
+        <v>790.7279852947323</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.887647692198938</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.40925e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-80.378</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.5990697604568355</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.552942595012983</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.256470623755742</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.265611788597336</v>
+      </c>
+      <c r="L27" t="n">
+        <v>30.61320336474484</v>
+      </c>
+      <c r="M27" t="n">
+        <v>87.06485746626791</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>19.50353336746041</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-8960.890612911184</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-303.1838840583536</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>8.130490827824994e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.9076742869282133</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>93.70499999999998</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7617239893673231</v>
+      </c>
+      <c r="D28" t="n">
+        <v>674.5254572751998</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7572021941990488</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.40216e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-80.526</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.7619811005484578</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.183091260408998</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.988371984112647</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.776744030066177</v>
+      </c>
+      <c r="L28" t="n">
+        <v>29.02189866035797</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.13659687627519</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>19.99301837574501</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-9088.720059306743</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-204.8377224163212</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.966910835692676e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9104862549558547</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>89.05399999999997</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7239162067031384</v>
+      </c>
+      <c r="D29" t="n">
+        <v>640.2949501238372</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7187760460915162</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.39602e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-80.64700000000001</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5892734246575295</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.70241243796654</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.540306905689112</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.915860305846135</v>
+      </c>
+      <c r="L29" t="n">
+        <v>29.47423711146282</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.99756703532763</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>19.0656463423861</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-8516.874534006982</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-179.2568176193269</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.834205066514079e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.912799689768508</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>88.11700000000002</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7162993732573548</v>
+      </c>
+      <c r="D30" t="n">
+        <v>650.8851577183826</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7306642978114829</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.39295e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-80.792</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.3477241245855221</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9500276694369202</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.974788373776023</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.80044601587177</v>
+      </c>
+      <c r="L30" t="n">
+        <v>30.23576260266869</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.14472927873885</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>20.0500574245267</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8878.657663706701</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-193.5523256474377</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.699376669980727e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9152875675368441</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>84.762</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6890267198842437</v>
+      </c>
+      <c r="D31" t="n">
+        <v>643.6518865161626</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7225444429320499</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.38897e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-80.92</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5612826695462825</v>
+      </c>
+      <c r="I31" t="n">
+        <v>1.181093393257172</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.924972686406323</v>
+      </c>
+      <c r="K31" t="n">
+        <v>3.05729772029831</v>
+      </c>
+      <c r="L31" t="n">
+        <v>31.7829148001345</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.12928594521571</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.94201658718402</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8718.879094286116</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-191.7583540516859</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.579703599375671e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9175166126156107</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>83.26099999999997</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6768251542469738</v>
+      </c>
+      <c r="D32" t="n">
+        <v>638.2272842255301</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7164549459192658</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.38463e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-81.033</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.2226021309923061</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9776475871479843</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.194538745994547</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.049002249284264</v>
+      </c>
+      <c r="L32" t="n">
+        <v>32.47172063626965</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.17486865025123</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>20.26431028717905</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-8776.357454076953</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-190.8227927245464</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.476361312322177e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9194328954308543</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>82.06399999999996</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.667094791776746</v>
+      </c>
+      <c r="D33" t="n">
+        <v>630.032410020683</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7072556241410164</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.38079e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-81.13500000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4321459692223827</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.062883715545529</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.952985140021669</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.213794953543763</v>
+      </c>
+      <c r="L33" t="n">
+        <v>32.86381915467833</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.23000221781973</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20.66829579176916</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-8867.959509423963</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-187.3401148119506</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.38636039839273e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9211144844976697</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>78.935</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6416592828633442</v>
+      </c>
+      <c r="D34" t="n">
+        <v>622.8105647353455</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6991485956556666</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.38024e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-81.221</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.01519574087747258</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.7930543059485983</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.746863884360521</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.848432668905209</v>
+      </c>
+      <c r="L34" t="n">
+        <v>32.46682382219134</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.17390846088941</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>20.25741413617275</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-8588.119164103447</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-184.6446192182759</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.313274669477334e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9225964107236322</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79.26299999999998</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6443255810172576</v>
+      </c>
+      <c r="D35" t="n">
+        <v>643.6487059516686</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7225408725250509</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.3775e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-81.29900000000001</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3986826700490189</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.289527006091306</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.078687275684449</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.272934469178723</v>
+      </c>
+      <c r="L35" t="n">
+        <v>34.47728634871119</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.31095941786431</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>21.29149921179159</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-8983.087148939432</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-206.7042505412327</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.24701217516823e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9238740285267643</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79.89800000000002</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6494874692115726</v>
+      </c>
+      <c r="D36" t="n">
+        <v>684.3202530346027</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.76819754027644</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.37654e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-81.40900000000001</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.896774922013251</v>
+      </c>
+      <c r="I36" t="n">
+        <v>2.20519170497895</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.978680142721921</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.971597406906195</v>
+      </c>
+      <c r="L36" t="n">
+        <v>33.58969867692985</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.47135818949879</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>22.64400418001273</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-9509.995708780943</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-246.592144197742</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.16790368695532e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9254795226227149</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>77.23200000000003</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6278156677532376</v>
+      </c>
+      <c r="D37" t="n">
+        <v>641.3491074593886</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7199594117286486</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.3758e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-81.482</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5529189196139203</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.518478942944718</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.851285512719434</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.632592122783522</v>
+      </c>
+      <c r="L37" t="n">
+        <v>33.15186767796791</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.40001507291713</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>22.02183785256468</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-9138.471431213011</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-211.3258935830842</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.11348877747008e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.92660086639399</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>75.50099999999998</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6137444418251135</v>
+      </c>
+      <c r="D38" t="n">
+        <v>645.0870740543824</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7241555417294431</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.37357e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-81.551</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.5371905581476721</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.334460577611811</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.066987066847668</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.427173111871302</v>
+      </c>
+      <c r="L38" t="n">
+        <v>35.73244134806395</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.41102247673675</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>22.11559519269355</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-9095.562659639783</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-218.2938765975551</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.058668754276769e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9276890120226792</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>73.53300000000002</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5977466529016316</v>
+      </c>
+      <c r="D39" t="n">
+        <v>615.1150618124929</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6905098532096987</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.37256e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-81.62</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.4131698078420023</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.120851246717673</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.969022637589614</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.162376291679404</v>
+      </c>
+      <c r="L39" t="n">
+        <v>35.05904922523229</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.34533099165118</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>21.56757551452696</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-8768.552856788556</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-194.2191250344509</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.006918199967112e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9287636180396069</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>73.10199999999998</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5942430720957265</v>
+      </c>
+      <c r="D40" t="n">
+        <v>624.2221036186855</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7007331471772356</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.37343e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-81.717</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3917927230189602</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.086239504056887</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.987026126241638</v>
+      </c>
+      <c r="K40" t="n">
+        <v>3.134529208477979</v>
+      </c>
+      <c r="L40" t="n">
+        <v>35.10312664746759</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.44064922809999</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>22.37194960079927</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-9033.73252079194</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-205.4017636837808</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>6.943042421514423e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9301653470366122</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>72.32600000000002</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5879350008535408</v>
+      </c>
+      <c r="D41" t="n">
+        <v>646.2979826484388</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7255148716620715</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.37165e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-81.806</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4158627640689363</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.474027121981117</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.1300547322357</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.402016674772887</v>
+      </c>
+      <c r="L41" t="n">
+        <v>37.60258927116103</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.50195610308231</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>22.92172320695897</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-9187.912833391589</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-228.8797853593273</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>6.88108748222111e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9314461273523972</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>71.55400000000003</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5816594454425</v>
+      </c>
+      <c r="D42" t="n">
+        <v>653.0677228483986</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7331143804401007</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.37066e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-81.869</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.7218498449233445</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.094878462762556</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.099488340375157</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.086430746289308</v>
+      </c>
+      <c r="L42" t="n">
+        <v>35.24183328729301</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.53564373187106</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>23.23545678525143</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-9241.637290420997</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-238.1401655315058</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>6.83569896970495e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9324109709795777</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>69.53000000000003</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5652064348829839</v>
+      </c>
+      <c r="D43" t="n">
+        <v>196.4027710076599</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.2204759027991711</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.36996e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-81.92700000000001</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.3146995967741957</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.038226905758256</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.949135719967094</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.867476322719746</v>
+      </c>
+      <c r="L43" t="n">
+        <v>34.48569394164862</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.47095526829668</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>22.640391903774</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-8897.678884716743</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>193.7208211975801</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>5.980132610953426e-09</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.952124785920649</v>
       </c>
     </row>
@@ -2470,7 +4206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3788,6 +5524,1182 @@
         <v>6.538806611654203e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9337020090745738</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>129.108</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>924.944178539187</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.28239e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-79.121</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7580044085163533</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.047039608695946</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.53369756647797</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.3428777038827</v>
+      </c>
+      <c r="L23" t="n">
+        <v>20.75046368617551</v>
+      </c>
+      <c r="M23" t="n">
+        <v>86.13945377474806</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>14.81889945804878</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-7446.211464551119</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-371.9545901492489</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>9.922148824033418e-07</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8731068589040796</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>109.101</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8450367134492053</v>
+      </c>
+      <c r="D24" t="n">
+        <v>792.5134678690961</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.8568230237642603</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.26096e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-80.06699999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.4331237516949231</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.9027047774675002</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.646491777668277</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.508118438070054</v>
+      </c>
+      <c r="L24" t="n">
+        <v>25.23207274223694</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.61714570465722</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>16.91742601746587</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-8081.026531394899</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-284.0336269309548</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>8.529639486165217e-07</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8950227877615352</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>103.232</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.7995786473340147</v>
+      </c>
+      <c r="D25" t="n">
+        <v>649.8685256919792</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7026029686660127</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.2453e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-80.383</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.2641051089198811</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.9133340111180765</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.792818019064352</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.753906751123438</v>
+      </c>
+      <c r="L25" t="n">
+        <v>27.82674561578071</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.72188768178023</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>17.45920898904154</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-8188.275960781168</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-166.065337630556</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>8.125703972419277e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.9017663342807797</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>103.322</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8002757381417108</v>
+      </c>
+      <c r="D26" t="n">
+        <v>688.3038293387863</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7441571559765485</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.23514e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-80.604</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.7449740286358222</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.727533627246282</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.983613256898368</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.077063720019141</v>
+      </c>
+      <c r="L26" t="n">
+        <v>30.33115552566098</v>
+      </c>
+      <c r="M26" t="n">
+        <v>87.04977891610596</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>19.40367594529323</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-9059.944754414106</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-205.2208735624151</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>7.88163149573542e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.9059829782551166</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97.82499999999999</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.75769898069833</v>
+      </c>
+      <c r="D27" t="n">
+        <v>634.2510942852081</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.6857182400854873</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.22845e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-80.76900000000001</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1071144234081276</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8668935149178595</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.602737724316307</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.7010504938406</v>
+      </c>
+      <c r="L27" t="n">
+        <v>29.54076198576941</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.87749246948361</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>18.33111504406767</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-8396.355584876788</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-162.2597938941771</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>7.704798527426754e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.909159406293183</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>96.84500000000003</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7501084363478639</v>
+      </c>
+      <c r="D28" t="n">
+        <v>687.732110874048</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7435390446591269</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.22367e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-80.926</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.641641405493112</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.137491425722362</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.765405575116243</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.868952816744496</v>
+      </c>
+      <c r="L28" t="n">
+        <v>30.57225729730976</v>
+      </c>
+      <c r="M28" t="n">
+        <v>87.02747491937123</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>19.25782407896265</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-8742.078544092812</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-214.6985584267318</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>7.550447286602293e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.912034098651431</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93.31200000000001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.722743749419091</v>
+      </c>
+      <c r="D29" t="n">
+        <v>659.677259800504</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7132076455060964</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.2209e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-81.066</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.5471248430038087</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.073639714871742</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.87414251502297</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.068525781654061</v>
+      </c>
+      <c r="L29" t="n">
+        <v>33.34317869809441</v>
+      </c>
+      <c r="M29" t="n">
+        <v>87.03897266560439</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>19.33273680129014</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-8657.704968765431</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-195.1947530998923</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>7.417855691438191e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9145978154303235</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90.22899999999998</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.6988645165287974</v>
+      </c>
+      <c r="D30" t="n">
+        <v>647.5867012695221</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7001359825760403</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.22084e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-81.17100000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.5272051621102377</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.8960002680996696</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.758519088455415</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.632086654818046</v>
+      </c>
+      <c r="L30" t="n">
+        <v>31.77494872331662</v>
+      </c>
+      <c r="M30" t="n">
+        <v>87.02591137060513</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19.24768159069383</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8507.557493821065</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-189.4372526049461</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>7.318785446524434e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9166306031253019</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>88.00999999999999</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6816773553923846</v>
+      </c>
+      <c r="D31" t="n">
+        <v>641.4360985182248</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.6934862810113347</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.21893e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-81.298</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.5089215687668838</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.9840161176847104</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.780361765517368</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.698849499303962</v>
+      </c>
+      <c r="L31" t="n">
+        <v>31.66683623950517</v>
+      </c>
+      <c r="M31" t="n">
+        <v>87.05236168936062</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>19.42070786791356</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8480.874046406934</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-188.7955050041217</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>7.208276239277801e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9188212921463067</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>87.58699999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6784010285962139</v>
+      </c>
+      <c r="D32" t="n">
+        <v>668.4411682316008</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7226827129041508</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.21756e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-81.41</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.6311116594471925</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1.190788364940084</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.715450167153055</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.941862173878197</v>
+      </c>
+      <c r="L32" t="n">
+        <v>33.21851543396568</v>
+      </c>
+      <c r="M32" t="n">
+        <v>87.22185598824058</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>20.60759638013381</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-8937.783194451338</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-217.3297993797185</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>7.111089980067962e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9208507833971519</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>84.745</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6563884499798618</v>
+      </c>
+      <c r="D33" t="n">
+        <v>645.8744082522161</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6982847432720529</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.21658e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-81.482</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4698890342363808</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.7989095471713057</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.856665351090147</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.792718594106645</v>
+      </c>
+      <c r="L33" t="n">
+        <v>33.43842937593461</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.15281124632121</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>20.10706528054541</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-8607.0140055543</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-201.2111258224724</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.044464394495368e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9222454363731062</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>83.46300000000002</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.646458778696905</v>
+      </c>
+      <c r="D34" t="n">
+        <v>757.4273148847637</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.8188897583862937</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.21741e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-81.566</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.4745324101330487</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.263886113271488</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.101033021062743</v>
+      </c>
+      <c r="K34" t="n">
+        <v>3.064672468352813</v>
+      </c>
+      <c r="L34" t="n">
+        <v>34.73556627684425</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.20564446519681</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>20.48785275607478</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-8691.97638429313</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-305.0796776148887</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>6.981204294314548e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.923637857137142</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>81.57900000000001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6318663444558045</v>
+      </c>
+      <c r="D35" t="n">
+        <v>641.6868004158442</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6937573264467635</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.21776e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-81.652</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2622054142834409</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.011102131540446</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.780667617535387</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.651165291170198</v>
+      </c>
+      <c r="L35" t="n">
+        <v>34.13302308270965</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.21069814602048</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>20.52503169611332</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-8616.6647375128</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-205.4966477610842</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>6.916289298655832e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.925056602424427</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79.45000000000005</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6153762741270877</v>
+      </c>
+      <c r="D36" t="n">
+        <v>812.3894634449966</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.8783118833485131</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.21873e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-81.748</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3954160199403361</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.145370196000948</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.579323807179243</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.774708509500377</v>
+      </c>
+      <c r="L36" t="n">
+        <v>33.07536172581578</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.21677231629147</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>20.56989670041561</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-8548.286852487357</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-362.1087468886236</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>6.85072256865229e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9265142162307757</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78.75599999999997</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.61000092945441</v>
+      </c>
+      <c r="D37" t="n">
+        <v>654.2322331828811</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7073207749857343</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.21857e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-81.818</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6146277395404575</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.289789068764456</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.984390466918733</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.125616519698762</v>
+      </c>
+      <c r="L37" t="n">
+        <v>36.43333848300041</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.29973932488761</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>21.20289869332894</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-8751.372774631207</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-223.761241014258</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>6.798831791571903e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9276594653105199</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>76.27600000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5907922049756793</v>
+      </c>
+      <c r="D38" t="n">
+        <v>613.8454678219282</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6636567720134275</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.21774e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-81.87</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.152219029873058</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.9192870978648067</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.762397076333466</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.665762339594186</v>
+      </c>
+      <c r="L38" t="n">
+        <v>34.23526805482251</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.20030488207833</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>20.44871620035842</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-8336.351888326819</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-190.7819027150718</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>6.754387727039867e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9286325555176161</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>75.935</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5881510053598538</v>
+      </c>
+      <c r="D39" t="n">
+        <v>658.6256329963803</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7120706830509301</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.21905e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-81.938</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.517624912684474</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.203165765149636</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.033210888546007</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.19446017912051</v>
+      </c>
+      <c r="L39" t="n">
+        <v>36.49612277351245</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.33122650575744</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>21.45342700606522</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-8702.470732248117</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-234.3556032162101</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>6.711142224885672e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9296439902348186</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>74.28999999999996</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5754097344858565</v>
+      </c>
+      <c r="D40" t="n">
+        <v>625.9088100280799</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6766990101138974</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.22086e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-81.989</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.2957908723988649</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.206673206556426</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.670764053232117</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.764689538576051</v>
+      </c>
+      <c r="L40" t="n">
+        <v>33.70069565210456</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.30840048171451</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>21.27122735732923</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-8541.704394462253</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-208.091937467248</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>6.675263665375564e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9305279391280012</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>72.767</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5636134089289586</v>
+      </c>
+      <c r="D41" t="n">
+        <v>633.285487718741</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6846742780941896</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.22095e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-82.065</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4362367820946644</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.9002696537244468</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.975667884444588</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.094909033016787</v>
+      </c>
+      <c r="L41" t="n">
+        <v>37.05390261795557</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.31407338683741</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>21.31622009243743</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-8481.65815018914</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-218.1396467300041</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>6.626457979894738e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9316335793742081</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>71.50700000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5538541376212164</v>
+      </c>
+      <c r="D42" t="n">
+        <v>624.7008809413474</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6753930620202079</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.22186e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-82.13200000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.2175472542250773</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.006346500702574</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.079224648957275</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.833176732287887</v>
+      </c>
+      <c r="L42" t="n">
+        <v>35.56765125367694</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.31091147042447</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>21.29111901845852</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-8392.940558782655</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-213.3195050597832</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>6.582015866471859e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.932678957115012</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>71.55099999999999</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5541949375716453</v>
+      </c>
+      <c r="D43" t="n">
+        <v>635.4014722437877</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.686961966988441</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.22288e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-82.20699999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.5209849125716777</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9781083559493974</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.83056779949244</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.807092832729078</v>
+      </c>
+      <c r="L43" t="n">
+        <v>35.01261744818088</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.39840699619239</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>22.00820717278198</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-8624.156160304748</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-225.8695645912653</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>6.538806611654203e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9337020090745738</v>
       </c>
     </row>
@@ -3802,7 +6714,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4504,6 +7416,566 @@
         <v>7.29545926736977e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9259093123015187</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>124.143</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>241.0606047039136</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.58367e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-77.13800000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.1463203083764137</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.302056891951591</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.9470774943129501</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.957631634162051</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.53871839119138</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.17588870299647</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.803779561330455</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-4623.594987243592</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>192.8857394327653</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.596573730614208e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9610827027210566</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>84.48000000000002</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6805055460235376</v>
+      </c>
+      <c r="D13" t="n">
+        <v>784.4993196551222</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.25436551782775</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.64888e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-78.84</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.2234503193713178</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.8073057277272875</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.459098554930882</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.562275791618747</v>
+      </c>
+      <c r="L13" t="n">
+        <v>15.49385348336992</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.33752804804207</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.26157581781073</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-5156.460874532487</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-326.746939530548</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.982360272586506e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8852216569213783</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>75.40500000000003</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6074043643217906</v>
+      </c>
+      <c r="D14" t="n">
+        <v>690.0117743031244</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.862399582671926</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.62057e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-79.514</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3147502930828046</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.9692613725208954</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.586678488291368</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.705887141717686</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.26524941121385</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.77189009505075</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>13.52654953524155</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-5514.607458360963</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-258.0713151230814</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>9.120585127132215e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8977624772184749</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>70.87700000000001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.5709302981239379</v>
+      </c>
+      <c r="D15" t="n">
+        <v>619.759674402243</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.570970379683036</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.58705e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-79.92700000000001</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.5120185371398708</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.704682049369021</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.621382130168136</v>
+      </c>
+      <c r="L15" t="n">
+        <v>18.30818891504761</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.93663182450629</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.07691549036024</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-5623.004521106845</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-202.5464275769428</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.648920944189094e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9045702042963808</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>69.327</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5584446968415457</v>
+      </c>
+      <c r="D16" t="n">
+        <v>660.706573873902</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.740831811508251</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.5565e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-80.252</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1947864930130442</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.8273499509849747</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.677622250412332</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.7819155473789</v>
+      </c>
+      <c r="L16" t="n">
+        <v>19.40002475287198</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.16882978339994</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.93286866830128</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-5891.785405700944</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-245.5062242080124</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>8.299639251073624e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9097148724775582</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>67.33199999999999</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.542374519707112</v>
+      </c>
+      <c r="D17" t="n">
+        <v>695.4368395551065</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.884904567501967</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.53261e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-80.533</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.8770368025089244</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.9956636552152082</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.90254474665536</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.659554075953091</v>
+      </c>
+      <c r="L17" t="n">
+        <v>20.13699362018835</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.36335575721175</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.73396077110964</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-6129.945738199643</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-282.4761105245378</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.025533379876564e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.913935640009838</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>64.70999999999998</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5212537154732848</v>
+      </c>
+      <c r="D18" t="n">
+        <v>719.7696968076889</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.985845396396301</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.51167e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-80.76600000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.4062677964833233</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.217862213406838</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.199471402173077</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.967107142805292</v>
+      </c>
+      <c r="L18" t="n">
+        <v>21.76080150509097</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.44976604876672</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>16.11793292668291</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-6183.843153199383</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-310.1518536443224</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.800550646503015e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9174801160845886</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>62.04999999999995</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.499826812627373</v>
+      </c>
+      <c r="D19" t="n">
+        <v>716.9444477324491</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.974125318456938</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.49551e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-80.988</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.2970371076996507</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.137128534543391</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.066446039623483</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.845722264070799</v>
+      </c>
+      <c r="L19" t="n">
+        <v>22.35762264150804</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.54388671203137</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.55798474291716</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-6260.834587116743</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-313.5390175917836</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.609167513772127e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9206359726549826</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>60.31</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4858107182845591</v>
+      </c>
+      <c r="D20" t="n">
+        <v>705.9082758581737</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.928343586979782</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.47803e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-81.163</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.5304710000706385</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.133417628803185</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.09633733628851</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.813605256805852</v>
+      </c>
+      <c r="L20" t="n">
+        <v>22.5816287823947</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.61620074139398</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16.91269064094116</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-6308.094701077208</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-308.5556411180816</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.449007832611085e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9232423324097968</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>59.291</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4776024423447154</v>
+      </c>
+      <c r="D21" t="n">
+        <v>761.5120186922959</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.159006506383051</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.46535e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-81.36</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.8416803435876054</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.29058777787983</v>
+      </c>
+      <c r="J21" t="n">
+        <v>2.005536711153777</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.81958777244175</v>
+      </c>
+      <c r="L21" t="n">
+        <v>23.52136848929209</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.76947872918841</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17.71697076076464</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-6541.747066667391</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-364.1132545080574</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.29545926736977e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9259093123015187</v>
       </c>
     </row>
@@ -4518,7 +7990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5836,6 +9308,1182 @@
         <v>7.103629344653632e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.928042798095171</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>126.633</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>867.463698725094</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.62212e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-77.533</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.2431147979108321</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.7762854345776665</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.376202406963833</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.156349881133764</v>
+      </c>
+      <c r="L23" t="n">
+        <v>15.51323369961583</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.19589780308293</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.89846587395262</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-5928.530747659112</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-323.9405137689279</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.312691647084753e-06</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8430872232040106</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>109.67</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.866045975377666</v>
+      </c>
+      <c r="D24" t="n">
+        <v>671.4789005599085</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.7740714701338821</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.59991e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-78.64400000000001</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.6017770693438421</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.164326744949632</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.57427558654892</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.608102878218628</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18.88448549009986</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.93749408650241</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>14.07991333942035</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-6692.468863382832</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-179.1349910558224</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.074401804569402e-06</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8722769932975619</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>102.344</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8081937567616653</v>
+      </c>
+      <c r="D25" t="n">
+        <v>624.0897988191389</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7194419774987239</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.57266e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-79.117</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.1188891375863978</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.6612520285518163</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.339316486386084</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.523463437044482</v>
+      </c>
+      <c r="L25" t="n">
+        <v>20.39312345716109</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.11405165353406</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.72173476384452</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-6860.358282151244</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-145.2106911655713</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.967437724492801e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8825948931388248</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>101.124</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7985596171614033</v>
+      </c>
+      <c r="D26" t="n">
+        <v>715.868845533541</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.8252435768616589</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.54742e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-79.43300000000001</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.5995335870248248</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.9780207895237867</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.642039133933071</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.791090578730343</v>
+      </c>
+      <c r="L26" t="n">
+        <v>22.08222797597267</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.38286258754704</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>15.81904002354427</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-7310.533424839303</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-231.7657078063641</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.500555416419336e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8889321327035962</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97.53200000000004</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7701941831907956</v>
+      </c>
+      <c r="D27" t="n">
+        <v>653.3829303184647</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7532106891374677</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.52903e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-79.693</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.1486552050200159</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.6228018153241636</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.574913261526477</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.685102450538515</v>
+      </c>
+      <c r="L27" t="n">
+        <v>22.81717006988999</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.40908360630586</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.93485767343772</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-7253.939141756458</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-181.3292214739071</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.148654314970473e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8939534840873773</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>94.90600000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7494570925430178</v>
+      </c>
+      <c r="D28" t="n">
+        <v>631.5009959526739</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7279855017342939</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.51503e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-79.92100000000001</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.1636563353997005</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.027678262561383</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.687178102884416</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.746857459335125</v>
+      </c>
+      <c r="L28" t="n">
+        <v>24.39167720784301</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.52511975594811</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>16.46834134292472</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-7410.799510043837</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-167.1906474469674</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.865235839604954e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8981973383088065</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>93.04000000000002</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7347215970560595</v>
+      </c>
+      <c r="D29" t="n">
+        <v>648.2139157882707</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7472519215973494</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.50016e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-80.12</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.1196566316599201</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.8761862047949257</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.874230061387735</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.583498309381157</v>
+      </c>
+      <c r="L29" t="n">
+        <v>24.12551441331144</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.66171887850922</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>17.1438320757833</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-7632.948425748457</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-187.3937214025432</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.617305433626118e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9019582986173899</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>90.173</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7120813689954433</v>
+      </c>
+      <c r="D30" t="n">
+        <v>649.4871196159793</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7487196531342193</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.48717e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-80.29900000000001</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.6741443795002749</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.116995891298605</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.620709191932643</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.649998209069935</v>
+      </c>
+      <c r="L30" t="n">
+        <v>24.80613335068082</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.73939803914961</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>17.55317427152207</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-7727.753523083717</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-193.4779641317593</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.409253555724308e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9051804329360816</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>87.74800000000005</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6929315423309882</v>
+      </c>
+      <c r="D31" t="n">
+        <v>623.5663124121921</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7188385097020702</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.47817e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-80.49299999999999</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.116864659370492</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7499596405437363</v>
+      </c>
+      <c r="J31" t="n">
+        <v>1.736718790107192</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.710733340992654</v>
+      </c>
+      <c r="L31" t="n">
+        <v>26.47674219985563</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.76321307466895</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>17.68260202793824</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-7688.241306720884</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-174.744657867946</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.211383059960402e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9084283692325341</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>86.12</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6800754937496544</v>
+      </c>
+      <c r="D32" t="n">
+        <v>631.730451167754</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7282500144919083</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.46873e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-80.629</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5006006002350949</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9932322585569578</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.100630783927933</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.822556704834637</v>
+      </c>
+      <c r="L32" t="n">
+        <v>27.70198015683637</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.84478497143563</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>18.14071282561955</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-7815.289419813595</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-186.1803113639423</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.063701352079936e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9108344549519343</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>85.72300000000001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6769404499617002</v>
+      </c>
+      <c r="D33" t="n">
+        <v>640.136112300947</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7379399428953063</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.45936e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-80.765</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.8560662265338262</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.996947515693811</v>
+      </c>
+      <c r="J33" t="n">
+        <v>1.76234036100377</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.747803343014812</v>
+      </c>
+      <c r="L33" t="n">
+        <v>27.85302455033056</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.96952641648392</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>18.88890926099844</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-8081.105502885852</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-197.2991343575597</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>7.926384331754758e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9130852599706556</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>82.25900000000001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.649585810965546</v>
+      </c>
+      <c r="D34" t="n">
+        <v>672.0287425789184</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7747053203109189</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.45247e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-80.878</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.05214015702900616</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.5747935290142421</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.62403235385791</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.607447803069926</v>
+      </c>
+      <c r="L34" t="n">
+        <v>27.16379414055731</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.89056668718435</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>18.40834429132125</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-7775.94910073984</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-229.5337288287176</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.814934457548496e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9149875159325446</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>82.39699999999999</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6506755742973788</v>
+      </c>
+      <c r="D35" t="n">
+        <v>619.923743452076</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7146394072318808</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.44504e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-80.977</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.6500869484669535</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.204129815563921</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.879388107853398</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.969197782342656</v>
+      </c>
+      <c r="L35" t="n">
+        <v>29.37968596747114</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.99326370493998</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>19.03830896839971</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-7988.5966968354</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-186.1144178922866</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.716591258289905e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9166372125299204</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80.50900000000001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6357663484241863</v>
+      </c>
+      <c r="D36" t="n">
+        <v>627.1012086450543</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7229134885606177</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.43868e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-81.093</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3494183904713054</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1.458579466504667</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2.186867206119076</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3.223656601366077</v>
+      </c>
+      <c r="L36" t="n">
+        <v>30.9071456711145</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.06119563420363</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>19.47918882612264</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-8110.328318765581</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-195.9353276752529</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.612174688380247e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9184570620464072</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79.62600000000003</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6287934424676033</v>
+      </c>
+      <c r="D37" t="n">
+        <v>620.6287675622171</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7154521491497009</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.4356e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-81.188</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.4729260390438598</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.138845252122794</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.924941098874144</v>
+      </c>
+      <c r="K37" t="n">
+        <v>2.816271616049777</v>
+      </c>
+      <c r="L37" t="n">
+        <v>29.94970937344211</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.06598764755772</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19.51105928412112</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-8048.507284433118</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-193.2567974255184</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.530725144062699e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9199711053264399</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>77.30199999999996</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6104411962126771</v>
+      </c>
+      <c r="D38" t="n">
+        <v>608.3178199568971</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7012602612085532</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.42902e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-81.29300000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.2505220786918179</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.175612510913872</v>
+      </c>
+      <c r="J38" t="n">
+        <v>2.013912801438306</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.959250103598053</v>
+      </c>
+      <c r="L38" t="n">
+        <v>31.28553970527411</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.04669351874476</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>19.38336851785602</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-7914.748228115303</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-185.3169481193873</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.440256920703068e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9215555928106822</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>76.89300000000003</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.6072113903958685</v>
+      </c>
+      <c r="D39" t="n">
+        <v>690.4618400831339</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7959547368931995</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.42504e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-81.392</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.5160697144644095</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.926100674199054</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.739834193225407</v>
+      </c>
+      <c r="K39" t="n">
+        <v>2.933940000541746</v>
+      </c>
+      <c r="L39" t="n">
+        <v>30.41293140374787</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.12844946748636</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>19.9361977773622</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-8083.850856494796</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-262.22137496996</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.358434797363799e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9230799910191222</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>75.31400000000002</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.594742286765693</v>
+      </c>
+      <c r="D40" t="n">
+        <v>666.6569740636429</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7685128208170838</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.42194e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-81.462</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.3268530045486853</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9258068955943083</v>
+      </c>
+      <c r="J40" t="n">
+        <v>1.88274302439386</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.93387623618843</v>
+      </c>
+      <c r="L40" t="n">
+        <v>31.34639243627744</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.16442505823083</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>20.18955428858366</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-8124.66929687184</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-244.0621697154552</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>7.300207471263049e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9241690328716775</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>75.01399999999995</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5923732360443165</v>
+      </c>
+      <c r="D41" t="n">
+        <v>626.4913924537649</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7222105009979269</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.41998e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-81.56100000000001</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.4362144775262793</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.229256742440439</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.971876764895818</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.217635716338387</v>
+      </c>
+      <c r="L41" t="n">
+        <v>32.9071024858909</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.22282850808183</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20.61482414321637</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-8232.125132821564</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-210.8592403037833</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.227657215465091e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9255939660528533</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>73.20400000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5780799633586821</v>
+      </c>
+      <c r="D42" t="n">
+        <v>607.9840241428614</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7008754660701211</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.41749e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-81.64700000000001</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.3395909422383063</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.9546750307990517</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.682906699589026</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.690532180267566</v>
+      </c>
+      <c r="L42" t="n">
+        <v>31.00696512859828</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.19541185281336</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>20.41298341297195</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-8065.044971962247</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-197.4987919087744</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>7.159869467681006e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9269266376916596</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>71.86399999999998</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5674982034698692</v>
+      </c>
+      <c r="D43" t="n">
+        <v>610.9082687126024</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.704246494245754</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.4155e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-81.724</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4305789690475726</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.113593186149117</v>
+      </c>
+      <c r="J43" t="n">
+        <v>1.913686830970686</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.241324788414472</v>
+      </c>
+      <c r="L43" t="n">
+        <v>33.69801905733078</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.21832621275446</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>20.58140553137124</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-8061.252527263254</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-203.1640149339285</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.103629344653632e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.928042798095171</v>
       </c>
     </row>
@@ -5850,7 +10498,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6552,6 +11200,566 @@
         <v>8.035422719802362e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.9198480491341916</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>121.092</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>218.2783649959942</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.8887e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-76.15000000000001</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2883807891840778</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.5321887964661228</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.046348451220827</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.829887672908616</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.21769244937792</v>
+      </c>
+      <c r="M12" t="n">
+        <v>83.78116345221645</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.177055286031266</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-4283.493809854624</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>213.5454479374106</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.267413916442455e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9603570875998705</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>83.94799999999998</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6932580186965278</v>
+      </c>
+      <c r="D13" t="n">
+        <v>772.7007721063693</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.539978742833948</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.96942e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-77.90900000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.01771462920432121</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7900758989984019</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.414944697999545</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.278831558907785</v>
+      </c>
+      <c r="L13" t="n">
+        <v>13.736387337216</v>
+      </c>
+      <c r="M13" t="n">
+        <v>84.95858072274089</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.33566486623271</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-4759.723635532172</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-318.2760904130394</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.167982552580774e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8720335294883568</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>76.423</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.631115185148482</v>
+      </c>
+      <c r="D14" t="n">
+        <v>798.2110072868692</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.656848938288124</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.93326e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-78.60299999999999</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.317524724824112</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.7753778490641553</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.796786024792982</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.440617107243188</v>
+      </c>
+      <c r="L14" t="n">
+        <v>15.15050099366386</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.40294984965661</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.4368407549619</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-5075.480918343761</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-355.6781913084482</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.057263656926392e-06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8857564486800935</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>73.19899999999996</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.6044908003831791</v>
+      </c>
+      <c r="D15" t="n">
+        <v>674.1764143097242</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.0886085037429</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.891439999999999e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-79.069</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.411623251149394</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.082766739584801</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.609062161150477</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.726828601762241</v>
+      </c>
+      <c r="L15" t="n">
+        <v>16.51203503602854</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.68953496840582</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>13.26716342533937</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-5329.797388394029</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-251.176451212601</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.933647794257932e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8937343265313835</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>68.11800000000005</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.562530968189476</v>
+      </c>
+      <c r="D16" t="n">
+        <v>632.6553113386441</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.898387622384172</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.85406e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-79.43600000000001</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6907115191387228</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.571388191479304</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.720839364322617</v>
+      </c>
+      <c r="L16" t="n">
+        <v>17.48952097215687</v>
+      </c>
+      <c r="M16" t="n">
+        <v>85.76830569346231</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>13.51505032843908</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-5324.500811857602</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-219.8408627208923</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.460835482645655e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.8998354049591756</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>66.875</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5522660456512402</v>
+      </c>
+      <c r="D17" t="n">
+        <v>672.5921549952449</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.081350526918177</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.8182e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-79.753</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.2555665193909649</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8490121594829868</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.713350156144967</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.709595061188523</v>
+      </c>
+      <c r="L17" t="n">
+        <v>18.31633276072394</v>
+      </c>
+      <c r="M17" t="n">
+        <v>85.98534782726016</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>14.2483031972898</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-5542.81532576788</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-261.6950407583697</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>9.079446112459932e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.904846474563714</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>64.42599999999999</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.532041753377597</v>
+      </c>
+      <c r="D18" t="n">
+        <v>673.4428226431781</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.085247695783029</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.78968e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-80.051</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.1531508361439901</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.8188503572383034</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.507520394695414</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.786339152844548</v>
+      </c>
+      <c r="L18" t="n">
+        <v>19.01499402521065</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.1179253403461</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>14.73646981245748</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-5645.649043492897</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-268.2343773639902</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.75602241623646e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9093469545645744</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>62.57499999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.5167558550523567</v>
+      </c>
+      <c r="D19" t="n">
+        <v>685.5180876685932</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.14056818082348</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.76339e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-80.32599999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.1839326477271538</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.9785566142369828</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.070528077283066</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.023096351056176</v>
+      </c>
+      <c r="L19" t="n">
+        <v>20.43472388221183</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.29248315753577</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>15.43237441152464</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-5835.431609975895</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-285.0004103577767</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.473050545763279e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9134011861238815</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>60.048</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4958874244376175</v>
+      </c>
+      <c r="D20" t="n">
+        <v>704.8650864423106</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3.22920270387423</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.73825e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-80.574</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2391212664022261</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.9157932615623966</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.879885299195631</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.87321016345282</v>
+      </c>
+      <c r="L20" t="n">
+        <v>21.02856807254446</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.39895569203611</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>15.88992324757191</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-5922.040076180075</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-308.1243694287617</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>8.225130505633036e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9170265949096936</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57.11200000000002</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4716413966240545</v>
+      </c>
+      <c r="D21" t="n">
+        <v>648.3934053039452</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.970488647905368</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.71744e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-80.77</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.2382283908017906</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.6565990320108703</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.689928116190377</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.644874138205106</v>
+      </c>
+      <c r="L21" t="n">
+        <v>20.85108052391334</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.39634014755802</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>15.87835986706932</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-5821.152911643883</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-261.6972801778527</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>8.035422719802362e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.9198480491341916</v>
       </c>
     </row>
@@ -6566,7 +11774,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7884,6 +13092,1182 @@
         <v>7.359385478192486e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9279323355349972</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>123.676</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>829.7450073918599</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.84296e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-77.185</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.1623965435353185</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.8092800366591126</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.316430163586498</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.202748515029585</v>
+      </c>
+      <c r="L23" t="n">
+        <v>14.64030760710914</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.12960059451331</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>11.73573382103866</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-5683.331757794689</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-305.5240465686219</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.44353238429869e-06</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8359661112213421</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>107.541</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8695381480642971</v>
+      </c>
+      <c r="D24" t="n">
+        <v>646.2123305300097</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.778808338433094</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.81725e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-78.242</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.3814980439111771</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.272972744264743</v>
+      </c>
+      <c r="J24" t="n">
+        <v>1.852466773046397</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.909291168545661</v>
+      </c>
+      <c r="L24" t="n">
+        <v>18.20706193145119</v>
+      </c>
+      <c r="M24" t="n">
+        <v>85.79000605363042</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>13.58496681241171</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-6306.152240210211</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-166.5213896684205</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.185563077314297e-06</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8645279071681522</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>103.253</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8348669103140468</v>
+      </c>
+      <c r="D25" t="n">
+        <v>642.25651211527</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7740408274755119</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.78223e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-78.70999999999999</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.5213230390529552</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.004711469730084</v>
+      </c>
+      <c r="J25" t="n">
+        <v>1.779428672820511</v>
+      </c>
+      <c r="K25" t="n">
+        <v>2.784266052922787</v>
+      </c>
+      <c r="L25" t="n">
+        <v>18.82812041795541</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.09604588803867</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>14.65362622124289</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-6706.368759949533</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-170.1129057672607</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1.096061458687113e-06</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8751476842042138</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98.27499999999998</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.7946165788026779</v>
+      </c>
+      <c r="D26" t="n">
+        <v>589.4710114108022</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.710424294403034</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.75225e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-79.051</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5121455487054143</v>
+      </c>
+      <c r="J26" t="n">
+        <v>1.595991076440078</v>
+      </c>
+      <c r="K26" t="n">
+        <v>2.412217662441499</v>
+      </c>
+      <c r="L26" t="n">
+        <v>19.35929534743119</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.07010806880217</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>14.55660931081341</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-6538.013673325883</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-128.3052133163929</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.038776231899943e-06</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8822300035820875</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98.31</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7948995763123</v>
+      </c>
+      <c r="D27" t="n">
+        <v>670.2710807892486</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.8078036924815176</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.7266e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-79.343</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.8140840546572412</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1.243309414853227</v>
+      </c>
+      <c r="J27" t="n">
+        <v>2.256356632628583</v>
+      </c>
+      <c r="K27" t="n">
+        <v>3.111021107059876</v>
+      </c>
+      <c r="L27" t="n">
+        <v>22.34143144567199</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.3974213244698</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>15.88313774120423</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-7090.955058926787</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-204.9986302155662</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.937445627067558e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8880242328620667</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>94.524</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7642873314143408</v>
+      </c>
+      <c r="D28" t="n">
+        <v>615.7394420020415</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7420827320642727</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.7051e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-79.599</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.03167957378555899</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1.05799267816026</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.846316946268489</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.866833868380211</v>
+      </c>
+      <c r="L28" t="n">
+        <v>22.83206017039094</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.39990871394555</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>15.89414074963146</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-6975.740533092861</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-162.5268547626645</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>9.567497309654283e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.8930081884427498</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91.20700000000005</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7374672531453157</v>
+      </c>
+      <c r="D29" t="n">
+        <v>610.8557490550479</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.7361969564302083</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.68669e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-79.828</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.2476222924378204</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.9489861593759239</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.818868025082613</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.449168017004949</v>
+      </c>
+      <c r="L29" t="n">
+        <v>22.30368778780296</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.52055460344455</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>16.44668120124397</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-7128.935944885306</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-163.5480279973164</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>9.260766037454285e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.8972817891371527</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>88.71699999999998</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7173340017464989</v>
+      </c>
+      <c r="D30" t="n">
+        <v>682.6366321692227</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.8227065256047236</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.66931e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-80.042</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.2196336436880204</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.9043474548469617</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1.42452217486419</v>
+      </c>
+      <c r="K30" t="n">
+        <v>2.524003465387857</v>
+      </c>
+      <c r="L30" t="n">
+        <v>23.16760104759276</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.61093400004739</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>16.88634639481359</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-7229.801554616858</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-232.691933950591</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.986873886286346e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9012238717351333</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>86.673</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.7008069471845791</v>
+      </c>
+      <c r="D31" t="n">
+        <v>615.4718246805639</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7417602024689229</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.65709e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-80.233</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3101274608736999</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.8747583848827745</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.009664899115111</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.601448608230351</v>
+      </c>
+      <c r="L31" t="n">
+        <v>23.94576419934643</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.69588850910867</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>17.32152567040469</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-7331.279047687674</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-177.6116615469635</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.768879609255373e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.9044926105548891</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>84.81299999999999</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6857676509589572</v>
+      </c>
+      <c r="D32" t="n">
+        <v>605.0940261387564</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.7292529882653351</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.64191e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-80.40600000000001</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.4523687698168246</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.9177662989676423</v>
+      </c>
+      <c r="J32" t="n">
+        <v>2.002530197280932</v>
+      </c>
+      <c r="K32" t="n">
+        <v>3.066245506968277</v>
+      </c>
+      <c r="L32" t="n">
+        <v>26.25759194382906</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.74793919765791</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>17.59937519132789</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-7361.997937760949</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-172.708389191219</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.561757955896253e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9075872903422426</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>82.91899999999998</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6704534428668456</v>
+      </c>
+      <c r="D33" t="n">
+        <v>608.3933309406218</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.7332292758868011</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.63033e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-80.53700000000001</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.4270857647481843</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.212496589357122</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.015776108282767</v>
+      </c>
+      <c r="K33" t="n">
+        <v>3.08968663734819</v>
+      </c>
+      <c r="L33" t="n">
+        <v>26.69928541848866</v>
+      </c>
+      <c r="M33" t="n">
+        <v>86.80761449780843</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>17.92906166017158</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-7422.984814473733</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-179.8525384945917</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.407841750404369e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9099342884053379</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>81.91500000000002</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6623354571622629</v>
+      </c>
+      <c r="D34" t="n">
+        <v>618.1980856916543</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.7450458637103926</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.62104e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-80.702</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.2424974841333522</v>
+      </c>
+      <c r="I34" t="n">
+        <v>1.149520551129594</v>
+      </c>
+      <c r="J34" t="n">
+        <v>2.050908912207502</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.535372101897286</v>
+      </c>
+      <c r="L34" t="n">
+        <v>25.96298396349746</v>
+      </c>
+      <c r="M34" t="n">
+        <v>86.90405563077231</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>18.48870629030299</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-7584.6203970385</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-192.5282530058229</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>8.243302362294342e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9125830831068515</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>78.851</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6375610466056471</v>
+      </c>
+      <c r="D35" t="n">
+        <v>578.232493096681</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6968797497368993</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.61169e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-80.84</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.3352050718671497</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.958755746146509</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2.001668244491126</v>
+      </c>
+      <c r="K35" t="n">
+        <v>3.123675625299848</v>
+      </c>
+      <c r="L35" t="n">
+        <v>27.77352621232956</v>
+      </c>
+      <c r="M35" t="n">
+        <v>86.85032697074804</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>18.17269683844975</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-7356.407800720732</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-160.1414708819688</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>8.10485472374145e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9148156246906155</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>77.49299999999999</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6265807432323167</v>
+      </c>
+      <c r="D36" t="n">
+        <v>627.641168209968</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.7564265679438488</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.6039e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-80.958</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.3572078547478958</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.6480608949260144</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.631086403487551</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.689751497767332</v>
+      </c>
+      <c r="L36" t="n">
+        <v>26.48262219080131</v>
+      </c>
+      <c r="M36" t="n">
+        <v>86.91608356221145</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>18.5609564643298</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-7444.025720975245</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-208.2536776418214</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.985641322860091e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9167876429668199</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>76.70600000000002</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.6202173420873899</v>
+      </c>
+      <c r="D37" t="n">
+        <v>605.2262769639079</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7294123755758622</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.59584e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-81.07899999999999</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.5552965071706004</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.482768992555256</v>
+      </c>
+      <c r="J37" t="n">
+        <v>2.043931506468009</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.230491285076649</v>
+      </c>
+      <c r="L37" t="n">
+        <v>29.43307112087036</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.04139134951386</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>19.34856961724427</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-7707.084684646431</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-191.7777975760882</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.872979423758546e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9186516067912844</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>75.99000000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.6144280216048386</v>
+      </c>
+      <c r="D38" t="n">
+        <v>608.7563581516555</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7336667924826222</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.5913e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-81.176</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.436268012858271</v>
+      </c>
+      <c r="I38" t="n">
+        <v>1.248635917128191</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.866266752416742</v>
+      </c>
+      <c r="K38" t="n">
+        <v>3.154088624055564</v>
+      </c>
+      <c r="L38" t="n">
+        <v>29.83209795293848</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.08235123250444</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>19.62067773731119</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-7739.44327589951</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-198.5240715089367</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.782783084268183e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9202361608546163</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>74.08100000000002</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5989925288657462</v>
+      </c>
+      <c r="D39" t="n">
+        <v>605.8733815174843</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7301922592121741</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.58504e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-81.274</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.514638049620759</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.086332455754805</v>
+      </c>
+      <c r="J39" t="n">
+        <v>2.238722145157286</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.187096065802534</v>
+      </c>
+      <c r="L39" t="n">
+        <v>29.57709165460403</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.0904819324337</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>19.67560283967531</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-7682.684802412933</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-199.4218618842946</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.697054488548521e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9216871260833548</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>72.64999999999998</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5874219735437756</v>
+      </c>
+      <c r="D40" t="n">
+        <v>597.2493443089675</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.719798659815144</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.5813e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-81.398</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4700349147343521</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.9619189249930687</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.299034811079055</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.829410159049698</v>
+      </c>
+      <c r="L40" t="n">
+        <v>29.73491710030678</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.12274139930787</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>19.89658084902466</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-7687.78264173453</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-195.1522181583273</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>7.596315165932298e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9235366745520968</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>71.572</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5787056502474207</v>
+      </c>
+      <c r="D41" t="n">
+        <v>595.9659076815213</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7182518754223335</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.5765e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-81.491</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.2929770961099574</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.175667931061104</v>
+      </c>
+      <c r="J41" t="n">
+        <v>1.866004361219266</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.822874190548094</v>
+      </c>
+      <c r="L41" t="n">
+        <v>29.41597137133795</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.14911157335852</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>20.0809287786944</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-7681.19113117973</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-197.3963970798098</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.51514431538005e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9250009720161539</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>70.94</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5735955237879621</v>
+      </c>
+      <c r="D42" t="n">
+        <v>598.372385788475</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.7211521376541219</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.57344e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-81.575</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.8270406033491171</v>
+      </c>
+      <c r="I42" t="n">
+        <v>1.380363339654291</v>
+      </c>
+      <c r="J42" t="n">
+        <v>1.809232970825728</v>
+      </c>
+      <c r="K42" t="n">
+        <v>3.341352473016772</v>
+      </c>
+      <c r="L42" t="n">
+        <v>31.63344129499119</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.22916975012306</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>20.66207652526992</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-7841.170060151584</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-203.012379385826</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>7.447306624467331e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9262621540039233</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>68.702</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5554998544584236</v>
+      </c>
+      <c r="D43" t="n">
+        <v>575.413501577973</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.693482330658032</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.57011e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-81.69199999999999</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.4288725566562775</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.8783699069976134</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.048508291328718</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.862473984124695</v>
+      </c>
+      <c r="L43" t="n">
+        <v>29.81380469916768</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.21428760940691</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>20.55152054250722</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-7703.352265908799</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-185.9230867997238</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.359385478192486e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9279323355349972</v>
       </c>
     </row>
@@ -7898,7 +14282,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8600,6 +14984,566 @@
         <v>7.698221397174921e-07</v>
       </c>
       <c r="AD11" t="n">
+        <v>0.925669087504264</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>124.192</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>263.3623335045764</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>5.06168e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-75.729</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.5001486590850153</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.7562228226069914</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.522026743938313</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.160764579501233</v>
+      </c>
+      <c r="L12" t="n">
+        <v>11.96880315907912</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.13590972262895</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>9.736477148276787</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-4706.862100501113</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>181.7227949464663</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.804388133672855e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9436007953100107</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80.36900000000003</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.6471350811646488</v>
+      </c>
+      <c r="D13" t="n">
+        <v>791.1795251521104</v>
+      </c>
+      <c r="E13" t="n">
+        <v>3.004148370892082</v>
+      </c>
+      <c r="F13" t="n">
+        <v>5.05983e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-77.738</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.5808939926402973</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.388584761184423</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.366079639626519</v>
+      </c>
+      <c r="L13" t="n">
+        <v>14.37234780327933</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.06619720273187</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>11.58418635750227</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-4976.356265492807</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-328.4985620148368</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.17313974285562e-06</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8744203424859919</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>72.76999999999998</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.5859475650605515</v>
+      </c>
+      <c r="D14" t="n">
+        <v>700.6548159608938</v>
+      </c>
+      <c r="E14" t="n">
+        <v>2.660421506132799</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.98707e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-78.54900000000001</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.1424282531357242</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.8589615223274628</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.565193277231401</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.673473578485488</v>
+      </c>
+      <c r="L14" t="n">
+        <v>16.46437352006917</v>
+      </c>
+      <c r="M14" t="n">
+        <v>85.58516677937202</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>12.95232212560322</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-5411.809530377352</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-261.3865237720325</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.042702286983623e-06</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.8897456183513072</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>71.12</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.572661685132698</v>
+      </c>
+      <c r="D15" t="n">
+        <v>726.153639715642</v>
+      </c>
+      <c r="E15" t="n">
+        <v>2.757241819863446</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.91899e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-79.108</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.5893254520247888</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.285754398867361</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.0273833269426</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.968174921257336</v>
+      </c>
+      <c r="L15" t="n">
+        <v>18.32366201674681</v>
+      </c>
+      <c r="M15" t="n">
+        <v>85.99007229705575</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>14.26514549216907</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-5882.445877498227</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-291.7843537052828</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>9.667632009195438e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.8988976992951779</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>66.69199999999995</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.537007214635403</v>
+      </c>
+      <c r="D16" t="n">
+        <v>684.8457382966888</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2.600393644692506</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.86304e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-79.521</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1849589041422322</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.6327020060024939</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.68958607681293</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.494243346784313</v>
+      </c>
+      <c r="L16" t="n">
+        <v>18.88314099900246</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.08654354099457</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>14.61793493990395</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-5912.550917972069</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-260.275972515546</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>9.154067010114607e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.905276494417247</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>65.197</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5249694022159239</v>
+      </c>
+      <c r="D17" t="n">
+        <v>733.709415439338</v>
+      </c>
+      <c r="E17" t="n">
+        <v>2.78593147955453</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.81797e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-79.883</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.6486647436649666</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.8560208691567313</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.785096156789869</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.615233704197306</v>
+      </c>
+      <c r="L17" t="n">
+        <v>20.07945041236714</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.33257021576475</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>15.60152813550097</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-6235.442365587123</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-310.6265914353693</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>8.743835325129439e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9106807515897078</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>61.40999999999997</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.4944762947693893</v>
+      </c>
+      <c r="D18" t="n">
+        <v>680.1839629842051</v>
+      </c>
+      <c r="E18" t="n">
+        <v>2.582692649829462</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.7786e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-80.18600000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.4740426777675529</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1.573847299797207</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.63391102063363</v>
+      </c>
+      <c r="L18" t="n">
+        <v>20.80610951758174</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.34633725051124</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>15.66047541250164</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-6135.528995056597</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-267.7890935644051</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>8.417608574416963e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9151058740197378</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>61.18799999999999</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.49268874001546</v>
+      </c>
+      <c r="D19" t="n">
+        <v>786.2440739197071</v>
+      </c>
+      <c r="E19" t="n">
+        <v>2.985408214823722</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.74438e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-80.47199999999999</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.8234537176857212</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.682203796314076</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.95193306293261</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.110994581119319</v>
+      </c>
+      <c r="L19" t="n">
+        <v>22.36865819095963</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.62592367176711</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>16.96154055982626</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-6578.014354393819</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-371.0733222104357</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>8.130776909525363e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9191796398091944</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57.14799999999997</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4601584643133212</v>
+      </c>
+      <c r="D20" t="n">
+        <v>691.9842054607199</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2.627498762835405</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.71805e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-80.72</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.2350043506940432</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.914260050956486</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1.778509844187109</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.905110282901658</v>
+      </c>
+      <c r="L20" t="n">
+        <v>22.99686477583796</v>
+      </c>
+      <c r="M20" t="n">
+        <v>86.60634163310644</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>16.8634420269123</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-6410.809512081318</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-290.5535614825365</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.900417733723573e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9225975243207039</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>55.91800000000001</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4502544447307397</v>
+      </c>
+      <c r="D21" t="n">
+        <v>749.5695146089056</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2.84615307221175</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.69256e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-80.943</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.4666709475032766</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.041937800938761</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.658584385776407</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.684840930116787</v>
+      </c>
+      <c r="L21" t="n">
+        <v>23.23310998169568</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.73447448770771</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>17.52665144331503</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-6576.716637615972</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-349.1975388163781</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>7.698221397174921e-07</v>
+      </c>
+      <c r="AD21" t="n">
         <v>0.925669087504264</v>
       </c>
     </row>
@@ -8614,7 +15558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD22"/>
+  <dimension ref="A1:AD43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9932,6 +16876,1182 @@
         <v>7.201651642019925e-07</v>
       </c>
       <c r="AD22" t="n">
+        <v>0.9307596279854847</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>1.428571428571429</v>
+      </c>
+      <c r="B23" t="n">
+        <v>121.722</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>938.0708632003845</v>
+      </c>
+      <c r="E23" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" t="n">
+        <v>4.76632e-07</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-77.64400000000001</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.7771873896084369</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.083176045982918</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.626548869867174</v>
+      </c>
+      <c r="K23" t="n">
+        <v>2.644994475207516</v>
+      </c>
+      <c r="L23" t="n">
+        <v>18.18406376769286</v>
+      </c>
+      <c r="M23" t="n">
+        <v>85.78537421927085</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>13.56998315772325</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>-6843.161697481773</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>-386.6727171573197</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.266813073883723e-06</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.8533406657864562</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="B24" t="n">
+        <v>102.705</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.8437669443485977</v>
+      </c>
+      <c r="D24" t="n">
+        <v>715.4025492260971</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.762631670261437</v>
+      </c>
+      <c r="F24" t="n">
+        <v>4.74076e-07</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-78.58799999999999</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.1198867299119269</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8053831467700157</v>
+      </c>
+      <c r="J24" t="n">
+        <v>2.020858217434877</v>
+      </c>
+      <c r="K24" t="n">
+        <v>2.53392835076507</v>
+      </c>
+      <c r="L24" t="n">
+        <v>20.44507927159098</v>
+      </c>
+      <c r="M24" t="n">
+        <v>86.18804292050878</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>15.0083579993464</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>-7204.231455318031</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>-215.8954856914332</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.068721946864941e-06</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.8779243616846807</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>4.285714285714286</v>
+      </c>
+      <c r="B25" t="n">
+        <v>100.697</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.8272703373260382</v>
+      </c>
+      <c r="D25" t="n">
+        <v>689.9065032989724</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.7354524379376222</v>
+      </c>
+      <c r="F25" t="n">
+        <v>4.70895e-07</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-79.021</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0.8531281030710763</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.248330204912236</v>
+      </c>
+      <c r="J25" t="n">
+        <v>2.232020104681853</v>
+      </c>
+      <c r="K25" t="n">
+        <v>3.207373042269441</v>
+      </c>
+      <c r="L25" t="n">
+        <v>23.57772090874782</v>
+      </c>
+      <c r="M25" t="n">
+        <v>86.57986956023579</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>16.73261071831124</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>-7940.519382880433</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>-201.0340038309096</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>9.979548136303341e-07</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0.8871396027937497</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>5.714285714285714</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97.654</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.8022707480981254</v>
+      </c>
+      <c r="D26" t="n">
+        <v>704.3672356997928</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.7508678324116443</v>
+      </c>
+      <c r="F26" t="n">
+        <v>4.68432e-07</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-79.331</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0.9719800631099487</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1.764185951249406</v>
+      </c>
+      <c r="J26" t="n">
+        <v>2.38583202821234</v>
+      </c>
+      <c r="K26" t="n">
+        <v>3.396476314054961</v>
+      </c>
+      <c r="L26" t="n">
+        <v>25.78162705559582</v>
+      </c>
+      <c r="M26" t="n">
+        <v>86.74344256078949</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>17.57502176229121</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>-8239.342518949676</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>-219.9721970500926</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>9.531497859256004e-07</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.8931999939610994</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>7.142857142857143</v>
+      </c>
+      <c r="B27" t="n">
+        <v>92.14100000000002</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.7569790177617853</v>
+      </c>
+      <c r="D27" t="n">
+        <v>663.169226516481</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7069500317427716</v>
+      </c>
+      <c r="F27" t="n">
+        <v>4.66149e-07</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-79.56999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0.3124801425364943</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.8468746452961974</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.848534340910579</v>
+      </c>
+      <c r="K27" t="n">
+        <v>2.664541904079427</v>
+      </c>
+      <c r="L27" t="n">
+        <v>24.38174846657641</v>
+      </c>
+      <c r="M27" t="n">
+        <v>86.6698738062922</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>17.18590952855711</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>-7911.982102012559</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>-188.6416346107046</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.194333412358749e-07</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0.8978543656938922</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>8.571428571428571</v>
+      </c>
+      <c r="B28" t="n">
+        <v>89.60300000000001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.7361282266147453</v>
+      </c>
+      <c r="D28" t="n">
+        <v>661.2874947867507</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.7049440727011376</v>
+      </c>
+      <c r="F28" t="n">
+        <v>4.64535e-07</v>
+      </c>
+      <c r="G28" t="n">
+        <v>-79.794</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.2435525135550979</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.8500694502118552</v>
+      </c>
+      <c r="J28" t="n">
+        <v>1.729553403228067</v>
+      </c>
+      <c r="K28" t="n">
+        <v>2.494546836641941</v>
+      </c>
+      <c r="L28" t="n">
+        <v>24.98309728818039</v>
+      </c>
+      <c r="M28" t="n">
+        <v>86.75137463566472</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>17.61802663241954</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>-8009.399682345235</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>-192.1424400268764</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>8.916486933032104e-07</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0.9019026317153118</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>10</v>
+      </c>
+      <c r="B29" t="n">
+        <v>87.36600000000004</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.7177502834327406</v>
+      </c>
+      <c r="D29" t="n">
+        <v>648.9472467385509</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.6917891517540153</v>
+      </c>
+      <c r="F29" t="n">
+        <v>4.63123e-07</v>
+      </c>
+      <c r="G29" t="n">
+        <v>-79.994</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0.230455214431745</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.7372203931744692</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.983281513832002</v>
+      </c>
+      <c r="K29" t="n">
+        <v>2.643018619430513</v>
+      </c>
+      <c r="L29" t="n">
+        <v>27.01499627703845</v>
+      </c>
+      <c r="M29" t="n">
+        <v>86.78347182229572</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>17.79420940878632</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>-7983.603048873175</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>-186.4323159454435</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>8.676512223636543e-07</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0.9055252247396053</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>11.42857142857143</v>
+      </c>
+      <c r="B30" t="n">
+        <v>86.68400000000003</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.7121473521631262</v>
+      </c>
+      <c r="D30" t="n">
+        <v>672.3152709206338</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.7166998755583546</v>
+      </c>
+      <c r="F30" t="n">
+        <v>4.61892e-07</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-80.187</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.8028156818980049</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.475966743823961</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.171522233287315</v>
+      </c>
+      <c r="K30" t="n">
+        <v>3.223567482670965</v>
+      </c>
+      <c r="L30" t="n">
+        <v>29.56097891629726</v>
+      </c>
+      <c r="M30" t="n">
+        <v>86.9922843357253</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>19.03209833642563</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>-8475.388206199019</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>-212.548298892838</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>8.46008907412597e-07</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0.9089000637390241</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>12.85714285714286</v>
+      </c>
+      <c r="B31" t="n">
+        <v>82.69300000000004</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.6793595241616146</v>
+      </c>
+      <c r="D31" t="n">
+        <v>657.9285759346675</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.7013634062676619</v>
+      </c>
+      <c r="F31" t="n">
+        <v>4.60773e-07</v>
+      </c>
+      <c r="G31" t="n">
+        <v>-80.339</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.3354035625223621</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.7852928017883515</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.030389885209108</v>
+      </c>
+      <c r="K31" t="n">
+        <v>2.896014498207722</v>
+      </c>
+      <c r="L31" t="n">
+        <v>28.73348711450161</v>
+      </c>
+      <c r="M31" t="n">
+        <v>86.92996472219281</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>18.64504174366195</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>-8181.955223618737</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>-204.4090591017565</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>8.290154829325843e-07</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0.911578649492281</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>14.28571428571429</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80.03100000000001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.6574900182382808</v>
+      </c>
+      <c r="D32" t="n">
+        <v>631.866565164574</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6735808454905596</v>
+      </c>
+      <c r="F32" t="n">
+        <v>4.59828e-07</v>
+      </c>
+      <c r="G32" t="n">
+        <v>-80.47799999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.1012091108841455</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.8141289940926068</v>
+      </c>
+      <c r="J32" t="n">
+        <v>1.75641338604335</v>
+      </c>
+      <c r="K32" t="n">
+        <v>2.644005310281202</v>
+      </c>
+      <c r="L32" t="n">
+        <v>28.03220630902175</v>
+      </c>
+      <c r="M32" t="n">
+        <v>86.94504947383524</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>18.73728335358576</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>-8129.735377625187</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>-184.9602425810246</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>8.139573087446793e-07</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0.9140190537441225</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>15.71428571428572</v>
+      </c>
+      <c r="B33" t="n">
+        <v>78.76499999999999</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.6470892689899936</v>
+      </c>
+      <c r="D33" t="n">
+        <v>637.3487426821201</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.6794249429171045</v>
+      </c>
+      <c r="F33" t="n">
+        <v>4.58991e-07</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-80.61199999999999</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.1603568218766196</v>
+      </c>
+      <c r="I33" t="n">
+        <v>1.054795122423983</v>
+      </c>
+      <c r="J33" t="n">
+        <v>2.002924902444626</v>
+      </c>
+      <c r="K33" t="n">
+        <v>2.942700943214583</v>
+      </c>
+      <c r="L33" t="n">
+        <v>29.4336183416531</v>
+      </c>
+      <c r="M33" t="n">
+        <v>87.02624608748611</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>19.24985194861765</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>-8281.152765069404</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>-194.0207744415579</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>8.004479004707351e-07</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0.9162497946736372</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>17.14285714285714</v>
+      </c>
+      <c r="B34" t="n">
+        <v>77.476</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.6364995645815876</v>
+      </c>
+      <c r="D34" t="n">
+        <v>646.7391830801783</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6894353171504766</v>
+      </c>
+      <c r="F34" t="n">
+        <v>4.58185e-07</v>
+      </c>
+      <c r="G34" t="n">
+        <v>-80.72799999999999</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.3643271049418509</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.976858856830971</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1.801837662497254</v>
+      </c>
+      <c r="K34" t="n">
+        <v>2.91016269346947</v>
+      </c>
+      <c r="L34" t="n">
+        <v>30.64638431007635</v>
+      </c>
+      <c r="M34" t="n">
+        <v>87.09347352354551</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>19.69588912243694</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>-8401.525297760061</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>-206.126524907084</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>7.887622345882293e-07</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0.9181883494430608</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>18.57142857142857</v>
+      </c>
+      <c r="B35" t="n">
+        <v>77.07600000000002</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0.6332133878838668</v>
+      </c>
+      <c r="D35" t="n">
+        <v>658.7972437373702</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.7022894213873929</v>
+      </c>
+      <c r="F35" t="n">
+        <v>4.57753e-07</v>
+      </c>
+      <c r="G35" t="n">
+        <v>-80.842</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.2737734101181623</v>
+      </c>
+      <c r="I35" t="n">
+        <v>1.226616297558083</v>
+      </c>
+      <c r="J35" t="n">
+        <v>1.989846585499752</v>
+      </c>
+      <c r="K35" t="n">
+        <v>2.891775176486245</v>
+      </c>
+      <c r="L35" t="n">
+        <v>29.95241704508424</v>
+      </c>
+      <c r="M35" t="n">
+        <v>87.18717141016353</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>20.35308590966891</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>-8622.338619069558</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>-220.3501807834406</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>7.789540139398641e-07</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0.9199148681923197</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>20</v>
+      </c>
+      <c r="B36" t="n">
+        <v>74.57299999999998</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0.6126501371978771</v>
+      </c>
+      <c r="D36" t="n">
+        <v>628.3821722091365</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.6698664214612811</v>
+      </c>
+      <c r="F36" t="n">
+        <v>4.5734e-07</v>
+      </c>
+      <c r="G36" t="n">
+        <v>-80.961</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.37344005728242</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.9597814403458185</v>
+      </c>
+      <c r="J36" t="n">
+        <v>1.844441439904753</v>
+      </c>
+      <c r="K36" t="n">
+        <v>2.93608211158811</v>
+      </c>
+      <c r="L36" t="n">
+        <v>30.86579938698311</v>
+      </c>
+      <c r="M36" t="n">
+        <v>87.15478327222786</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>20.12102449232445</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>-8429.467215093911</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>-196.1450321636349</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>7.685070499554922e-07</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0.9217976267939785</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>21.42857142857143</v>
+      </c>
+      <c r="B37" t="n">
+        <v>74.93699999999995</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0.615640557992803</v>
+      </c>
+      <c r="D37" t="n">
+        <v>665.1021888079617</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.7090106034621471</v>
+      </c>
+      <c r="F37" t="n">
+        <v>4.56802e-07</v>
+      </c>
+      <c r="G37" t="n">
+        <v>-81.039</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.6297353114811841</v>
+      </c>
+      <c r="I37" t="n">
+        <v>1.336810448744086</v>
+      </c>
+      <c r="J37" t="n">
+        <v>1.702099686311896</v>
+      </c>
+      <c r="K37" t="n">
+        <v>3.070800069441218</v>
+      </c>
+      <c r="L37" t="n">
+        <v>31.71038897979813</v>
+      </c>
+      <c r="M37" t="n">
+        <v>87.28882799704577</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>21.11743919611612</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>-8803.436857199689</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>-232.8247776817662</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>7.613762932077516e-07</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0.9230196628031975</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>22.85714285714286</v>
+      </c>
+      <c r="B38" t="n">
+        <v>70.38400000000001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>0.5782356517309938</v>
+      </c>
+      <c r="D38" t="n">
+        <v>585.8401086591512</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.6245158352541303</v>
+      </c>
+      <c r="F38" t="n">
+        <v>4.56379e-07</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-81.13200000000001</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.2766780142113958</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.543756870255331</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.740977706870704</v>
+      </c>
+      <c r="L38" t="n">
+        <v>31.60564304574271</v>
+      </c>
+      <c r="M38" t="n">
+        <v>87.00821877162034</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>19.1336505894647</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>-7837.110899560415</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>-164.133884534203</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>7.534795476309633e-07</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0.9244483286258287</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>24.28571428571428</v>
+      </c>
+      <c r="B39" t="n">
+        <v>71.27600000000001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>0.5855638257669117</v>
+      </c>
+      <c r="D39" t="n">
+        <v>618.0068941786535</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.6588061930313244</v>
+      </c>
+      <c r="F39" t="n">
+        <v>4.55973e-07</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-81.23</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.09677482252185085</v>
+      </c>
+      <c r="I39" t="n">
+        <v>1.012815570676912</v>
+      </c>
+      <c r="J39" t="n">
+        <v>1.999707488786076</v>
+      </c>
+      <c r="K39" t="n">
+        <v>3.093573834962346</v>
+      </c>
+      <c r="L39" t="n">
+        <v>33.72816077482798</v>
+      </c>
+      <c r="M39" t="n">
+        <v>87.21952144430335</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>20.59026668016892</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>-8408.379533294215</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>-196.2871156829</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>7.456470208592552e-07</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.9258764166958136</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>25.71428571428572</v>
+      </c>
+      <c r="B40" t="n">
+        <v>70.56200000000001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>0.5796980003614797</v>
+      </c>
+      <c r="D40" t="n">
+        <v>636.2196128832412</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.6782212707392621</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4.55624e-07</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-81.31999999999999</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.4195969550492009</v>
+      </c>
+      <c r="I40" t="n">
+        <v>1.538649390452874</v>
+      </c>
+      <c r="J40" t="n">
+        <v>2.151265977815468</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.979356815025025</v>
+      </c>
+      <c r="L40" t="n">
+        <v>33.49271493661889</v>
+      </c>
+      <c r="M40" t="n">
+        <v>87.30897587273675</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>21.27578223913298</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>-8633.112353307812</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>-215.9880793427617</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>7.381962876302981e-07</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.9272713516423379</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>27.14285714285714</v>
+      </c>
+      <c r="B41" t="n">
+        <v>69.02999999999997</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.5671119436092077</v>
+      </c>
+      <c r="D41" t="n">
+        <v>622.7932776574197</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.6639085618038034</v>
+      </c>
+      <c r="F41" t="n">
+        <v>4.55382e-07</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-81.392</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.3598447761619862</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.7282904800313691</v>
+      </c>
+      <c r="J41" t="n">
+        <v>2.081237558101108</v>
+      </c>
+      <c r="K41" t="n">
+        <v>3.301899835515345</v>
+      </c>
+      <c r="L41" t="n">
+        <v>34.47729140310153</v>
+      </c>
+      <c r="M41" t="n">
+        <v>87.28953721596211</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>21.12297303489289</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>-8490.745996283242</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>-206.7065352140513</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>7.326524191337869e-07</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>0.9283223804751827</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>28.57142857142857</v>
+      </c>
+      <c r="B42" t="n">
+        <v>67.68700000000001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>0.5560786053466097</v>
+      </c>
+      <c r="D42" t="n">
+        <v>606.7541861770104</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.6468106088563158</v>
+      </c>
+      <c r="F42" t="n">
+        <v>4.55044e-07</v>
+      </c>
+      <c r="G42" t="n">
+        <v>-81.479</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.03975724526578119</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.7507491670410263</v>
+      </c>
+      <c r="J42" t="n">
+        <v>2.395055773194267</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.806491621768894</v>
+      </c>
+      <c r="L42" t="n">
+        <v>33.47534483144656</v>
+      </c>
+      <c r="M42" t="n">
+        <v>87.28350759337729</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>21.07601763621516</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>-8394.224795684553</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>-195.0340353260374</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>7.259537778530464e-07</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>0.9295846152132796</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>30</v>
+      </c>
+      <c r="B43" t="n">
+        <v>67.94100000000003</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.5581653275496626</v>
+      </c>
+      <c r="D43" t="n">
+        <v>652.4669626123602</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.6955412306340706</v>
+      </c>
+      <c r="F43" t="n">
+        <v>4.54982e-07</v>
+      </c>
+      <c r="G43" t="n">
+        <v>-81.562</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.629143386497851</v>
+      </c>
+      <c r="I43" t="n">
+        <v>1.527654774718521</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2.35989606077202</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3.261838021127298</v>
+      </c>
+      <c r="L43" t="n">
+        <v>36.5086044093004</v>
+      </c>
+      <c r="M43" t="n">
+        <v>87.45211959884001</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>22.47280027713964</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>-8914.659985291592</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>-239.8277837411201</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>7.201651642019925e-07</v>
+      </c>
+      <c r="AD43" t="n">
         <v>0.9307596279854847</v>
       </c>
     </row>
@@ -9946,7 +18066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AD21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10651,6 +18771,566 @@
         <v>0.9351523850912739</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="B12" t="n">
+        <v>108.78</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>200.6559842744659</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" t="n">
+        <v>4.77106e-07</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-77.402</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0.2391220231295112</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.4677179285621796</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1.031620251708121</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1.935681700930658</v>
+      </c>
+      <c r="L12" t="n">
+        <v>12.82834797222325</v>
+      </c>
+      <c r="M12" t="n">
+        <v>84.41381906368633</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>10.22417985599863</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>-4547.682375547115</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>212.4090150716961</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.915502938325848e-09</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9744008564404721</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B13" t="n">
+        <v>73.56599999999997</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.676282404853833</v>
+      </c>
+      <c r="D13" t="n">
+        <v>827.4846959260403</v>
+      </c>
+      <c r="E13" t="n">
+        <v>4.12389742034392</v>
+      </c>
+      <c r="F13" t="n">
+        <v>4.76293e-07</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-79.16200000000001</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.4616697440533737</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.7660777820712275</v>
+      </c>
+      <c r="J13" t="n">
+        <v>1.48491294348374</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.815396372467346</v>
+      </c>
+      <c r="L13" t="n">
+        <v>16.14121171012069</v>
+      </c>
+      <c r="M13" t="n">
+        <v>85.56221718859311</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>12.8850738157596</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>-5149.39981701879</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>-387.9120029698407</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>9.575416816390405e-07</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.8952915193310079</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>66.85599999999999</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.6145982717411287</v>
+      </c>
+      <c r="D14" t="n">
+        <v>738.6190633854836</v>
+      </c>
+      <c r="E14" t="n">
+        <v>3.681021854674259</v>
+      </c>
+      <c r="F14" t="n">
+        <v>4.69554e-07</v>
+      </c>
+      <c r="G14" t="n">
+        <v>-79.904</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.3404743735288339</v>
+      </c>
+      <c r="I14" t="n">
+        <v>1.353293402458386</v>
+      </c>
+      <c r="J14" t="n">
+        <v>1.977045484888226</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.866688355591487</v>
+      </c>
+      <c r="L14" t="n">
+        <v>17.90561527678474</v>
+      </c>
+      <c r="M14" t="n">
+        <v>86.05377117096188</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>14.49615693941547</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>-5636.568039942341</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>-322.5827782642048</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>8.694549085997285e-07</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.9075045683677057</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>6</v>
+      </c>
+      <c r="B15" t="n">
+        <v>63.73900000000003</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.585944107372679</v>
+      </c>
+      <c r="D15" t="n">
+        <v>677.7832673733857</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.377837296127109</v>
+      </c>
+      <c r="F15" t="n">
+        <v>4.64099e-07</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-80.376</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0.3126867925963355</v>
+      </c>
+      <c r="I15" t="n">
+        <v>1.143332880137172</v>
+      </c>
+      <c r="J15" t="n">
+        <v>1.865604262284245</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.776391343502419</v>
+      </c>
+      <c r="L15" t="n">
+        <v>19.38343415737194</v>
+      </c>
+      <c r="M15" t="n">
+        <v>86.32404876641756</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>15.56526217967302</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>-5954.809487507271</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>-273.0992946095611</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>8.201765853489458e-07</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.9144184688814156</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="B16" t="n">
+        <v>60.34499999999997</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.5547435190292329</v>
+      </c>
+      <c r="D16" t="n">
+        <v>664.7189846403451</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3.312729431139784</v>
+      </c>
+      <c r="F16" t="n">
+        <v>4.5952e-07</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-80.738</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0.1657627458050188</v>
+      </c>
+      <c r="I16" t="n">
+        <v>1.200167355316335</v>
+      </c>
+      <c r="J16" t="n">
+        <v>1.732267628032193</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.13956058229931</v>
+      </c>
+      <c r="L16" t="n">
+        <v>21.20116145234182</v>
+      </c>
+      <c r="M16" t="n">
+        <v>86.43077153242696</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>16.03193689452932</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>-6018.307491526186</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>-267.6251971377018</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>7.845546070895618e-07</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.9195380809221833</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57.44199999999995</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.5280566280566275</v>
+      </c>
+      <c r="D17" t="n">
+        <v>668.8492535373529</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3.333313262277152</v>
+      </c>
+      <c r="F17" t="n">
+        <v>4.56141e-07</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-81.06</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.7606699664169325</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1.709185618074626</v>
+      </c>
+      <c r="K17" t="n">
+        <v>2.616158702049958</v>
+      </c>
+      <c r="L17" t="n">
+        <v>21.85360288835843</v>
+      </c>
+      <c r="M17" t="n">
+        <v>86.55080728929757</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>16.59128788962701</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>-6123.038141008891</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>-277.1422727265744</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>7.564184407878399e-07</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.9238620000756955</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57.26400000000001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.5264202978488692</v>
+      </c>
+      <c r="D18" t="n">
+        <v>769.6773810086326</v>
+      </c>
+      <c r="E18" t="n">
+        <v>3.835805763738571</v>
+      </c>
+      <c r="F18" t="n">
+        <v>4.5332e-07</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-81.285</v>
+      </c>
+      <c r="H18" t="n">
+        <v>1.10418152927704</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.152327272624091</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2.012381738611669</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.123012618967273</v>
+      </c>
+      <c r="L18" t="n">
+        <v>23.42290491972876</v>
+      </c>
+      <c r="M18" t="n">
+        <v>86.75641427325557</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>17.64545889602354</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>-6434.766853772477</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>-374.7386397946453</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.361551241341882e-07</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.9269799310526019</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" t="n">
+        <v>54.125</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.4975638904210332</v>
+      </c>
+      <c r="D19" t="n">
+        <v>750.9182800401468</v>
+      </c>
+      <c r="E19" t="n">
+        <v>3.742316895034679</v>
+      </c>
+      <c r="F19" t="n">
+        <v>4.51184e-07</v>
+      </c>
+      <c r="G19" t="n">
+        <v>-81.535</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.4153092397717863</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.148004031052643</v>
+      </c>
+      <c r="J19" t="n">
+        <v>2.044066794046389</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.775124178158655</v>
+      </c>
+      <c r="L19" t="n">
+        <v>24.02169692235111</v>
+      </c>
+      <c r="M19" t="n">
+        <v>86.85473311335363</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>18.19820593688107</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>-6526.29454549875</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>-363.5992775212521</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7.1652088650224e-07</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.9303094907850217</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="B20" t="n">
+        <v>53.63499999999999</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.4930593859165285</v>
+      </c>
+      <c r="D20" t="n">
+        <v>871.5548550558807</v>
+      </c>
+      <c r="E20" t="n">
+        <v>4.343527845467745</v>
+      </c>
+      <c r="F20" t="n">
+        <v>4.49307e-07</v>
+      </c>
+      <c r="G20" t="n">
+        <v>-81.727</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.113825854839255</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.280145708246429</v>
+      </c>
+      <c r="J20" t="n">
+        <v>2.251616509255678</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.187998412161114</v>
+      </c>
+      <c r="L20" t="n">
+        <v>25.15029856009681</v>
+      </c>
+      <c r="M20" t="n">
+        <v>87.01209275556037</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>19.15850352757258</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>-6790.270708425777</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>-480.0431614340723</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>7.016495281387601e-07</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0.9328129290911628</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B21" t="n">
+        <v>49.94299999999998</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.4591193234050374</v>
+      </c>
+      <c r="D21" t="n">
+        <v>747.3006453296449</v>
+      </c>
+      <c r="E21" t="n">
+        <v>3.724287855314869</v>
+      </c>
+      <c r="F21" t="n">
+        <v>4.47867e-07</v>
+      </c>
+      <c r="G21" t="n">
+        <v>-81.908</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.237363673091897</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.189953050283336</v>
+      </c>
+      <c r="J21" t="n">
+        <v>1.539982400362601</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.682516985600774</v>
+      </c>
+      <c r="L21" t="n">
+        <v>25.0590033346918</v>
+      </c>
+      <c r="M21" t="n">
+        <v>86.95363110797396</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>18.79016639086698</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>-6526.385286717029</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>-371.4544966293365</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.885139484362863e-07</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.9351523850912739</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
